--- a/dataCaseStudy_WtE/raw_results/technology_selection/Summary.xlsx
+++ b/dataCaseStudy_WtE/raw_results/technology_selection/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE51"/>
+  <dimension ref="A1:AE54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5732,6 +5732,315 @@
       <c r="AE51" t="inlineStr">
         <is>
           <t>dataCaseStudy_WtE\raw_results\technology_selection\20251204200317_DH_ratio_0.75_carbon_tax_150_el_price_125</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>19578347.87756129</v>
+      </c>
+      <c r="B52" t="n">
+        <v>7082943.251772646</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>4524006.911486896</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>11606950.16325954</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>116.2909854684304</v>
+      </c>
+      <c r="I52" t="n">
+        <v>-2679937.637982209</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>10651219.06129849</v>
+      </c>
+      <c r="M52" t="n">
+        <v>19578347.87756129</v>
+      </c>
+      <c r="N52" t="n">
+        <v>213024.3812259698</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>213024.3812259698</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>213024.3812259698</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>5.377999782562256</v>
+      </c>
+      <c r="W52" t="n">
+        <v>19578347.87756132</v>
+      </c>
+      <c r="X52" t="n">
+        <v>19578347.87756129</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>-2.60770320892334e-08</v>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.5_carbon_tax_50_el_price_25</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260113183219_dh_ratio_0.5_carbon_tax_50_el_price_25</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>16898410.23957908</v>
+      </c>
+      <c r="B53" t="n">
+        <v>7082943.251772646</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>4524006.911486896</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>11606950.16325954</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>116.2909854684305</v>
+      </c>
+      <c r="I53" t="n">
+        <v>-5359875.275964418</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>10651219.06129849</v>
+      </c>
+      <c r="M53" t="n">
+        <v>16898410.23957908</v>
+      </c>
+      <c r="N53" t="n">
+        <v>213024.3812259698</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>213024.3812259698</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>213024.3812259698</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>6.682999849319458</v>
+      </c>
+      <c r="W53" t="n">
+        <v>16898410.23957904</v>
+      </c>
+      <c r="X53" t="n">
+        <v>16898410.23957908</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>4.097819328308105e-08</v>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.5_carbon_tax_50_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260113183550_dh_ratio_0.5_carbon_tax_50_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>14213505.80113169</v>
+      </c>
+      <c r="B54" t="n">
+        <v>7082943.251772646</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>4524006.911486896</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>11606950.16325954</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>22421.42501391864</v>
+      </c>
+      <c r="I54" t="n">
+        <v>-8073962.264765704</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>10658096.47762393</v>
+      </c>
+      <c r="M54" t="n">
+        <v>14213505.80113169</v>
+      </c>
+      <c r="N54" t="n">
+        <v>213161.9295524785</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>213161.9295524785</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>213161.9295524786</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>8.459000110626221</v>
+      </c>
+      <c r="W54" t="n">
+        <v>14213505.8011316</v>
+      </c>
+      <c r="X54" t="n">
+        <v>14213505.80113169</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>8.940696716308594e-08</v>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.5_carbon_tax_50_el_price_75</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260113185505_dh_ratio_0.5_carbon_tax_50_el_price_75</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_WtE/raw_results/technology_selection/Summary.xlsx
+++ b/dataCaseStudy_WtE/raw_results/technology_selection/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE41"/>
+  <dimension ref="A1:AE81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4702,6 +4702,4126 @@
       <c r="AE41" t="inlineStr">
         <is>
           <t>dataCaseStudy_WtE\raw_results\technology_selection\20260127201550_dh_1_ctax_250_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>24009219.09686941</v>
+      </c>
+      <c r="B42" t="n">
+        <v>10993339.82043108</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3262369.350295471</v>
+      </c>
+      <c r="D42" t="n">
+        <v>7686861.115812124</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>18680200.9362432</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3262369.350295471</v>
+      </c>
+      <c r="H42" t="n">
+        <v>155.0546472912402</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-1158791.32356797</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>3225285.07925142</v>
+      </c>
+      <c r="M42" t="n">
+        <v>24009219.09686941</v>
+      </c>
+      <c r="N42" t="n">
+        <v>32255.11043664422</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>32255.11043664422</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>32252.85079251405</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2.259644130418196</v>
+      </c>
+      <c r="V42" t="n">
+        <v>14.61800003051758</v>
+      </c>
+      <c r="W42" t="n">
+        <v>24009219.09686941</v>
+      </c>
+      <c r="X42" t="n">
+        <v>24009219.09686941</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128151650_dh_0.5_ctax_100_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>22186581.85844579</v>
+      </c>
+      <c r="B43" t="n">
+        <v>7082943.251772646</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>4524006.911486896</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>11606950.16325954</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>16256.29726210878</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-10746509.5493822</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>21309884.94730634</v>
+      </c>
+      <c r="M43" t="n">
+        <v>22186581.85844579</v>
+      </c>
+      <c r="N43" t="n">
+        <v>213098.8494730633</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>213098.8494730633</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>213098.8494730633</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>15.59400010108948</v>
+      </c>
+      <c r="W43" t="n">
+        <v>22186581.85844579</v>
+      </c>
+      <c r="X43" t="n">
+        <v>22186581.85844579</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128151932_dh_0.5_ctax_100_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>16770938.89632442</v>
+      </c>
+      <c r="B44" t="n">
+        <v>7082943.251772646</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>4524006.911486896</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>11606950.16325954</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>251892.889191721</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-16506771.02720062</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>21418866.87107379</v>
+      </c>
+      <c r="M44" t="n">
+        <v>16770938.89632442</v>
+      </c>
+      <c r="N44" t="n">
+        <v>214188.6687107377</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>214188.6687107377</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>214188.6687107378</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>4.873999834060669</v>
+      </c>
+      <c r="W44" t="n">
+        <v>16770938.89632424</v>
+      </c>
+      <c r="X44" t="n">
+        <v>16770938.89632442</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.844018697738647e-07</v>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128152225_dh_0.5_ctax_100_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>11149877.1917611</v>
+      </c>
+      <c r="B45" t="n">
+        <v>7082943.251772646</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>4524006.911486896</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>11606950.16325954</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>876781.4848603354</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-23041732.30292929</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>21707877.84657052</v>
+      </c>
+      <c r="M45" t="n">
+        <v>11149877.1917611</v>
+      </c>
+      <c r="N45" t="n">
+        <v>217078.7784657051</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>217078.7784657051</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>217078.7784657051</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>4.80400013923645</v>
+      </c>
+      <c r="W45" t="n">
+        <v>11149877.19176109</v>
+      </c>
+      <c r="X45" t="n">
+        <v>11149877.1917611</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.862645149230957e-08</v>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128152503_dh_0.5_ctax_100_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>5248969.809365015</v>
+      </c>
+      <c r="B46" t="n">
+        <v>7082943.251772646</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>4524006.911486896</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>11606950.16325954</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1647033.57777678</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-30069133.37121569</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>22064119.43954438</v>
+      </c>
+      <c r="M46" t="n">
+        <v>5248969.809365015</v>
+      </c>
+      <c r="N46" t="n">
+        <v>220641.1943954437</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>220641.1943954437</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>220641.1943954437</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>5.030999898910522</v>
+      </c>
+      <c r="W46" t="n">
+        <v>5248969.809364995</v>
+      </c>
+      <c r="X46" t="n">
+        <v>5248969.809365015</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>2.048909664154053e-08</v>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128152733_dh_0.5_ctax_100_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>25314339.14210834</v>
+      </c>
+      <c r="B47" t="n">
+        <v>11077964.07282776</v>
+      </c>
+      <c r="C47" t="n">
+        <v>3302109.800850721</v>
+      </c>
+      <c r="D47" t="n">
+        <v>7799514.41518131</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>18877478.48800907</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3302109.800850721</v>
+      </c>
+      <c r="H47" t="n">
+        <v>533480.8313765341</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-1111504.908340733</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>3712774.930212754</v>
+      </c>
+      <c r="M47" t="n">
+        <v>25314339.14210834</v>
+      </c>
+      <c r="N47" t="n">
+        <v>24754.21710783603</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>24754.21710783603</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>24751.83286808512</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2.384239750940718</v>
+      </c>
+      <c r="V47" t="n">
+        <v>11.10199999809265</v>
+      </c>
+      <c r="W47" t="n">
+        <v>25314339.14210834</v>
+      </c>
+      <c r="X47" t="n">
+        <v>25314339.14210834</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128153005_dh_0.5_ctax_150_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>24197995.79140298</v>
+      </c>
+      <c r="B48" t="n">
+        <v>11054920.85371765</v>
+      </c>
+      <c r="C48" t="n">
+        <v>3291288.459642456</v>
+      </c>
+      <c r="D48" t="n">
+        <v>7785379.797947165</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>18840300.65166482</v>
+      </c>
+      <c r="G48" t="n">
+        <v>3291288.459642456</v>
+      </c>
+      <c r="H48" t="n">
+        <v>538536.342109165</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-2255654.895589798</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>3783525.233576341</v>
+      </c>
+      <c r="M48" t="n">
+        <v>24197995.79140298</v>
+      </c>
+      <c r="N48" t="n">
+        <v>25225.88019333961</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>25225.88019333961</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>25223.50155717558</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2.378636164041317</v>
+      </c>
+      <c r="V48" t="n">
+        <v>13.0239999294281</v>
+      </c>
+      <c r="W48" t="n">
+        <v>24197995.79140298</v>
+      </c>
+      <c r="X48" t="n">
+        <v>24197995.79140298</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128153247_dh_0.5_ctax_150_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>23021485.41821741</v>
+      </c>
+      <c r="B49" t="n">
+        <v>11007812.52167561</v>
+      </c>
+      <c r="C49" t="n">
+        <v>3269165.884999415</v>
+      </c>
+      <c r="D49" t="n">
+        <v>7754361.054584316</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>18762173.57625993</v>
+      </c>
+      <c r="G49" t="n">
+        <v>3269165.884999415</v>
+      </c>
+      <c r="H49" t="n">
+        <v>754851.6182332117</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-3879385.046016911</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>4114679.384741759</v>
+      </c>
+      <c r="M49" t="n">
+        <v>23021485.41821741</v>
+      </c>
+      <c r="N49" t="n">
+        <v>27433.5594439898</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>27433.5594439898</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>27431.19589827826</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2.363545711678455</v>
+      </c>
+      <c r="V49" t="n">
+        <v>17.30800008773804</v>
+      </c>
+      <c r="W49" t="n">
+        <v>23021485.41821741</v>
+      </c>
+      <c r="X49" t="n">
+        <v>23021485.41821741</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128153542_dh_0.5_ctax_150_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>21343789.21094676</v>
+      </c>
+      <c r="B50" t="n">
+        <v>10944002.43943042</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3239199.990512042</v>
+      </c>
+      <c r="D50" t="n">
+        <v>7707301.859127443</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>18651304.29855786</v>
+      </c>
+      <c r="G50" t="n">
+        <v>3239199.990512042</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2470788.153655807</v>
+      </c>
+      <c r="I50" t="n">
+        <v>-8671527.366657559</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>5654024.134878608</v>
+      </c>
+      <c r="M50" t="n">
+        <v>21343789.21094676</v>
+      </c>
+      <c r="N50" t="n">
+        <v>37695.82870208837</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>37695.82870208837</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>37693.49423252409</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2.334469563454501</v>
+      </c>
+      <c r="V50" t="n">
+        <v>25.76999998092651</v>
+      </c>
+      <c r="W50" t="n">
+        <v>21343789.21094676</v>
+      </c>
+      <c r="X50" t="n">
+        <v>21343789.21094676</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128153802_dh_0.5_ctax_150_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>16225848.05948762</v>
+      </c>
+      <c r="B51" t="n">
+        <v>7082943.251772646</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>4524006.911486896</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>11606950.16325954</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1144370.416970435</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-29272929.11224952</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>32747456.59150717</v>
+      </c>
+      <c r="M51" t="n">
+        <v>16225848.05948762</v>
+      </c>
+      <c r="N51" t="n">
+        <v>218316.3772767143</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>218316.3772767143</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>218316.3772767143</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>12.93600010871887</v>
+      </c>
+      <c r="W51" t="n">
+        <v>15934861.15097855</v>
+      </c>
+      <c r="X51" t="n">
+        <v>16225848.05948762</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>290986.9085090701</v>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128154118_dh_0.5_ctax_150_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>26540787.87649507</v>
+      </c>
+      <c r="B52" t="n">
+        <v>11105518.2420969</v>
+      </c>
+      <c r="C52" t="n">
+        <v>3315049.532315627</v>
+      </c>
+      <c r="D52" t="n">
+        <v>7815394.596493641</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>18920912.83859054</v>
+      </c>
+      <c r="G52" t="n">
+        <v>3315049.532315627</v>
+      </c>
+      <c r="H52" t="n">
+        <v>534783.2387115362</v>
+      </c>
+      <c r="I52" t="n">
+        <v>-1102305.130975597</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>4872347.397852964</v>
+      </c>
+      <c r="M52" t="n">
+        <v>26540787.87649507</v>
+      </c>
+      <c r="N52" t="n">
+        <v>24364.12618050969</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>24364.12618050969</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>24361.73698926487</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2.389191244850025</v>
+      </c>
+      <c r="V52" t="n">
+        <v>16.95499992370605</v>
+      </c>
+      <c r="W52" t="n">
+        <v>26540787.87649507</v>
+      </c>
+      <c r="X52" t="n">
+        <v>26540787.87649507</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128154333_dh_0.5_ctax_200_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>25436822.43911521</v>
+      </c>
+      <c r="B53" t="n">
+        <v>11093907.37777177</v>
+      </c>
+      <c r="C53" t="n">
+        <v>3309596.946720497</v>
+      </c>
+      <c r="D53" t="n">
+        <v>7808833.745614777</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>18902741.12338654</v>
+      </c>
+      <c r="G53" t="n">
+        <v>3309596.946720497</v>
+      </c>
+      <c r="H53" t="n">
+        <v>534308.9304601339</v>
+      </c>
+      <c r="I53" t="n">
+        <v>-2211533.489091419</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>4901708.927639459</v>
+      </c>
+      <c r="M53" t="n">
+        <v>25436822.43911521</v>
+      </c>
+      <c r="N53" t="n">
+        <v>24510.93196692576</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>24510.93196692576</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>24508.54463819744</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2.387328728292584</v>
+      </c>
+      <c r="V53" t="n">
+        <v>22.50600004196167</v>
+      </c>
+      <c r="W53" t="n">
+        <v>25436822.43911521</v>
+      </c>
+      <c r="X53" t="n">
+        <v>25436822.43911521</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128154652_dh_0.5_ctax_200_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>24312529.18527127</v>
+      </c>
+      <c r="B54" t="n">
+        <v>11080103.56406964</v>
+      </c>
+      <c r="C54" t="n">
+        <v>3303114.528733135</v>
+      </c>
+      <c r="D54" t="n">
+        <v>7800786.386162451</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>18880889.95023209</v>
+      </c>
+      <c r="G54" t="n">
+        <v>3303114.528733135</v>
+      </c>
+      <c r="H54" t="n">
+        <v>593029.7712397473</v>
+      </c>
+      <c r="I54" t="n">
+        <v>-3462736.43041174</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>4998231.365478043</v>
+      </c>
+      <c r="M54" t="n">
+        <v>24312529.18527127</v>
+      </c>
+      <c r="N54" t="n">
+        <v>24993.54151826473</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>24993.54151826473</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>24991.15682739007</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2.384690874535248</v>
+      </c>
+      <c r="V54" t="n">
+        <v>34.36500000953674</v>
+      </c>
+      <c r="W54" t="n">
+        <v>24312529.18527127</v>
+      </c>
+      <c r="X54" t="n">
+        <v>24312529.18527127</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128154915_dh_0.5_ctax_200_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>22979474.6777918</v>
+      </c>
+      <c r="B55" t="n">
+        <v>11060254.22012746</v>
+      </c>
+      <c r="C55" t="n">
+        <v>3293793.065332896</v>
+      </c>
+      <c r="D55" t="n">
+        <v>7788717.699527155</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>18848971.91965462</v>
+      </c>
+      <c r="G55" t="n">
+        <v>3293793.065332896</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1458057.250126028</v>
+      </c>
+      <c r="I55" t="n">
+        <v>-6494033.260181566</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>5872685.702859823</v>
+      </c>
+      <c r="M55" t="n">
+        <v>22979474.6777918</v>
+      </c>
+      <c r="N55" t="n">
+        <v>29365.80856117877</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>29365.80856117877</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>29363.42851429919</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2.380046879571997</v>
+      </c>
+      <c r="V55" t="n">
+        <v>30.2350001335144</v>
+      </c>
+      <c r="W55" t="n">
+        <v>22979474.6777918</v>
+      </c>
+      <c r="X55" t="n">
+        <v>22979474.6777918</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128155304_dh_0.5_ctax_200_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>19353805.78175656</v>
+      </c>
+      <c r="B56" t="n">
+        <v>30697160.46189612</v>
+      </c>
+      <c r="C56" t="n">
+        <v>4349856.014430569</v>
+      </c>
+      <c r="D56" t="n">
+        <v>21930923.53233438</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>52628083.99423049</v>
+      </c>
+      <c r="G56" t="n">
+        <v>4349856.014430569</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3266064.629486933</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-50529783.18484081</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>9639584.328449372</v>
+      </c>
+      <c r="M56" t="n">
+        <v>19353805.78175656</v>
+      </c>
+      <c r="N56" t="n">
+        <v>48202.62692843245</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>48202.62692843245</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>48197.92164224685</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>4.705286185579991</v>
+      </c>
+      <c r="V56" t="n">
+        <v>33.4539999961853</v>
+      </c>
+      <c r="W56" t="n">
+        <v>19353805.78175656</v>
+      </c>
+      <c r="X56" t="n">
+        <v>19353805.78175656</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128155535_dh_0.5_ctax_200_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>27754478.97248523</v>
+      </c>
+      <c r="B57" t="n">
+        <v>11120454.80856366</v>
+      </c>
+      <c r="C57" t="n">
+        <v>3322063.903070181</v>
+      </c>
+      <c r="D57" t="n">
+        <v>7823576.875016074</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>18944031.68357973</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3322063.903070181</v>
+      </c>
+      <c r="H57" t="n">
+        <v>535204.1193386901</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-1098650.487655586</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>6051829.754152212</v>
+      </c>
+      <c r="M57" t="n">
+        <v>27754478.97248523</v>
+      </c>
+      <c r="N57" t="n">
+        <v>24209.71016241052</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>24209.71016241052</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>24207.3190166089</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2.391145801669482</v>
+      </c>
+      <c r="V57" t="n">
+        <v>23.18899989128113</v>
+      </c>
+      <c r="W57" t="n">
+        <v>27754478.97248523</v>
+      </c>
+      <c r="X57" t="n">
+        <v>27754478.97248523</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128155812_dh_0.5_ctax_250_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>26655211.11755402</v>
+      </c>
+      <c r="B58" t="n">
+        <v>11114746.51277371</v>
+      </c>
+      <c r="C58" t="n">
+        <v>3319383.226548138</v>
+      </c>
+      <c r="D58" t="n">
+        <v>7820484.779402622</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>18935231.29217633</v>
+      </c>
+      <c r="G58" t="n">
+        <v>3319383.226548138</v>
+      </c>
+      <c r="H58" t="n">
+        <v>535056.3695936643</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-2199862.236681958</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>6065402.465917845</v>
+      </c>
+      <c r="M58" t="n">
+        <v>26655211.11755402</v>
+      </c>
+      <c r="N58" t="n">
+        <v>24264.0003222956</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>24264.0003222956</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>24261.60986367137</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2.390458624299067</v>
+      </c>
+      <c r="V58" t="n">
+        <v>22.90900015830994</v>
+      </c>
+      <c r="W58" t="n">
+        <v>26655211.11755402</v>
+      </c>
+      <c r="X58" t="n">
+        <v>26655211.11755402</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128160210_dh_0.5_ctax_250_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>25547667.21295319</v>
+      </c>
+      <c r="B59" t="n">
+        <v>11106412.51769343</v>
+      </c>
+      <c r="C59" t="n">
+        <v>3315469.493663821</v>
+      </c>
+      <c r="D59" t="n">
+        <v>7815892.800687781</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>18922305.31838121</v>
+      </c>
+      <c r="G59" t="n">
+        <v>3315469.493663821</v>
+      </c>
+      <c r="H59" t="n">
+        <v>558908.2998361967</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-3364719.421063356</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>6115703.522135326</v>
+      </c>
+      <c r="M59" t="n">
+        <v>25547667.21295319</v>
+      </c>
+      <c r="N59" t="n">
+        <v>24465.20341105248</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>24465.20341105248</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>24462.81408854124</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2.38932251120534</v>
+      </c>
+      <c r="V59" t="n">
+        <v>24.39300012588501</v>
+      </c>
+      <c r="W59" t="n">
+        <v>25547667.21295319</v>
+      </c>
+      <c r="X59" t="n">
+        <v>25547667.21295319</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128160437_dh_0.5_ctax_250_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>24361788.70604995</v>
+      </c>
+      <c r="B60" t="n">
+        <v>11095365.65133169</v>
+      </c>
+      <c r="C60" t="n">
+        <v>3310281.767521423</v>
+      </c>
+      <c r="D60" t="n">
+        <v>7809667.247081369</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>18905032.89841305</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3310281.767521423</v>
+      </c>
+      <c r="H60" t="n">
+        <v>891482.2841544072</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-5280122.700324489</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>6535114.456285553</v>
+      </c>
+      <c r="M60" t="n">
+        <v>24361788.70604995</v>
+      </c>
+      <c r="N60" t="n">
+        <v>26142.84540404028</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>26142.84540404028</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>26140.45782514229</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2.387578897966224</v>
+      </c>
+      <c r="V60" t="n">
+        <v>43.58700013160706</v>
+      </c>
+      <c r="W60" t="n">
+        <v>24361788.70604995</v>
+      </c>
+      <c r="X60" t="n">
+        <v>24361788.70604995</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128160710_dh_0.5_ctax_250_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>21445626.02069269</v>
+      </c>
+      <c r="B61" t="n">
+        <v>24245935.83043829</v>
+      </c>
+      <c r="C61" t="n">
+        <v>4040113.946205718</v>
+      </c>
+      <c r="D61" t="n">
+        <v>17144078.88084171</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>41390014.71127999</v>
+      </c>
+      <c r="G61" t="n">
+        <v>4040113.946205718</v>
+      </c>
+      <c r="H61" t="n">
+        <v>2638342.28913348</v>
+      </c>
+      <c r="I61" t="n">
+        <v>-34919353.4159596</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>8296508.490033099</v>
+      </c>
+      <c r="M61" t="n">
+        <v>21445626.02069269</v>
+      </c>
+      <c r="N61" t="n">
+        <v>33190.02955435691</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>33190.02955435691</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>33186.03396013251</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3.995594224477699</v>
+      </c>
+      <c r="V61" t="n">
+        <v>43.12800002098083</v>
+      </c>
+      <c r="W61" t="n">
+        <v>21445626.02069269</v>
+      </c>
+      <c r="X61" t="n">
+        <v>21445626.02069269</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128161006_dh_0.5_ctax_250_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>26626324.35264248</v>
+      </c>
+      <c r="B62" t="n">
+        <v>10966747.81318222</v>
+      </c>
+      <c r="C62" t="n">
+        <v>3249881.460366655</v>
+      </c>
+      <c r="D62" t="n">
+        <v>7485173.474074902</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>18451921.28725712</v>
+      </c>
+      <c r="G62" t="n">
+        <v>3249881.460366655</v>
+      </c>
+      <c r="H62" t="n">
+        <v>116795.5611062836</v>
+      </c>
+      <c r="I62" t="n">
+        <v>-1062669.751939387</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>5870395.795851803</v>
+      </c>
+      <c r="M62" t="n">
+        <v>26626324.35264248</v>
+      </c>
+      <c r="N62" t="n">
+        <v>58705.89370708811</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>58705.89370708811</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>58703.95795851788</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1.935748570122809</v>
+      </c>
+      <c r="V62" t="n">
+        <v>18.16299986839294</v>
+      </c>
+      <c r="W62" t="n">
+        <v>26626324.35264248</v>
+      </c>
+      <c r="X62" t="n">
+        <v>26626324.35264248</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128161449_dh_1_ctax_100_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>23792395.83473156</v>
+      </c>
+      <c r="B63" t="n">
+        <v>7082943.251772646</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>4524006.911486896</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>11606950.16325954</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>136352.8646669782</v>
+      </c>
+      <c r="I63" t="n">
+        <v>-9316336.802926052</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>21365429.60973109</v>
+      </c>
+      <c r="M63" t="n">
+        <v>23792395.83473156</v>
+      </c>
+      <c r="N63" t="n">
+        <v>213654.2960973108</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>213654.2960973108</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>213654.2960973109</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>16.1100001335144</v>
+      </c>
+      <c r="W63" t="n">
+        <v>23792395.83473156</v>
+      </c>
+      <c r="X63" t="n">
+        <v>23792395.83473156</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128161715_dh_1_ctax_100_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>19058444.97207163</v>
+      </c>
+      <c r="B64" t="n">
+        <v>7082943.251772646</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>4524006.911486896</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>11606950.16325954</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>578486.0919676765</v>
+      </c>
+      <c r="I64" t="n">
+        <v>-14696907.51051326</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>21569916.22735767</v>
+      </c>
+      <c r="M64" t="n">
+        <v>19058444.97207163</v>
+      </c>
+      <c r="N64" t="n">
+        <v>215699.1622735765</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>215699.1622735765</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>215699.1622735766</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>10.01300001144409</v>
+      </c>
+      <c r="W64" t="n">
+        <v>19058444.97207145</v>
+      </c>
+      <c r="X64" t="n">
+        <v>19058444.97207163</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>1.71363353729248e-07</v>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128161938_dh_1_ctax_100_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>13930489.22366568</v>
+      </c>
+      <c r="B65" t="n">
+        <v>7082943.251772646</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>4524006.911486896</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>11606950.16325954</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1782376.769846283</v>
+      </c>
+      <c r="I65" t="n">
+        <v>-21585553.37531666</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>22126715.66587652</v>
+      </c>
+      <c r="M65" t="n">
+        <v>13930489.22366568</v>
+      </c>
+      <c r="N65" t="n">
+        <v>221267.1566587651</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>221267.1566587651</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>221267.1566587652</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>7.004999876022339</v>
+      </c>
+      <c r="W65" t="n">
+        <v>13930489.22366566</v>
+      </c>
+      <c r="X65" t="n">
+        <v>13930489.22366568</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>1.676380634307861e-08</v>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128162158_dh_1_ctax_100_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>8257919.006492823</v>
+      </c>
+      <c r="B66" t="n">
+        <v>7082943.251772646</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" t="n">
+        <v>4524006.911486896</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>11606950.16325954</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>3298136.66063236</v>
+      </c>
+      <c r="I66" t="n">
+        <v>-29474922.43276415</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>22827754.61536508</v>
+      </c>
+      <c r="M66" t="n">
+        <v>8257919.006492823</v>
+      </c>
+      <c r="N66" t="n">
+        <v>228277.5461536508</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>228277.5461536508</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>228277.5461536508</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>6.824000120162964</v>
+      </c>
+      <c r="W66" t="n">
+        <v>8257919.006492818</v>
+      </c>
+      <c r="X66" t="n">
+        <v>8257919.006492823</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>5.587935447692871e-09</v>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128162635_dh_1_ctax_100_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>28470748.82376258</v>
+      </c>
+      <c r="B67" t="n">
+        <v>11075433.64472805</v>
+      </c>
+      <c r="C67" t="n">
+        <v>3300921.484854632</v>
+      </c>
+      <c r="D67" t="n">
+        <v>7798001.39289048</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>18873435.03761853</v>
+      </c>
+      <c r="G67" t="n">
+        <v>3300921.484854632</v>
+      </c>
+      <c r="H67" t="n">
+        <v>2331985.698475967</v>
+      </c>
+      <c r="I67" t="n">
+        <v>-1002661.096508253</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>4967067.699321708</v>
+      </c>
+      <c r="M67" t="n">
+        <v>28470748.82376258</v>
+      </c>
+      <c r="N67" t="n">
+        <v>33116.1683535609</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>33116.1683535609</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>33113.78466214484</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2.383691416144157</v>
+      </c>
+      <c r="V67" t="n">
+        <v>16.47499990463257</v>
+      </c>
+      <c r="W67" t="n">
+        <v>28470748.82376258</v>
+      </c>
+      <c r="X67" t="n">
+        <v>28470748.82376258</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128162854_dh_1_ctax_150_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>27462978.78535136</v>
+      </c>
+      <c r="B68" t="n">
+        <v>11050142.23670552</v>
+      </c>
+      <c r="C68" t="n">
+        <v>3289044.370179745</v>
+      </c>
+      <c r="D68" t="n">
+        <v>7782355.527632554</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>18832497.76433808</v>
+      </c>
+      <c r="G68" t="n">
+        <v>3289044.370179745</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2332207.657152853</v>
+      </c>
+      <c r="I68" t="n">
+        <v>-2034513.076613918</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>5043742.070294598</v>
+      </c>
+      <c r="M68" t="n">
+        <v>27462978.78535136</v>
+      </c>
+      <c r="N68" t="n">
+        <v>33627.32445001485</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>33627.32445001485</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>33624.94713529748</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2.377314717215757</v>
+      </c>
+      <c r="V68" t="n">
+        <v>18.62999987602234</v>
+      </c>
+      <c r="W68" t="n">
+        <v>27462978.78535136</v>
+      </c>
+      <c r="X68" t="n">
+        <v>27462978.78535136</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128163124_dh_1_ctax_150_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>26398287.94813013</v>
+      </c>
+      <c r="B69" t="n">
+        <v>10996808.59585372</v>
+      </c>
+      <c r="C69" t="n">
+        <v>3263998.324192037</v>
+      </c>
+      <c r="D69" t="n">
+        <v>7745688.574730601</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>18742497.17058432</v>
+      </c>
+      <c r="G69" t="n">
+        <v>3263998.324192037</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2516008.047508392</v>
+      </c>
+      <c r="I69" t="n">
+        <v>-3532316.47003173</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>5408100.875877116</v>
+      </c>
+      <c r="M69" t="n">
+        <v>26398287.94813013</v>
+      </c>
+      <c r="N69" t="n">
+        <v>36056.36341662479</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>36056.36341662479</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>36054.00583918083</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2.357577443484644</v>
+      </c>
+      <c r="V69" t="n">
+        <v>25.72200012207031</v>
+      </c>
+      <c r="W69" t="n">
+        <v>26398287.94813013</v>
+      </c>
+      <c r="X69" t="n">
+        <v>26398287.94813013</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128163400_dh_1_ctax_150_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>24842391.98215753</v>
+      </c>
+      <c r="B70" t="n">
+        <v>10933716.67810085</v>
+      </c>
+      <c r="C70" t="n">
+        <v>3234369.687401952</v>
+      </c>
+      <c r="D70" t="n">
+        <v>7692966.534294176</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>18626683.21239503</v>
+      </c>
+      <c r="G70" t="n">
+        <v>3234369.687401952</v>
+      </c>
+      <c r="H70" t="n">
+        <v>4158093.735207669</v>
+      </c>
+      <c r="I70" t="n">
+        <v>-8196283.718149751</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>7019529.065302633</v>
+      </c>
+      <c r="M70" t="n">
+        <v>24842391.98215753</v>
+      </c>
+      <c r="N70" t="n">
+        <v>46799.17866019108</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>46799.17866019108</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>46796.86043535134</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2.318224839852628</v>
+      </c>
+      <c r="V70" t="n">
+        <v>35.90399980545044</v>
+      </c>
+      <c r="W70" t="n">
+        <v>24842391.98215753</v>
+      </c>
+      <c r="X70" t="n">
+        <v>24842391.98215753</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128163642_dh_1_ctax_150_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>19562938.59504388</v>
+      </c>
+      <c r="B71" t="n">
+        <v>7082943.251772646</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>4524006.911486896</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>11606950.16325954</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>2308052.909671388</v>
+      </c>
+      <c r="I71" t="n">
+        <v>-27906825.7987055</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>33554761.32081845</v>
+      </c>
+      <c r="M71" t="n">
+        <v>19562938.59504388</v>
+      </c>
+      <c r="N71" t="n">
+        <v>223698.4088054562</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>223698.4088054562</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>223698.4088054562</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>18.6949999332428</v>
+      </c>
+      <c r="W71" t="n">
+        <v>19272960.17627706</v>
+      </c>
+      <c r="X71" t="n">
+        <v>19562938.59504388</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>289978.4187668115</v>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128164232_dh_1_ctax_150_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>30114711.43749392</v>
+      </c>
+      <c r="B72" t="n">
+        <v>11104038.32854973</v>
+      </c>
+      <c r="C72" t="n">
+        <v>3314354.549146122</v>
+      </c>
+      <c r="D72" t="n">
+        <v>7814567.650507092</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>18918605.97905682</v>
+      </c>
+      <c r="G72" t="n">
+        <v>3314354.549146122</v>
+      </c>
+      <c r="H72" t="n">
+        <v>2334393.915379992</v>
+      </c>
+      <c r="I72" t="n">
+        <v>-993173.9153408579</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>6540530.909251847</v>
+      </c>
+      <c r="M72" t="n">
+        <v>30114711.43749392</v>
+      </c>
+      <c r="N72" t="n">
+        <v>32705.04351602709</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>32705.04351602709</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>32702.65454625951</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2.388969767632488</v>
+      </c>
+      <c r="V72" t="n">
+        <v>30.26399993896484</v>
+      </c>
+      <c r="W72" t="n">
+        <v>30114711.43749392</v>
+      </c>
+      <c r="X72" t="n">
+        <v>30114711.43749392</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128164508_dh_1_ctax_200_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>29119849.96453739</v>
+      </c>
+      <c r="B73" t="n">
+        <v>11092140.98258755</v>
+      </c>
+      <c r="C73" t="n">
+        <v>3308767.428721919</v>
+      </c>
+      <c r="D73" t="n">
+        <v>7807820.333169898</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>18899961.31575745</v>
+      </c>
+      <c r="G73" t="n">
+        <v>3308767.428721919</v>
+      </c>
+      <c r="H73" t="n">
+        <v>2333546.500204339</v>
+      </c>
+      <c r="I73" t="n">
+        <v>-1993381.492701963</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>6570956.212555639</v>
+      </c>
+      <c r="M73" t="n">
+        <v>29119849.96453739</v>
+      </c>
+      <c r="N73" t="n">
+        <v>32857.168081973</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>32857.168081973</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>32854.78106277801</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2.387019194986164</v>
+      </c>
+      <c r="V73" t="n">
+        <v>27.90400004386902</v>
+      </c>
+      <c r="W73" t="n">
+        <v>29119849.96453739</v>
+      </c>
+      <c r="X73" t="n">
+        <v>29119849.96453739</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128164756_dh_1_ctax_200_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>28109203.44989083</v>
+      </c>
+      <c r="B74" t="n">
+        <v>11078138.04829068</v>
+      </c>
+      <c r="C74" t="n">
+        <v>3302191.501581731</v>
+      </c>
+      <c r="D74" t="n">
+        <v>7799618.079352205</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>18877756.12764288</v>
+      </c>
+      <c r="G74" t="n">
+        <v>3302191.501581731</v>
+      </c>
+      <c r="H74" t="n">
+        <v>2379171.372392404</v>
+      </c>
+      <c r="I74" t="n">
+        <v>-3106952.574287405</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>6657037.022561215</v>
+      </c>
+      <c r="M74" t="n">
+        <v>28109203.44989083</v>
+      </c>
+      <c r="N74" t="n">
+        <v>33287.56938963838</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>33287.56938963838</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>33285.18511280632</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>2.384276832284183</v>
+      </c>
+      <c r="V74" t="n">
+        <v>38.95500016212463</v>
+      </c>
+      <c r="W74" t="n">
+        <v>28109203.44989083</v>
+      </c>
+      <c r="X74" t="n">
+        <v>28109203.44989083</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128165043_dh_1_ctax_200_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>26902431.94739144</v>
+      </c>
+      <c r="B75" t="n">
+        <v>11057410.89565116</v>
+      </c>
+      <c r="C75" t="n">
+        <v>3292457.8098646</v>
+      </c>
+      <c r="D75" t="n">
+        <v>7785960.477552787</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>18843371.37320394</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3292457.8098646</v>
+      </c>
+      <c r="H75" t="n">
+        <v>3198165.830169241</v>
+      </c>
+      <c r="I75" t="n">
+        <v>-5952669.67457174</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>7521106.608725394</v>
+      </c>
+      <c r="M75" t="n">
+        <v>26902431.94739144</v>
+      </c>
+      <c r="N75" t="n">
+        <v>37607.91066422647</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>37607.91066422647</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>37605.53304362662</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2.377620600239152</v>
+      </c>
+      <c r="V75" t="n">
+        <v>50.02600002288818</v>
+      </c>
+      <c r="W75" t="n">
+        <v>26902431.94739144</v>
+      </c>
+      <c r="X75" t="n">
+        <v>26902431.94739144</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128165343_dh_1_ctax_200_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>22911380.94014698</v>
+      </c>
+      <c r="B76" t="n">
+        <v>30697160.46189612</v>
+      </c>
+      <c r="C76" t="n">
+        <v>4349856.014430569</v>
+      </c>
+      <c r="D76" t="n">
+        <v>21930923.53233438</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>52628083.99423049</v>
+      </c>
+      <c r="G76" t="n">
+        <v>4349856.014430569</v>
+      </c>
+      <c r="H76" t="n">
+        <v>4044522.644788196</v>
+      </c>
+      <c r="I76" t="n">
+        <v>-48470739.70590532</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>10359657.99260304</v>
+      </c>
+      <c r="M76" t="n">
+        <v>22911380.94014698</v>
+      </c>
+      <c r="N76" t="n">
+        <v>51802.9952492008</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>51802.9952492008</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>51798.28996301519</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="n">
+        <v>4.705286185579991</v>
+      </c>
+      <c r="V76" t="n">
+        <v>45.125</v>
+      </c>
+      <c r="W76" t="n">
+        <v>22911380.94014698</v>
+      </c>
+      <c r="X76" t="n">
+        <v>22911380.94014698</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128165655_dh_1_ctax_200_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>31745134.888399</v>
+      </c>
+      <c r="B77" t="n">
+        <v>11119904.7863203</v>
+      </c>
+      <c r="C77" t="n">
+        <v>3321805.606764483</v>
+      </c>
+      <c r="D77" t="n">
+        <v>7823280.84176599</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>18943185.62808629</v>
+      </c>
+      <c r="G77" t="n">
+        <v>3321805.606764483</v>
+      </c>
+      <c r="H77" t="n">
+        <v>2335164.241315592</v>
+      </c>
+      <c r="I77" t="n">
+        <v>-989313.2402424782</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>8134292.652475117</v>
+      </c>
+      <c r="M77" t="n">
+        <v>31745134.888399</v>
+      </c>
+      <c r="N77" t="n">
+        <v>32539.56169275145</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>32539.56169275145</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>32537.17060990033</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>2.391082851305129</v>
+      </c>
+      <c r="V77" t="n">
+        <v>27.50499987602234</v>
+      </c>
+      <c r="W77" t="n">
+        <v>31745134.888399</v>
+      </c>
+      <c r="X77" t="n">
+        <v>31745134.888399</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128170001_dh_1_ctax_250_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>30755168.99287045</v>
+      </c>
+      <c r="B78" t="n">
+        <v>11114055.63875498</v>
+      </c>
+      <c r="C78" t="n">
+        <v>3319058.784748018</v>
+      </c>
+      <c r="D78" t="n">
+        <v>7820107.293559941</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>18934162.93231492</v>
+      </c>
+      <c r="G78" t="n">
+        <v>3319058.784748018</v>
+      </c>
+      <c r="H78" t="n">
+        <v>2334916.27421442</v>
+      </c>
+      <c r="I78" t="n">
+        <v>-1981234.163063414</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>8148265.164656507</v>
+      </c>
+      <c r="M78" t="n">
+        <v>30755168.99287045</v>
+      </c>
+      <c r="N78" t="n">
+        <v>32595.45102851606</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>32595.45102851606</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>32593.06065862608</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" t="n">
+        <v>2.390369890098021</v>
+      </c>
+      <c r="V78" t="n">
+        <v>33.26600003242493</v>
+      </c>
+      <c r="W78" t="n">
+        <v>30755168.99287045</v>
+      </c>
+      <c r="X78" t="n">
+        <v>30755168.99287045</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128170633_dh_1_ctax_250_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>29759139.21174509</v>
+      </c>
+      <c r="B79" t="n">
+        <v>11105593.47657387</v>
+      </c>
+      <c r="C79" t="n">
+        <v>3315084.863227596</v>
+      </c>
+      <c r="D79" t="n">
+        <v>7815436.564999547</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>18921030.04157341</v>
+      </c>
+      <c r="G79" t="n">
+        <v>3315084.863227596</v>
+      </c>
+      <c r="H79" t="n">
+        <v>2351582.798662393</v>
+      </c>
+      <c r="I79" t="n">
+        <v>-3019444.477018431</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>8190885.985300119</v>
+      </c>
+      <c r="M79" t="n">
+        <v>29759139.21174509</v>
+      </c>
+      <c r="N79" t="n">
+        <v>32765.93314358331</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>32765.93314358331</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>32763.54394120063</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="n">
+        <v>2.389202382510487</v>
+      </c>
+      <c r="V79" t="n">
+        <v>48.67799997329712</v>
+      </c>
+      <c r="W79" t="n">
+        <v>29759139.21174509</v>
+      </c>
+      <c r="X79" t="n">
+        <v>29759139.21174509</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128170923_dh_1_ctax_250_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>28694739.52498302</v>
+      </c>
+      <c r="B80" t="n">
+        <v>11094582.75138945</v>
+      </c>
+      <c r="C80" t="n">
+        <v>3309914.109367134</v>
+      </c>
+      <c r="D80" t="n">
+        <v>7809220.179688528</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>18903802.93107798</v>
+      </c>
+      <c r="G80" t="n">
+        <v>3309914.109367134</v>
+      </c>
+      <c r="H80" t="n">
+        <v>2654222.965119759</v>
+      </c>
+      <c r="I80" t="n">
+        <v>-4749155.878977406</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>8575955.398395561</v>
+      </c>
+      <c r="M80" t="n">
+        <v>28694739.52498302</v>
+      </c>
+      <c r="N80" t="n">
+        <v>34306.20903887904</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>34306.20903887904</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>34303.8215935824</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="n">
+        <v>2.387445296479032</v>
+      </c>
+      <c r="V80" t="n">
+        <v>52.65400004386902</v>
+      </c>
+      <c r="W80" t="n">
+        <v>28694739.52498302</v>
+      </c>
+      <c r="X80" t="n">
+        <v>28694739.52498302</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128171230_dh_1_ctax_250_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>25276313.40598446</v>
+      </c>
+      <c r="B81" t="n">
+        <v>24312211.32030427</v>
+      </c>
+      <c r="C81" t="n">
+        <v>4046411.555473888</v>
+      </c>
+      <c r="D81" t="n">
+        <v>17189990.00543324</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>41502201.32573751</v>
+      </c>
+      <c r="G81" t="n">
+        <v>4046411.555473888</v>
+      </c>
+      <c r="H81" t="n">
+        <v>3355008.934142923</v>
+      </c>
+      <c r="I81" t="n">
+        <v>-32727778.12433406</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>9100469.714964205</v>
+      </c>
+      <c r="M81" t="n">
+        <v>25276313.40598446</v>
+      </c>
+      <c r="N81" t="n">
+        <v>36405.88260742889</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>36405.88260742889</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>36401.87885985701</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="n">
+        <v>4.003747571932321</v>
+      </c>
+      <c r="V81" t="n">
+        <v>39.21000003814697</v>
+      </c>
+      <c r="W81" t="n">
+        <v>25276313.40598446</v>
+      </c>
+      <c r="X81" t="n">
+        <v>25276313.40598446</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260128171543_dh_1_ctax_250_el_price_250</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_WtE/raw_results/technology_selection/Summary.xlsx
+++ b/dataCaseStudy_WtE/raw_results/technology_selection/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE41"/>
+  <dimension ref="A1:AE105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4702,6 +4702,6598 @@
       <c r="AE41" t="inlineStr">
         <is>
           <t>dataCaseStudy_WtE\raw_results\technology_selection\20260202181933_dh_1_ctax_250_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>12747285.48778955</v>
+      </c>
+      <c r="B42" t="n">
+        <v>3910396.568658433</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3262369.350295471</v>
+      </c>
+      <c r="D42" t="n">
+        <v>3507870.75850491</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>7418267.327163343</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3262369.350295471</v>
+      </c>
+      <c r="H42" t="n">
+        <v>155.0546472912402</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-1158791.32356797</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>3225285.07925142</v>
+      </c>
+      <c r="M42" t="n">
+        <v>12747285.48778955</v>
+      </c>
+      <c r="N42" t="n">
+        <v>32255.11043664422</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>32255.11043664422</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>32252.85079251405</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2.259644130418196</v>
+      </c>
+      <c r="V42" t="n">
+        <v>14.51399993896484</v>
+      </c>
+      <c r="W42" t="n">
+        <v>12747285.48778955</v>
+      </c>
+      <c r="X42" t="n">
+        <v>12747285.48778955</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203181303_dh_0.5_ctax_100_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>10924648.24936593</v>
+      </c>
+      <c r="B43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>16256.29726210878</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-10746509.5493822</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>21309884.94730634</v>
+      </c>
+      <c r="M43" t="n">
+        <v>10924648.24936593</v>
+      </c>
+      <c r="N43" t="n">
+        <v>213098.8494730633</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>213098.8494730633</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>213098.8494730633</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>15.13199996948242</v>
+      </c>
+      <c r="W43" t="n">
+        <v>10924648.24936593</v>
+      </c>
+      <c r="X43" t="n">
+        <v>10924648.24936593</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203181542_dh_0.5_ctax_100_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>5509005.287244566</v>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>251892.889191721</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-16506771.02720062</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>21418866.87107379</v>
+      </c>
+      <c r="M44" t="n">
+        <v>5509005.287244566</v>
+      </c>
+      <c r="N44" t="n">
+        <v>214188.6687107377</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>214188.6687107377</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>214188.6687107378</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>5.101999998092651</v>
+      </c>
+      <c r="W44" t="n">
+        <v>5509005.28724438</v>
+      </c>
+      <c r="X44" t="n">
+        <v>5509005.287244566</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.862645149230957e-07</v>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203181827_dh_0.5_ctax_100_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>-112056.4173187539</v>
+      </c>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>876781.4848603354</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-23041732.30292929</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>21707877.84657052</v>
+      </c>
+      <c r="M45" t="n">
+        <v>-112056.4173187539</v>
+      </c>
+      <c r="N45" t="n">
+        <v>217078.7784657051</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>217078.7784657051</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>217078.7784657051</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>4.457000017166138</v>
+      </c>
+      <c r="W45" t="n">
+        <v>-112056.4173187745</v>
+      </c>
+      <c r="X45" t="n">
+        <v>-112056.4173187539</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>2.060551196336746e-08</v>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203182106_dh_0.5_ctax_100_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>-6012963.799714845</v>
+      </c>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1647033.57777678</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-30069133.37121569</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>22064119.43954438</v>
+      </c>
+      <c r="M46" t="n">
+        <v>-6012963.799714845</v>
+      </c>
+      <c r="N46" t="n">
+        <v>220641.1943954437</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>220641.1943954437</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>220641.1943954437</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>4.572999954223633</v>
+      </c>
+      <c r="W46" t="n">
+        <v>-6012963.799714865</v>
+      </c>
+      <c r="X46" t="n">
+        <v>-6012963.799714845</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>2.048909664154053e-08</v>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203182333_dh_0.5_ctax_100_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>-12075343.63557519</v>
+      </c>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1943719.78314256</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-36565416.78242347</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>22201336.80952604</v>
+      </c>
+      <c r="M47" t="n">
+        <v>-12075343.63557519</v>
+      </c>
+      <c r="N47" t="n">
+        <v>222013.3680952604</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>222013.3680952604</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>222013.3680952604</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>5.055999994277954</v>
+      </c>
+      <c r="W47" t="n">
+        <v>-12075343.63557523</v>
+      </c>
+      <c r="X47" t="n">
+        <v>-12075343.63557519</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>4.097819328308105e-08</v>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203182602_dh_0.5_ctax_100_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>-18184351.20943364</v>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>2061813.094625736</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-42847135.82432608</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>22255954.96608702</v>
+      </c>
+      <c r="M48" t="n">
+        <v>-18184351.20943364</v>
+      </c>
+      <c r="N48" t="n">
+        <v>222559.5496608701</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>222559.5496608701</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>222559.5496608701</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>5.606000185012817</v>
+      </c>
+      <c r="W48" t="n">
+        <v>-18184351.20943364</v>
+      </c>
+      <c r="X48" t="n">
+        <v>-18184351.20943364</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203182838_dh_0.5_ctax_100_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>-24309389.53214457</v>
+      </c>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2094069.069521545</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-49019348.51032212</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>22270873.35447633</v>
+      </c>
+      <c r="M49" t="n">
+        <v>-24309389.53214457</v>
+      </c>
+      <c r="N49" t="n">
+        <v>222708.7335447632</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>222708.7335447632</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>222708.7335447632</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>5.396000146865845</v>
+      </c>
+      <c r="W49" t="n">
+        <v>-24309389.53214457</v>
+      </c>
+      <c r="X49" t="n">
+        <v>-24309389.53214457</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203183121_dh_0.5_ctax_100_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>14052405.53302848</v>
+      </c>
+      <c r="B50" t="n">
+        <v>3995020.821055111</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3302109.800850721</v>
+      </c>
+      <c r="D50" t="n">
+        <v>3620524.057874097</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>7615544.878929209</v>
+      </c>
+      <c r="G50" t="n">
+        <v>3302109.800850721</v>
+      </c>
+      <c r="H50" t="n">
+        <v>533480.8313765341</v>
+      </c>
+      <c r="I50" t="n">
+        <v>-1111504.908340733</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>3712774.930212754</v>
+      </c>
+      <c r="M50" t="n">
+        <v>14052405.53302848</v>
+      </c>
+      <c r="N50" t="n">
+        <v>24754.21710783603</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>24754.21710783603</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>24751.83286808512</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2.384239750940718</v>
+      </c>
+      <c r="V50" t="n">
+        <v>10.96300005912781</v>
+      </c>
+      <c r="W50" t="n">
+        <v>14052405.53302848</v>
+      </c>
+      <c r="X50" t="n">
+        <v>14052405.53302848</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203183325_dh_0.5_ctax_150_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>12936062.18232312</v>
+      </c>
+      <c r="B51" t="n">
+        <v>3971977.60194501</v>
+      </c>
+      <c r="C51" t="n">
+        <v>3291288.459642456</v>
+      </c>
+      <c r="D51" t="n">
+        <v>3606389.440639952</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>7578367.042584963</v>
+      </c>
+      <c r="G51" t="n">
+        <v>3291288.459642456</v>
+      </c>
+      <c r="H51" t="n">
+        <v>538536.342109165</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-2255654.895589798</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>3783525.233576339</v>
+      </c>
+      <c r="M51" t="n">
+        <v>12936062.18232312</v>
+      </c>
+      <c r="N51" t="n">
+        <v>25225.8801933396</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>25225.8801933396</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>25223.50155717556</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2.378636164041317</v>
+      </c>
+      <c r="V51" t="n">
+        <v>13.03299999237061</v>
+      </c>
+      <c r="W51" t="n">
+        <v>12936062.18232312</v>
+      </c>
+      <c r="X51" t="n">
+        <v>12936062.18232312</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203183623_dh_0.5_ctax_150_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>11759551.80913755</v>
+      </c>
+      <c r="B52" t="n">
+        <v>3924869.269902967</v>
+      </c>
+      <c r="C52" t="n">
+        <v>3269165.884999414</v>
+      </c>
+      <c r="D52" t="n">
+        <v>3575370.6972771</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>7500239.967180068</v>
+      </c>
+      <c r="G52" t="n">
+        <v>3269165.884999414</v>
+      </c>
+      <c r="H52" t="n">
+        <v>754851.6182332116</v>
+      </c>
+      <c r="I52" t="n">
+        <v>-3879385.046016912</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>4114679.384741763</v>
+      </c>
+      <c r="M52" t="n">
+        <v>11759551.80913755</v>
+      </c>
+      <c r="N52" t="n">
+        <v>27433.55944398982</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>27433.55944398982</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>27431.19589827828</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2.363545711678455</v>
+      </c>
+      <c r="V52" t="n">
+        <v>12.97099995613098</v>
+      </c>
+      <c r="W52" t="n">
+        <v>11759551.80913755</v>
+      </c>
+      <c r="X52" t="n">
+        <v>11759551.80913755</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203183833_dh_0.5_ctax_150_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>10081855.6018669</v>
+      </c>
+      <c r="B53" t="n">
+        <v>3861059.187657773</v>
+      </c>
+      <c r="C53" t="n">
+        <v>3239199.990512042</v>
+      </c>
+      <c r="D53" t="n">
+        <v>3528311.501820231</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>7389370.689478003</v>
+      </c>
+      <c r="G53" t="n">
+        <v>3239199.990512042</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2470788.153655807</v>
+      </c>
+      <c r="I53" t="n">
+        <v>-8671527.366657559</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>5654024.134878608</v>
+      </c>
+      <c r="M53" t="n">
+        <v>10081855.6018669</v>
+      </c>
+      <c r="N53" t="n">
+        <v>37695.82870208837</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>37695.82870208837</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>37693.49423252409</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2.334469563454501</v>
+      </c>
+      <c r="V53" t="n">
+        <v>14.76200008392334</v>
+      </c>
+      <c r="W53" t="n">
+        <v>10081855.6018669</v>
+      </c>
+      <c r="X53" t="n">
+        <v>10081855.6018669</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203184145_dh_0.5_ctax_150_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>4963914.450407762</v>
+      </c>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1144370.416970435</v>
+      </c>
+      <c r="I54" t="n">
+        <v>-29272929.11224952</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>32747456.59150717</v>
+      </c>
+      <c r="M54" t="n">
+        <v>4963914.450407762</v>
+      </c>
+      <c r="N54" t="n">
+        <v>218316.3772767143</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>218316.3772767143</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>218316.3772767143</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>17.35500001907349</v>
+      </c>
+      <c r="W54" t="n">
+        <v>4963914.450407762</v>
+      </c>
+      <c r="X54" t="n">
+        <v>4963914.450407762</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203184359_dh_0.5_ctax_150_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>-996747.9443654828</v>
+      </c>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>345016.5541796839</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>345016.5541796861</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1709345.297483764</v>
+      </c>
+      <c r="I55" t="n">
+        <v>-36190517.71089222</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>33139407.91486328</v>
+      </c>
+      <c r="M55" t="n">
+        <v>-996747.9443654828</v>
+      </c>
+      <c r="N55" t="n">
+        <v>220929.3860990884</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>220929.3860990884</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>220929.3860990885</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>7.180000066757202</v>
+      </c>
+      <c r="W55" t="n">
+        <v>-996747.9443654828</v>
+      </c>
+      <c r="X55" t="n">
+        <v>-996747.9443654828</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203184728_dh_0.5_ctax_150_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>-7068936.434910126</v>
+      </c>
+      <c r="B56" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1949433.947739025</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-42669356.35280671</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>33305969.41597787</v>
+      </c>
+      <c r="M56" t="n">
+        <v>-7068936.434910126</v>
+      </c>
+      <c r="N56" t="n">
+        <v>222039.7961065191</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>222039.7961065191</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>222039.7961065191</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>7.960000038146973</v>
+      </c>
+      <c r="W56" t="n">
+        <v>-7068936.434910126</v>
+      </c>
+      <c r="X56" t="n">
+        <v>-7068936.434910126</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203184935_dh_0.5_ctax_150_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>-14474743.1863176</v>
+      </c>
+      <c r="B57" t="n">
+        <v>31226380.04370678</v>
+      </c>
+      <c r="C57" t="n">
+        <v>4400143.355196329</v>
+      </c>
+      <c r="D57" t="n">
+        <v>22302671.72336628</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>53529051.76707305</v>
+      </c>
+      <c r="G57" t="n">
+        <v>4400143.355196329</v>
+      </c>
+      <c r="H57" t="n">
+        <v>4625886.449575543</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-84740641.25643563</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>7710816.498273114</v>
+      </c>
+      <c r="M57" t="n">
+        <v>-14474743.1863176</v>
+      </c>
+      <c r="N57" t="n">
+        <v>51410.22919468472</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>51410.22919468472</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>51405.44332181967</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>4.785872864007008</v>
+      </c>
+      <c r="V57" t="n">
+        <v>8.093000173568726</v>
+      </c>
+      <c r="W57" t="n">
+        <v>-14474743.1863176</v>
+      </c>
+      <c r="X57" t="n">
+        <v>-14474743.1863176</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203185142_dh_0.5_ctax_150_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>15278854.26741521</v>
+      </c>
+      <c r="B58" t="n">
+        <v>4022574.990324257</v>
+      </c>
+      <c r="C58" t="n">
+        <v>3315049.532315627</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3636404.239186428</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>7658979.229510684</v>
+      </c>
+      <c r="G58" t="n">
+        <v>3315049.532315627</v>
+      </c>
+      <c r="H58" t="n">
+        <v>534783.2387115362</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-1102305.130975596</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>4872347.397852963</v>
+      </c>
+      <c r="M58" t="n">
+        <v>15278854.26741521</v>
+      </c>
+      <c r="N58" t="n">
+        <v>24364.12618050969</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>24364.12618050969</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>24361.73698926486</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2.389191244850025</v>
+      </c>
+      <c r="V58" t="n">
+        <v>10.59700012207031</v>
+      </c>
+      <c r="W58" t="n">
+        <v>15278854.26741521</v>
+      </c>
+      <c r="X58" t="n">
+        <v>15278854.26741521</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203185520_dh_0.5_ctax_200_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>14174888.83003536</v>
+      </c>
+      <c r="B59" t="n">
+        <v>4010964.125999122</v>
+      </c>
+      <c r="C59" t="n">
+        <v>3309596.946720497</v>
+      </c>
+      <c r="D59" t="n">
+        <v>3629843.388307563</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>7640807.514306685</v>
+      </c>
+      <c r="G59" t="n">
+        <v>3309596.946720497</v>
+      </c>
+      <c r="H59" t="n">
+        <v>534308.9304601339</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-2211533.489091419</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>4901708.927639459</v>
+      </c>
+      <c r="M59" t="n">
+        <v>14174888.83003536</v>
+      </c>
+      <c r="N59" t="n">
+        <v>24510.93196692576</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>24510.93196692576</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>24508.54463819744</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2.387328728292584</v>
+      </c>
+      <c r="V59" t="n">
+        <v>15.35400009155273</v>
+      </c>
+      <c r="W59" t="n">
+        <v>14174888.83003536</v>
+      </c>
+      <c r="X59" t="n">
+        <v>14174888.83003536</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203185731_dh_0.5_ctax_200_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>13050595.57619142</v>
+      </c>
+      <c r="B60" t="n">
+        <v>3997160.312296993</v>
+      </c>
+      <c r="C60" t="n">
+        <v>3303114.528733135</v>
+      </c>
+      <c r="D60" t="n">
+        <v>3621796.028855239</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>7618956.341152232</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3303114.528733135</v>
+      </c>
+      <c r="H60" t="n">
+        <v>593029.7712397474</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-3462736.43041174</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>4998231.365478043</v>
+      </c>
+      <c r="M60" t="n">
+        <v>13050595.57619142</v>
+      </c>
+      <c r="N60" t="n">
+        <v>24993.54151826473</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>24993.54151826473</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>24991.15682739007</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2.384690874535248</v>
+      </c>
+      <c r="V60" t="n">
+        <v>21.62899994850159</v>
+      </c>
+      <c r="W60" t="n">
+        <v>13050595.57619142</v>
+      </c>
+      <c r="X60" t="n">
+        <v>13050595.57619142</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203185946_dh_0.5_ctax_200_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>11717541.06871194</v>
+      </c>
+      <c r="B61" t="n">
+        <v>3977310.968354817</v>
+      </c>
+      <c r="C61" t="n">
+        <v>3293793.065332896</v>
+      </c>
+      <c r="D61" t="n">
+        <v>3609727.342219941</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>7587038.310574759</v>
+      </c>
+      <c r="G61" t="n">
+        <v>3293793.065332896</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1458057.250126028</v>
+      </c>
+      <c r="I61" t="n">
+        <v>-6494033.260181566</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>5872685.702859823</v>
+      </c>
+      <c r="M61" t="n">
+        <v>11717541.06871194</v>
+      </c>
+      <c r="N61" t="n">
+        <v>29365.80856117877</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>29365.80856117877</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>29363.42851429919</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2.380046879571997</v>
+      </c>
+      <c r="V61" t="n">
+        <v>24.21799993515015</v>
+      </c>
+      <c r="W61" t="n">
+        <v>11491774.54664642</v>
+      </c>
+      <c r="X61" t="n">
+        <v>11717541.06871194</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>225766.5220655203</v>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203190211_dh_0.5_ctax_200_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>9647931.251341309</v>
+      </c>
+      <c r="B62" t="n">
+        <v>3945722.237364023</v>
+      </c>
+      <c r="C62" t="n">
+        <v>3278958.660697234</v>
+      </c>
+      <c r="D62" t="n">
+        <v>3589422.799112685</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>7535145.036476707</v>
+      </c>
+      <c r="G62" t="n">
+        <v>3278958.660697234</v>
+      </c>
+      <c r="H62" t="n">
+        <v>3820418.498166881</v>
+      </c>
+      <c r="I62" t="n">
+        <v>-13192796.2856021</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>8206205.34160259</v>
+      </c>
+      <c r="M62" t="n">
+        <v>9647931.251341309</v>
+      </c>
+      <c r="N62" t="n">
+        <v>41033.3974839242</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>41033.3974839242</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>41031.02670801261</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2.370775911802941</v>
+      </c>
+      <c r="V62" t="n">
+        <v>23.93899989128113</v>
+      </c>
+      <c r="W62" t="n">
+        <v>9647931.251341309</v>
+      </c>
+      <c r="X62" t="n">
+        <v>9647931.251341309</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203190625_dh_0.5_ctax_200_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>6334032.070192313</v>
+      </c>
+      <c r="B63" t="n">
+        <v>3915853.289731215</v>
+      </c>
+      <c r="C63" t="n">
+        <v>3264931.884649927</v>
+      </c>
+      <c r="D63" t="n">
+        <v>3569135.187273225</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>7484988.477004441</v>
+      </c>
+      <c r="G63" t="n">
+        <v>3264931.884649927</v>
+      </c>
+      <c r="H63" t="n">
+        <v>7517718.025792934</v>
+      </c>
+      <c r="I63" t="n">
+        <v>-23729895.88902042</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>11796289.57176543</v>
+      </c>
+      <c r="M63" t="n">
+        <v>6334032.070192313</v>
+      </c>
+      <c r="N63" t="n">
+        <v>58983.808004602</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>58983.808004602</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>58981.4478588261</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2.360145776358654</v>
+      </c>
+      <c r="V63" t="n">
+        <v>20.83200001716614</v>
+      </c>
+      <c r="W63" t="n">
+        <v>6334032.070192313</v>
+      </c>
+      <c r="X63" t="n">
+        <v>6334032.070192313</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203190854_dh_0.5_ctax_200_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>-1386927.71550343</v>
+      </c>
+      <c r="B64" t="n">
+        <v>31572859.92774189</v>
+      </c>
+      <c r="C64" t="n">
+        <v>4433066.460455096</v>
+      </c>
+      <c r="D64" t="n">
+        <v>22542686.79304919</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>54115546.72079108</v>
+      </c>
+      <c r="G64" t="n">
+        <v>4433066.460455096</v>
+      </c>
+      <c r="H64" t="n">
+        <v>4379556.888946415</v>
+      </c>
+      <c r="I64" t="n">
+        <v>-73999708.32992733</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>9684610.544231305</v>
+      </c>
+      <c r="M64" t="n">
+        <v>-1386927.71550343</v>
+      </c>
+      <c r="N64" t="n">
+        <v>48427.88679236333</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>48427.88679236333</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>48423.05272115547</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>4.834071206764879</v>
+      </c>
+      <c r="V64" t="n">
+        <v>27.99699997901917</v>
+      </c>
+      <c r="W64" t="n">
+        <v>-1386927.71550343</v>
+      </c>
+      <c r="X64" t="n">
+        <v>-1386927.71550343</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203191120_dh_0.5_ctax_200_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>-12002131.27383834</v>
+      </c>
+      <c r="B65" t="n">
+        <v>31845651.8151454</v>
+      </c>
+      <c r="C65" t="n">
+        <v>4458987.607501583</v>
+      </c>
+      <c r="D65" t="n">
+        <v>22729601.76450172</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>54575253.57964712</v>
+      </c>
+      <c r="G65" t="n">
+        <v>4458987.607501583</v>
+      </c>
+      <c r="H65" t="n">
+        <v>4566362.935086612</v>
+      </c>
+      <c r="I65" t="n">
+        <v>-85191196.80956975</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>9588461.413496096</v>
+      </c>
+      <c r="M65" t="n">
+        <v>-12002131.27383834</v>
+      </c>
+      <c r="N65" t="n">
+        <v>47947.17630382952</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>47947.17630382952</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>47942.30706748046</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>4.869236349029798</v>
+      </c>
+      <c r="V65" t="n">
+        <v>21.76999998092651</v>
+      </c>
+      <c r="W65" t="n">
+        <v>-12002131.27383834</v>
+      </c>
+      <c r="X65" t="n">
+        <v>-12002131.27383834</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203191353_dh_0.5_ctax_200_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>16492545.36340537</v>
+      </c>
+      <c r="B66" t="n">
+        <v>4037511.55679101</v>
+      </c>
+      <c r="C66" t="n">
+        <v>3322063.903070181</v>
+      </c>
+      <c r="D66" t="n">
+        <v>3644586.51770886</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>7682098.074499871</v>
+      </c>
+      <c r="G66" t="n">
+        <v>3322063.903070181</v>
+      </c>
+      <c r="H66" t="n">
+        <v>535204.1193386901</v>
+      </c>
+      <c r="I66" t="n">
+        <v>-1098650.487655586</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>6051829.754152212</v>
+      </c>
+      <c r="M66" t="n">
+        <v>16492545.36340537</v>
+      </c>
+      <c r="N66" t="n">
+        <v>24209.71016241052</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>24209.71016241052</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>24207.3190166089</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2.391145801669482</v>
+      </c>
+      <c r="V66" t="n">
+        <v>17.49600005149841</v>
+      </c>
+      <c r="W66" t="n">
+        <v>16492545.36340537</v>
+      </c>
+      <c r="X66" t="n">
+        <v>16492545.36340537</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203191835_dh_0.5_ctax_250_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>15393277.50847416</v>
+      </c>
+      <c r="B67" t="n">
+        <v>4031803.261001063</v>
+      </c>
+      <c r="C67" t="n">
+        <v>3319383.226548138</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3641494.422095409</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>7673297.683096472</v>
+      </c>
+      <c r="G67" t="n">
+        <v>3319383.226548138</v>
+      </c>
+      <c r="H67" t="n">
+        <v>535056.3695936643</v>
+      </c>
+      <c r="I67" t="n">
+        <v>-2199862.236681958</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>6065402.465917845</v>
+      </c>
+      <c r="M67" t="n">
+        <v>15393277.50847416</v>
+      </c>
+      <c r="N67" t="n">
+        <v>24264.0003222956</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>24264.0003222956</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>24261.60986367137</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2.390458624299067</v>
+      </c>
+      <c r="V67" t="n">
+        <v>22.94099998474121</v>
+      </c>
+      <c r="W67" t="n">
+        <v>15393277.50847416</v>
+      </c>
+      <c r="X67" t="n">
+        <v>15393277.50847416</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203192057_dh_0.5_ctax_250_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>14285733.60387333</v>
+      </c>
+      <c r="B68" t="n">
+        <v>4023469.265920782</v>
+      </c>
+      <c r="C68" t="n">
+        <v>3315469.493663821</v>
+      </c>
+      <c r="D68" t="n">
+        <v>3636902.443380567</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>7660371.709301349</v>
+      </c>
+      <c r="G68" t="n">
+        <v>3315469.493663821</v>
+      </c>
+      <c r="H68" t="n">
+        <v>558908.2998361967</v>
+      </c>
+      <c r="I68" t="n">
+        <v>-3364719.421063356</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>6115703.522135326</v>
+      </c>
+      <c r="M68" t="n">
+        <v>14285733.60387333</v>
+      </c>
+      <c r="N68" t="n">
+        <v>24465.20341105248</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>24465.20341105248</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>24462.81408854124</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2.38932251120534</v>
+      </c>
+      <c r="V68" t="n">
+        <v>24.64499998092651</v>
+      </c>
+      <c r="W68" t="n">
+        <v>14285733.60387333</v>
+      </c>
+      <c r="X68" t="n">
+        <v>14285733.60387333</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203192325_dh_0.5_ctax_250_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>13099855.09697009</v>
+      </c>
+      <c r="B69" t="n">
+        <v>4012422.399559041</v>
+      </c>
+      <c r="C69" t="n">
+        <v>3310281.767521423</v>
+      </c>
+      <c r="D69" t="n">
+        <v>3630676.889774156</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>7643099.289333197</v>
+      </c>
+      <c r="G69" t="n">
+        <v>3310281.767521423</v>
+      </c>
+      <c r="H69" t="n">
+        <v>891482.2841544072</v>
+      </c>
+      <c r="I69" t="n">
+        <v>-5280122.700324489</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>6535114.456285553</v>
+      </c>
+      <c r="M69" t="n">
+        <v>13099855.09697009</v>
+      </c>
+      <c r="N69" t="n">
+        <v>26142.84540404028</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>26142.84540404028</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>26140.45782514229</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2.387578897966224</v>
+      </c>
+      <c r="V69" t="n">
+        <v>31.43600010871887</v>
+      </c>
+      <c r="W69" t="n">
+        <v>13099855.09697009</v>
+      </c>
+      <c r="X69" t="n">
+        <v>13099855.09697009</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203192554_dh_0.5_ctax_250_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>11460865.64756212</v>
+      </c>
+      <c r="B70" t="n">
+        <v>4000845.17301723</v>
+      </c>
+      <c r="C70" t="n">
+        <v>3304844.978587736</v>
+      </c>
+      <c r="D70" t="n">
+        <v>3623972.20077942</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>7624817.37379665</v>
+      </c>
+      <c r="G70" t="n">
+        <v>3304844.978587736</v>
+      </c>
+      <c r="H70" t="n">
+        <v>2299634.237263725</v>
+      </c>
+      <c r="I70" t="n">
+        <v>-9974440.478880623</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>8206009.536794627</v>
+      </c>
+      <c r="M70" t="n">
+        <v>11460865.64756212</v>
+      </c>
+      <c r="N70" t="n">
+        <v>32826.42359010752</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>32826.42359010752</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>32824.03814717881</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2.3854429287299</v>
+      </c>
+      <c r="V70" t="n">
+        <v>39.58399987220764</v>
+      </c>
+      <c r="W70" t="n">
+        <v>11460865.64756212</v>
+      </c>
+      <c r="X70" t="n">
+        <v>11460865.64756212</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203192837_dh_0.5_ctax_250_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>8947775.562099539</v>
+      </c>
+      <c r="B71" t="n">
+        <v>3988508.123751353</v>
+      </c>
+      <c r="C71" t="n">
+        <v>3299051.368807291</v>
+      </c>
+      <c r="D71" t="n">
+        <v>3616607.582977143</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>7605115.706728496</v>
+      </c>
+      <c r="G71" t="n">
+        <v>3299051.368807291</v>
+      </c>
+      <c r="H71" t="n">
+        <v>5069226.004902262</v>
+      </c>
+      <c r="I71" t="n">
+        <v>-18487021.36194453</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>11461403.84360602</v>
+      </c>
+      <c r="M71" t="n">
+        <v>8947775.562099539</v>
+      </c>
+      <c r="N71" t="n">
+        <v>45847.99816466246</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>45847.99816466246</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>45845.61537442465</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2.38279023745593</v>
+      </c>
+      <c r="V71" t="n">
+        <v>41.71499991416931</v>
+      </c>
+      <c r="W71" t="n">
+        <v>8947775.562099539</v>
+      </c>
+      <c r="X71" t="n">
+        <v>8947775.562099539</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203193411_dh_0.5_ctax_250_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>945553.7037764285</v>
+      </c>
+      <c r="B72" t="n">
+        <v>32022539.03271048</v>
+      </c>
+      <c r="C72" t="n">
+        <v>4475795.730429251</v>
+      </c>
+      <c r="D72" t="n">
+        <v>22849642.92781117</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>54872181.96052165</v>
+      </c>
+      <c r="G72" t="n">
+        <v>4475795.730429251</v>
+      </c>
+      <c r="H72" t="n">
+        <v>4140287.815133134</v>
+      </c>
+      <c r="I72" t="n">
+        <v>-73832675.44835924</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>11289963.64605163</v>
+      </c>
+      <c r="M72" t="n">
+        <v>945553.7037764285</v>
+      </c>
+      <c r="N72" t="n">
+        <v>45164.7450509393</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>45164.7450509393</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>45159.85458420651</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>4.890466732799332</v>
+      </c>
+      <c r="V72" t="n">
+        <v>32.69700002670288</v>
+      </c>
+      <c r="W72" t="n">
+        <v>945553.7037764285</v>
+      </c>
+      <c r="X72" t="n">
+        <v>945553.7037764285</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203193707_dh_0.5_ctax_250_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>-9658276.826592447</v>
+      </c>
+      <c r="B73" t="n">
+        <v>32192029.80639484</v>
+      </c>
+      <c r="C73" t="n">
+        <v>4491901.030735327</v>
+      </c>
+      <c r="D73" t="n">
+        <v>22963687.6213389</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>55155717.42773373</v>
+      </c>
+      <c r="G73" t="n">
+        <v>4491901.030735327</v>
+      </c>
+      <c r="H73" t="n">
+        <v>4460597.507690292</v>
+      </c>
+      <c r="I73" t="n">
+        <v>-85244987.08654992</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>11478494.29379812</v>
+      </c>
+      <c r="M73" t="n">
+        <v>-9658276.826592447</v>
+      </c>
+      <c r="N73" t="n">
+        <v>45918.88666141008</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>45918.88666141008</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>45913.97717519248</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>4.909486217584692</v>
+      </c>
+      <c r="V73" t="n">
+        <v>19.77800011634827</v>
+      </c>
+      <c r="W73" t="n">
+        <v>-9658276.826592447</v>
+      </c>
+      <c r="X73" t="n">
+        <v>-9658276.826592447</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203193952_dh_0.5_ctax_250_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>15364390.74356262</v>
+      </c>
+      <c r="B74" t="n">
+        <v>3883804.561409576</v>
+      </c>
+      <c r="C74" t="n">
+        <v>3249881.460366655</v>
+      </c>
+      <c r="D74" t="n">
+        <v>3306183.116767689</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>7189987.678177265</v>
+      </c>
+      <c r="G74" t="n">
+        <v>3249881.460366655</v>
+      </c>
+      <c r="H74" t="n">
+        <v>116795.5611062836</v>
+      </c>
+      <c r="I74" t="n">
+        <v>-1062669.751939387</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>5870395.795851803</v>
+      </c>
+      <c r="M74" t="n">
+        <v>15364390.74356262</v>
+      </c>
+      <c r="N74" t="n">
+        <v>58705.89370708811</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>58705.89370708811</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>58703.95795851787</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1.935748570122809</v>
+      </c>
+      <c r="V74" t="n">
+        <v>20.37400007247925</v>
+      </c>
+      <c r="W74" t="n">
+        <v>15364390.74356262</v>
+      </c>
+      <c r="X74" t="n">
+        <v>15364390.74356262</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203194226_dh_1_ctax_100_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>12530462.2256517</v>
+      </c>
+      <c r="B75" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>136352.8646669782</v>
+      </c>
+      <c r="I75" t="n">
+        <v>-9316336.802926052</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>21365429.60973109</v>
+      </c>
+      <c r="M75" t="n">
+        <v>12530462.2256517</v>
+      </c>
+      <c r="N75" t="n">
+        <v>213654.2960973108</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>213654.2960973108</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>213654.2960973109</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>17.67000007629395</v>
+      </c>
+      <c r="W75" t="n">
+        <v>12530462.2256517</v>
+      </c>
+      <c r="X75" t="n">
+        <v>12530462.2256517</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203194501_dh_1_ctax_100_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>7796511.362991767</v>
+      </c>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>578486.0919676765</v>
+      </c>
+      <c r="I76" t="n">
+        <v>-14696907.51051326</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>21569916.22735767</v>
+      </c>
+      <c r="M76" t="n">
+        <v>7796511.362991767</v>
+      </c>
+      <c r="N76" t="n">
+        <v>215699.1622735765</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>215699.1622735765</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>215699.1622735766</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" t="n">
+        <v>10.4779999256134</v>
+      </c>
+      <c r="W76" t="n">
+        <v>7796511.362991592</v>
+      </c>
+      <c r="X76" t="n">
+        <v>7796511.362991767</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>1.7508864402771e-07</v>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203194735_dh_1_ctax_100_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2668555.614585821</v>
+      </c>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1782376.769846283</v>
+      </c>
+      <c r="I77" t="n">
+        <v>-21585553.37531666</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>22126715.66587652</v>
+      </c>
+      <c r="M77" t="n">
+        <v>2668555.614585821</v>
+      </c>
+      <c r="N77" t="n">
+        <v>221267.1566587651</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>221267.1566587651</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>221267.1566587652</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" t="n">
+        <v>8.269000053405762</v>
+      </c>
+      <c r="W77" t="n">
+        <v>2668555.614585802</v>
+      </c>
+      <c r="X77" t="n">
+        <v>2668555.614585821</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>1.816079020500183e-08</v>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203194959_dh_1_ctax_100_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>-3004014.602587033</v>
+      </c>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>3298136.66063236</v>
+      </c>
+      <c r="I78" t="n">
+        <v>-29474922.43276415</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>22827754.61536508</v>
+      </c>
+      <c r="M78" t="n">
+        <v>-3004014.602587033</v>
+      </c>
+      <c r="N78" t="n">
+        <v>228277.5461536508</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>228277.5461536508</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>228277.5461536508</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" t="n">
+        <v>8.253000020980835</v>
+      </c>
+      <c r="W78" t="n">
+        <v>-3004014.602587042</v>
+      </c>
+      <c r="X78" t="n">
+        <v>-3004014.602587033</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>8.847564458847046e-09</v>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203195552_dh_1_ctax_100_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>-8995375.593067665</v>
+      </c>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>3887042.836429428</v>
+      </c>
+      <c r="I79" t="n">
+        <v>-36327558.705348</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>23100123.72167123</v>
+      </c>
+      <c r="M79" t="n">
+        <v>-8995375.593067665</v>
+      </c>
+      <c r="N79" t="n">
+        <v>231001.2372167122</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>231001.2372167122</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>231001.2372167122</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" t="n">
+        <v>8.662999868392944</v>
+      </c>
+      <c r="W79" t="n">
+        <v>-8995375.593067702</v>
+      </c>
+      <c r="X79" t="n">
+        <v>-8995375.593067665</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>3.725290298461914e-08</v>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203195820_dh_1_ctax_100_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>-15079222.79095962</v>
+      </c>
+      <c r="B80" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>4120212.559996934</v>
+      </c>
+      <c r="I80" t="n">
+        <v>-42752416.62395743</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>23207964.71882119</v>
+      </c>
+      <c r="M80" t="n">
+        <v>-15079222.79095962</v>
+      </c>
+      <c r="N80" t="n">
+        <v>232079.6471882118</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>232079.6471882118</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>232079.6471882119</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" t="n">
+        <v>12.63199996948242</v>
+      </c>
+      <c r="W80" t="n">
+        <v>-15079222.79095962</v>
+      </c>
+      <c r="X80" t="n">
+        <v>-15079222.79095962</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203200047_dh_1_ctax_100_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>-21194748.71856795</v>
+      </c>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>4184724.50978855</v>
+      </c>
+      <c r="I81" t="n">
+        <v>-48962291.278136</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>23237801.49559982</v>
+      </c>
+      <c r="M81" t="n">
+        <v>-21194748.71856795</v>
+      </c>
+      <c r="N81" t="n">
+        <v>232378.0149559981</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>232378.0149559981</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>232378.0149559981</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" t="n">
+        <v>13.17899990081787</v>
+      </c>
+      <c r="W81" t="n">
+        <v>-21194748.71856795</v>
+      </c>
+      <c r="X81" t="n">
+        <v>-21194748.71856795</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203200318_dh_1_ctax_100_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>17208815.21468272</v>
+      </c>
+      <c r="B82" t="n">
+        <v>3992490.392955404</v>
+      </c>
+      <c r="C82" t="n">
+        <v>3300921.484854632</v>
+      </c>
+      <c r="D82" t="n">
+        <v>3619011.035583267</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="n">
+        <v>7611501.428538671</v>
+      </c>
+      <c r="G82" t="n">
+        <v>3300921.484854632</v>
+      </c>
+      <c r="H82" t="n">
+        <v>2331985.698475967</v>
+      </c>
+      <c r="I82" t="n">
+        <v>-1002661.096508253</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>4967067.699321708</v>
+      </c>
+      <c r="M82" t="n">
+        <v>17208815.21468272</v>
+      </c>
+      <c r="N82" t="n">
+        <v>33116.1683535609</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>33116.1683535609</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>33113.78466214484</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" t="n">
+        <v>2.383691416144157</v>
+      </c>
+      <c r="V82" t="n">
+        <v>18.17799997329712</v>
+      </c>
+      <c r="W82" t="n">
+        <v>17208815.21468272</v>
+      </c>
+      <c r="X82" t="n">
+        <v>17208815.21468272</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203200549_dh_1_ctax_150_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>16201045.1762715</v>
+      </c>
+      <c r="B83" t="n">
+        <v>3967198.984932876</v>
+      </c>
+      <c r="C83" t="n">
+        <v>3289044.370179745</v>
+      </c>
+      <c r="D83" t="n">
+        <v>3603365.17032534</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>7570564.155258216</v>
+      </c>
+      <c r="G83" t="n">
+        <v>3289044.370179745</v>
+      </c>
+      <c r="H83" t="n">
+        <v>2332207.657152853</v>
+      </c>
+      <c r="I83" t="n">
+        <v>-2034513.076613918</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>5043742.070294598</v>
+      </c>
+      <c r="M83" t="n">
+        <v>16201045.1762715</v>
+      </c>
+      <c r="N83" t="n">
+        <v>33627.32445001485</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>33627.32445001485</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>33624.94713529748</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="n">
+        <v>2.377314717215757</v>
+      </c>
+      <c r="V83" t="n">
+        <v>18.73700022697449</v>
+      </c>
+      <c r="W83" t="n">
+        <v>16201045.1762715</v>
+      </c>
+      <c r="X83" t="n">
+        <v>16201045.1762715</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203200829_dh_1_ctax_150_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>15136354.33905027</v>
+      </c>
+      <c r="B84" t="n">
+        <v>3913865.344081072</v>
+      </c>
+      <c r="C84" t="n">
+        <v>3263998.324192037</v>
+      </c>
+      <c r="D84" t="n">
+        <v>3566698.217423387</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>7480563.561504459</v>
+      </c>
+      <c r="G84" t="n">
+        <v>3263998.324192037</v>
+      </c>
+      <c r="H84" t="n">
+        <v>2516008.047508392</v>
+      </c>
+      <c r="I84" t="n">
+        <v>-3532316.47003173</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>5408100.875877116</v>
+      </c>
+      <c r="M84" t="n">
+        <v>15136354.33905027</v>
+      </c>
+      <c r="N84" t="n">
+        <v>36056.36341662479</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>36056.36341662479</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>36054.00583918083</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" t="n">
+        <v>2.357577443484644</v>
+      </c>
+      <c r="V84" t="n">
+        <v>22.10999989509583</v>
+      </c>
+      <c r="W84" t="n">
+        <v>15136354.33905027</v>
+      </c>
+      <c r="X84" t="n">
+        <v>15136354.33905027</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203201104_dh_1_ctax_150_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>13580458.37307767</v>
+      </c>
+      <c r="B85" t="n">
+        <v>3850773.426328206</v>
+      </c>
+      <c r="C85" t="n">
+        <v>3234369.687401952</v>
+      </c>
+      <c r="D85" t="n">
+        <v>3513976.176986963</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>7364749.603315169</v>
+      </c>
+      <c r="G85" t="n">
+        <v>3234369.687401952</v>
+      </c>
+      <c r="H85" t="n">
+        <v>4158093.735207669</v>
+      </c>
+      <c r="I85" t="n">
+        <v>-8196283.71814975</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>7019529.065302631</v>
+      </c>
+      <c r="M85" t="n">
+        <v>13580458.37307767</v>
+      </c>
+      <c r="N85" t="n">
+        <v>46799.17866019106</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>46799.17866019106</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>46796.86043535132</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" t="n">
+        <v>2.318224839852628</v>
+      </c>
+      <c r="V85" t="n">
+        <v>27.94800019264221</v>
+      </c>
+      <c r="W85" t="n">
+        <v>13580458.37307767</v>
+      </c>
+      <c r="X85" t="n">
+        <v>13580458.37307767</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203201342_dh_1_ctax_150_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>8301004.985964015</v>
+      </c>
+      <c r="B86" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>2308052.909671388</v>
+      </c>
+      <c r="I86" t="n">
+        <v>-27906825.7987055</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>33554761.32081845</v>
+      </c>
+      <c r="M86" t="n">
+        <v>8301004.985964015</v>
+      </c>
+      <c r="N86" t="n">
+        <v>223698.4088054562</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>223698.4088054562</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>223698.4088054562</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" t="n">
+        <v>23.78699994087219</v>
+      </c>
+      <c r="W86" t="n">
+        <v>8301004.985964015</v>
+      </c>
+      <c r="X86" t="n">
+        <v>8301004.985964015</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203202049_dh_1_ctax_150_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>2510886.93562004</v>
+      </c>
+      <c r="B87" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>3421700.540555991</v>
+      </c>
+      <c r="I87" t="n">
+        <v>-35583184.52386028</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>34327354.36474465</v>
+      </c>
+      <c r="M87" t="n">
+        <v>2510886.93562004</v>
+      </c>
+      <c r="N87" t="n">
+        <v>228849.0290982975</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>228849.0290982975</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>228849.0290982976</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" t="n">
+        <v>0</v>
+      </c>
+      <c r="U87" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" t="n">
+        <v>14.57099986076355</v>
+      </c>
+      <c r="W87" t="n">
+        <v>2510886.93562004</v>
+      </c>
+      <c r="X87" t="n">
+        <v>2510886.93562004</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203202327_dh_1_ctax_150_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>-3499956.871096313</v>
+      </c>
+      <c r="B88" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>3898421.046107692</v>
+      </c>
+      <c r="I88" t="n">
+        <v>-42401473.68685482</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>34658079.21547113</v>
+      </c>
+      <c r="M88" t="n">
+        <v>-3499956.871096313</v>
+      </c>
+      <c r="N88" t="n">
+        <v>231053.8614364742</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>231053.8614364742</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>231053.8614364742</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" t="n">
+        <v>13.73099994659424</v>
+      </c>
+      <c r="W88" t="n">
+        <v>-3499956.871096313</v>
+      </c>
+      <c r="X88" t="n">
+        <v>-3499956.871096313</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203202553_dh_1_ctax_150_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>-10880124.06699132</v>
+      </c>
+      <c r="B89" t="n">
+        <v>31226380.04370679</v>
+      </c>
+      <c r="C89" t="n">
+        <v>4400143.355196329</v>
+      </c>
+      <c r="D89" t="n">
+        <v>22302671.72336628</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>53529051.76707308</v>
+      </c>
+      <c r="G89" t="n">
+        <v>4400143.355196329</v>
+      </c>
+      <c r="H89" t="n">
+        <v>6680329.928234284</v>
+      </c>
+      <c r="I89" t="n">
+        <v>-84625735.77908763</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>9136086.661592619</v>
+      </c>
+      <c r="M89" t="n">
+        <v>-10880124.06699132</v>
+      </c>
+      <c r="N89" t="n">
+        <v>60912.03028348144</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>60912.03028348144</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>60907.24441061635</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="n">
+        <v>4.785872864007008</v>
+      </c>
+      <c r="V89" t="n">
+        <v>17.90499997138977</v>
+      </c>
+      <c r="W89" t="n">
+        <v>-10880124.06699132</v>
+      </c>
+      <c r="X89" t="n">
+        <v>-10880124.06699132</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203202819_dh_1_ctax_150_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>18852777.82841406</v>
+      </c>
+      <c r="B90" t="n">
+        <v>4021095.076777081</v>
+      </c>
+      <c r="C90" t="n">
+        <v>3314354.549146122</v>
+      </c>
+      <c r="D90" t="n">
+        <v>3635577.29319988</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>7656672.36997696</v>
+      </c>
+      <c r="G90" t="n">
+        <v>3314354.549146122</v>
+      </c>
+      <c r="H90" t="n">
+        <v>2334393.915379992</v>
+      </c>
+      <c r="I90" t="n">
+        <v>-993173.9153408579</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>6540530.909251847</v>
+      </c>
+      <c r="M90" t="n">
+        <v>18852777.82841406</v>
+      </c>
+      <c r="N90" t="n">
+        <v>32705.04351602709</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>32705.04351602709</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>32702.65454625951</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" t="n">
+        <v>2.388969767632488</v>
+      </c>
+      <c r="V90" t="n">
+        <v>18.73799991607666</v>
+      </c>
+      <c r="W90" t="n">
+        <v>18852777.82841406</v>
+      </c>
+      <c r="X90" t="n">
+        <v>18852777.82841406</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203203050_dh_1_ctax_200_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>17857916.35545753</v>
+      </c>
+      <c r="B91" t="n">
+        <v>4009197.730814908</v>
+      </c>
+      <c r="C91" t="n">
+        <v>3308767.428721919</v>
+      </c>
+      <c r="D91" t="n">
+        <v>3628829.975862685</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>7638027.706677593</v>
+      </c>
+      <c r="G91" t="n">
+        <v>3308767.428721919</v>
+      </c>
+      <c r="H91" t="n">
+        <v>2333546.500204339</v>
+      </c>
+      <c r="I91" t="n">
+        <v>-1993381.492701963</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>6570956.212555635</v>
+      </c>
+      <c r="M91" t="n">
+        <v>17857916.35545753</v>
+      </c>
+      <c r="N91" t="n">
+        <v>32857.16808197299</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>32857.16808197299</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>32854.78106277801</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" t="n">
+        <v>2.387019194986164</v>
+      </c>
+      <c r="V91" t="n">
+        <v>22.41999983787537</v>
+      </c>
+      <c r="W91" t="n">
+        <v>17857916.35545753</v>
+      </c>
+      <c r="X91" t="n">
+        <v>17857916.35545753</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203203322_dh_1_ctax_200_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>16847269.84081097</v>
+      </c>
+      <c r="B92" t="n">
+        <v>3995194.796518032</v>
+      </c>
+      <c r="C92" t="n">
+        <v>3302191.501581731</v>
+      </c>
+      <c r="D92" t="n">
+        <v>3620627.722044992</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>7615822.518563025</v>
+      </c>
+      <c r="G92" t="n">
+        <v>3302191.501581731</v>
+      </c>
+      <c r="H92" t="n">
+        <v>2379171.372392403</v>
+      </c>
+      <c r="I92" t="n">
+        <v>-3106952.574287405</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>6657037.022561216</v>
+      </c>
+      <c r="M92" t="n">
+        <v>16847269.84081097</v>
+      </c>
+      <c r="N92" t="n">
+        <v>33287.56938963837</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>33287.56938963837</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>33285.18511280632</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" t="n">
+        <v>2.384276832284183</v>
+      </c>
+      <c r="V92" t="n">
+        <v>27.93899989128113</v>
+      </c>
+      <c r="W92" t="n">
+        <v>16847269.84081097</v>
+      </c>
+      <c r="X92" t="n">
+        <v>16847269.84081097</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203203558_dh_1_ctax_200_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>15640498.33831158</v>
+      </c>
+      <c r="B93" t="n">
+        <v>3974467.643878512</v>
+      </c>
+      <c r="C93" t="n">
+        <v>3292457.8098646</v>
+      </c>
+      <c r="D93" t="n">
+        <v>3606970.120245574</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>7581437.764124085</v>
+      </c>
+      <c r="G93" t="n">
+        <v>3292457.8098646</v>
+      </c>
+      <c r="H93" t="n">
+        <v>3198165.830169241</v>
+      </c>
+      <c r="I93" t="n">
+        <v>-5952669.67457174</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>7521106.608725394</v>
+      </c>
+      <c r="M93" t="n">
+        <v>15640498.33831158</v>
+      </c>
+      <c r="N93" t="n">
+        <v>37607.91066422647</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>37607.91066422647</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>37605.53304362662</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" t="n">
+        <v>2.377620600239152</v>
+      </c>
+      <c r="V93" t="n">
+        <v>45.41199994087219</v>
+      </c>
+      <c r="W93" t="n">
+        <v>15640498.33831158</v>
+      </c>
+      <c r="X93" t="n">
+        <v>15640498.33831158</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203203841_dh_1_ctax_200_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>13719077.52163734</v>
+      </c>
+      <c r="B94" t="n">
+        <v>3941763.723489471</v>
+      </c>
+      <c r="C94" t="n">
+        <v>3277099.700405727</v>
+      </c>
+      <c r="D94" t="n">
+        <v>3583456.629534142</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>7525220.353023613</v>
+      </c>
+      <c r="G94" t="n">
+        <v>3277099.700405727</v>
+      </c>
+      <c r="H94" t="n">
+        <v>5443056.932678772</v>
+      </c>
+      <c r="I94" t="n">
+        <v>-12345780.91526832</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>9819481.450797547</v>
+      </c>
+      <c r="M94" t="n">
+        <v>13719077.52163734</v>
+      </c>
+      <c r="N94" t="n">
+        <v>49099.77100892796</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
+        <v>49099.77100892796</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>49097.40725398785</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" t="n">
+        <v>2.363754939473468</v>
+      </c>
+      <c r="V94" t="n">
+        <v>32.85199999809265</v>
+      </c>
+      <c r="W94" t="n">
+        <v>13719077.52163734</v>
+      </c>
+      <c r="X94" t="n">
+        <v>13719077.52163734</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD94" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203204139_dh_1_ctax_200_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>10581849.43048641</v>
+      </c>
+      <c r="B95" t="n">
+        <v>3905257.390648999</v>
+      </c>
+      <c r="C95" t="n">
+        <v>3259955.937546828</v>
+      </c>
+      <c r="D95" t="n">
+        <v>3550294.699408923</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>7455552.090057923</v>
+      </c>
+      <c r="G95" t="n">
+        <v>3259955.937546828</v>
+      </c>
+      <c r="H95" t="n">
+        <v>8952106.481126565</v>
+      </c>
+      <c r="I95" t="n">
+        <v>-22588204.86667816</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>13502439.78843325</v>
+      </c>
+      <c r="M95" t="n">
+        <v>10581849.43048641</v>
+      </c>
+      <c r="N95" t="n">
+        <v>67514.53537913569</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
+        <v>67514.53537913569</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>67512.19894216491</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" t="n">
+        <v>2.33643697039089</v>
+      </c>
+      <c r="V95" t="n">
+        <v>34.01099991798401</v>
+      </c>
+      <c r="W95" t="n">
+        <v>10581849.43048641</v>
+      </c>
+      <c r="X95" t="n">
+        <v>10581849.43048641</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203204428_dh_1_ctax_200_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>2616020.057554567</v>
+      </c>
+      <c r="B96" t="n">
+        <v>31572859.92774189</v>
+      </c>
+      <c r="C96" t="n">
+        <v>4433066.460455096</v>
+      </c>
+      <c r="D96" t="n">
+        <v>22542686.79304919</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="n">
+        <v>54115546.72079108</v>
+      </c>
+      <c r="G96" t="n">
+        <v>4433066.460455096</v>
+      </c>
+      <c r="H96" t="n">
+        <v>6167393.042496535</v>
+      </c>
+      <c r="I96" t="n">
+        <v>-73438345.1524533</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>11338358.98626516</v>
+      </c>
+      <c r="M96" t="n">
+        <v>2616020.057554567</v>
+      </c>
+      <c r="N96" t="n">
+        <v>56696.62900253265</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>56696.62900253265</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>56691.79493132478</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" t="n">
+        <v>4.834071206764879</v>
+      </c>
+      <c r="V96" t="n">
+        <v>37.08699989318848</v>
+      </c>
+      <c r="W96" t="n">
+        <v>2616020.057554567</v>
+      </c>
+      <c r="X96" t="n">
+        <v>2616020.057554567</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203205235_dh_1_ctax_200_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>-7944204.665519098</v>
+      </c>
+      <c r="B97" t="n">
+        <v>31845651.8151454</v>
+      </c>
+      <c r="C97" t="n">
+        <v>4458987.607501583</v>
+      </c>
+      <c r="D97" t="n">
+        <v>22729601.76450172</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
+        <v>54575253.57964712</v>
+      </c>
+      <c r="G97" t="n">
+        <v>4458987.607501583</v>
+      </c>
+      <c r="H97" t="n">
+        <v>6519518.053030788</v>
+      </c>
+      <c r="I97" t="n">
+        <v>-84893093.80329305</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>11395129.89759446</v>
+      </c>
+      <c r="M97" t="n">
+        <v>-7944204.665519098</v>
+      </c>
+      <c r="N97" t="n">
+        <v>56980.51872432132</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>56980.51872432132</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>56975.64948797227</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" t="n">
+        <v>4.869236349029798</v>
+      </c>
+      <c r="V97" t="n">
+        <v>31.5789999961853</v>
+      </c>
+      <c r="W97" t="n">
+        <v>-7944204.665519098</v>
+      </c>
+      <c r="X97" t="n">
+        <v>-7944204.665519098</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203205526_dh_1_ctax_200_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>20483201.27931914</v>
+      </c>
+      <c r="B98" t="n">
+        <v>4036961.534547652</v>
+      </c>
+      <c r="C98" t="n">
+        <v>3321805.606764483</v>
+      </c>
+      <c r="D98" t="n">
+        <v>3644290.484458776</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="n">
+        <v>7681252.019006427</v>
+      </c>
+      <c r="G98" t="n">
+        <v>3321805.606764483</v>
+      </c>
+      <c r="H98" t="n">
+        <v>2335164.241315592</v>
+      </c>
+      <c r="I98" t="n">
+        <v>-989313.2402424782</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>8134292.652475117</v>
+      </c>
+      <c r="M98" t="n">
+        <v>20483201.27931914</v>
+      </c>
+      <c r="N98" t="n">
+        <v>32539.56169275145</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
+        <v>32539.56169275145</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>32537.17060990033</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" t="n">
+        <v>2.391082851305129</v>
+      </c>
+      <c r="V98" t="n">
+        <v>27.20799994468689</v>
+      </c>
+      <c r="W98" t="n">
+        <v>20483201.27931914</v>
+      </c>
+      <c r="X98" t="n">
+        <v>20483201.27931914</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203205815_dh_1_ctax_250_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>19493235.38379059</v>
+      </c>
+      <c r="B99" t="n">
+        <v>4031112.386982329</v>
+      </c>
+      <c r="C99" t="n">
+        <v>3319058.784748018</v>
+      </c>
+      <c r="D99" t="n">
+        <v>3641116.936252727</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>7672229.323235056</v>
+      </c>
+      <c r="G99" t="n">
+        <v>3319058.784748018</v>
+      </c>
+      <c r="H99" t="n">
+        <v>2334916.274214419</v>
+      </c>
+      <c r="I99" t="n">
+        <v>-1981234.163063415</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>8148265.164656507</v>
+      </c>
+      <c r="M99" t="n">
+        <v>19493235.38379059</v>
+      </c>
+      <c r="N99" t="n">
+        <v>32595.45102851605</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>32595.45102851605</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>32593.06065862608</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="n">
+        <v>0</v>
+      </c>
+      <c r="T99" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" t="n">
+        <v>2.390369890098021</v>
+      </c>
+      <c r="V99" t="n">
+        <v>28.20499992370605</v>
+      </c>
+      <c r="W99" t="n">
+        <v>19493235.38379059</v>
+      </c>
+      <c r="X99" t="n">
+        <v>19493235.38379059</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203210058_dh_1_ctax_250_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>18497205.60266523</v>
+      </c>
+      <c r="B100" t="n">
+        <v>4022650.224801221</v>
+      </c>
+      <c r="C100" t="n">
+        <v>3315084.863227596</v>
+      </c>
+      <c r="D100" t="n">
+        <v>3636446.207692333</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>7659096.432493554</v>
+      </c>
+      <c r="G100" t="n">
+        <v>3315084.863227596</v>
+      </c>
+      <c r="H100" t="n">
+        <v>2351582.798662393</v>
+      </c>
+      <c r="I100" t="n">
+        <v>-3019444.477018431</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>8190885.985300119</v>
+      </c>
+      <c r="M100" t="n">
+        <v>18497205.60266523</v>
+      </c>
+      <c r="N100" t="n">
+        <v>32765.93314358331</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" t="n">
+        <v>32765.93314358331</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>32763.54394120063</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="n">
+        <v>0</v>
+      </c>
+      <c r="T100" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" t="n">
+        <v>2.389202382510487</v>
+      </c>
+      <c r="V100" t="n">
+        <v>28.79299998283386</v>
+      </c>
+      <c r="W100" t="n">
+        <v>18497205.60266523</v>
+      </c>
+      <c r="X100" t="n">
+        <v>18497205.60266523</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203210344_dh_1_ctax_250_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>17432805.91590317</v>
+      </c>
+      <c r="B101" t="n">
+        <v>4011639.499616803</v>
+      </c>
+      <c r="C101" t="n">
+        <v>3309914.109367134</v>
+      </c>
+      <c r="D101" t="n">
+        <v>3630229.822381314</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="n">
+        <v>7641869.321998117</v>
+      </c>
+      <c r="G101" t="n">
+        <v>3309914.109367134</v>
+      </c>
+      <c r="H101" t="n">
+        <v>2654222.965119759</v>
+      </c>
+      <c r="I101" t="n">
+        <v>-4749155.878977406</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>8575955.398395561</v>
+      </c>
+      <c r="M101" t="n">
+        <v>17432805.91590317</v>
+      </c>
+      <c r="N101" t="n">
+        <v>34306.20903887904</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>34306.20903887904</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>34303.8215935824</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="n">
+        <v>0</v>
+      </c>
+      <c r="T101" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" t="n">
+        <v>2.387445296479032</v>
+      </c>
+      <c r="V101" t="n">
+        <v>33.6159999370575</v>
+      </c>
+      <c r="W101" t="n">
+        <v>17432805.91590317</v>
+      </c>
+      <c r="X101" t="n">
+        <v>17432805.91590317</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203210630_dh_1_ctax_250_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>15933623.50511108</v>
+      </c>
+      <c r="B102" t="n">
+        <v>4000081.622868036</v>
+      </c>
+      <c r="C102" t="n">
+        <v>3304486.407302423</v>
+      </c>
+      <c r="D102" t="n">
+        <v>3622540.696768277</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>7622622.319636313</v>
+      </c>
+      <c r="G102" t="n">
+        <v>3304486.407302423</v>
+      </c>
+      <c r="H102" t="n">
+        <v>4010400.798729356</v>
+      </c>
+      <c r="I102" t="n">
+        <v>-9224667.800024241</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>10220781.77946723</v>
+      </c>
+      <c r="M102" t="n">
+        <v>15933623.50511108</v>
+      </c>
+      <c r="N102" t="n">
+        <v>40885.51072587717</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>40885.51072587717</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>40883.12711786891</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" t="n">
+        <v>2.383608008431006</v>
+      </c>
+      <c r="V102" t="n">
+        <v>40.30899977684021</v>
+      </c>
+      <c r="W102" t="n">
+        <v>15933623.50511108</v>
+      </c>
+      <c r="X102" t="n">
+        <v>15933623.50511108</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203210922_dh_1_ctax_250_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>13592914.30577072</v>
+      </c>
+      <c r="B103" t="n">
+        <v>3987188.494376964</v>
+      </c>
+      <c r="C103" t="n">
+        <v>3298431.656793076</v>
+      </c>
+      <c r="D103" t="n">
+        <v>3613313.610115452</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="n">
+        <v>7600502.104492416</v>
+      </c>
+      <c r="G103" t="n">
+        <v>3298431.656793076</v>
+      </c>
+      <c r="H103" t="n">
+        <v>6645627.035761591</v>
+      </c>
+      <c r="I103" t="n">
+        <v>-17327269.38501025</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>13375622.89373389</v>
+      </c>
+      <c r="M103" t="n">
+        <v>13592914.30577072</v>
+      </c>
+      <c r="N103" t="n">
+        <v>53504.8697899043</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>53504.8697899043</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>53502.49157493464</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" t="n">
+        <v>2.378214969546107</v>
+      </c>
+      <c r="V103" t="n">
+        <v>39.02699995040894</v>
+      </c>
+      <c r="W103" t="n">
+        <v>13592914.30577072</v>
+      </c>
+      <c r="X103" t="n">
+        <v>13592914.30577072</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203211221_dh_1_ctax_250_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>5330041.744131675</v>
+      </c>
+      <c r="B104" t="n">
+        <v>32022539.03271048</v>
+      </c>
+      <c r="C104" t="n">
+        <v>4475795.730429251</v>
+      </c>
+      <c r="D104" t="n">
+        <v>22849642.92781117</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
+        <v>54872181.96052165</v>
+      </c>
+      <c r="G104" t="n">
+        <v>4475795.730429251</v>
+      </c>
+      <c r="H104" t="n">
+        <v>5662361.563641375</v>
+      </c>
+      <c r="I104" t="n">
+        <v>-72730158.92822489</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>13049861.41776429</v>
+      </c>
+      <c r="M104" t="n">
+        <v>5330041.744131675</v>
+      </c>
+      <c r="N104" t="n">
+        <v>52204.33613778993</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
+        <v>52204.33613778993</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>52199.44567105712</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" t="n">
+        <v>4.890466732799332</v>
+      </c>
+      <c r="V104" t="n">
+        <v>39.54399991035461</v>
+      </c>
+      <c r="W104" t="n">
+        <v>5330041.744131675</v>
+      </c>
+      <c r="X104" t="n">
+        <v>5330041.744131675</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203211521_dh_1_ctax_250_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>-5162657.295494519</v>
+      </c>
+      <c r="B105" t="n">
+        <v>32192029.80639484</v>
+      </c>
+      <c r="C105" t="n">
+        <v>4491901.030735327</v>
+      </c>
+      <c r="D105" t="n">
+        <v>22963687.6213389</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>55155717.42773373</v>
+      </c>
+      <c r="G105" t="n">
+        <v>4491901.030735327</v>
+      </c>
+      <c r="H105" t="n">
+        <v>6288426.099288421</v>
+      </c>
+      <c r="I105" t="n">
+        <v>-84690622.95608546</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>13591921.10283346</v>
+      </c>
+      <c r="M105" t="n">
+        <v>-5162657.295494519</v>
+      </c>
+      <c r="N105" t="n">
+        <v>54372.59389755144</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="n">
+        <v>54372.59389755144</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>54367.68441133383</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" t="n">
+        <v>4.909486217584692</v>
+      </c>
+      <c r="V105" t="n">
+        <v>34.78900003433228</v>
+      </c>
+      <c r="W105" t="n">
+        <v>-5162657.295494519</v>
+      </c>
+      <c r="X105" t="n">
+        <v>-5162657.295494519</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203211822_dh_1_ctax_250_el_price_400</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_WtE/raw_results/technology_selection/Summary.xlsx
+++ b/dataCaseStudy_WtE/raw_results/technology_selection/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE105"/>
+  <dimension ref="A1:AE169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11294,6 +11294,6598 @@
       <c r="AE105" t="inlineStr">
         <is>
           <t>dataCaseStudy_WtE\raw_results\technology_selection\20260203211822_dh_1_ctax_250_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>12745932.76795995</v>
+      </c>
+      <c r="B106" t="n">
+        <v>3909477.192737371</v>
+      </c>
+      <c r="C106" t="n">
+        <v>3262369.350295471</v>
+      </c>
+      <c r="D106" t="n">
+        <v>3507437.414596368</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="n">
+        <v>7416914.607333738</v>
+      </c>
+      <c r="G106" t="n">
+        <v>3262369.350295471</v>
+      </c>
+      <c r="H106" t="n">
+        <v>155.0546472912402</v>
+      </c>
+      <c r="I106" t="n">
+        <v>-1158791.323567969</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>3225285.079251419</v>
+      </c>
+      <c r="M106" t="n">
+        <v>12745932.76795995</v>
+      </c>
+      <c r="N106" t="n">
+        <v>32255.11043664421</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>32255.11043664421</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>32252.85079251404</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" t="n">
+        <v>2.259644130418197</v>
+      </c>
+      <c r="V106" t="n">
+        <v>15.94000005722046</v>
+      </c>
+      <c r="W106" t="n">
+        <v>12745932.76795995</v>
+      </c>
+      <c r="X106" t="n">
+        <v>12745932.76795995</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302220217_dh_0.5_ctax_100_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>10924648.24936593</v>
+      </c>
+      <c r="B107" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>16256.29726210878</v>
+      </c>
+      <c r="I107" t="n">
+        <v>-10746509.5493822</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>21309884.94730634</v>
+      </c>
+      <c r="M107" t="n">
+        <v>10924648.24936593</v>
+      </c>
+      <c r="N107" t="n">
+        <v>213098.8494730633</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>213098.8494730633</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>213098.8494730633</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" t="n">
+        <v>14.86500000953674</v>
+      </c>
+      <c r="W107" t="n">
+        <v>10924648.24936593</v>
+      </c>
+      <c r="X107" t="n">
+        <v>10924648.24936593</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302220504_dh_0.5_ctax_100_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>5509005.287244566</v>
+      </c>
+      <c r="B108" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>251892.889191721</v>
+      </c>
+      <c r="I108" t="n">
+        <v>-16506771.02720062</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>21418866.87107379</v>
+      </c>
+      <c r="M108" t="n">
+        <v>5509005.287244566</v>
+      </c>
+      <c r="N108" t="n">
+        <v>214188.6687107377</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>214188.6687107377</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>214188.6687107378</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="n">
+        <v>0</v>
+      </c>
+      <c r="T108" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" t="n">
+        <v>5.30400013923645</v>
+      </c>
+      <c r="W108" t="n">
+        <v>5509005.28724438</v>
+      </c>
+      <c r="X108" t="n">
+        <v>5509005.287244566</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>1.862645149230957e-07</v>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302220758_dh_0.5_ctax_100_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>-112056.4173187539</v>
+      </c>
+      <c r="B109" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>876781.4848603354</v>
+      </c>
+      <c r="I109" t="n">
+        <v>-23041732.30292929</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>21707877.84657052</v>
+      </c>
+      <c r="M109" t="n">
+        <v>-112056.4173187539</v>
+      </c>
+      <c r="N109" t="n">
+        <v>217078.7784657051</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>217078.7784657051</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>217078.7784657051</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" t="n">
+        <v>5.365000009536743</v>
+      </c>
+      <c r="W109" t="n">
+        <v>-112056.4173187745</v>
+      </c>
+      <c r="X109" t="n">
+        <v>-112056.4173187539</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>2.060551196336746e-08</v>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302221043_dh_0.5_ctax_100_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>-6012963.799714845</v>
+      </c>
+      <c r="B110" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>1647033.57777678</v>
+      </c>
+      <c r="I110" t="n">
+        <v>-30069133.37121569</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>22064119.43954438</v>
+      </c>
+      <c r="M110" t="n">
+        <v>-6012963.799714845</v>
+      </c>
+      <c r="N110" t="n">
+        <v>220641.1943954437</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
+        <v>220641.1943954437</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>220641.1943954437</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" t="n">
+        <v>5.218000173568726</v>
+      </c>
+      <c r="W110" t="n">
+        <v>-6012963.799714865</v>
+      </c>
+      <c r="X110" t="n">
+        <v>-6012963.799714845</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>2.048909664154053e-08</v>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302221318_dh_0.5_ctax_100_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>-12075343.63557519</v>
+      </c>
+      <c r="B111" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>1943719.78314256</v>
+      </c>
+      <c r="I111" t="n">
+        <v>-36565416.78242347</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
+        <v>22201336.80952604</v>
+      </c>
+      <c r="M111" t="n">
+        <v>-12075343.63557519</v>
+      </c>
+      <c r="N111" t="n">
+        <v>222013.3680952604</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
+        <v>222013.3680952604</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>222013.3680952604</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" t="n">
+        <v>0</v>
+      </c>
+      <c r="U111" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" t="n">
+        <v>5.519000053405762</v>
+      </c>
+      <c r="W111" t="n">
+        <v>-12075343.63557523</v>
+      </c>
+      <c r="X111" t="n">
+        <v>-12075343.63557519</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>4.097819328308105e-08</v>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302221558_dh_0.5_ctax_100_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>-18184351.20943364</v>
+      </c>
+      <c r="B112" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>2061813.094625736</v>
+      </c>
+      <c r="I112" t="n">
+        <v>-42847135.82432608</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="n">
+        <v>22255954.96608702</v>
+      </c>
+      <c r="M112" t="n">
+        <v>-18184351.20943364</v>
+      </c>
+      <c r="N112" t="n">
+        <v>222559.5496608701</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="n">
+        <v>222559.5496608701</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>222559.5496608701</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" t="n">
+        <v>6.180999994277954</v>
+      </c>
+      <c r="W112" t="n">
+        <v>-18184351.20943364</v>
+      </c>
+      <c r="X112" t="n">
+        <v>-18184351.20943364</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302221843_dh_0.5_ctax_100_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>-24309389.53214457</v>
+      </c>
+      <c r="B113" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>2094069.069521545</v>
+      </c>
+      <c r="I113" t="n">
+        <v>-49019348.51032212</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>22270873.35447633</v>
+      </c>
+      <c r="M113" t="n">
+        <v>-24309389.53214457</v>
+      </c>
+      <c r="N113" t="n">
+        <v>222708.7335447632</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>222708.7335447632</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>222708.7335447632</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" t="n">
+        <v>0</v>
+      </c>
+      <c r="V113" t="n">
+        <v>5.792999982833862</v>
+      </c>
+      <c r="W113" t="n">
+        <v>-24309389.53214457</v>
+      </c>
+      <c r="X113" t="n">
+        <v>-24309389.53214457</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302222139_dh_0.5_ctax_100_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>14051006.32513241</v>
+      </c>
+      <c r="B114" t="n">
+        <v>3994069.849523495</v>
+      </c>
+      <c r="C114" t="n">
+        <v>3302109.800850721</v>
+      </c>
+      <c r="D114" t="n">
+        <v>3620075.821509643</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="n">
+        <v>7614145.671033138</v>
+      </c>
+      <c r="G114" t="n">
+        <v>3302109.800850721</v>
+      </c>
+      <c r="H114" t="n">
+        <v>533480.8313765341</v>
+      </c>
+      <c r="I114" t="n">
+        <v>-1111504.908340733</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
+        <v>3712774.930212754</v>
+      </c>
+      <c r="M114" t="n">
+        <v>14051006.32513241</v>
+      </c>
+      <c r="N114" t="n">
+        <v>24754.21710783603</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" t="n">
+        <v>24754.21710783603</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>24751.83286808512</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" t="n">
+        <v>0</v>
+      </c>
+      <c r="T114" t="n">
+        <v>0</v>
+      </c>
+      <c r="U114" t="n">
+        <v>2.384239750940718</v>
+      </c>
+      <c r="V114" t="n">
+        <v>12.83200001716614</v>
+      </c>
+      <c r="W114" t="n">
+        <v>14051006.32513241</v>
+      </c>
+      <c r="X114" t="n">
+        <v>14051006.32513241</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302222347_dh_0.5_ctax_150_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>12934675.63314688</v>
+      </c>
+      <c r="B115" t="n">
+        <v>3971035.233911283</v>
+      </c>
+      <c r="C115" t="n">
+        <v>3291288.459642456</v>
+      </c>
+      <c r="D115" t="n">
+        <v>3605945.259497434</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" t="n">
+        <v>7576980.493408717</v>
+      </c>
+      <c r="G115" t="n">
+        <v>3291288.459642456</v>
+      </c>
+      <c r="H115" t="n">
+        <v>538536.342109165</v>
+      </c>
+      <c r="I115" t="n">
+        <v>-2255654.895589798</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>3783525.233576339</v>
+      </c>
+      <c r="M115" t="n">
+        <v>12934675.63314688</v>
+      </c>
+      <c r="N115" t="n">
+        <v>25225.8801933396</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>25225.8801933396</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>25223.50155717556</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="n">
+        <v>0</v>
+      </c>
+      <c r="T115" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" t="n">
+        <v>2.378636164041317</v>
+      </c>
+      <c r="V115" t="n">
+        <v>13.54800009727478</v>
+      </c>
+      <c r="W115" t="n">
+        <v>12934675.63314688</v>
+      </c>
+      <c r="X115" t="n">
+        <v>12934675.63314688</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302222700_dh_0.5_ctax_150_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>11758191.13569845</v>
+      </c>
+      <c r="B116" t="n">
+        <v>3924009.699961789</v>
+      </c>
+      <c r="C116" t="n">
+        <v>3269196.519540858</v>
+      </c>
+      <c r="D116" t="n">
+        <v>3574979.57676774</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="n">
+        <v>7498989.276729529</v>
+      </c>
+      <c r="G116" t="n">
+        <v>3269196.519540858</v>
+      </c>
+      <c r="H116" t="n">
+        <v>754865.4335602226</v>
+      </c>
+      <c r="I116" t="n">
+        <v>-3879260.736503338</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="n">
+        <v>4114400.642371173</v>
+      </c>
+      <c r="M116" t="n">
+        <v>11758191.13569845</v>
+      </c>
+      <c r="N116" t="n">
+        <v>27431.70118554661</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>27431.70118554661</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>27429.33761580786</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="n">
+        <v>0</v>
+      </c>
+      <c r="T116" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" t="n">
+        <v>2.363569738907928</v>
+      </c>
+      <c r="V116" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="W116" t="n">
+        <v>11758191.13569845</v>
+      </c>
+      <c r="X116" t="n">
+        <v>11758191.13569845</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302222916_dh_0.5_ctax_150_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>10080529.98485059</v>
+      </c>
+      <c r="B117" t="n">
+        <v>3860181.201244922</v>
+      </c>
+      <c r="C117" t="n">
+        <v>3239210.780900604</v>
+      </c>
+      <c r="D117" t="n">
+        <v>3527904.640511368</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" t="n">
+        <v>7388085.841756291</v>
+      </c>
+      <c r="G117" t="n">
+        <v>3239210.780900604</v>
+      </c>
+      <c r="H117" t="n">
+        <v>2470802.899013638</v>
+      </c>
+      <c r="I117" t="n">
+        <v>-8671460.618805613</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="n">
+        <v>5653891.081985671</v>
+      </c>
+      <c r="M117" t="n">
+        <v>10080529.98485059</v>
+      </c>
+      <c r="N117" t="n">
+        <v>37694.94169474217</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
+        <v>37694.94169474217</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>37692.60721323798</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0</v>
+      </c>
+      <c r="U117" t="n">
+        <v>2.334481503661577</v>
+      </c>
+      <c r="V117" t="n">
+        <v>15.2649998664856</v>
+      </c>
+      <c r="W117" t="n">
+        <v>10080529.98485059</v>
+      </c>
+      <c r="X117" t="n">
+        <v>10080529.98485059</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302223239_dh_0.5_ctax_150_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>4963914.450407762</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>1144370.416970435</v>
+      </c>
+      <c r="I118" t="n">
+        <v>-29272929.11224952</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="n">
+        <v>32747456.59150717</v>
+      </c>
+      <c r="M118" t="n">
+        <v>4963914.450407762</v>
+      </c>
+      <c r="N118" t="n">
+        <v>218316.3772767143</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>218316.3772767143</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>218316.3772767143</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0</v>
+      </c>
+      <c r="V118" t="n">
+        <v>14.90399980545044</v>
+      </c>
+      <c r="W118" t="n">
+        <v>4963914.450407762</v>
+      </c>
+      <c r="X118" t="n">
+        <v>4963914.450407762</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302223456_dh_0.5_ctax_150_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>-996747.9443654828</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>1709345.297483764</v>
+      </c>
+      <c r="I119" t="n">
+        <v>-36190517.71089222</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
+        <v>33139407.91486328</v>
+      </c>
+      <c r="M119" t="n">
+        <v>-996747.9443654828</v>
+      </c>
+      <c r="N119" t="n">
+        <v>220929.3860990884</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" t="n">
+        <v>220929.3860990884</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>220929.3860990885</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0</v>
+      </c>
+      <c r="V119" t="n">
+        <v>7.427999973297119</v>
+      </c>
+      <c r="W119" t="n">
+        <v>-996747.9443654828</v>
+      </c>
+      <c r="X119" t="n">
+        <v>-996747.9443654828</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302223837_dh_0.5_ctax_150_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>-7068936.434910126</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" t="n">
+        <v>345016.5541796833</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="n">
+        <v>345016.5541796847</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>1949433.947739025</v>
+      </c>
+      <c r="I120" t="n">
+        <v>-42669356.35280671</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>33305969.41597787</v>
+      </c>
+      <c r="M120" t="n">
+        <v>-7068936.434910126</v>
+      </c>
+      <c r="N120" t="n">
+        <v>222039.7961065191</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" t="n">
+        <v>222039.7961065191</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>222039.7961065191</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" t="n">
+        <v>7.663000106811523</v>
+      </c>
+      <c r="W120" t="n">
+        <v>-7068936.434910126</v>
+      </c>
+      <c r="X120" t="n">
+        <v>-7068936.434910126</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302224047_dh_0.5_ctax_150_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>-14474743.18631757</v>
+      </c>
+      <c r="B121" t="n">
+        <v>31226380.0437068</v>
+      </c>
+      <c r="C121" t="n">
+        <v>4400143.355196329</v>
+      </c>
+      <c r="D121" t="n">
+        <v>22302671.72336629</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="n">
+        <v>53529051.76707308</v>
+      </c>
+      <c r="G121" t="n">
+        <v>4400143.355196329</v>
+      </c>
+      <c r="H121" t="n">
+        <v>4625886.449575543</v>
+      </c>
+      <c r="I121" t="n">
+        <v>-84740641.25643563</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>7710816.498273114</v>
+      </c>
+      <c r="M121" t="n">
+        <v>-14474743.18631757</v>
+      </c>
+      <c r="N121" t="n">
+        <v>51410.22919468472</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>51410.22919468472</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>51405.44332181967</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" t="n">
+        <v>4.785872864007008</v>
+      </c>
+      <c r="V121" t="n">
+        <v>10.15599989891052</v>
+      </c>
+      <c r="W121" t="n">
+        <v>-14474743.18631757</v>
+      </c>
+      <c r="X121" t="n">
+        <v>-14474743.18631757</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302224257_dh_0.5_ctax_150_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>15277439.92272306</v>
+      </c>
+      <c r="B122" t="n">
+        <v>4021613.731070424</v>
+      </c>
+      <c r="C122" t="n">
+        <v>3315049.532315627</v>
+      </c>
+      <c r="D122" t="n">
+        <v>3635951.153748104</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" t="n">
+        <v>7657564.884818528</v>
+      </c>
+      <c r="G122" t="n">
+        <v>3315049.532315627</v>
+      </c>
+      <c r="H122" t="n">
+        <v>534783.2387115362</v>
+      </c>
+      <c r="I122" t="n">
+        <v>-1102305.130975596</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>4872347.397852963</v>
+      </c>
+      <c r="M122" t="n">
+        <v>15277439.92272306</v>
+      </c>
+      <c r="N122" t="n">
+        <v>24364.12618050969</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>24364.12618050969</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>24361.73698926486</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" t="n">
+        <v>2.389191244850025</v>
+      </c>
+      <c r="V122" t="n">
+        <v>11.33599996566772</v>
+      </c>
+      <c r="W122" t="n">
+        <v>15277439.92272306</v>
+      </c>
+      <c r="X122" t="n">
+        <v>15277439.92272306</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302224652_dh_0.5_ctax_200_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>14173480.86373494</v>
+      </c>
+      <c r="B123" t="n">
+        <v>4010007.201818711</v>
+      </c>
+      <c r="C123" t="n">
+        <v>3309596.946720497</v>
+      </c>
+      <c r="D123" t="n">
+        <v>3629392.346187558</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" t="n">
+        <v>7639399.548006268</v>
+      </c>
+      <c r="G123" t="n">
+        <v>3309596.946720497</v>
+      </c>
+      <c r="H123" t="n">
+        <v>534308.9304601339</v>
+      </c>
+      <c r="I123" t="n">
+        <v>-2211533.489091419</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="n">
+        <v>4901708.927639459</v>
+      </c>
+      <c r="M123" t="n">
+        <v>14173480.86373494</v>
+      </c>
+      <c r="N123" t="n">
+        <v>24510.93196692576</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>24510.93196692576</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>24508.54463819744</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" t="n">
+        <v>2.387328728292584</v>
+      </c>
+      <c r="V123" t="n">
+        <v>16.48000001907349</v>
+      </c>
+      <c r="W123" t="n">
+        <v>14173480.86373494</v>
+      </c>
+      <c r="X123" t="n">
+        <v>14173480.86373494</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302224909_dh_0.5_ctax_200_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>13049195.18288213</v>
+      </c>
+      <c r="B124" t="n">
+        <v>3996227.649448312</v>
+      </c>
+      <c r="C124" t="n">
+        <v>3303123.505165944</v>
+      </c>
+      <c r="D124" t="n">
+        <v>3621358.74916816</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" t="n">
+        <v>7617586.398616472</v>
+      </c>
+      <c r="G124" t="n">
+        <v>3303123.505165944</v>
+      </c>
+      <c r="H124" t="n">
+        <v>593030.9548426764</v>
+      </c>
+      <c r="I124" t="n">
+        <v>-3462714.40208795</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="n">
+        <v>4998168.726344986</v>
+      </c>
+      <c r="M124" t="n">
+        <v>13049195.18288213</v>
+      </c>
+      <c r="N124" t="n">
+        <v>24993.22832658271</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>24993.22832658271</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>24990.84363172489</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" t="n">
+        <v>2.384694857908107</v>
+      </c>
+      <c r="V124" t="n">
+        <v>22.88199996948242</v>
+      </c>
+      <c r="W124" t="n">
+        <v>13049195.18288213</v>
+      </c>
+      <c r="X124" t="n">
+        <v>13049195.18288213</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302225131_dh_0.5_ctax_200_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>11716151.58943036</v>
+      </c>
+      <c r="B125" t="n">
+        <v>3976371.987052227</v>
+      </c>
+      <c r="C125" t="n">
+        <v>3293795.591849682</v>
+      </c>
+      <c r="D125" t="n">
+        <v>3609285.571086115</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>7585657.558138343</v>
+      </c>
+      <c r="G125" t="n">
+        <v>3293795.591849682</v>
+      </c>
+      <c r="H125" t="n">
+        <v>1458058.104175233</v>
+      </c>
+      <c r="I125" t="n">
+        <v>-6494023.86987965</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="n">
+        <v>5872664.205146749</v>
+      </c>
+      <c r="M125" t="n">
+        <v>11716151.58943036</v>
+      </c>
+      <c r="N125" t="n">
+        <v>29365.70107400605</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>29365.70107400605</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>29363.32102573365</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" t="n">
+        <v>2.380048272553786</v>
+      </c>
+      <c r="V125" t="n">
+        <v>31.61199998855591</v>
+      </c>
+      <c r="W125" t="n">
+        <v>11716151.58943036</v>
+      </c>
+      <c r="X125" t="n">
+        <v>11716151.58943036</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302225400_dh_0.5_ctax_200_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>9646559.114619385</v>
+      </c>
+      <c r="B126" t="n">
+        <v>3944812.547830371</v>
+      </c>
+      <c r="C126" t="n">
+        <v>3278969.407384066</v>
+      </c>
+      <c r="D126" t="n">
+        <v>3588998.375707509</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="n">
+        <v>7533810.92353788</v>
+      </c>
+      <c r="G126" t="n">
+        <v>3278969.407384066</v>
+      </c>
+      <c r="H126" t="n">
+        <v>3820430.713663933</v>
+      </c>
+      <c r="I126" t="n">
+        <v>-13192749.28088502</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="n">
+        <v>8206097.350918525</v>
+      </c>
+      <c r="M126" t="n">
+        <v>9646559.114619385</v>
+      </c>
+      <c r="N126" t="n">
+        <v>41032.85753795988</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>41032.85753795988</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>41030.48675459274</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="n">
+        <v>2.370783367429113</v>
+      </c>
+      <c r="V126" t="n">
+        <v>31.97699999809265</v>
+      </c>
+      <c r="W126" t="n">
+        <v>9646559.114619385</v>
+      </c>
+      <c r="X126" t="n">
+        <v>9646559.114619385</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302225837_dh_0.5_ctax_200_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>6332676.348139726</v>
+      </c>
+      <c r="B127" t="n">
+        <v>3915023.344694053</v>
+      </c>
+      <c r="C127" t="n">
+        <v>3264974.855146367</v>
+      </c>
+      <c r="D127" t="n">
+        <v>3568764.678657647</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" t="n">
+        <v>7483788.0233517</v>
+      </c>
+      <c r="G127" t="n">
+        <v>3264974.855146367</v>
+      </c>
+      <c r="H127" t="n">
+        <v>7517831.097183368</v>
+      </c>
+      <c r="I127" t="n">
+        <v>-23729745.23284176</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
+        <v>11795827.60530005</v>
+      </c>
+      <c r="M127" t="n">
+        <v>6332676.348139726</v>
+      </c>
+      <c r="N127" t="n">
+        <v>58981.49820768446</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>58981.49820768446</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>58979.13802649931</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" t="n">
+        <v>2.360181186202498</v>
+      </c>
+      <c r="V127" t="n">
+        <v>22.24100017547607</v>
+      </c>
+      <c r="W127" t="n">
+        <v>6332676.348139726</v>
+      </c>
+      <c r="X127" t="n">
+        <v>6332676.348139726</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302230115_dh_0.5_ctax_200_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>-1386927.715503423</v>
+      </c>
+      <c r="B128" t="n">
+        <v>31572859.92774189</v>
+      </c>
+      <c r="C128" t="n">
+        <v>4433066.460455096</v>
+      </c>
+      <c r="D128" t="n">
+        <v>22542686.79304919</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" t="n">
+        <v>54115546.72079109</v>
+      </c>
+      <c r="G128" t="n">
+        <v>4433066.460455096</v>
+      </c>
+      <c r="H128" t="n">
+        <v>4379556.888946415</v>
+      </c>
+      <c r="I128" t="n">
+        <v>-73999708.32992733</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
+        <v>9684610.544231305</v>
+      </c>
+      <c r="M128" t="n">
+        <v>-1386927.715503423</v>
+      </c>
+      <c r="N128" t="n">
+        <v>48427.88679236333</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>48427.88679236333</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>48423.05272115547</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" t="n">
+        <v>4.834071206764879</v>
+      </c>
+      <c r="V128" t="n">
+        <v>22.46700000762939</v>
+      </c>
+      <c r="W128" t="n">
+        <v>-1386927.715503423</v>
+      </c>
+      <c r="X128" t="n">
+        <v>-1386927.715503423</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302230343_dh_0.5_ctax_200_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>-12002131.27383834</v>
+      </c>
+      <c r="B129" t="n">
+        <v>31845651.8151454</v>
+      </c>
+      <c r="C129" t="n">
+        <v>4458987.607501583</v>
+      </c>
+      <c r="D129" t="n">
+        <v>22729601.76450172</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" t="n">
+        <v>54575253.57964712</v>
+      </c>
+      <c r="G129" t="n">
+        <v>4458987.607501583</v>
+      </c>
+      <c r="H129" t="n">
+        <v>4566362.935086612</v>
+      </c>
+      <c r="I129" t="n">
+        <v>-85191196.80956975</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
+        <v>9588461.413496096</v>
+      </c>
+      <c r="M129" t="n">
+        <v>-12002131.27383834</v>
+      </c>
+      <c r="N129" t="n">
+        <v>47947.17630382952</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>47947.17630382952</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>47942.30706748046</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" t="n">
+        <v>4.869236349029798</v>
+      </c>
+      <c r="V129" t="n">
+        <v>20.3730001449585</v>
+      </c>
+      <c r="W129" t="n">
+        <v>-12002131.27383834</v>
+      </c>
+      <c r="X129" t="n">
+        <v>-12002131.27383834</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302230613_dh_0.5_ctax_200_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>16491122.81335748</v>
+      </c>
+      <c r="B130" t="n">
+        <v>4036544.720767827</v>
+      </c>
+      <c r="C130" t="n">
+        <v>3322063.903070181</v>
+      </c>
+      <c r="D130" t="n">
+        <v>3644130.803684153</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" t="n">
+        <v>7680675.524451979</v>
+      </c>
+      <c r="G130" t="n">
+        <v>3322063.903070181</v>
+      </c>
+      <c r="H130" t="n">
+        <v>535204.11933869</v>
+      </c>
+      <c r="I130" t="n">
+        <v>-1098650.487655586</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="n">
+        <v>6051829.754152213</v>
+      </c>
+      <c r="M130" t="n">
+        <v>16491122.81335748</v>
+      </c>
+      <c r="N130" t="n">
+        <v>24209.71016241052</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>24209.71016241052</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>24207.31901660891</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0</v>
+      </c>
+      <c r="U130" t="n">
+        <v>2.391145801669482</v>
+      </c>
+      <c r="V130" t="n">
+        <v>18.76799988746643</v>
+      </c>
+      <c r="W130" t="n">
+        <v>16491122.81335748</v>
+      </c>
+      <c r="X130" t="n">
+        <v>16491122.81335748</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302231108_dh_0.5_ctax_250_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>15391858.09426058</v>
+      </c>
+      <c r="B131" t="n">
+        <v>4030838.556247411</v>
+      </c>
+      <c r="C131" t="n">
+        <v>3319383.226548138</v>
+      </c>
+      <c r="D131" t="n">
+        <v>3641039.71263548</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" t="n">
+        <v>7671878.268882891</v>
+      </c>
+      <c r="G131" t="n">
+        <v>3319383.226548138</v>
+      </c>
+      <c r="H131" t="n">
+        <v>535056.3695936643</v>
+      </c>
+      <c r="I131" t="n">
+        <v>-2199862.236681958</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
+        <v>6065402.465917844</v>
+      </c>
+      <c r="M131" t="n">
+        <v>15391858.09426058</v>
+      </c>
+      <c r="N131" t="n">
+        <v>24264.0003222956</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>24264.0003222956</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>24261.60986367137</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0</v>
+      </c>
+      <c r="U131" t="n">
+        <v>2.390458624299067</v>
+      </c>
+      <c r="V131" t="n">
+        <v>26.51300001144409</v>
+      </c>
+      <c r="W131" t="n">
+        <v>15391858.09426058</v>
+      </c>
+      <c r="X131" t="n">
+        <v>15391858.09426058</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302231336_dh_0.5_ctax_250_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>14284318.7679137</v>
+      </c>
+      <c r="B132" t="n">
+        <v>4022507.672777046</v>
+      </c>
+      <c r="C132" t="n">
+        <v>3315469.493663821</v>
+      </c>
+      <c r="D132" t="n">
+        <v>3636449.200564665</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" t="n">
+        <v>7658956.873341711</v>
+      </c>
+      <c r="G132" t="n">
+        <v>3315469.493663821</v>
+      </c>
+      <c r="H132" t="n">
+        <v>558908.2998361967</v>
+      </c>
+      <c r="I132" t="n">
+        <v>-3364719.421063356</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>6115703.522135326</v>
+      </c>
+      <c r="M132" t="n">
+        <v>14284318.7679137</v>
+      </c>
+      <c r="N132" t="n">
+        <v>24465.20341105248</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>24465.20341105248</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>24462.81408854124</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0</v>
+      </c>
+      <c r="U132" t="n">
+        <v>2.38932251120534</v>
+      </c>
+      <c r="V132" t="n">
+        <v>34.57200002670288</v>
+      </c>
+      <c r="W132" t="n">
+        <v>14284318.7679137</v>
+      </c>
+      <c r="X132" t="n">
+        <v>14284318.7679137</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302231612_dh_0.5_ctax_250_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>13098446.32530966</v>
+      </c>
+      <c r="B133" t="n">
+        <v>4011481.978540709</v>
+      </c>
+      <c r="C133" t="n">
+        <v>3310289.776259458</v>
+      </c>
+      <c r="D133" t="n">
+        <v>3630235.313902473</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" t="n">
+        <v>7641717.292443182</v>
+      </c>
+      <c r="G133" t="n">
+        <v>3310289.776259458</v>
+      </c>
+      <c r="H133" t="n">
+        <v>891483.3115461282</v>
+      </c>
+      <c r="I133" t="n">
+        <v>-5280101.926802945</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
+        <v>6535057.871863842</v>
+      </c>
+      <c r="M133" t="n">
+        <v>13098446.32530966</v>
+      </c>
+      <c r="N133" t="n">
+        <v>26142.61906924193</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>26142.61906924193</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>26140.23148745548</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0</v>
+      </c>
+      <c r="U133" t="n">
+        <v>2.387581786583393</v>
+      </c>
+      <c r="V133" t="n">
+        <v>33.38499999046326</v>
+      </c>
+      <c r="W133" t="n">
+        <v>13098446.32530966</v>
+      </c>
+      <c r="X133" t="n">
+        <v>13098446.32530966</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302231857_dh_0.5_ctax_250_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>11459463.23911481</v>
+      </c>
+      <c r="B134" t="n">
+        <v>3999894.03428019</v>
+      </c>
+      <c r="C134" t="n">
+        <v>3304845.921634033</v>
+      </c>
+      <c r="D134" t="n">
+        <v>3623524.119128196</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" t="n">
+        <v>7623418.153408386</v>
+      </c>
+      <c r="G134" t="n">
+        <v>3304845.921634033</v>
+      </c>
+      <c r="H134" t="n">
+        <v>2299634.585953301</v>
+      </c>
+      <c r="I134" t="n">
+        <v>-9974437.366832625</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="n">
+        <v>8206001.944951719</v>
+      </c>
+      <c r="M134" t="n">
+        <v>11459463.23911481</v>
+      </c>
+      <c r="N134" t="n">
+        <v>32826.39322313534</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>32826.39322313534</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>32824.00777980671</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" t="n">
+        <v>2.385443328480667</v>
+      </c>
+      <c r="V134" t="n">
+        <v>41.76699995994568</v>
+      </c>
+      <c r="W134" t="n">
+        <v>11459463.23911481</v>
+      </c>
+      <c r="X134" t="n">
+        <v>11459463.23911481</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302232144_dh_0.5_ctax_250_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>8946379.918008542</v>
+      </c>
+      <c r="B135" t="n">
+        <v>3987736.947200131</v>
+      </c>
+      <c r="C135" t="n">
+        <v>3299134.691648404</v>
+      </c>
+      <c r="D135" t="n">
+        <v>3616268.06471293</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" t="n">
+        <v>7604005.011913061</v>
+      </c>
+      <c r="G135" t="n">
+        <v>3299134.691648404</v>
+      </c>
+      <c r="H135" t="n">
+        <v>5069314.975690713</v>
+      </c>
+      <c r="I135" t="n">
+        <v>-18486760.71252392</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
+        <v>11460685.95128029</v>
+      </c>
+      <c r="M135" t="n">
+        <v>8946379.918008542</v>
+      </c>
+      <c r="N135" t="n">
+        <v>45845.12663639685</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>45845.12663639685</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>45842.74380512154</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" t="n">
+        <v>2.382831275695926</v>
+      </c>
+      <c r="V135" t="n">
+        <v>33.28299999237061</v>
+      </c>
+      <c r="W135" t="n">
+        <v>8946379.918008542</v>
+      </c>
+      <c r="X135" t="n">
+        <v>8946379.918008542</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302232736_dh_0.5_ctax_250_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>945553.7037764285</v>
+      </c>
+      <c r="B136" t="n">
+        <v>32022539.03271049</v>
+      </c>
+      <c r="C136" t="n">
+        <v>4475795.730429251</v>
+      </c>
+      <c r="D136" t="n">
+        <v>22849642.92781117</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" t="n">
+        <v>54872181.96052165</v>
+      </c>
+      <c r="G136" t="n">
+        <v>4475795.730429251</v>
+      </c>
+      <c r="H136" t="n">
+        <v>4140287.815133134</v>
+      </c>
+      <c r="I136" t="n">
+        <v>-73832675.44835924</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
+        <v>11289963.64605163</v>
+      </c>
+      <c r="M136" t="n">
+        <v>945553.7037764285</v>
+      </c>
+      <c r="N136" t="n">
+        <v>45164.7450509393</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>45164.7450509393</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>45159.85458420651</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" t="n">
+        <v>4.890466732799332</v>
+      </c>
+      <c r="V136" t="n">
+        <v>29.03099989891052</v>
+      </c>
+      <c r="W136" t="n">
+        <v>945553.7037764285</v>
+      </c>
+      <c r="X136" t="n">
+        <v>945553.7037764285</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302233022_dh_0.5_ctax_250_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>-9658276.826592447</v>
+      </c>
+      <c r="B137" t="n">
+        <v>32192029.80639484</v>
+      </c>
+      <c r="C137" t="n">
+        <v>4491901.030735327</v>
+      </c>
+      <c r="D137" t="n">
+        <v>22963687.6213389</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" t="n">
+        <v>55155717.42773373</v>
+      </c>
+      <c r="G137" t="n">
+        <v>4491901.030735327</v>
+      </c>
+      <c r="H137" t="n">
+        <v>4460597.507690292</v>
+      </c>
+      <c r="I137" t="n">
+        <v>-85244987.08654992</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
+        <v>11478494.29379812</v>
+      </c>
+      <c r="M137" t="n">
+        <v>-9658276.826592447</v>
+      </c>
+      <c r="N137" t="n">
+        <v>45918.88666141008</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>45918.88666141008</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>45913.97717519248</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="n">
+        <v>4.909486217584692</v>
+      </c>
+      <c r="V137" t="n">
+        <v>20.50399994850159</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-9658276.826592447</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-9658276.826592447</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302233304_dh_0.5_ctax_250_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>15363052.63052356</v>
+      </c>
+      <c r="B138" t="n">
+        <v>3882898.423852363</v>
+      </c>
+      <c r="C138" t="n">
+        <v>3249883.015301116</v>
+      </c>
+      <c r="D138" t="n">
+        <v>3305756.69458566</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" t="n">
+        <v>7188655.118438022</v>
+      </c>
+      <c r="G138" t="n">
+        <v>3249883.015301116</v>
+      </c>
+      <c r="H138" t="n">
+        <v>116795.5611062836</v>
+      </c>
+      <c r="I138" t="n">
+        <v>-1062667.520885071</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>5870386.45656321</v>
+      </c>
+      <c r="M138" t="n">
+        <v>15363052.63052356</v>
+      </c>
+      <c r="N138" t="n">
+        <v>58705.80031537022</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>58705.80031537022</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>58703.86456563252</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0</v>
+      </c>
+      <c r="U138" t="n">
+        <v>1.935749737533876</v>
+      </c>
+      <c r="V138" t="n">
+        <v>22.21200013160706</v>
+      </c>
+      <c r="W138" t="n">
+        <v>15363052.63052356</v>
+      </c>
+      <c r="X138" t="n">
+        <v>15363052.63052356</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD138" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302233537_dh_1_ctax_100_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>12530462.2256517</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>136352.8646669782</v>
+      </c>
+      <c r="I139" t="n">
+        <v>-9316336.802926052</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
+        <v>21365429.60973109</v>
+      </c>
+      <c r="M139" t="n">
+        <v>12530462.2256517</v>
+      </c>
+      <c r="N139" t="n">
+        <v>213654.2960973108</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>213654.2960973108</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>213654.2960973109</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0</v>
+      </c>
+      <c r="V139" t="n">
+        <v>18.93499994277954</v>
+      </c>
+      <c r="W139" t="n">
+        <v>12530462.2256517</v>
+      </c>
+      <c r="X139" t="n">
+        <v>12530462.2256517</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302233813_dh_1_ctax_100_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>7796511.362991767</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>578486.0919676765</v>
+      </c>
+      <c r="I140" t="n">
+        <v>-14696907.51051326</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>21569916.22735767</v>
+      </c>
+      <c r="M140" t="n">
+        <v>7796511.362991767</v>
+      </c>
+      <c r="N140" t="n">
+        <v>215699.1622735765</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>215699.1622735765</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>215699.1622735766</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0</v>
+      </c>
+      <c r="V140" t="n">
+        <v>11.74699997901917</v>
+      </c>
+      <c r="W140" t="n">
+        <v>7796511.362991592</v>
+      </c>
+      <c r="X140" t="n">
+        <v>7796511.362991767</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>1.7508864402771e-07</v>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302234046_dh_1_ctax_100_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>2668555.614585821</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>1782376.769846283</v>
+      </c>
+      <c r="I141" t="n">
+        <v>-21585553.37531666</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="n">
+        <v>22126715.66587652</v>
+      </c>
+      <c r="M141" t="n">
+        <v>2668555.614585821</v>
+      </c>
+      <c r="N141" t="n">
+        <v>221267.1566587651</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
+        <v>221267.1566587651</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>221267.1566587652</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0</v>
+      </c>
+      <c r="V141" t="n">
+        <v>8.897000074386597</v>
+      </c>
+      <c r="W141" t="n">
+        <v>2668555.614585802</v>
+      </c>
+      <c r="X141" t="n">
+        <v>2668555.614585821</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>1.816079020500183e-08</v>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302234312_dh_1_ctax_100_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>-3004014.602587033</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>3298136.66063236</v>
+      </c>
+      <c r="I142" t="n">
+        <v>-29474922.43276415</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
+        <v>22827754.61536508</v>
+      </c>
+      <c r="M142" t="n">
+        <v>-3004014.602587033</v>
+      </c>
+      <c r="N142" t="n">
+        <v>228277.5461536508</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>228277.5461536508</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>228277.5461536508</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0</v>
+      </c>
+      <c r="V142" t="n">
+        <v>9.208000183105469</v>
+      </c>
+      <c r="W142" t="n">
+        <v>-3004014.602587042</v>
+      </c>
+      <c r="X142" t="n">
+        <v>-3004014.602587033</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>8.847564458847046e-09</v>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302234912_dh_1_ctax_100_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>-8995375.593067665</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>3887042.836429428</v>
+      </c>
+      <c r="I143" t="n">
+        <v>-36327558.705348</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" t="n">
+        <v>23100123.72167123</v>
+      </c>
+      <c r="M143" t="n">
+        <v>-8995375.593067665</v>
+      </c>
+      <c r="N143" t="n">
+        <v>231001.2372167122</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>231001.2372167122</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>231001.2372167122</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0</v>
+      </c>
+      <c r="V143" t="n">
+        <v>9.61899995803833</v>
+      </c>
+      <c r="W143" t="n">
+        <v>-8995375.593067702</v>
+      </c>
+      <c r="X143" t="n">
+        <v>-8995375.593067665</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>3.725290298461914e-08</v>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302235137_dh_1_ctax_100_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>-15079222.79095962</v>
+      </c>
+      <c r="B144" t="n">
+        <v>0</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>4120212.559996934</v>
+      </c>
+      <c r="I144" t="n">
+        <v>-42752416.62395743</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="n">
+        <v>23207964.71882119</v>
+      </c>
+      <c r="M144" t="n">
+        <v>-15079222.79095962</v>
+      </c>
+      <c r="N144" t="n">
+        <v>232079.6471882118</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" t="n">
+        <v>232079.6471882118</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>232079.6471882119</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" t="n">
+        <v>0</v>
+      </c>
+      <c r="T144" t="n">
+        <v>0</v>
+      </c>
+      <c r="U144" t="n">
+        <v>0</v>
+      </c>
+      <c r="V144" t="n">
+        <v>16.03300023078918</v>
+      </c>
+      <c r="W144" t="n">
+        <v>-15079222.79095962</v>
+      </c>
+      <c r="X144" t="n">
+        <v>-15079222.79095962</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302235404_dh_1_ctax_100_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>-21194748.71856795</v>
+      </c>
+      <c r="B145" t="n">
+        <v>0</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>4184724.50978855</v>
+      </c>
+      <c r="I145" t="n">
+        <v>-48962291.278136</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="n">
+        <v>23237801.49559982</v>
+      </c>
+      <c r="M145" t="n">
+        <v>-21194748.71856795</v>
+      </c>
+      <c r="N145" t="n">
+        <v>232378.0149559981</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" t="n">
+        <v>232378.0149559981</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>232378.0149559981</v>
+      </c>
+      <c r="R145" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" t="n">
+        <v>0</v>
+      </c>
+      <c r="T145" t="n">
+        <v>0</v>
+      </c>
+      <c r="U145" t="n">
+        <v>0</v>
+      </c>
+      <c r="V145" t="n">
+        <v>15.47500014305115</v>
+      </c>
+      <c r="W145" t="n">
+        <v>-21194748.71856795</v>
+      </c>
+      <c r="X145" t="n">
+        <v>-21194748.71856795</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302235637_dh_1_ctax_100_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>17207417.39686936</v>
+      </c>
+      <c r="B146" t="n">
+        <v>3991540.366193383</v>
+      </c>
+      <c r="C146" t="n">
+        <v>3300921.484854632</v>
+      </c>
+      <c r="D146" t="n">
+        <v>3618563.244531922</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" t="n">
+        <v>7610103.610725304</v>
+      </c>
+      <c r="G146" t="n">
+        <v>3300921.484854632</v>
+      </c>
+      <c r="H146" t="n">
+        <v>2331985.698475967</v>
+      </c>
+      <c r="I146" t="n">
+        <v>-1002661.096508253</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" t="n">
+        <v>4967067.699321709</v>
+      </c>
+      <c r="M146" t="n">
+        <v>17207417.39686936</v>
+      </c>
+      <c r="N146" t="n">
+        <v>33116.16835356091</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" t="n">
+        <v>33116.16835356091</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>33113.78466214484</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0</v>
+      </c>
+      <c r="S146" t="n">
+        <v>0</v>
+      </c>
+      <c r="T146" t="n">
+        <v>0</v>
+      </c>
+      <c r="U146" t="n">
+        <v>2.383691416144157</v>
+      </c>
+      <c r="V146" t="n">
+        <v>19.56800007820129</v>
+      </c>
+      <c r="W146" t="n">
+        <v>17207417.39686936</v>
+      </c>
+      <c r="X146" t="n">
+        <v>17207417.39686936</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260302235911_dh_1_ctax_150_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>16199661.24318459</v>
+      </c>
+      <c r="B147" t="n">
+        <v>3966328.158404192</v>
+      </c>
+      <c r="C147" t="n">
+        <v>3289077.141207071</v>
+      </c>
+      <c r="D147" t="n">
+        <v>3602966.192438853</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" t="n">
+        <v>7569294.350843045</v>
+      </c>
+      <c r="G147" t="n">
+        <v>3289077.141207071</v>
+      </c>
+      <c r="H147" t="n">
+        <v>2332219.907705339</v>
+      </c>
+      <c r="I147" t="n">
+        <v>-2034444.833808203</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" t="n">
+        <v>5043514.677237339</v>
+      </c>
+      <c r="M147" t="n">
+        <v>16199661.24318459</v>
+      </c>
+      <c r="N147" t="n">
+        <v>33625.80851595704</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" t="n">
+        <v>33625.80851595704</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>33623.43118158251</v>
+      </c>
+      <c r="R147" t="n">
+        <v>0</v>
+      </c>
+      <c r="S147" t="n">
+        <v>0</v>
+      </c>
+      <c r="T147" t="n">
+        <v>0</v>
+      </c>
+      <c r="U147" t="n">
+        <v>2.377334374872259</v>
+      </c>
+      <c r="V147" t="n">
+        <v>21.13899993896484</v>
+      </c>
+      <c r="W147" t="n">
+        <v>16199661.24318459</v>
+      </c>
+      <c r="X147" t="n">
+        <v>16199661.24318459</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD147" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303000150_dh_1_ctax_150_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>15134999.69979904</v>
+      </c>
+      <c r="B148" t="n">
+        <v>3912980.392469223</v>
+      </c>
+      <c r="C148" t="n">
+        <v>3264015.104679103</v>
+      </c>
+      <c r="D148" t="n">
+        <v>3566289.248751179</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" t="n">
+        <v>7479269.641220402</v>
+      </c>
+      <c r="G148" t="n">
+        <v>3264015.104679103</v>
+      </c>
+      <c r="H148" t="n">
+        <v>2516023.020036106</v>
+      </c>
+      <c r="I148" t="n">
+        <v>-3532251.898717223</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="n">
+        <v>5407943.832580653</v>
+      </c>
+      <c r="M148" t="n">
+        <v>15134999.69979904</v>
+      </c>
+      <c r="N148" t="n">
+        <v>36055.31647526737</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" t="n">
+        <v>36055.31647526737</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>36052.95888387087</v>
+      </c>
+      <c r="R148" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" t="n">
+        <v>0</v>
+      </c>
+      <c r="T148" t="n">
+        <v>0</v>
+      </c>
+      <c r="U148" t="n">
+        <v>2.357591396025277</v>
+      </c>
+      <c r="V148" t="n">
+        <v>23.05699992179871</v>
+      </c>
+      <c r="W148" t="n">
+        <v>15134999.69979904</v>
+      </c>
+      <c r="X148" t="n">
+        <v>15134999.69979904</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303000430_dh_1_ctax_150_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>13579138.40613125</v>
+      </c>
+      <c r="B149" t="n">
+        <v>3849885.64617222</v>
+      </c>
+      <c r="C149" t="n">
+        <v>3234374.072693884</v>
+      </c>
+      <c r="D149" t="n">
+        <v>3513560.667522029</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" t="n">
+        <v>7363446.31369425</v>
+      </c>
+      <c r="G149" t="n">
+        <v>3234374.072693884</v>
+      </c>
+      <c r="H149" t="n">
+        <v>4158101.33007372</v>
+      </c>
+      <c r="I149" t="n">
+        <v>-8196257.200510075</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="n">
+        <v>7019473.890179467</v>
+      </c>
+      <c r="M149" t="n">
+        <v>13579138.40613125</v>
+      </c>
+      <c r="N149" t="n">
+        <v>46798.8108310718</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" t="n">
+        <v>46798.8108310718</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>46796.49260119539</v>
+      </c>
+      <c r="R149" t="n">
+        <v>0</v>
+      </c>
+      <c r="S149" t="n">
+        <v>0</v>
+      </c>
+      <c r="T149" t="n">
+        <v>0</v>
+      </c>
+      <c r="U149" t="n">
+        <v>2.318229876857771</v>
+      </c>
+      <c r="V149" t="n">
+        <v>27.06699991226196</v>
+      </c>
+      <c r="W149" t="n">
+        <v>13579138.40613125</v>
+      </c>
+      <c r="X149" t="n">
+        <v>13579138.40613125</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303000711_dh_1_ctax_150_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>8301004.985964015</v>
+      </c>
+      <c r="B150" t="n">
+        <v>0</v>
+      </c>
+      <c r="C150" t="n">
+        <v>0</v>
+      </c>
+      <c r="D150" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>2308052.909671388</v>
+      </c>
+      <c r="I150" t="n">
+        <v>-27906825.7987055</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" t="n">
+        <v>33554761.32081845</v>
+      </c>
+      <c r="M150" t="n">
+        <v>8301004.985964015</v>
+      </c>
+      <c r="N150" t="n">
+        <v>223698.4088054562</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" t="n">
+        <v>223698.4088054562</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>223698.4088054562</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" t="n">
+        <v>0</v>
+      </c>
+      <c r="T150" t="n">
+        <v>0</v>
+      </c>
+      <c r="U150" t="n">
+        <v>0</v>
+      </c>
+      <c r="V150" t="n">
+        <v>25.52900004386902</v>
+      </c>
+      <c r="W150" t="n">
+        <v>8301004.985964015</v>
+      </c>
+      <c r="X150" t="n">
+        <v>8301004.985964015</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303001421_dh_1_ctax_150_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>2510886.93562004</v>
+      </c>
+      <c r="B151" t="n">
+        <v>0</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>3421700.540555991</v>
+      </c>
+      <c r="I151" t="n">
+        <v>-35583184.52386028</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" t="n">
+        <v>34327354.36474465</v>
+      </c>
+      <c r="M151" t="n">
+        <v>2510886.93562004</v>
+      </c>
+      <c r="N151" t="n">
+        <v>228849.0290982975</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" t="n">
+        <v>228849.0290982975</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>228849.0290982976</v>
+      </c>
+      <c r="R151" t="n">
+        <v>0</v>
+      </c>
+      <c r="S151" t="n">
+        <v>0</v>
+      </c>
+      <c r="T151" t="n">
+        <v>0</v>
+      </c>
+      <c r="U151" t="n">
+        <v>0</v>
+      </c>
+      <c r="V151" t="n">
+        <v>15.08999991416931</v>
+      </c>
+      <c r="W151" t="n">
+        <v>2510886.93562004</v>
+      </c>
+      <c r="X151" t="n">
+        <v>2510886.93562004</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303001707_dh_1_ctax_150_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>-3499956.871096313</v>
+      </c>
+      <c r="B152" t="n">
+        <v>0</v>
+      </c>
+      <c r="C152" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" t="n">
+        <v>345016.5541796822</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>3898421.046107692</v>
+      </c>
+      <c r="I152" t="n">
+        <v>-42401473.68685482</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" t="n">
+        <v>34658079.21547113</v>
+      </c>
+      <c r="M152" t="n">
+        <v>-3499956.871096313</v>
+      </c>
+      <c r="N152" t="n">
+        <v>231053.8614364742</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" t="n">
+        <v>231053.8614364742</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>231053.8614364742</v>
+      </c>
+      <c r="R152" t="n">
+        <v>0</v>
+      </c>
+      <c r="S152" t="n">
+        <v>0</v>
+      </c>
+      <c r="T152" t="n">
+        <v>0</v>
+      </c>
+      <c r="U152" t="n">
+        <v>0</v>
+      </c>
+      <c r="V152" t="n">
+        <v>15.93899989128113</v>
+      </c>
+      <c r="W152" t="n">
+        <v>-3499956.871096313</v>
+      </c>
+      <c r="X152" t="n">
+        <v>-3499956.871096313</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303001942_dh_1_ctax_150_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>-10880124.06699132</v>
+      </c>
+      <c r="B153" t="n">
+        <v>31226380.0437068</v>
+      </c>
+      <c r="C153" t="n">
+        <v>4400143.355196329</v>
+      </c>
+      <c r="D153" t="n">
+        <v>22302671.72336629</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" t="n">
+        <v>53529051.76707308</v>
+      </c>
+      <c r="G153" t="n">
+        <v>4400143.355196329</v>
+      </c>
+      <c r="H153" t="n">
+        <v>6680329.928234284</v>
+      </c>
+      <c r="I153" t="n">
+        <v>-84625735.77908763</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
+        <v>9136086.661592619</v>
+      </c>
+      <c r="M153" t="n">
+        <v>-10880124.06699132</v>
+      </c>
+      <c r="N153" t="n">
+        <v>60912.03028348144</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" t="n">
+        <v>60912.03028348144</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>60907.24441061635</v>
+      </c>
+      <c r="R153" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" t="n">
+        <v>0</v>
+      </c>
+      <c r="T153" t="n">
+        <v>0</v>
+      </c>
+      <c r="U153" t="n">
+        <v>4.785872864007008</v>
+      </c>
+      <c r="V153" t="n">
+        <v>20.66299986839294</v>
+      </c>
+      <c r="W153" t="n">
+        <v>-10880124.06699132</v>
+      </c>
+      <c r="X153" t="n">
+        <v>-10880124.06699132</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303002218_dh_1_ctax_150_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>18851364.29670775</v>
+      </c>
+      <c r="B154" t="n">
+        <v>4020134.370069011</v>
+      </c>
+      <c r="C154" t="n">
+        <v>3314354.549146122</v>
+      </c>
+      <c r="D154" t="n">
+        <v>3635124.468201638</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" t="n">
+        <v>7655258.838270648</v>
+      </c>
+      <c r="G154" t="n">
+        <v>3314354.549146122</v>
+      </c>
+      <c r="H154" t="n">
+        <v>2334393.915379992</v>
+      </c>
+      <c r="I154" t="n">
+        <v>-993173.915340858</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" t="n">
+        <v>6540530.909251847</v>
+      </c>
+      <c r="M154" t="n">
+        <v>18851364.29670775</v>
+      </c>
+      <c r="N154" t="n">
+        <v>32705.04351602709</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" t="n">
+        <v>32705.04351602709</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>32702.65454625951</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" t="n">
+        <v>0</v>
+      </c>
+      <c r="T154" t="n">
+        <v>0</v>
+      </c>
+      <c r="U154" t="n">
+        <v>2.388969767632488</v>
+      </c>
+      <c r="V154" t="n">
+        <v>18.80900001525879</v>
+      </c>
+      <c r="W154" t="n">
+        <v>18851364.29670775</v>
+      </c>
+      <c r="X154" t="n">
+        <v>18851364.29670775</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD154" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303002459_dh_1_ctax_200_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>17856509.35808223</v>
+      </c>
+      <c r="B155" t="n">
+        <v>4008324.223188636</v>
+      </c>
+      <c r="C155" t="n">
+        <v>3308806.306828395</v>
+      </c>
+      <c r="D155" t="n">
+        <v>3628426.824695332</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" t="n">
+        <v>7636751.047883968</v>
+      </c>
+      <c r="G155" t="n">
+        <v>3308806.306828395</v>
+      </c>
+      <c r="H155" t="n">
+        <v>2333553.233141046</v>
+      </c>
+      <c r="I155" t="n">
+        <v>-1993328.875672851</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" t="n">
+        <v>6570727.64590167</v>
+      </c>
+      <c r="M155" t="n">
+        <v>17856509.35808223</v>
+      </c>
+      <c r="N155" t="n">
+        <v>32856.02526337757</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" t="n">
+        <v>32856.02526337757</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>32853.63822950811</v>
+      </c>
+      <c r="R155" t="n">
+        <v>0</v>
+      </c>
+      <c r="S155" t="n">
+        <v>0</v>
+      </c>
+      <c r="T155" t="n">
+        <v>0</v>
+      </c>
+      <c r="U155" t="n">
+        <v>2.387033869649941</v>
+      </c>
+      <c r="V155" t="n">
+        <v>29.17199993133545</v>
+      </c>
+      <c r="W155" t="n">
+        <v>17856509.35808223</v>
+      </c>
+      <c r="X155" t="n">
+        <v>17856509.35808223</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303002739_dh_1_ctax_200_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>16845870.52103633</v>
+      </c>
+      <c r="B156" t="n">
+        <v>3994313.635987978</v>
+      </c>
+      <c r="C156" t="n">
+        <v>3302224.328332253</v>
+      </c>
+      <c r="D156" t="n">
+        <v>3620221.078522149</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" t="n">
+        <v>7614534.714510128</v>
+      </c>
+      <c r="G156" t="n">
+        <v>3302224.328332253</v>
+      </c>
+      <c r="H156" t="n">
+        <v>2379178.722351074</v>
+      </c>
+      <c r="I156" t="n">
+        <v>-3106873.112466991</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" t="n">
+        <v>6656805.868309862</v>
+      </c>
+      <c r="M156" t="n">
+        <v>16845870.52103633</v>
+      </c>
+      <c r="N156" t="n">
+        <v>33286.41363325305</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" t="n">
+        <v>33286.41363325305</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>33284.02934154904</v>
+      </c>
+      <c r="R156" t="n">
+        <v>0</v>
+      </c>
+      <c r="S156" t="n">
+        <v>0</v>
+      </c>
+      <c r="T156" t="n">
+        <v>0</v>
+      </c>
+      <c r="U156" t="n">
+        <v>2.384291704344384</v>
+      </c>
+      <c r="V156" t="n">
+        <v>32.64999985694885</v>
+      </c>
+      <c r="W156" t="n">
+        <v>16845870.52103633</v>
+      </c>
+      <c r="X156" t="n">
+        <v>16845870.52103633</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD156" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303003031_dh_1_ctax_200_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>15639110.40287342</v>
+      </c>
+      <c r="B157" t="n">
+        <v>3973575.667035407</v>
+      </c>
+      <c r="C157" t="n">
+        <v>3292481.919699083</v>
+      </c>
+      <c r="D157" t="n">
+        <v>3606557.611767134</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" t="n">
+        <v>7580133.278802542</v>
+      </c>
+      <c r="G157" t="n">
+        <v>3292481.919699083</v>
+      </c>
+      <c r="H157" t="n">
+        <v>3198176.991400389</v>
+      </c>
+      <c r="I157" t="n">
+        <v>-5952581.755016172</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" t="n">
+        <v>7520899.967987584</v>
+      </c>
+      <c r="M157" t="n">
+        <v>15639110.40287342</v>
+      </c>
+      <c r="N157" t="n">
+        <v>37606.87747409774</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="n">
+        <v>37606.87747409774</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>37604.49983993749</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0</v>
+      </c>
+      <c r="S157" t="n">
+        <v>0</v>
+      </c>
+      <c r="T157" t="n">
+        <v>0</v>
+      </c>
+      <c r="U157" t="n">
+        <v>2.377634160543942</v>
+      </c>
+      <c r="V157" t="n">
+        <v>55.71700000762939</v>
+      </c>
+      <c r="W157" t="n">
+        <v>15639110.40287342</v>
+      </c>
+      <c r="X157" t="n">
+        <v>15639110.40287342</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303003328_dh_1_ctax_200_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>13717707.57036005</v>
+      </c>
+      <c r="B158" t="n">
+        <v>3940832.636216401</v>
+      </c>
+      <c r="C158" t="n">
+        <v>3277099.700405727</v>
+      </c>
+      <c r="D158" t="n">
+        <v>3583017.765529915</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" t="n">
+        <v>7523850.401746316</v>
+      </c>
+      <c r="G158" t="n">
+        <v>3277099.700405727</v>
+      </c>
+      <c r="H158" t="n">
+        <v>5443056.932678772</v>
+      </c>
+      <c r="I158" t="n">
+        <v>-12345780.91526832</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
+        <v>9819481.450797547</v>
+      </c>
+      <c r="M158" t="n">
+        <v>13717707.57036005</v>
+      </c>
+      <c r="N158" t="n">
+        <v>49099.77100892797</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="n">
+        <v>49099.77100892797</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>49097.40725398785</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" t="n">
+        <v>0</v>
+      </c>
+      <c r="T158" t="n">
+        <v>0</v>
+      </c>
+      <c r="U158" t="n">
+        <v>2.363754939473468</v>
+      </c>
+      <c r="V158" t="n">
+        <v>37.95100021362305</v>
+      </c>
+      <c r="W158" t="n">
+        <v>13717707.57036005</v>
+      </c>
+      <c r="X158" t="n">
+        <v>13717707.57036005</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD158" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303003647_dh_1_ctax_200_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>10580499.53259607</v>
+      </c>
+      <c r="B159" t="n">
+        <v>3904343.671360159</v>
+      </c>
+      <c r="C159" t="n">
+        <v>3259957.69353688</v>
+      </c>
+      <c r="D159" t="n">
+        <v>3549864.886760653</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" t="n">
+        <v>7454208.558120811</v>
+      </c>
+      <c r="G159" t="n">
+        <v>3259957.69353688</v>
+      </c>
+      <c r="H159" t="n">
+        <v>8952110.857894575</v>
+      </c>
+      <c r="I159" t="n">
+        <v>-22588197.71786448</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
+        <v>13502420.14090828</v>
+      </c>
+      <c r="M159" t="n">
+        <v>10580499.53259607</v>
+      </c>
+      <c r="N159" t="n">
+        <v>67514.43714299382</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="n">
+        <v>67514.43714299382</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>67512.10070454179</v>
+      </c>
+      <c r="R159" t="n">
+        <v>0</v>
+      </c>
+      <c r="S159" t="n">
+        <v>0</v>
+      </c>
+      <c r="T159" t="n">
+        <v>0</v>
+      </c>
+      <c r="U159" t="n">
+        <v>2.33643845139308</v>
+      </c>
+      <c r="V159" t="n">
+        <v>33.99699997901917</v>
+      </c>
+      <c r="W159" t="n">
+        <v>10580499.53259607</v>
+      </c>
+      <c r="X159" t="n">
+        <v>10580499.53259607</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303003948_dh_1_ctax_200_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>2616020.057554567</v>
+      </c>
+      <c r="B160" t="n">
+        <v>31572859.92774189</v>
+      </c>
+      <c r="C160" t="n">
+        <v>4433066.460455096</v>
+      </c>
+      <c r="D160" t="n">
+        <v>22542686.79304919</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" t="n">
+        <v>54115546.72079108</v>
+      </c>
+      <c r="G160" t="n">
+        <v>4433066.460455096</v>
+      </c>
+      <c r="H160" t="n">
+        <v>6167393.042496535</v>
+      </c>
+      <c r="I160" t="n">
+        <v>-73438345.1524533</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" t="n">
+        <v>11338358.98626516</v>
+      </c>
+      <c r="M160" t="n">
+        <v>2616020.057554567</v>
+      </c>
+      <c r="N160" t="n">
+        <v>56696.62900253265</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" t="n">
+        <v>56696.62900253265</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>56691.79493132478</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" t="n">
+        <v>0</v>
+      </c>
+      <c r="T160" t="n">
+        <v>0</v>
+      </c>
+      <c r="U160" t="n">
+        <v>4.834071206764879</v>
+      </c>
+      <c r="V160" t="n">
+        <v>34.09000015258789</v>
+      </c>
+      <c r="W160" t="n">
+        <v>2616020.057554567</v>
+      </c>
+      <c r="X160" t="n">
+        <v>2616020.057554567</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303004813_dh_1_ctax_200_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>-7944204.665519098</v>
+      </c>
+      <c r="B161" t="n">
+        <v>31845651.8151454</v>
+      </c>
+      <c r="C161" t="n">
+        <v>4458987.607501583</v>
+      </c>
+      <c r="D161" t="n">
+        <v>22729601.76450172</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" t="n">
+        <v>54575253.57964712</v>
+      </c>
+      <c r="G161" t="n">
+        <v>4458987.607501583</v>
+      </c>
+      <c r="H161" t="n">
+        <v>6519518.053030788</v>
+      </c>
+      <c r="I161" t="n">
+        <v>-84893093.80329305</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" t="n">
+        <v>11395129.89759446</v>
+      </c>
+      <c r="M161" t="n">
+        <v>-7944204.665519098</v>
+      </c>
+      <c r="N161" t="n">
+        <v>56980.51872432132</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" t="n">
+        <v>56980.51872432132</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>56975.64948797227</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" t="n">
+        <v>0</v>
+      </c>
+      <c r="T161" t="n">
+        <v>0</v>
+      </c>
+      <c r="U161" t="n">
+        <v>4.869236349029798</v>
+      </c>
+      <c r="V161" t="n">
+        <v>30.59000015258789</v>
+      </c>
+      <c r="W161" t="n">
+        <v>-7944204.665519098</v>
+      </c>
+      <c r="X161" t="n">
+        <v>-7944204.665519098</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303005112_dh_1_ctax_200_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>20481779.03142424</v>
+      </c>
+      <c r="B162" t="n">
+        <v>4035994.903882721</v>
+      </c>
+      <c r="C162" t="n">
+        <v>3321805.606764483</v>
+      </c>
+      <c r="D162" t="n">
+        <v>3643834.867228802</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" t="n">
+        <v>7679829.771111523</v>
+      </c>
+      <c r="G162" t="n">
+        <v>3321805.606764483</v>
+      </c>
+      <c r="H162" t="n">
+        <v>2335164.241315593</v>
+      </c>
+      <c r="I162" t="n">
+        <v>-989313.2402424782</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="n">
+        <v>8134292.652475117</v>
+      </c>
+      <c r="M162" t="n">
+        <v>20481779.03142424</v>
+      </c>
+      <c r="N162" t="n">
+        <v>32539.56169275146</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" t="n">
+        <v>32539.56169275146</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>32537.17060990033</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="n">
+        <v>0</v>
+      </c>
+      <c r="T162" t="n">
+        <v>0</v>
+      </c>
+      <c r="U162" t="n">
+        <v>2.391082851305129</v>
+      </c>
+      <c r="V162" t="n">
+        <v>30.98099994659424</v>
+      </c>
+      <c r="W162" t="n">
+        <v>20481779.03142424</v>
+      </c>
+      <c r="X162" t="n">
+        <v>20481779.03142424</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303005408_dh_1_ctax_250_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>19491816.34910647</v>
+      </c>
+      <c r="B163" t="n">
+        <v>4030147.940175848</v>
+      </c>
+      <c r="C163" t="n">
+        <v>3319058.784748019</v>
+      </c>
+      <c r="D163" t="n">
+        <v>3640662.348375094</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" t="n">
+        <v>7670810.288550942</v>
+      </c>
+      <c r="G163" t="n">
+        <v>3319058.784748019</v>
+      </c>
+      <c r="H163" t="n">
+        <v>2334916.274214419</v>
+      </c>
+      <c r="I163" t="n">
+        <v>-1981234.163063414</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" t="n">
+        <v>8148265.164656505</v>
+      </c>
+      <c r="M163" t="n">
+        <v>19491816.34910647</v>
+      </c>
+      <c r="N163" t="n">
+        <v>32595.45102851604</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" t="n">
+        <v>32595.45102851604</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>32593.06065862607</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0</v>
+      </c>
+      <c r="S163" t="n">
+        <v>0</v>
+      </c>
+      <c r="T163" t="n">
+        <v>0</v>
+      </c>
+      <c r="U163" t="n">
+        <v>2.390369890098021</v>
+      </c>
+      <c r="V163" t="n">
+        <v>31.89100003242493</v>
+      </c>
+      <c r="W163" t="n">
+        <v>19491816.34910647</v>
+      </c>
+      <c r="X163" t="n">
+        <v>19491816.34910647</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303005703_dh_1_ctax_250_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>18495791.21664325</v>
+      </c>
+      <c r="B164" t="n">
+        <v>4021688.937457578</v>
+      </c>
+      <c r="C164" t="n">
+        <v>3315084.863227596</v>
+      </c>
+      <c r="D164" t="n">
+        <v>3635993.109013997</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" t="n">
+        <v>7657682.046471575</v>
+      </c>
+      <c r="G164" t="n">
+        <v>3315084.863227596</v>
+      </c>
+      <c r="H164" t="n">
+        <v>2351582.798662393</v>
+      </c>
+      <c r="I164" t="n">
+        <v>-3019444.477018431</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" t="n">
+        <v>8190885.98530012</v>
+      </c>
+      <c r="M164" t="n">
+        <v>18495791.21664325</v>
+      </c>
+      <c r="N164" t="n">
+        <v>32765.93314358331</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" t="n">
+        <v>32765.93314358331</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>32763.54394120063</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" t="n">
+        <v>0</v>
+      </c>
+      <c r="T164" t="n">
+        <v>0</v>
+      </c>
+      <c r="U164" t="n">
+        <v>2.389202382510487</v>
+      </c>
+      <c r="V164" t="n">
+        <v>37.03000020980835</v>
+      </c>
+      <c r="W164" t="n">
+        <v>18495791.21664325</v>
+      </c>
+      <c r="X164" t="n">
+        <v>18495791.21664325</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD164" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303010003_dh_1_ctax_250_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>17431397.57858838</v>
+      </c>
+      <c r="B165" t="n">
+        <v>4010682.323276507</v>
+      </c>
+      <c r="C165" t="n">
+        <v>3309914.109367134</v>
+      </c>
+      <c r="D165" t="n">
+        <v>3629778.661406825</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0</v>
+      </c>
+      <c r="F165" t="n">
+        <v>7640460.984683331</v>
+      </c>
+      <c r="G165" t="n">
+        <v>3309914.109367134</v>
+      </c>
+      <c r="H165" t="n">
+        <v>2654222.965119759</v>
+      </c>
+      <c r="I165" t="n">
+        <v>-4749155.878977406</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" t="n">
+        <v>8575955.398395561</v>
+      </c>
+      <c r="M165" t="n">
+        <v>17431397.57858838</v>
+      </c>
+      <c r="N165" t="n">
+        <v>34306.20903887904</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" t="n">
+        <v>34306.20903887904</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>34303.8215935824</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0</v>
+      </c>
+      <c r="S165" t="n">
+        <v>0</v>
+      </c>
+      <c r="T165" t="n">
+        <v>0</v>
+      </c>
+      <c r="U165" t="n">
+        <v>2.387445296479032</v>
+      </c>
+      <c r="V165" t="n">
+        <v>39.20600008964539</v>
+      </c>
+      <c r="W165" t="n">
+        <v>17431397.57858838</v>
+      </c>
+      <c r="X165" t="n">
+        <v>17431397.57858838</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303010313_dh_1_ctax_250_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>15932221.51671704</v>
+      </c>
+      <c r="B166" t="n">
+        <v>3999134.411350717</v>
+      </c>
+      <c r="C166" t="n">
+        <v>3304489.061374334</v>
+      </c>
+      <c r="D166" t="n">
+        <v>3622094.89829098</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" t="n">
+        <v>7621229.309641697</v>
+      </c>
+      <c r="G166" t="n">
+        <v>3304489.061374334</v>
+      </c>
+      <c r="H166" t="n">
+        <v>4010401.942904818</v>
+      </c>
+      <c r="I166" t="n">
+        <v>-9224659.111176839</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" t="n">
+        <v>10220760.31397303</v>
+      </c>
+      <c r="M166" t="n">
+        <v>15932221.51671704</v>
+      </c>
+      <c r="N166" t="n">
+        <v>40885.42486503948</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" t="n">
+        <v>40885.42486503948</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>40883.04125589196</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" t="n">
+        <v>0</v>
+      </c>
+      <c r="T166" t="n">
+        <v>0</v>
+      </c>
+      <c r="U166" t="n">
+        <v>2.383609147853361</v>
+      </c>
+      <c r="V166" t="n">
+        <v>53.72899985313416</v>
+      </c>
+      <c r="W166" t="n">
+        <v>15932221.51671704</v>
+      </c>
+      <c r="X166" t="n">
+        <v>15932221.51671704</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD166" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303010628_dh_1_ctax_250_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>13591519.40053864</v>
+      </c>
+      <c r="B167" t="n">
+        <v>3986240.447150572</v>
+      </c>
+      <c r="C167" t="n">
+        <v>3298431.656793076</v>
+      </c>
+      <c r="D167" t="n">
+        <v>3612866.752109759</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" t="n">
+        <v>7599107.199260331</v>
+      </c>
+      <c r="G167" t="n">
+        <v>3298431.656793076</v>
+      </c>
+      <c r="H167" t="n">
+        <v>6645627.035761591</v>
+      </c>
+      <c r="I167" t="n">
+        <v>-17327269.38501025</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" t="n">
+        <v>13375622.89373389</v>
+      </c>
+      <c r="M167" t="n">
+        <v>13591519.40053864</v>
+      </c>
+      <c r="N167" t="n">
+        <v>53504.8697899043</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" t="n">
+        <v>53504.8697899043</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>53502.49157493463</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0</v>
+      </c>
+      <c r="S167" t="n">
+        <v>0</v>
+      </c>
+      <c r="T167" t="n">
+        <v>0</v>
+      </c>
+      <c r="U167" t="n">
+        <v>2.378214969546107</v>
+      </c>
+      <c r="V167" t="n">
+        <v>46.53200006484985</v>
+      </c>
+      <c r="W167" t="n">
+        <v>13591519.40053864</v>
+      </c>
+      <c r="X167" t="n">
+        <v>13591519.40053864</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303010956_dh_1_ctax_250_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>5330041.744131675</v>
+      </c>
+      <c r="B168" t="n">
+        <v>32022539.03271048</v>
+      </c>
+      <c r="C168" t="n">
+        <v>4475795.730429251</v>
+      </c>
+      <c r="D168" t="n">
+        <v>22849642.92781117</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" t="n">
+        <v>54872181.96052165</v>
+      </c>
+      <c r="G168" t="n">
+        <v>4475795.730429251</v>
+      </c>
+      <c r="H168" t="n">
+        <v>5662361.563641375</v>
+      </c>
+      <c r="I168" t="n">
+        <v>-72730158.92822489</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" t="n">
+        <v>13049861.41776429</v>
+      </c>
+      <c r="M168" t="n">
+        <v>5330041.744131675</v>
+      </c>
+      <c r="N168" t="n">
+        <v>52204.33613778993</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
+        <v>52204.33613778993</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>52199.44567105712</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0</v>
+      </c>
+      <c r="S168" t="n">
+        <v>0</v>
+      </c>
+      <c r="T168" t="n">
+        <v>0</v>
+      </c>
+      <c r="U168" t="n">
+        <v>4.890466732799332</v>
+      </c>
+      <c r="V168" t="n">
+        <v>38.09899997711182</v>
+      </c>
+      <c r="W168" t="n">
+        <v>5330041.744131675</v>
+      </c>
+      <c r="X168" t="n">
+        <v>5330041.744131675</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD168" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303011321_dh_1_ctax_250_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>-5162657.295494519</v>
+      </c>
+      <c r="B169" t="n">
+        <v>32192029.80639484</v>
+      </c>
+      <c r="C169" t="n">
+        <v>4491901.030735327</v>
+      </c>
+      <c r="D169" t="n">
+        <v>22963687.6213389</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" t="n">
+        <v>55155717.42773373</v>
+      </c>
+      <c r="G169" t="n">
+        <v>4491901.030735327</v>
+      </c>
+      <c r="H169" t="n">
+        <v>6288426.099288421</v>
+      </c>
+      <c r="I169" t="n">
+        <v>-84690622.95608546</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" t="n">
+        <v>13591921.10283346</v>
+      </c>
+      <c r="M169" t="n">
+        <v>-5162657.295494519</v>
+      </c>
+      <c r="N169" t="n">
+        <v>54372.59389755144</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" t="n">
+        <v>54372.59389755144</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>54367.68441133383</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0</v>
+      </c>
+      <c r="S169" t="n">
+        <v>0</v>
+      </c>
+      <c r="T169" t="n">
+        <v>0</v>
+      </c>
+      <c r="U169" t="n">
+        <v>4.909486217584692</v>
+      </c>
+      <c r="V169" t="n">
+        <v>34.81900000572205</v>
+      </c>
+      <c r="W169" t="n">
+        <v>-5162657.295494519</v>
+      </c>
+      <c r="X169" t="n">
+        <v>-5162657.295494519</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303011634_dh_1_ctax_250_el_price_400</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_WtE/raw_results/technology_selection/Summary.xlsx
+++ b/dataCaseStudy_WtE/raw_results/technology_selection/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE169"/>
+  <dimension ref="A1:AE201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17886,6 +17886,3302 @@
       <c r="AE169" t="inlineStr">
         <is>
           <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303011634_dh_1_ctax_250_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>16288277.5823403</v>
+      </c>
+      <c r="B170" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C170" t="n">
+        <v>0</v>
+      </c>
+      <c r="D170" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>155.0546472912404</v>
+      </c>
+      <c r="I170" t="n">
+        <v>-5359875.275964418</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L170" t="n">
+        <v>21302438.12259698</v>
+      </c>
+      <c r="M170" t="n">
+        <v>16288277.5823403</v>
+      </c>
+      <c r="N170" t="n">
+        <v>213024.3812259698</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" t="n">
+        <v>213024.3812259698</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>213024.3812259698</v>
+      </c>
+      <c r="R170" t="n">
+        <v>0</v>
+      </c>
+      <c r="S170" t="n">
+        <v>0</v>
+      </c>
+      <c r="T170" t="n">
+        <v>0</v>
+      </c>
+      <c r="U170" t="n">
+        <v>0</v>
+      </c>
+      <c r="V170" t="n">
+        <v>2.365000009536743</v>
+      </c>
+      <c r="W170" t="n">
+        <v>16288277.5823403</v>
+      </c>
+      <c r="X170" t="n">
+        <v>16288277.5823403</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303183248_dh_0.5_ctax_100_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>10925191.3762467</v>
+      </c>
+      <c r="B171" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C171" t="n">
+        <v>0</v>
+      </c>
+      <c r="D171" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" t="n">
+        <v>16256.29726210878</v>
+      </c>
+      <c r="I171" t="n">
+        <v>-10746509.54938219</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="n">
+        <v>0</v>
+      </c>
+      <c r="L171" t="n">
+        <v>21309884.94730634</v>
+      </c>
+      <c r="M171" t="n">
+        <v>10925191.3762467</v>
+      </c>
+      <c r="N171" t="n">
+        <v>213098.8494730633</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" t="n">
+        <v>213098.8494730633</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>213098.8494730633</v>
+      </c>
+      <c r="R171" t="n">
+        <v>0</v>
+      </c>
+      <c r="S171" t="n">
+        <v>0</v>
+      </c>
+      <c r="T171" t="n">
+        <v>0</v>
+      </c>
+      <c r="U171" t="n">
+        <v>0</v>
+      </c>
+      <c r="V171" t="n">
+        <v>1.797000169754028</v>
+      </c>
+      <c r="W171" t="n">
+        <v>10925191.37624663</v>
+      </c>
+      <c r="X171" t="n">
+        <v>10925191.3762467</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>6.705522537231445e-08</v>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303183508_dh_0.5_ctax_100_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>5509548.414125333</v>
+      </c>
+      <c r="B172" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C172" t="n">
+        <v>0</v>
+      </c>
+      <c r="D172" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" t="n">
+        <v>251892.889191721</v>
+      </c>
+      <c r="I172" t="n">
+        <v>-16506771.02720062</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="n">
+        <v>0</v>
+      </c>
+      <c r="L172" t="n">
+        <v>21418866.87107379</v>
+      </c>
+      <c r="M172" t="n">
+        <v>5509548.414125333</v>
+      </c>
+      <c r="N172" t="n">
+        <v>214188.6687107377</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="P172" t="n">
+        <v>214188.6687107377</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>214188.6687107378</v>
+      </c>
+      <c r="R172" t="n">
+        <v>0</v>
+      </c>
+      <c r="S172" t="n">
+        <v>0</v>
+      </c>
+      <c r="T172" t="n">
+        <v>0</v>
+      </c>
+      <c r="U172" t="n">
+        <v>0</v>
+      </c>
+      <c r="V172" t="n">
+        <v>1.769000053405762</v>
+      </c>
+      <c r="W172" t="n">
+        <v>5509548.414125187</v>
+      </c>
+      <c r="X172" t="n">
+        <v>5509548.414125333</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>1.452863216400146e-07</v>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD172" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303183718_dh_0.5_ctax_100_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>-111513.2904379889</v>
+      </c>
+      <c r="B173" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0</v>
+      </c>
+      <c r="D173" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="n">
+        <v>876781.4848603355</v>
+      </c>
+      <c r="I173" t="n">
+        <v>-23041732.30292929</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L173" t="n">
+        <v>21707877.84657052</v>
+      </c>
+      <c r="M173" t="n">
+        <v>-111513.2904379889</v>
+      </c>
+      <c r="N173" t="n">
+        <v>217078.7784657051</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0</v>
+      </c>
+      <c r="P173" t="n">
+        <v>217078.7784657051</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>217078.7784657051</v>
+      </c>
+      <c r="R173" t="n">
+        <v>0</v>
+      </c>
+      <c r="S173" t="n">
+        <v>0</v>
+      </c>
+      <c r="T173" t="n">
+        <v>0</v>
+      </c>
+      <c r="U173" t="n">
+        <v>0</v>
+      </c>
+      <c r="V173" t="n">
+        <v>1.784999847412109</v>
+      </c>
+      <c r="W173" t="n">
+        <v>-111513.2904379889</v>
+      </c>
+      <c r="X173" t="n">
+        <v>-111513.2904379889</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303183937_dh_0.5_ctax_100_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>-6012420.672834076</v>
+      </c>
+      <c r="B174" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0</v>
+      </c>
+      <c r="D174" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" t="n">
+        <v>1647033.57777678</v>
+      </c>
+      <c r="I174" t="n">
+        <v>-30069133.37121568</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" t="n">
+        <v>0</v>
+      </c>
+      <c r="L174" t="n">
+        <v>22064119.43954438</v>
+      </c>
+      <c r="M174" t="n">
+        <v>-6012420.672834076</v>
+      </c>
+      <c r="N174" t="n">
+        <v>220641.1943954437</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" t="n">
+        <v>220641.1943954437</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>220641.1943954437</v>
+      </c>
+      <c r="R174" t="n">
+        <v>0</v>
+      </c>
+      <c r="S174" t="n">
+        <v>0</v>
+      </c>
+      <c r="T174" t="n">
+        <v>0</v>
+      </c>
+      <c r="U174" t="n">
+        <v>0</v>
+      </c>
+      <c r="V174" t="n">
+        <v>2.006999969482422</v>
+      </c>
+      <c r="W174" t="n">
+        <v>-6012420.672834076</v>
+      </c>
+      <c r="X174" t="n">
+        <v>-6012420.672834076</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC174" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD174" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE174" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303184145_dh_0.5_ctax_100_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>-12074800.50869442</v>
+      </c>
+      <c r="B175" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0</v>
+      </c>
+      <c r="D175" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" t="n">
+        <v>1943719.78314256</v>
+      </c>
+      <c r="I175" t="n">
+        <v>-36565416.78242347</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" t="n">
+        <v>0</v>
+      </c>
+      <c r="L175" t="n">
+        <v>22201336.80952604</v>
+      </c>
+      <c r="M175" t="n">
+        <v>-12074800.50869442</v>
+      </c>
+      <c r="N175" t="n">
+        <v>222013.3680952604</v>
+      </c>
+      <c r="O175" t="n">
+        <v>0</v>
+      </c>
+      <c r="P175" t="n">
+        <v>222013.3680952604</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>222013.3680952604</v>
+      </c>
+      <c r="R175" t="n">
+        <v>0</v>
+      </c>
+      <c r="S175" t="n">
+        <v>0</v>
+      </c>
+      <c r="T175" t="n">
+        <v>0</v>
+      </c>
+      <c r="U175" t="n">
+        <v>0</v>
+      </c>
+      <c r="V175" t="n">
+        <v>2.183000087738037</v>
+      </c>
+      <c r="W175" t="n">
+        <v>-12074800.50869448</v>
+      </c>
+      <c r="X175" t="n">
+        <v>-12074800.50869442</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>5.587935447692871e-08</v>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD175" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303184409_dh_0.5_ctax_100_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>-18183808.08255287</v>
+      </c>
+      <c r="B176" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C176" t="n">
+        <v>0</v>
+      </c>
+      <c r="D176" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" t="n">
+        <v>2061813.094625738</v>
+      </c>
+      <c r="I176" t="n">
+        <v>-42847135.82432608</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" t="n">
+        <v>0</v>
+      </c>
+      <c r="L176" t="n">
+        <v>22255954.96608701</v>
+      </c>
+      <c r="M176" t="n">
+        <v>-18183808.08255287</v>
+      </c>
+      <c r="N176" t="n">
+        <v>222559.5496608701</v>
+      </c>
+      <c r="O176" t="n">
+        <v>0</v>
+      </c>
+      <c r="P176" t="n">
+        <v>222559.5496608701</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>222559.5496608701</v>
+      </c>
+      <c r="R176" t="n">
+        <v>0</v>
+      </c>
+      <c r="S176" t="n">
+        <v>0</v>
+      </c>
+      <c r="T176" t="n">
+        <v>0</v>
+      </c>
+      <c r="U176" t="n">
+        <v>0</v>
+      </c>
+      <c r="V176" t="n">
+        <v>1.847000122070312</v>
+      </c>
+      <c r="W176" t="n">
+        <v>-18183808.08255288</v>
+      </c>
+      <c r="X176" t="n">
+        <v>-18183808.08255287</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>7.450580596923828e-09</v>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD176" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303184703_dh_0.5_ctax_100_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>-24308846.4052638</v>
+      </c>
+      <c r="B177" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C177" t="n">
+        <v>0</v>
+      </c>
+      <c r="D177" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E177" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="n">
+        <v>2094069.069521546</v>
+      </c>
+      <c r="I177" t="n">
+        <v>-49019348.51032212</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="n">
+        <v>0</v>
+      </c>
+      <c r="L177" t="n">
+        <v>22270873.35447633</v>
+      </c>
+      <c r="M177" t="n">
+        <v>-24308846.4052638</v>
+      </c>
+      <c r="N177" t="n">
+        <v>222708.7335447632</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" t="n">
+        <v>222708.7335447632</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>222708.7335447632</v>
+      </c>
+      <c r="R177" t="n">
+        <v>0</v>
+      </c>
+      <c r="S177" t="n">
+        <v>0</v>
+      </c>
+      <c r="T177" t="n">
+        <v>0</v>
+      </c>
+      <c r="U177" t="n">
+        <v>0</v>
+      </c>
+      <c r="V177" t="n">
+        <v>1.91700005531311</v>
+      </c>
+      <c r="W177" t="n">
+        <v>-24308846.40526384</v>
+      </c>
+      <c r="X177" t="n">
+        <v>-24308846.4052638</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>3.725290298461914e-08</v>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD177" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303184935_dh_0.5_ctax_100_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>26939496.6436388</v>
+      </c>
+      <c r="B178" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0</v>
+      </c>
+      <c r="D178" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" t="n">
+        <v>155.0546472912404</v>
+      </c>
+      <c r="I178" t="n">
+        <v>-5359875.275964418</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" t="n">
+        <v>0</v>
+      </c>
+      <c r="L178" t="n">
+        <v>31953657.18389548</v>
+      </c>
+      <c r="M178" t="n">
+        <v>26939496.6436388</v>
+      </c>
+      <c r="N178" t="n">
+        <v>213024.3812259698</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" t="n">
+        <v>213024.3812259698</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>213024.3812259698</v>
+      </c>
+      <c r="R178" t="n">
+        <v>0</v>
+      </c>
+      <c r="S178" t="n">
+        <v>0</v>
+      </c>
+      <c r="T178" t="n">
+        <v>0</v>
+      </c>
+      <c r="U178" t="n">
+        <v>0</v>
+      </c>
+      <c r="V178" t="n">
+        <v>1.920000076293945</v>
+      </c>
+      <c r="W178" t="n">
+        <v>26939496.6436388</v>
+      </c>
+      <c r="X178" t="n">
+        <v>26939496.6436388</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD178" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE178" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303185208_dh_0.5_ctax_150_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>21579106.17715645</v>
+      </c>
+      <c r="B179" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C179" t="n">
+        <v>0</v>
+      </c>
+      <c r="D179" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0</v>
+      </c>
+      <c r="F179" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="n">
+        <v>7417.093733416082</v>
+      </c>
+      <c r="I179" t="n">
+        <v>-10732565.82114889</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="n">
+        <v>0</v>
+      </c>
+      <c r="L179" t="n">
+        <v>31958695.22351148</v>
+      </c>
+      <c r="M179" t="n">
+        <v>21579106.17715645</v>
+      </c>
+      <c r="N179" t="n">
+        <v>213057.9681567431</v>
+      </c>
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
+      <c r="P179" t="n">
+        <v>213057.9681567431</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>213057.9681567431</v>
+      </c>
+      <c r="R179" t="n">
+        <v>0</v>
+      </c>
+      <c r="S179" t="n">
+        <v>0</v>
+      </c>
+      <c r="T179" t="n">
+        <v>0</v>
+      </c>
+      <c r="U179" t="n">
+        <v>0</v>
+      </c>
+      <c r="V179" t="n">
+        <v>1.688999891281128</v>
+      </c>
+      <c r="W179" t="n">
+        <v>21579106.17715633</v>
+      </c>
+      <c r="X179" t="n">
+        <v>21579106.17715645</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>1.229345798492432e-07</v>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC179" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD179" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303185357_dh_0.5_ctax_150_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>16197266.25525175</v>
+      </c>
+      <c r="B180" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0</v>
+      </c>
+      <c r="D180" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E180" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" t="n">
+        <v>84354.75926208599</v>
+      </c>
+      <c r="I180" t="n">
+        <v>-16244718.91404278</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L180" t="n">
+        <v>32012070.728972</v>
+      </c>
+      <c r="M180" t="n">
+        <v>16197266.25525175</v>
+      </c>
+      <c r="N180" t="n">
+        <v>213413.8048598132</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" t="n">
+        <v>213413.8048598132</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>213413.8048598132</v>
+      </c>
+      <c r="R180" t="n">
+        <v>0</v>
+      </c>
+      <c r="S180" t="n">
+        <v>0</v>
+      </c>
+      <c r="T180" t="n">
+        <v>0</v>
+      </c>
+      <c r="U180" t="n">
+        <v>0</v>
+      </c>
+      <c r="V180" t="n">
+        <v>1.884000062942505</v>
+      </c>
+      <c r="W180" t="n">
+        <v>16197266.25525155</v>
+      </c>
+      <c r="X180" t="n">
+        <v>16197266.25525175</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>2.048909664154053e-07</v>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD180" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303185642_dh_0.5_ctax_150_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>10693572.4615687</v>
+      </c>
+      <c r="B181" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0</v>
+      </c>
+      <c r="D181" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E181" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="n">
+        <v>475452.0461187353</v>
+      </c>
+      <c r="I181" t="n">
+        <v>-22410833.73733928</v>
+      </c>
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
+      <c r="K181" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" t="n">
+        <v>32283394.4717288</v>
+      </c>
+      <c r="M181" t="n">
+        <v>10693572.4615687</v>
+      </c>
+      <c r="N181" t="n">
+        <v>215222.6298115252</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" t="n">
+        <v>215222.6298115252</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>215222.6298115252</v>
+      </c>
+      <c r="R181" t="n">
+        <v>0</v>
+      </c>
+      <c r="S181" t="n">
+        <v>0</v>
+      </c>
+      <c r="T181" t="n">
+        <v>0</v>
+      </c>
+      <c r="U181" t="n">
+        <v>0</v>
+      </c>
+      <c r="V181" t="n">
+        <v>1.677000045776367</v>
+      </c>
+      <c r="W181" t="n">
+        <v>10693572.46156869</v>
+      </c>
+      <c r="X181" t="n">
+        <v>10693572.4615687</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>7.450580596923828e-09</v>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC181" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD181" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303185832_dh_0.5_ctax_150_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>4964457.577288527</v>
+      </c>
+      <c r="B182" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C182" t="n">
+        <v>0</v>
+      </c>
+      <c r="D182" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" t="n">
+        <v>1144370.416970436</v>
+      </c>
+      <c r="I182" t="n">
+        <v>-29272929.11224952</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" t="n">
+        <v>0</v>
+      </c>
+      <c r="L182" t="n">
+        <v>32747456.59150717</v>
+      </c>
+      <c r="M182" t="n">
+        <v>4964457.577288527</v>
+      </c>
+      <c r="N182" t="n">
+        <v>218316.3772767143</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" t="n">
+        <v>218316.3772767143</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>218316.3772767144</v>
+      </c>
+      <c r="R182" t="n">
+        <v>0</v>
+      </c>
+      <c r="S182" t="n">
+        <v>0</v>
+      </c>
+      <c r="T182" t="n">
+        <v>0</v>
+      </c>
+      <c r="U182" t="n">
+        <v>0</v>
+      </c>
+      <c r="V182" t="n">
+        <v>1.808000087738037</v>
+      </c>
+      <c r="W182" t="n">
+        <v>4964457.577288481</v>
+      </c>
+      <c r="X182" t="n">
+        <v>4964457.577288527</v>
+      </c>
+      <c r="Y182" t="n">
+        <v>4.563480615615845e-08</v>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC182" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD182" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303190128_dh_0.5_ctax_150_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>-996204.8174847178</v>
+      </c>
+      <c r="B183" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C183" t="n">
+        <v>0</v>
+      </c>
+      <c r="D183" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0</v>
+      </c>
+      <c r="F183" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" t="n">
+        <v>1709345.297483764</v>
+      </c>
+      <c r="I183" t="n">
+        <v>-36190517.71089222</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" t="n">
+        <v>0</v>
+      </c>
+      <c r="L183" t="n">
+        <v>33139407.91486328</v>
+      </c>
+      <c r="M183" t="n">
+        <v>-996204.8174847178</v>
+      </c>
+      <c r="N183" t="n">
+        <v>220929.3860990884</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+      <c r="P183" t="n">
+        <v>220929.3860990884</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>220929.3860990885</v>
+      </c>
+      <c r="R183" t="n">
+        <v>0</v>
+      </c>
+      <c r="S183" t="n">
+        <v>0</v>
+      </c>
+      <c r="T183" t="n">
+        <v>0</v>
+      </c>
+      <c r="U183" t="n">
+        <v>0</v>
+      </c>
+      <c r="V183" t="n">
+        <v>1.611999988555908</v>
+      </c>
+      <c r="W183" t="n">
+        <v>-996204.8174847807</v>
+      </c>
+      <c r="X183" t="n">
+        <v>-996204.8174847178</v>
+      </c>
+      <c r="Y183" t="n">
+        <v>6.28642737865448e-08</v>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC183" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD183" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303190316_dh_0.5_ctax_150_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>-7068393.308029361</v>
+      </c>
+      <c r="B184" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C184" t="n">
+        <v>0</v>
+      </c>
+      <c r="D184" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0</v>
+      </c>
+      <c r="F184" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" t="n">
+        <v>1949433.947739025</v>
+      </c>
+      <c r="I184" t="n">
+        <v>-42669356.35280671</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" t="n">
+        <v>0</v>
+      </c>
+      <c r="L184" t="n">
+        <v>33305969.41597787</v>
+      </c>
+      <c r="M184" t="n">
+        <v>-7068393.308029361</v>
+      </c>
+      <c r="N184" t="n">
+        <v>222039.7961065191</v>
+      </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+      <c r="P184" t="n">
+        <v>222039.7961065191</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>222039.7961065191</v>
+      </c>
+      <c r="R184" t="n">
+        <v>0</v>
+      </c>
+      <c r="S184" t="n">
+        <v>0</v>
+      </c>
+      <c r="T184" t="n">
+        <v>0</v>
+      </c>
+      <c r="U184" t="n">
+        <v>0</v>
+      </c>
+      <c r="V184" t="n">
+        <v>1.636999845504761</v>
+      </c>
+      <c r="W184" t="n">
+        <v>-7068393.308029442</v>
+      </c>
+      <c r="X184" t="n">
+        <v>-7068393.308029361</v>
+      </c>
+      <c r="Y184" t="n">
+        <v>8.102506399154663e-08</v>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC184" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD184" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303190503_dh_0.5_ctax_150_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>-13176895.49283775</v>
+      </c>
+      <c r="B185" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0</v>
+      </c>
+      <c r="D185" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E185" t="n">
+        <v>0</v>
+      </c>
+      <c r="F185" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="n">
+        <v>2057857.107913282</v>
+      </c>
+      <c r="I185" t="n">
+        <v>-48961500.26516025</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0</v>
+      </c>
+      <c r="K185" t="n">
+        <v>0</v>
+      </c>
+      <c r="L185" t="n">
+        <v>33381187.98334876</v>
+      </c>
+      <c r="M185" t="n">
+        <v>-13176895.49283775</v>
+      </c>
+      <c r="N185" t="n">
+        <v>222541.253222325</v>
+      </c>
+      <c r="O185" t="n">
+        <v>0</v>
+      </c>
+      <c r="P185" t="n">
+        <v>222541.253222325</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>222541.253222325</v>
+      </c>
+      <c r="R185" t="n">
+        <v>0</v>
+      </c>
+      <c r="S185" t="n">
+        <v>0</v>
+      </c>
+      <c r="T185" t="n">
+        <v>0</v>
+      </c>
+      <c r="U185" t="n">
+        <v>0</v>
+      </c>
+      <c r="V185" t="n">
+        <v>1.580999851226807</v>
+      </c>
+      <c r="W185" t="n">
+        <v>-13176895.49283778</v>
+      </c>
+      <c r="X185" t="n">
+        <v>-13176895.49283775</v>
+      </c>
+      <c r="Y185" t="n">
+        <v>3.352761268615723e-08</v>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC185" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD185" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303190813_dh_0.5_ctax_150_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>37590715.70493729</v>
+      </c>
+      <c r="B186" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0</v>
+      </c>
+      <c r="D186" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" t="n">
+        <v>155.0546472912404</v>
+      </c>
+      <c r="I186" t="n">
+        <v>-5359875.275964418</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" t="n">
+        <v>0</v>
+      </c>
+      <c r="L186" t="n">
+        <v>42604876.24519397</v>
+      </c>
+      <c r="M186" t="n">
+        <v>37590715.70493729</v>
+      </c>
+      <c r="N186" t="n">
+        <v>213024.3812259698</v>
+      </c>
+      <c r="O186" t="n">
+        <v>0</v>
+      </c>
+      <c r="P186" t="n">
+        <v>213024.3812259698</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>213024.3812259698</v>
+      </c>
+      <c r="R186" t="n">
+        <v>0</v>
+      </c>
+      <c r="S186" t="n">
+        <v>0</v>
+      </c>
+      <c r="T186" t="n">
+        <v>0</v>
+      </c>
+      <c r="U186" t="n">
+        <v>0</v>
+      </c>
+      <c r="V186" t="n">
+        <v>1.616000175476074</v>
+      </c>
+      <c r="W186" t="n">
+        <v>37590715.70493698</v>
+      </c>
+      <c r="X186" t="n">
+        <v>37590715.70493729</v>
+      </c>
+      <c r="Y186" t="n">
+        <v>3.05473804473877e-07</v>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC186" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD186" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303190959_dh_0.5_ctax_200_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>32230840.42897287</v>
+      </c>
+      <c r="B187" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C187" t="n">
+        <v>0</v>
+      </c>
+      <c r="D187" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" t="n">
+        <v>155.0546472912404</v>
+      </c>
+      <c r="I187" t="n">
+        <v>-10719750.55192884</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" t="n">
+        <v>0</v>
+      </c>
+      <c r="L187" t="n">
+        <v>42604876.24519397</v>
+      </c>
+      <c r="M187" t="n">
+        <v>32230840.42897287</v>
+      </c>
+      <c r="N187" t="n">
+        <v>213024.3812259698</v>
+      </c>
+      <c r="O187" t="n">
+        <v>0</v>
+      </c>
+      <c r="P187" t="n">
+        <v>213024.3812259698</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>213024.3812259698</v>
+      </c>
+      <c r="R187" t="n">
+        <v>0</v>
+      </c>
+      <c r="S187" t="n">
+        <v>0</v>
+      </c>
+      <c r="T187" t="n">
+        <v>0</v>
+      </c>
+      <c r="U187" t="n">
+        <v>0</v>
+      </c>
+      <c r="V187" t="n">
+        <v>1.601999998092651</v>
+      </c>
+      <c r="W187" t="n">
+        <v>32230840.42897287</v>
+      </c>
+      <c r="X187" t="n">
+        <v>32230840.42897287</v>
+      </c>
+      <c r="Y187" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC187" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD187" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303191147_dh_0.5_ctax_200_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>26859881.41254083</v>
+      </c>
+      <c r="B188" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C188" t="n">
+        <v>0</v>
+      </c>
+      <c r="D188" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="n">
+        <v>31344.87401919085</v>
+      </c>
+      <c r="I188" t="n">
+        <v>-16150749.97065179</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" t="n">
+        <v>0</v>
+      </c>
+      <c r="L188" t="n">
+        <v>42633726.82811298</v>
+      </c>
+      <c r="M188" t="n">
+        <v>26859881.41254083</v>
+      </c>
+      <c r="N188" t="n">
+        <v>213168.6341405648</v>
+      </c>
+      <c r="O188" t="n">
+        <v>0</v>
+      </c>
+      <c r="P188" t="n">
+        <v>213168.6341405648</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>213168.6341405649</v>
+      </c>
+      <c r="R188" t="n">
+        <v>0</v>
+      </c>
+      <c r="S188" t="n">
+        <v>0</v>
+      </c>
+      <c r="T188" t="n">
+        <v>0</v>
+      </c>
+      <c r="U188" t="n">
+        <v>0</v>
+      </c>
+      <c r="V188" t="n">
+        <v>1.648000001907349</v>
+      </c>
+      <c r="W188" t="n">
+        <v>26859881.41254083</v>
+      </c>
+      <c r="X188" t="n">
+        <v>26859881.41254083</v>
+      </c>
+      <c r="Y188" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD188" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE188" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303191516_dh_0.5_ctax_200_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>21426076.2459629</v>
+      </c>
+      <c r="B189" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0</v>
+      </c>
+      <c r="D189" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E189" t="n">
+        <v>0</v>
+      </c>
+      <c r="F189" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" t="n">
+        <v>258336.8895810759</v>
+      </c>
+      <c r="I189" t="n">
+        <v>-22021514.76718635</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0</v>
+      </c>
+      <c r="K189" t="n">
+        <v>0</v>
+      </c>
+      <c r="L189" t="n">
+        <v>42843694.44250772</v>
+      </c>
+      <c r="M189" t="n">
+        <v>21426076.2459629</v>
+      </c>
+      <c r="N189" t="n">
+        <v>214218.4722125385</v>
+      </c>
+      <c r="O189" t="n">
+        <v>0</v>
+      </c>
+      <c r="P189" t="n">
+        <v>214218.4722125385</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>214218.4722125386</v>
+      </c>
+      <c r="R189" t="n">
+        <v>0</v>
+      </c>
+      <c r="S189" t="n">
+        <v>0</v>
+      </c>
+      <c r="T189" t="n">
+        <v>0</v>
+      </c>
+      <c r="U189" t="n">
+        <v>0</v>
+      </c>
+      <c r="V189" t="n">
+        <v>1.526000022888184</v>
+      </c>
+      <c r="W189" t="n">
+        <v>21426076.24596276</v>
+      </c>
+      <c r="X189" t="n">
+        <v>21426076.2459629</v>
+      </c>
+      <c r="Y189" t="n">
+        <v>1.378357410430908e-07</v>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC189" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD189" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303191706_dh_0.5_ctax_200_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>15829633.97238819</v>
+      </c>
+      <c r="B190" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0</v>
+      </c>
+      <c r="D190" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" t="n">
+        <v>741276.9201512345</v>
+      </c>
+      <c r="I190" t="n">
+        <v>-28547616.59960862</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" t="n">
+        <v>0</v>
+      </c>
+      <c r="L190" t="n">
+        <v>43290413.97078513</v>
+      </c>
+      <c r="M190" t="n">
+        <v>15829633.97238819</v>
+      </c>
+      <c r="N190" t="n">
+        <v>216452.0698539255</v>
+      </c>
+      <c r="O190" t="n">
+        <v>0</v>
+      </c>
+      <c r="P190" t="n">
+        <v>216452.0698539255</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>216452.0698539256</v>
+      </c>
+      <c r="R190" t="n">
+        <v>0</v>
+      </c>
+      <c r="S190" t="n">
+        <v>0</v>
+      </c>
+      <c r="T190" t="n">
+        <v>0</v>
+      </c>
+      <c r="U190" t="n">
+        <v>0</v>
+      </c>
+      <c r="V190" t="n">
+        <v>1.58899998664856</v>
+      </c>
+      <c r="W190" t="n">
+        <v>15829633.97238819</v>
+      </c>
+      <c r="X190" t="n">
+        <v>15829633.97238819</v>
+      </c>
+      <c r="Y190" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC190" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD190" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303191853_dh_0.5_ctax_200_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>10015193.2898675</v>
+      </c>
+      <c r="B191" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0</v>
+      </c>
+      <c r="D191" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" t="n">
+        <v>1355408.143731272</v>
+      </c>
+      <c r="I191" t="n">
+        <v>-35544259.88752087</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0</v>
+      </c>
+      <c r="K191" t="n">
+        <v>0</v>
+      </c>
+      <c r="L191" t="n">
+        <v>43858485.35259665</v>
+      </c>
+      <c r="M191" t="n">
+        <v>10015193.2898675</v>
+      </c>
+      <c r="N191" t="n">
+        <v>219292.4267629832</v>
+      </c>
+      <c r="O191" t="n">
+        <v>0</v>
+      </c>
+      <c r="P191" t="n">
+        <v>219292.4267629832</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>219292.4267629832</v>
+      </c>
+      <c r="R191" t="n">
+        <v>0</v>
+      </c>
+      <c r="S191" t="n">
+        <v>0</v>
+      </c>
+      <c r="T191" t="n">
+        <v>0</v>
+      </c>
+      <c r="U191" t="n">
+        <v>0</v>
+      </c>
+      <c r="V191" t="n">
+        <v>1.546999931335449</v>
+      </c>
+      <c r="W191" t="n">
+        <v>10015193.28986724</v>
+      </c>
+      <c r="X191" t="n">
+        <v>10015193.2898675</v>
+      </c>
+      <c r="Y191" t="n">
+        <v>2.60770320892334e-07</v>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB191" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC191" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD191" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303192042_dh_0.5_ctax_200_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>4016596.377110831</v>
+      </c>
+      <c r="B192" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C192" t="n">
+        <v>0</v>
+      </c>
+      <c r="D192" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E192" t="n">
+        <v>0</v>
+      </c>
+      <c r="F192" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" t="n">
+        <v>1785665.021901865</v>
+      </c>
+      <c r="I192" t="n">
+        <v>-42371101.29075594</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" t="n">
+        <v>44256472.96490446</v>
+      </c>
+      <c r="M192" t="n">
+        <v>4016596.377110831</v>
+      </c>
+      <c r="N192" t="n">
+        <v>221282.3648245222</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0</v>
+      </c>
+      <c r="P192" t="n">
+        <v>221282.3648245222</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>221282.3648245222</v>
+      </c>
+      <c r="R192" t="n">
+        <v>0</v>
+      </c>
+      <c r="S192" t="n">
+        <v>0</v>
+      </c>
+      <c r="T192" t="n">
+        <v>0</v>
+      </c>
+      <c r="U192" t="n">
+        <v>0</v>
+      </c>
+      <c r="V192" t="n">
+        <v>1.651999950408936</v>
+      </c>
+      <c r="W192" t="n">
+        <v>4016596.377110831</v>
+      </c>
+      <c r="X192" t="n">
+        <v>4016596.377110831</v>
+      </c>
+      <c r="Y192" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC192" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD192" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303192429_dh_0.5_ctax_200_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>-2062051.013089806</v>
+      </c>
+      <c r="B193" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C193" t="n">
+        <v>0</v>
+      </c>
+      <c r="D193" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E193" t="n">
+        <v>0</v>
+      </c>
+      <c r="F193" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" t="n">
+        <v>1953601.967314534</v>
+      </c>
+      <c r="I193" t="n">
+        <v>-48773027.30087596</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" t="n">
+        <v>44411814.63941117</v>
+      </c>
+      <c r="M193" t="n">
+        <v>-2062051.013089806</v>
+      </c>
+      <c r="N193" t="n">
+        <v>222059.0731970558</v>
+      </c>
+      <c r="O193" t="n">
+        <v>0</v>
+      </c>
+      <c r="P193" t="n">
+        <v>222059.0731970558</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>222059.0731970558</v>
+      </c>
+      <c r="R193" t="n">
+        <v>0</v>
+      </c>
+      <c r="S193" t="n">
+        <v>0</v>
+      </c>
+      <c r="T193" t="n">
+        <v>0</v>
+      </c>
+      <c r="U193" t="n">
+        <v>0</v>
+      </c>
+      <c r="V193" t="n">
+        <v>1.523000001907349</v>
+      </c>
+      <c r="W193" t="n">
+        <v>-2062051.013089807</v>
+      </c>
+      <c r="X193" t="n">
+        <v>-2062051.013089806</v>
+      </c>
+      <c r="Y193" t="n">
+        <v>9.313225746154785e-10</v>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC193" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303192616_dh_0.5_ctax_200_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>48241934.76623576</v>
+      </c>
+      <c r="B194" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C194" t="n">
+        <v>0</v>
+      </c>
+      <c r="D194" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E194" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+      <c r="H194" t="n">
+        <v>155.0546472912404</v>
+      </c>
+      <c r="I194" t="n">
+        <v>-5359875.275964418</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" t="n">
+        <v>53256095.30649244</v>
+      </c>
+      <c r="M194" t="n">
+        <v>48241934.76623576</v>
+      </c>
+      <c r="N194" t="n">
+        <v>213024.3812259698</v>
+      </c>
+      <c r="O194" t="n">
+        <v>0</v>
+      </c>
+      <c r="P194" t="n">
+        <v>213024.3812259698</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>213024.3812259698</v>
+      </c>
+      <c r="R194" t="n">
+        <v>0</v>
+      </c>
+      <c r="S194" t="n">
+        <v>0</v>
+      </c>
+      <c r="T194" t="n">
+        <v>0</v>
+      </c>
+      <c r="U194" t="n">
+        <v>0</v>
+      </c>
+      <c r="V194" t="n">
+        <v>1.529999971389771</v>
+      </c>
+      <c r="W194" t="n">
+        <v>48241934.7662353</v>
+      </c>
+      <c r="X194" t="n">
+        <v>48241934.76623576</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>4.619359970092773e-07</v>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD194" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303192803_dh_0.5_ctax_250_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>42882059.49027134</v>
+      </c>
+      <c r="B195" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0</v>
+      </c>
+      <c r="D195" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E195" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" t="n">
+        <v>155.0546472912404</v>
+      </c>
+      <c r="I195" t="n">
+        <v>-10719750.55192884</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K195" t="n">
+        <v>0</v>
+      </c>
+      <c r="L195" t="n">
+        <v>53256095.30649244</v>
+      </c>
+      <c r="M195" t="n">
+        <v>42882059.49027134</v>
+      </c>
+      <c r="N195" t="n">
+        <v>213024.3812259698</v>
+      </c>
+      <c r="O195" t="n">
+        <v>0</v>
+      </c>
+      <c r="P195" t="n">
+        <v>213024.3812259698</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>213024.3812259698</v>
+      </c>
+      <c r="R195" t="n">
+        <v>0</v>
+      </c>
+      <c r="S195" t="n">
+        <v>0</v>
+      </c>
+      <c r="T195" t="n">
+        <v>0</v>
+      </c>
+      <c r="U195" t="n">
+        <v>0</v>
+      </c>
+      <c r="V195" t="n">
+        <v>1.523000001907349</v>
+      </c>
+      <c r="W195" t="n">
+        <v>42882059.49027134</v>
+      </c>
+      <c r="X195" t="n">
+        <v>42882059.49027134</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD195" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303192950_dh_0.5_ctax_250_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>37516744.16002905</v>
+      </c>
+      <c r="B196" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C196" t="n">
+        <v>0</v>
+      </c>
+      <c r="D196" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E196" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="n">
+        <v>17022.10600403212</v>
+      </c>
+      <c r="I196" t="n">
+        <v>-16121435.4616591</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" t="n">
+        <v>0</v>
+      </c>
+      <c r="L196" t="n">
+        <v>53275597.83462367</v>
+      </c>
+      <c r="M196" t="n">
+        <v>37516744.16002905</v>
+      </c>
+      <c r="N196" t="n">
+        <v>213102.3913384947</v>
+      </c>
+      <c r="O196" t="n">
+        <v>0</v>
+      </c>
+      <c r="P196" t="n">
+        <v>213102.3913384947</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>213102.3913384947</v>
+      </c>
+      <c r="R196" t="n">
+        <v>0</v>
+      </c>
+      <c r="S196" t="n">
+        <v>0</v>
+      </c>
+      <c r="T196" t="n">
+        <v>0</v>
+      </c>
+      <c r="U196" t="n">
+        <v>0</v>
+      </c>
+      <c r="V196" t="n">
+        <v>1.559999942779541</v>
+      </c>
+      <c r="W196" t="n">
+        <v>37516744.16002876</v>
+      </c>
+      <c r="X196" t="n">
+        <v>37516744.16002905</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>2.905726432800293e-07</v>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC196" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD196" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303193137_dh_0.5_ctax_250_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>32121607.49167487</v>
+      </c>
+      <c r="B197" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C197" t="n">
+        <v>0</v>
+      </c>
+      <c r="D197" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E197" t="n">
+        <v>0</v>
+      </c>
+      <c r="F197" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" t="n">
+        <v>124767.6003512254</v>
+      </c>
+      <c r="I197" t="n">
+        <v>-21748898.35219942</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" t="n">
+        <v>53400178.56246262</v>
+      </c>
+      <c r="M197" t="n">
+        <v>32121607.49167487</v>
+      </c>
+      <c r="N197" t="n">
+        <v>213600.7142498505</v>
+      </c>
+      <c r="O197" t="n">
+        <v>0</v>
+      </c>
+      <c r="P197" t="n">
+        <v>213600.7142498505</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>213600.7142498505</v>
+      </c>
+      <c r="R197" t="n">
+        <v>0</v>
+      </c>
+      <c r="S197" t="n">
+        <v>0</v>
+      </c>
+      <c r="T197" t="n">
+        <v>0</v>
+      </c>
+      <c r="U197" t="n">
+        <v>0</v>
+      </c>
+      <c r="V197" t="n">
+        <v>1.553999900817871</v>
+      </c>
+      <c r="W197" t="n">
+        <v>32121607.49167449</v>
+      </c>
+      <c r="X197" t="n">
+        <v>32121607.49167487</v>
+      </c>
+      <c r="Y197" t="n">
+        <v>3.874301910400391e-07</v>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC197" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD197" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303193550_dh_0.5_ctax_250_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>26612206.66289517</v>
+      </c>
+      <c r="B198" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C198" t="n">
+        <v>0</v>
+      </c>
+      <c r="D198" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E198" t="n">
+        <v>0</v>
+      </c>
+      <c r="F198" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="n">
+        <v>432120.8995392584</v>
+      </c>
+      <c r="I198" t="n">
+        <v>-27921029.73235332</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" t="n">
+        <v>0</v>
+      </c>
+      <c r="L198" t="n">
+        <v>53755555.81464878</v>
+      </c>
+      <c r="M198" t="n">
+        <v>26612206.66289517</v>
+      </c>
+      <c r="N198" t="n">
+        <v>215022.2232585951</v>
+      </c>
+      <c r="O198" t="n">
+        <v>0</v>
+      </c>
+      <c r="P198" t="n">
+        <v>215022.2232585951</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>215022.2232585952</v>
+      </c>
+      <c r="R198" t="n">
+        <v>0</v>
+      </c>
+      <c r="S198" t="n">
+        <v>0</v>
+      </c>
+      <c r="T198" t="n">
+        <v>0</v>
+      </c>
+      <c r="U198" t="n">
+        <v>0</v>
+      </c>
+      <c r="V198" t="n">
+        <v>1.556999921798706</v>
+      </c>
+      <c r="W198" t="n">
+        <v>26612206.66289499</v>
+      </c>
+      <c r="X198" t="n">
+        <v>26612206.66289517</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>1.825392246246338e-07</v>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC198" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD198" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303193737_dh_0.5_ctax_250_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>20928591.1067262</v>
+      </c>
+      <c r="B199" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C199" t="n">
+        <v>0</v>
+      </c>
+      <c r="D199" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E199" t="n">
+        <v>0</v>
+      </c>
+      <c r="F199" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="n">
+        <v>925534.8617191213</v>
+      </c>
+      <c r="I199" t="n">
+        <v>-34668569.14447261</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" t="n">
+        <v>54326065.70841925</v>
+      </c>
+      <c r="M199" t="n">
+        <v>20928591.1067262</v>
+      </c>
+      <c r="N199" t="n">
+        <v>217304.262833677</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0</v>
+      </c>
+      <c r="P199" t="n">
+        <v>217304.262833677</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>217304.262833677</v>
+      </c>
+      <c r="R199" t="n">
+        <v>0</v>
+      </c>
+      <c r="S199" t="n">
+        <v>0</v>
+      </c>
+      <c r="T199" t="n">
+        <v>0</v>
+      </c>
+      <c r="U199" t="n">
+        <v>0</v>
+      </c>
+      <c r="V199" t="n">
+        <v>1.657000064849854</v>
+      </c>
+      <c r="W199" t="n">
+        <v>20928591.10672571</v>
+      </c>
+      <c r="X199" t="n">
+        <v>20928591.1067262</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>4.954636096954346e-07</v>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC199" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303193923_dh_0.5_ctax_250_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>15048394.76819916</v>
+      </c>
+      <c r="B200" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C200" t="n">
+        <v>0</v>
+      </c>
+      <c r="D200" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E200" t="n">
+        <v>0</v>
+      </c>
+      <c r="F200" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="n">
+        <v>1516134.934118922</v>
+      </c>
+      <c r="I200" t="n">
+        <v>-41822246.88911173</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" t="n">
+        <v>0</v>
+      </c>
+      <c r="L200" t="n">
+        <v>55008947.04213152</v>
+      </c>
+      <c r="M200" t="n">
+        <v>15048394.76819916</v>
+      </c>
+      <c r="N200" t="n">
+        <v>220035.7881685261</v>
+      </c>
+      <c r="O200" t="n">
+        <v>0</v>
+      </c>
+      <c r="P200" t="n">
+        <v>220035.7881685261</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>220035.7881685261</v>
+      </c>
+      <c r="R200" t="n">
+        <v>0</v>
+      </c>
+      <c r="S200" t="n">
+        <v>0</v>
+      </c>
+      <c r="T200" t="n">
+        <v>0</v>
+      </c>
+      <c r="U200" t="n">
+        <v>0</v>
+      </c>
+      <c r="V200" t="n">
+        <v>1.631999969482422</v>
+      </c>
+      <c r="W200" t="n">
+        <v>15048394.76819916</v>
+      </c>
+      <c r="X200" t="n">
+        <v>15048394.76819916</v>
+      </c>
+      <c r="Y200" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC200" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD200" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303194114_dh_0.5_ctax_250_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>9026728.141834624</v>
+      </c>
+      <c r="B201" t="n">
+        <v>298.9250021439932</v>
+      </c>
+      <c r="C201" t="n">
+        <v>0</v>
+      </c>
+      <c r="D201" t="n">
+        <v>345260.7560583042</v>
+      </c>
+      <c r="E201" t="n">
+        <v>0</v>
+      </c>
+      <c r="F201" t="n">
+        <v>345559.6810604482</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" t="n">
+        <v>1826239.049474173</v>
+      </c>
+      <c r="I201" t="n">
+        <v>-48512575.51421103</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" t="n">
+        <v>0</v>
+      </c>
+      <c r="L201" t="n">
+        <v>55367504.92551103</v>
+      </c>
+      <c r="M201" t="n">
+        <v>9026728.141834624</v>
+      </c>
+      <c r="N201" t="n">
+        <v>221470.0197020441</v>
+      </c>
+      <c r="O201" t="n">
+        <v>0</v>
+      </c>
+      <c r="P201" t="n">
+        <v>221470.0197020441</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>221470.0197020441</v>
+      </c>
+      <c r="R201" t="n">
+        <v>0</v>
+      </c>
+      <c r="S201" t="n">
+        <v>0</v>
+      </c>
+      <c r="T201" t="n">
+        <v>0</v>
+      </c>
+      <c r="U201" t="n">
+        <v>0</v>
+      </c>
+      <c r="V201" t="n">
+        <v>1.555999994277954</v>
+      </c>
+      <c r="W201" t="n">
+        <v>9026728.14183452</v>
+      </c>
+      <c r="X201" t="n">
+        <v>9026728.141834624</v>
+      </c>
+      <c r="Y201" t="n">
+        <v>1.043081283569336e-07</v>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC201" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD201" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303194302_dh_0.5_ctax_250_el_price_400</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_WtE/raw_results/technology_selection/Summary.xlsx
+++ b/dataCaseStudy_WtE/raw_results/technology_selection/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE201"/>
+  <dimension ref="A1:AE265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21182,6 +21182,6598 @@
       <c r="AE201" t="inlineStr">
         <is>
           <t>dataCaseStudy_WtE\raw_results\technology_selection\20260303194302_dh_0.5_ctax_250_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>10671989.399703</v>
+      </c>
+      <c r="B202" t="n">
+        <v>3929731.163454658</v>
+      </c>
+      <c r="C202" t="n">
+        <v>3271845.116526119</v>
+      </c>
+      <c r="D202" t="n">
+        <v>3665529.733313536</v>
+      </c>
+      <c r="E202" t="n">
+        <v>0</v>
+      </c>
+      <c r="F202" t="n">
+        <v>7595260.896768194</v>
+      </c>
+      <c r="G202" t="n">
+        <v>3271845.116526119</v>
+      </c>
+      <c r="H202" t="n">
+        <v>0</v>
+      </c>
+      <c r="I202" t="n">
+        <v>-2628486.4274322</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0</v>
+      </c>
+      <c r="K202" t="n">
+        <v>0</v>
+      </c>
+      <c r="L202" t="n">
+        <v>2433369.813840889</v>
+      </c>
+      <c r="M202" t="n">
+        <v>10671989.399703</v>
+      </c>
+      <c r="N202" t="n">
+        <v>24336.05676298326</v>
+      </c>
+      <c r="O202" t="n">
+        <v>0</v>
+      </c>
+      <c r="P202" t="n">
+        <v>24336.05676298326</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>24333.69813840888</v>
+      </c>
+      <c r="R202" t="n">
+        <v>0</v>
+      </c>
+      <c r="S202" t="n">
+        <v>0</v>
+      </c>
+      <c r="T202" t="n">
+        <v>0</v>
+      </c>
+      <c r="U202" t="n">
+        <v>2.358624574497713</v>
+      </c>
+      <c r="V202" t="n">
+        <v>11.73799991607666</v>
+      </c>
+      <c r="W202" t="n">
+        <v>10671989.399703</v>
+      </c>
+      <c r="X202" t="n">
+        <v>10671989.399703</v>
+      </c>
+      <c r="Y202" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC202" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409185052_dh_0.5_ctax_100_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>7692927.423242366</v>
+      </c>
+      <c r="B203" t="n">
+        <v>0</v>
+      </c>
+      <c r="C203" t="n">
+        <v>0</v>
+      </c>
+      <c r="D203" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E203" t="n">
+        <v>0</v>
+      </c>
+      <c r="F203" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" t="n">
+        <v>16087.92112087848</v>
+      </c>
+      <c r="I203" t="n">
+        <v>-14068696.34301499</v>
+      </c>
+      <c r="J203" t="n">
+        <v>0</v>
+      </c>
+      <c r="K203" t="n">
+        <v>0</v>
+      </c>
+      <c r="L203" t="n">
+        <v>21309807.07334101</v>
+      </c>
+      <c r="M203" t="n">
+        <v>7692927.423242366</v>
+      </c>
+      <c r="N203" t="n">
+        <v>213098.07073341</v>
+      </c>
+      <c r="O203" t="n">
+        <v>0</v>
+      </c>
+      <c r="P203" t="n">
+        <v>213098.07073341</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>213098.07073341</v>
+      </c>
+      <c r="R203" t="n">
+        <v>0</v>
+      </c>
+      <c r="S203" t="n">
+        <v>0</v>
+      </c>
+      <c r="T203" t="n">
+        <v>0</v>
+      </c>
+      <c r="U203" t="n">
+        <v>0</v>
+      </c>
+      <c r="V203" t="n">
+        <v>12.59200000762939</v>
+      </c>
+      <c r="W203" t="n">
+        <v>7692927.423242366</v>
+      </c>
+      <c r="X203" t="n">
+        <v>7692927.423242366</v>
+      </c>
+      <c r="Y203" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC203" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409185329_dh_0.5_ctax_100_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>616427.8433460556</v>
+      </c>
+      <c r="B204" t="n">
+        <v>0</v>
+      </c>
+      <c r="C204" t="n">
+        <v>0</v>
+      </c>
+      <c r="D204" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E204" t="n">
+        <v>0</v>
+      </c>
+      <c r="F204" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" t="n">
+        <v>250352.7371741842</v>
+      </c>
+      <c r="I204" t="n">
+        <v>-21487808.21638926</v>
+      </c>
+      <c r="J204" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" t="n">
+        <v>0</v>
+      </c>
+      <c r="L204" t="n">
+        <v>21418154.55076566</v>
+      </c>
+      <c r="M204" t="n">
+        <v>616427.8433460556</v>
+      </c>
+      <c r="N204" t="n">
+        <v>214181.5455076566</v>
+      </c>
+      <c r="O204" t="n">
+        <v>0</v>
+      </c>
+      <c r="P204" t="n">
+        <v>214181.5455076566</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>214181.5455076566</v>
+      </c>
+      <c r="R204" t="n">
+        <v>0</v>
+      </c>
+      <c r="S204" t="n">
+        <v>0</v>
+      </c>
+      <c r="T204" t="n">
+        <v>0</v>
+      </c>
+      <c r="U204" t="n">
+        <v>0</v>
+      </c>
+      <c r="V204" t="n">
+        <v>4.540999889373779</v>
+      </c>
+      <c r="W204" t="n">
+        <v>616427.8433459736</v>
+      </c>
+      <c r="X204" t="n">
+        <v>616427.8433460556</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>8.195638656616211e-08</v>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC204" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD204" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409185559_dh_0.5_ctax_100_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>-6664264.485831395</v>
+      </c>
+      <c r="B205" t="n">
+        <v>0</v>
+      </c>
+      <c r="C205" t="n">
+        <v>0</v>
+      </c>
+      <c r="D205" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E205" t="n">
+        <v>0</v>
+      </c>
+      <c r="F205" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" t="n">
+        <v>871463.3829878251</v>
+      </c>
+      <c r="I205" t="n">
+        <v>-29676874.86506916</v>
+      </c>
+      <c r="J205" t="n">
+        <v>0</v>
+      </c>
+      <c r="K205" t="n">
+        <v>0</v>
+      </c>
+      <c r="L205" t="n">
+        <v>21705418.22445447</v>
+      </c>
+      <c r="M205" t="n">
+        <v>-6664264.485831395</v>
+      </c>
+      <c r="N205" t="n">
+        <v>217054.1822445446</v>
+      </c>
+      <c r="O205" t="n">
+        <v>0</v>
+      </c>
+      <c r="P205" t="n">
+        <v>217054.1822445446</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>217054.1822445447</v>
+      </c>
+      <c r="R205" t="n">
+        <v>0</v>
+      </c>
+      <c r="S205" t="n">
+        <v>0</v>
+      </c>
+      <c r="T205" t="n">
+        <v>0</v>
+      </c>
+      <c r="U205" t="n">
+        <v>0</v>
+      </c>
+      <c r="V205" t="n">
+        <v>4.621000051498413</v>
+      </c>
+      <c r="W205" t="n">
+        <v>-6664264.485831395</v>
+      </c>
+      <c r="X205" t="n">
+        <v>-6664264.485831395</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC205" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409185830_dh_0.5_ctax_100_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>-14223105.46445471</v>
+      </c>
+      <c r="B206" t="n">
+        <v>0</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0</v>
+      </c>
+      <c r="D206" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E206" t="n">
+        <v>0</v>
+      </c>
+      <c r="F206" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0</v>
+      </c>
+      <c r="H206" t="n">
+        <v>1637043.526087382</v>
+      </c>
+      <c r="I206" t="n">
+        <v>-38355376.80297558</v>
+      </c>
+      <c r="J206" t="n">
+        <v>0</v>
+      </c>
+      <c r="K206" t="n">
+        <v>0</v>
+      </c>
+      <c r="L206" t="n">
+        <v>22059499.04063802</v>
+      </c>
+      <c r="M206" t="n">
+        <v>-14223105.46445471</v>
+      </c>
+      <c r="N206" t="n">
+        <v>220594.9904063801</v>
+      </c>
+      <c r="O206" t="n">
+        <v>0</v>
+      </c>
+      <c r="P206" t="n">
+        <v>220594.9904063801</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>220594.9904063801</v>
+      </c>
+      <c r="R206" t="n">
+        <v>0</v>
+      </c>
+      <c r="S206" t="n">
+        <v>0</v>
+      </c>
+      <c r="T206" t="n">
+        <v>0</v>
+      </c>
+      <c r="U206" t="n">
+        <v>0</v>
+      </c>
+      <c r="V206" t="n">
+        <v>4.361000061035156</v>
+      </c>
+      <c r="W206" t="n">
+        <v>-14223105.46445471</v>
+      </c>
+      <c r="X206" t="n">
+        <v>-14223105.46445471</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409190051_dh_0.5_ctax_100_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>-21942439.48836367</v>
+      </c>
+      <c r="B207" t="n">
+        <v>0</v>
+      </c>
+      <c r="C207" t="n">
+        <v>0</v>
+      </c>
+      <c r="D207" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E207" t="n">
+        <v>0</v>
+      </c>
+      <c r="F207" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" t="n">
+        <v>1931930.186764378</v>
+      </c>
+      <c r="I207" t="n">
+        <v>-46505982.56812464</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" t="n">
+        <v>0</v>
+      </c>
+      <c r="L207" t="n">
+        <v>22195884.12120113</v>
+      </c>
+      <c r="M207" t="n">
+        <v>-21942439.48836367</v>
+      </c>
+      <c r="N207" t="n">
+        <v>221958.8412120113</v>
+      </c>
+      <c r="O207" t="n">
+        <v>0</v>
+      </c>
+      <c r="P207" t="n">
+        <v>221958.8412120113</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>221958.8412120112</v>
+      </c>
+      <c r="R207" t="n">
+        <v>0</v>
+      </c>
+      <c r="S207" t="n">
+        <v>0</v>
+      </c>
+      <c r="T207" t="n">
+        <v>0</v>
+      </c>
+      <c r="U207" t="n">
+        <v>0</v>
+      </c>
+      <c r="V207" t="n">
+        <v>4.648000001907349</v>
+      </c>
+      <c r="W207" t="n">
+        <v>-21942439.48836367</v>
+      </c>
+      <c r="X207" t="n">
+        <v>-21942439.48836367</v>
+      </c>
+      <c r="Y207" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409190317_dh_0.5_ctax_100_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>-29708118.43058869</v>
+      </c>
+      <c r="B208" t="n">
+        <v>0</v>
+      </c>
+      <c r="C208" t="n">
+        <v>0</v>
+      </c>
+      <c r="D208" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="n">
+        <v>2049307.205451946</v>
+      </c>
+      <c r="I208" t="n">
+        <v>-54443325.40018023</v>
+      </c>
+      <c r="J208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" t="n">
+        <v>0</v>
+      </c>
+      <c r="L208" t="n">
+        <v>22250170.99234413</v>
+      </c>
+      <c r="M208" t="n">
+        <v>-29708118.43058869</v>
+      </c>
+      <c r="N208" t="n">
+        <v>222501.7099234413</v>
+      </c>
+      <c r="O208" t="n">
+        <v>0</v>
+      </c>
+      <c r="P208" t="n">
+        <v>222501.7099234413</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>222501.7099234412</v>
+      </c>
+      <c r="R208" t="n">
+        <v>0</v>
+      </c>
+      <c r="S208" t="n">
+        <v>0</v>
+      </c>
+      <c r="T208" t="n">
+        <v>0</v>
+      </c>
+      <c r="U208" t="n">
+        <v>0</v>
+      </c>
+      <c r="V208" t="n">
+        <v>5.531000137329102</v>
+      </c>
+      <c r="W208" t="n">
+        <v>-29708118.43058869</v>
+      </c>
+      <c r="X208" t="n">
+        <v>-29708118.43058869</v>
+      </c>
+      <c r="Y208" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC208" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409190547_dh_0.5_ctax_100_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>-37489730.88745569</v>
+      </c>
+      <c r="B209" t="n">
+        <v>0</v>
+      </c>
+      <c r="C209" t="n">
+        <v>0</v>
+      </c>
+      <c r="D209" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E209" t="n">
+        <v>0</v>
+      </c>
+      <c r="F209" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" t="n">
+        <v>2081367.532328885</v>
+      </c>
+      <c r="I209" t="n">
+        <v>-62271826.08510476</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0</v>
+      </c>
+      <c r="L209" t="n">
+        <v>22264998.89352471</v>
+      </c>
+      <c r="M209" t="n">
+        <v>-37489730.88745569</v>
+      </c>
+      <c r="N209" t="n">
+        <v>222649.9889352471</v>
+      </c>
+      <c r="O209" t="n">
+        <v>0</v>
+      </c>
+      <c r="P209" t="n">
+        <v>222649.9889352471</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>222649.9889352471</v>
+      </c>
+      <c r="R209" t="n">
+        <v>0</v>
+      </c>
+      <c r="S209" t="n">
+        <v>0</v>
+      </c>
+      <c r="T209" t="n">
+        <v>0</v>
+      </c>
+      <c r="U209" t="n">
+        <v>0</v>
+      </c>
+      <c r="V209" t="n">
+        <v>5.409999847412109</v>
+      </c>
+      <c r="W209" t="n">
+        <v>-37489730.88745569</v>
+      </c>
+      <c r="X209" t="n">
+        <v>-37489730.88745569</v>
+      </c>
+      <c r="Y209" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC209" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409190824_dh_0.5_ctax_100_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>11820772.52045355</v>
+      </c>
+      <c r="B210" t="n">
+        <v>3997859.377765794</v>
+      </c>
+      <c r="C210" t="n">
+        <v>3303850.926371455</v>
+      </c>
+      <c r="D210" t="n">
+        <v>3713055.68275591</v>
+      </c>
+      <c r="E210" t="n">
+        <v>0</v>
+      </c>
+      <c r="F210" t="n">
+        <v>7710915.060521705</v>
+      </c>
+      <c r="G210" t="n">
+        <v>3303850.926371455</v>
+      </c>
+      <c r="H210" t="n">
+        <v>37234.21128322011</v>
+      </c>
+      <c r="I210" t="n">
+        <v>-2590432.704115328</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" t="n">
+        <v>0</v>
+      </c>
+      <c r="L210" t="n">
+        <v>3359205.026392499</v>
+      </c>
+      <c r="M210" t="n">
+        <v>11820772.52045355</v>
+      </c>
+      <c r="N210" t="n">
+        <v>22397.08519060196</v>
+      </c>
+      <c r="O210" t="n">
+        <v>0</v>
+      </c>
+      <c r="P210" t="n">
+        <v>22397.08519060196</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>22394.70017595007</v>
+      </c>
+      <c r="R210" t="n">
+        <v>0</v>
+      </c>
+      <c r="S210" t="n">
+        <v>0</v>
+      </c>
+      <c r="T210" t="n">
+        <v>0</v>
+      </c>
+      <c r="U210" t="n">
+        <v>2.38501465186826</v>
+      </c>
+      <c r="V210" t="n">
+        <v>10.29800009727478</v>
+      </c>
+      <c r="W210" t="n">
+        <v>11820772.52045355</v>
+      </c>
+      <c r="X210" t="n">
+        <v>11820772.52045355</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409191108_dh_0.5_ctax_150_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>9225368.729848098</v>
+      </c>
+      <c r="B211" t="n">
+        <v>3976456.762358493</v>
+      </c>
+      <c r="C211" t="n">
+        <v>3293795.591849681</v>
+      </c>
+      <c r="D211" t="n">
+        <v>3700067.044498175</v>
+      </c>
+      <c r="E211" t="n">
+        <v>0</v>
+      </c>
+      <c r="F211" t="n">
+        <v>7676523.806856668</v>
+      </c>
+      <c r="G211" t="n">
+        <v>3293795.591849681</v>
+      </c>
+      <c r="H211" t="n">
+        <v>46513.99660724854</v>
+      </c>
+      <c r="I211" t="n">
+        <v>-5216704.094700267</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" t="n">
+        <v>0</v>
+      </c>
+      <c r="L211" t="n">
+        <v>3425239.429234767</v>
+      </c>
+      <c r="M211" t="n">
+        <v>9225368.729848098</v>
+      </c>
+      <c r="N211" t="n">
+        <v>22837.30957650436</v>
+      </c>
+      <c r="O211" t="n">
+        <v>0</v>
+      </c>
+      <c r="P211" t="n">
+        <v>22837.30957650436</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>22834.9295282317</v>
+      </c>
+      <c r="R211" t="n">
+        <v>0</v>
+      </c>
+      <c r="S211" t="n">
+        <v>0</v>
+      </c>
+      <c r="T211" t="n">
+        <v>0</v>
+      </c>
+      <c r="U211" t="n">
+        <v>2.380048272553785</v>
+      </c>
+      <c r="V211" t="n">
+        <v>10.1159999370575</v>
+      </c>
+      <c r="W211" t="n">
+        <v>9225368.729848098</v>
+      </c>
+      <c r="X211" t="n">
+        <v>9225368.729848098</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409191319_dh_0.5_ctax_150_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>6563905.329636291</v>
+      </c>
+      <c r="B212" t="n">
+        <v>3931979.015164822</v>
+      </c>
+      <c r="C212" t="n">
+        <v>3272901.090348371</v>
+      </c>
+      <c r="D212" t="n">
+        <v>3671133.545451759</v>
+      </c>
+      <c r="E212" t="n">
+        <v>0</v>
+      </c>
+      <c r="F212" t="n">
+        <v>7603112.560616582</v>
+      </c>
+      <c r="G212" t="n">
+        <v>3272901.090348371</v>
+      </c>
+      <c r="H212" t="n">
+        <v>291926.0130670846</v>
+      </c>
+      <c r="I212" t="n">
+        <v>-8363237.820038021</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" t="n">
+        <v>0</v>
+      </c>
+      <c r="L212" t="n">
+        <v>3759203.485642273</v>
+      </c>
+      <c r="M212" t="n">
+        <v>6563905.329636291</v>
+      </c>
+      <c r="N212" t="n">
+        <v>25063.72297676516</v>
+      </c>
+      <c r="O212" t="n">
+        <v>0</v>
+      </c>
+      <c r="P212" t="n">
+        <v>25063.72297676516</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>25061.35657094863</v>
+      </c>
+      <c r="R212" t="n">
+        <v>0</v>
+      </c>
+      <c r="S212" t="n">
+        <v>0</v>
+      </c>
+      <c r="T212" t="n">
+        <v>0</v>
+      </c>
+      <c r="U212" t="n">
+        <v>2.366405816721408</v>
+      </c>
+      <c r="V212" t="n">
+        <v>10.80599999427795</v>
+      </c>
+      <c r="W212" t="n">
+        <v>6563905.329636291</v>
+      </c>
+      <c r="X212" t="n">
+        <v>6563905.329636291</v>
+      </c>
+      <c r="Y212" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC212" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD212" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409191617_dh_0.5_ctax_150_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>3374570.251458642</v>
+      </c>
+      <c r="B213" t="n">
+        <v>3867077.615875191</v>
+      </c>
+      <c r="C213" t="n">
+        <v>3242410.94747646</v>
+      </c>
+      <c r="D213" t="n">
+        <v>3623924.721897461</v>
+      </c>
+      <c r="E213" t="n">
+        <v>0</v>
+      </c>
+      <c r="F213" t="n">
+        <v>7491002.337772653</v>
+      </c>
+      <c r="G213" t="n">
+        <v>3242410.94747646</v>
+      </c>
+      <c r="H213" t="n">
+        <v>2088691.024305767</v>
+      </c>
+      <c r="I213" t="n">
+        <v>-14794666.66023103</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="n">
+        <v>0</v>
+      </c>
+      <c r="L213" t="n">
+        <v>5347132.602134789</v>
+      </c>
+      <c r="M213" t="n">
+        <v>3374570.251458642</v>
+      </c>
+      <c r="N213" t="n">
+        <v>35649.88863476644</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0</v>
+      </c>
+      <c r="P213" t="n">
+        <v>35649.88863476644</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>35647.55068089842</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0</v>
+      </c>
+      <c r="S213" t="n">
+        <v>0</v>
+      </c>
+      <c r="T213" t="n">
+        <v>0</v>
+      </c>
+      <c r="U213" t="n">
+        <v>2.337953867559271</v>
+      </c>
+      <c r="V213" t="n">
+        <v>11.54800009727478</v>
+      </c>
+      <c r="W213" t="n">
+        <v>3374570.251458642</v>
+      </c>
+      <c r="X213" t="n">
+        <v>3374570.251458642</v>
+      </c>
+      <c r="Y213" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD213" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409191827_dh_0.5_ctax_150_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>-3248202.711602185</v>
+      </c>
+      <c r="B214" t="n">
+        <v>0</v>
+      </c>
+      <c r="C214" t="n">
+        <v>0</v>
+      </c>
+      <c r="D214" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E214" t="n">
+        <v>0</v>
+      </c>
+      <c r="F214" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" t="n">
+        <v>1137429.25938166</v>
+      </c>
+      <c r="I214" t="n">
+        <v>-37564001.90620925</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" t="n">
+        <v>0</v>
+      </c>
+      <c r="L214" t="n">
+        <v>32742641.16342994</v>
+      </c>
+      <c r="M214" t="n">
+        <v>-3248202.711602185</v>
+      </c>
+      <c r="N214" t="n">
+        <v>218284.2744228661</v>
+      </c>
+      <c r="O214" t="n">
+        <v>0</v>
+      </c>
+      <c r="P214" t="n">
+        <v>218284.2744228661</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>218284.2744228661</v>
+      </c>
+      <c r="R214" t="n">
+        <v>0</v>
+      </c>
+      <c r="S214" t="n">
+        <v>0</v>
+      </c>
+      <c r="T214" t="n">
+        <v>0</v>
+      </c>
+      <c r="U214" t="n">
+        <v>0</v>
+      </c>
+      <c r="V214" t="n">
+        <v>14.19000005722046</v>
+      </c>
+      <c r="W214" t="n">
+        <v>-3248202.711602185</v>
+      </c>
+      <c r="X214" t="n">
+        <v>-3248202.711602185</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD214" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409192038_dh_0.5_ctax_150_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>-10866436.25968079</v>
+      </c>
+      <c r="B215" t="n">
+        <v>0</v>
+      </c>
+      <c r="C215" t="n">
+        <v>0</v>
+      </c>
+      <c r="D215" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0</v>
+      </c>
+      <c r="F215" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="n">
+        <v>1698977.295211495</v>
+      </c>
+      <c r="I215" t="n">
+        <v>-46133357.43997464</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" t="n">
+        <v>0</v>
+      </c>
+      <c r="L215" t="n">
+        <v>33132215.11328689</v>
+      </c>
+      <c r="M215" t="n">
+        <v>-10866436.25968079</v>
+      </c>
+      <c r="N215" t="n">
+        <v>220881.4340885791</v>
+      </c>
+      <c r="O215" t="n">
+        <v>0</v>
+      </c>
+      <c r="P215" t="n">
+        <v>220881.4340885791</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>220881.4340885791</v>
+      </c>
+      <c r="R215" t="n">
+        <v>0</v>
+      </c>
+      <c r="S215" t="n">
+        <v>0</v>
+      </c>
+      <c r="T215" t="n">
+        <v>0</v>
+      </c>
+      <c r="U215" t="n">
+        <v>0</v>
+      </c>
+      <c r="V215" t="n">
+        <v>6.473000049591064</v>
+      </c>
+      <c r="W215" t="n">
+        <v>-10866436.25968079</v>
+      </c>
+      <c r="X215" t="n">
+        <v>-10866436.25968079</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD215" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409192349_dh_0.5_ctax_150_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>-18595519.44406056</v>
+      </c>
+      <c r="B216" t="n">
+        <v>0</v>
+      </c>
+      <c r="C216" t="n">
+        <v>0</v>
+      </c>
+      <c r="D216" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E216" t="n">
+        <v>0</v>
+      </c>
+      <c r="F216" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="n">
+        <v>1937609.692201218</v>
+      </c>
+      <c r="I216" t="n">
+        <v>-54266624.24675574</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" t="n">
+        <v>0</v>
+      </c>
+      <c r="L216" t="n">
+        <v>33297766.33869851</v>
+      </c>
+      <c r="M216" t="n">
+        <v>-18595519.44406056</v>
+      </c>
+      <c r="N216" t="n">
+        <v>221985.1089246566</v>
+      </c>
+      <c r="O216" t="n">
+        <v>0</v>
+      </c>
+      <c r="P216" t="n">
+        <v>221985.1089246566</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>221985.1089246566</v>
+      </c>
+      <c r="R216" t="n">
+        <v>0</v>
+      </c>
+      <c r="S216" t="n">
+        <v>0</v>
+      </c>
+      <c r="T216" t="n">
+        <v>0</v>
+      </c>
+      <c r="U216" t="n">
+        <v>0</v>
+      </c>
+      <c r="V216" t="n">
+        <v>7.295000076293945</v>
+      </c>
+      <c r="W216" t="n">
+        <v>-18595519.44406056</v>
+      </c>
+      <c r="X216" t="n">
+        <v>-18595519.44406056</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC216" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD216" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409192553_dh_0.5_ctax_150_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>-27658000.62926254</v>
+      </c>
+      <c r="B217" t="n">
+        <v>31226380.04370679</v>
+      </c>
+      <c r="C217" t="n">
+        <v>4400143.355196329</v>
+      </c>
+      <c r="D217" t="n">
+        <v>22393383.94098206</v>
+      </c>
+      <c r="E217" t="n">
+        <v>0</v>
+      </c>
+      <c r="F217" t="n">
+        <v>53619763.98468885</v>
+      </c>
+      <c r="G217" t="n">
+        <v>4400143.355196329</v>
+      </c>
+      <c r="H217" t="n">
+        <v>4613404.555365955</v>
+      </c>
+      <c r="I217" t="n">
+        <v>-97993469.70867887</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" t="n">
+        <v>0</v>
+      </c>
+      <c r="L217" t="n">
+        <v>7702157.184165204</v>
+      </c>
+      <c r="M217" t="n">
+        <v>-27658000.62926254</v>
+      </c>
+      <c r="N217" t="n">
+        <v>51352.50043396534</v>
+      </c>
+      <c r="O217" t="n">
+        <v>0</v>
+      </c>
+      <c r="P217" t="n">
+        <v>51352.50043396534</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>51347.71456110029</v>
+      </c>
+      <c r="R217" t="n">
+        <v>0</v>
+      </c>
+      <c r="S217" t="n">
+        <v>0</v>
+      </c>
+      <c r="T217" t="n">
+        <v>0</v>
+      </c>
+      <c r="U217" t="n">
+        <v>4.785872864007006</v>
+      </c>
+      <c r="V217" t="n">
+        <v>8.240000009536743</v>
+      </c>
+      <c r="W217" t="n">
+        <v>-27658000.62926254</v>
+      </c>
+      <c r="X217" t="n">
+        <v>-27658000.62926254</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC217" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD217" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409192913_dh_0.5_ctax_150_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>12930457.16750125</v>
+      </c>
+      <c r="B218" t="n">
+        <v>4023435.234931632</v>
+      </c>
+      <c r="C218" t="n">
+        <v>3315867.067768763</v>
+      </c>
+      <c r="D218" t="n">
+        <v>3727698.422331503</v>
+      </c>
+      <c r="E218" t="n">
+        <v>0</v>
+      </c>
+      <c r="F218" t="n">
+        <v>7751133.657263136</v>
+      </c>
+      <c r="G218" t="n">
+        <v>3315867.067768763</v>
+      </c>
+      <c r="H218" t="n">
+        <v>37234.21128322011</v>
+      </c>
+      <c r="I218" t="n">
+        <v>-2581828.10388802</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" t="n">
+        <v>0</v>
+      </c>
+      <c r="L218" t="n">
+        <v>4408050.335074153</v>
+      </c>
+      <c r="M218" t="n">
+        <v>12930457.16750125</v>
+      </c>
+      <c r="N218" t="n">
+        <v>22042.6411206288</v>
+      </c>
+      <c r="O218" t="n">
+        <v>0</v>
+      </c>
+      <c r="P218" t="n">
+        <v>22042.6411206288</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>22040.25167537072</v>
+      </c>
+      <c r="R218" t="n">
+        <v>0</v>
+      </c>
+      <c r="S218" t="n">
+        <v>0</v>
+      </c>
+      <c r="T218" t="n">
+        <v>0</v>
+      </c>
+      <c r="U218" t="n">
+        <v>2.389445258125502</v>
+      </c>
+      <c r="V218" t="n">
+        <v>10.01999998092651</v>
+      </c>
+      <c r="W218" t="n">
+        <v>12930457.16750125</v>
+      </c>
+      <c r="X218" t="n">
+        <v>12930457.16750125</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC218" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD218" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409193120_dh_0.5_ctax_200_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>10347085.40614747</v>
+      </c>
+      <c r="B219" t="n">
+        <v>4012232.225124456</v>
+      </c>
+      <c r="C219" t="n">
+        <v>3310603.766944425</v>
+      </c>
+      <c r="D219" t="n">
+        <v>3721395.318614198</v>
+      </c>
+      <c r="E219" t="n">
+        <v>0</v>
+      </c>
+      <c r="F219" t="n">
+        <v>7733627.543738655</v>
+      </c>
+      <c r="G219" t="n">
+        <v>3310603.766944425</v>
+      </c>
+      <c r="H219" t="n">
+        <v>37234.21128322012</v>
+      </c>
+      <c r="I219" t="n">
+        <v>-5170442.097161287</v>
+      </c>
+      <c r="J219" t="n">
+        <v>0</v>
+      </c>
+      <c r="K219" t="n">
+        <v>0</v>
+      </c>
+      <c r="L219" t="n">
+        <v>4436061.981342457</v>
+      </c>
+      <c r="M219" t="n">
+        <v>10347085.40614747</v>
+      </c>
+      <c r="N219" t="n">
+        <v>22182.69760124243</v>
+      </c>
+      <c r="O219" t="n">
+        <v>0</v>
+      </c>
+      <c r="P219" t="n">
+        <v>22182.69760124243</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>22180.3099067122</v>
+      </c>
+      <c r="R219" t="n">
+        <v>0</v>
+      </c>
+      <c r="S219" t="n">
+        <v>0</v>
+      </c>
+      <c r="T219" t="n">
+        <v>0</v>
+      </c>
+      <c r="U219" t="n">
+        <v>2.387694530233733</v>
+      </c>
+      <c r="V219" t="n">
+        <v>8.413999795913696</v>
+      </c>
+      <c r="W219" t="n">
+        <v>10347085.40614747</v>
+      </c>
+      <c r="X219" t="n">
+        <v>10347085.40614747</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC219" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD219" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409193328_dh_0.5_ctax_200_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>7739374.381027966</v>
+      </c>
+      <c r="B220" t="n">
+        <v>3998898.72771472</v>
+      </c>
+      <c r="C220" t="n">
+        <v>3304339.25005025</v>
+      </c>
+      <c r="D220" t="n">
+        <v>3713669.423627916</v>
+      </c>
+      <c r="E220" t="n">
+        <v>0</v>
+      </c>
+      <c r="F220" t="n">
+        <v>7712568.151342636</v>
+      </c>
+      <c r="G220" t="n">
+        <v>3304339.25005025</v>
+      </c>
+      <c r="H220" t="n">
+        <v>107308.4269386298</v>
+      </c>
+      <c r="I220" t="n">
+        <v>-7925207.001382195</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" t="n">
+        <v>0</v>
+      </c>
+      <c r="L220" t="n">
+        <v>4540365.554078644</v>
+      </c>
+      <c r="M220" t="n">
+        <v>7739374.381027966</v>
+      </c>
+      <c r="N220" t="n">
+        <v>22704.21299711572</v>
+      </c>
+      <c r="O220" t="n">
+        <v>0</v>
+      </c>
+      <c r="P220" t="n">
+        <v>22704.21299711572</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>22701.82777039321</v>
+      </c>
+      <c r="R220" t="n">
+        <v>0</v>
+      </c>
+      <c r="S220" t="n">
+        <v>0</v>
+      </c>
+      <c r="T220" t="n">
+        <v>0</v>
+      </c>
+      <c r="U220" t="n">
+        <v>2.385226722530299</v>
+      </c>
+      <c r="V220" t="n">
+        <v>15.89800000190735</v>
+      </c>
+      <c r="W220" t="n">
+        <v>7739374.381027966</v>
+      </c>
+      <c r="X220" t="n">
+        <v>7739374.381027966</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC220" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD220" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE220" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409193535_dh_0.5_ctax_200_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>4906848.509564165</v>
+      </c>
+      <c r="B221" t="n">
+        <v>3978823.310273046</v>
+      </c>
+      <c r="C221" t="n">
+        <v>3294907.325783867</v>
+      </c>
+      <c r="D221" t="n">
+        <v>3701536.939192132</v>
+      </c>
+      <c r="E221" t="n">
+        <v>0</v>
+      </c>
+      <c r="F221" t="n">
+        <v>7680360.249465178</v>
+      </c>
+      <c r="G221" t="n">
+        <v>3294907.325783867</v>
+      </c>
+      <c r="H221" t="n">
+        <v>1019525.637268486</v>
+      </c>
+      <c r="I221" t="n">
+        <v>-12545258.89394215</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" t="n">
+        <v>0</v>
+      </c>
+      <c r="L221" t="n">
+        <v>5457314.190988785</v>
+      </c>
+      <c r="M221" t="n">
+        <v>4906848.509564165</v>
+      </c>
+      <c r="N221" t="n">
+        <v>27288.95160993393</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
+      <c r="P221" t="n">
+        <v>27288.95160993393</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>27286.57095494387</v>
+      </c>
+      <c r="R221" t="n">
+        <v>0</v>
+      </c>
+      <c r="S221" t="n">
+        <v>0</v>
+      </c>
+      <c r="T221" t="n">
+        <v>0</v>
+      </c>
+      <c r="U221" t="n">
+        <v>2.380654990195611</v>
+      </c>
+      <c r="V221" t="n">
+        <v>22.99100017547607</v>
+      </c>
+      <c r="W221" t="n">
+        <v>4906848.509564165</v>
+      </c>
+      <c r="X221" t="n">
+        <v>4906848.509564165</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC221" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD221" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409193919_dh_0.5_ctax_200_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>1307238.910861056</v>
+      </c>
+      <c r="B222" t="n">
+        <v>3948000.511357153</v>
+      </c>
+      <c r="C222" t="n">
+        <v>3280427.690154821</v>
+      </c>
+      <c r="D222" t="n">
+        <v>3681828.317568954</v>
+      </c>
+      <c r="E222" t="n">
+        <v>0</v>
+      </c>
+      <c r="F222" t="n">
+        <v>7629828.828926107</v>
+      </c>
+      <c r="G222" t="n">
+        <v>3280427.690154821</v>
+      </c>
+      <c r="H222" t="n">
+        <v>3485196.427326003</v>
+      </c>
+      <c r="I222" t="n">
+        <v>-20968164.39163966</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" t="n">
+        <v>0</v>
+      </c>
+      <c r="L222" t="n">
+        <v>7879950.356093787</v>
+      </c>
+      <c r="M222" t="n">
+        <v>1307238.910861056</v>
+      </c>
+      <c r="N222" t="n">
+        <v>39402.12356729097</v>
+      </c>
+      <c r="O222" t="n">
+        <v>0</v>
+      </c>
+      <c r="P222" t="n">
+        <v>39402.12356729097</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>39399.75178046872</v>
+      </c>
+      <c r="R222" t="n">
+        <v>0</v>
+      </c>
+      <c r="S222" t="n">
+        <v>0</v>
+      </c>
+      <c r="T222" t="n">
+        <v>0</v>
+      </c>
+      <c r="U222" t="n">
+        <v>2.37178682242675</v>
+      </c>
+      <c r="V222" t="n">
+        <v>28.15799999237061</v>
+      </c>
+      <c r="W222" t="n">
+        <v>1307238.910861056</v>
+      </c>
+      <c r="X222" t="n">
+        <v>1307238.910861056</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC222" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD222" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409194141_dh_0.5_ctax_200_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>-3587301.734222217</v>
+      </c>
+      <c r="B223" t="n">
+        <v>3916854.517749421</v>
+      </c>
+      <c r="C223" t="n">
+        <v>3265796.051669369</v>
+      </c>
+      <c r="D223" t="n">
+        <v>3660761.574100852</v>
+      </c>
+      <c r="E223" t="n">
+        <v>0</v>
+      </c>
+      <c r="F223" t="n">
+        <v>7577616.091850273</v>
+      </c>
+      <c r="G223" t="n">
+        <v>3265796.051669369</v>
+      </c>
+      <c r="H223" t="n">
+        <v>7336283.232034723</v>
+      </c>
+      <c r="I223" t="n">
+        <v>-33384132.18692982</v>
+      </c>
+      <c r="J223" t="n">
+        <v>0</v>
+      </c>
+      <c r="K223" t="n">
+        <v>0</v>
+      </c>
+      <c r="L223" t="n">
+        <v>11617135.07715324</v>
+      </c>
+      <c r="M223" t="n">
+        <v>-3587301.734222217</v>
+      </c>
+      <c r="N223" t="n">
+        <v>58088.03623949944</v>
+      </c>
+      <c r="O223" t="n">
+        <v>0</v>
+      </c>
+      <c r="P223" t="n">
+        <v>58088.03623949944</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>58085.67538576618</v>
+      </c>
+      <c r="R223" t="n">
+        <v>0</v>
+      </c>
+      <c r="S223" t="n">
+        <v>0</v>
+      </c>
+      <c r="T223" t="n">
+        <v>0</v>
+      </c>
+      <c r="U223" t="n">
+        <v>2.360853733257755</v>
+      </c>
+      <c r="V223" t="n">
+        <v>20.04500007629395</v>
+      </c>
+      <c r="W223" t="n">
+        <v>-3587301.734222217</v>
+      </c>
+      <c r="X223" t="n">
+        <v>-3587301.734222217</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC223" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD223" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409194410_dh_0.5_ctax_200_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>-12916141.96983256</v>
+      </c>
+      <c r="B224" t="n">
+        <v>31572859.92774187</v>
+      </c>
+      <c r="C224" t="n">
+        <v>4433066.460455095</v>
+      </c>
+      <c r="D224" t="n">
+        <v>22633399.01066496</v>
+      </c>
+      <c r="E224" t="n">
+        <v>0</v>
+      </c>
+      <c r="F224" t="n">
+        <v>54206258.93840683</v>
+      </c>
+      <c r="G224" t="n">
+        <v>4433066.460455095</v>
+      </c>
+      <c r="H224" t="n">
+        <v>4368725.970797903</v>
+      </c>
+      <c r="I224" t="n">
+        <v>-85598785.28443633</v>
+      </c>
+      <c r="J224" t="n">
+        <v>0</v>
+      </c>
+      <c r="K224" t="n">
+        <v>0</v>
+      </c>
+      <c r="L224" t="n">
+        <v>9674591.944943933</v>
+      </c>
+      <c r="M224" t="n">
+        <v>-12916141.96983256</v>
+      </c>
+      <c r="N224" t="n">
+        <v>48377.79379592646</v>
+      </c>
+      <c r="O224" t="n">
+        <v>0</v>
+      </c>
+      <c r="P224" t="n">
+        <v>48377.79379592646</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>48372.95972471861</v>
+      </c>
+      <c r="R224" t="n">
+        <v>0</v>
+      </c>
+      <c r="S224" t="n">
+        <v>0</v>
+      </c>
+      <c r="T224" t="n">
+        <v>0</v>
+      </c>
+      <c r="U224" t="n">
+        <v>4.834071206764877</v>
+      </c>
+      <c r="V224" t="n">
+        <v>19.86500000953674</v>
+      </c>
+      <c r="W224" t="n">
+        <v>-12916141.96983256</v>
+      </c>
+      <c r="X224" t="n">
+        <v>-12916141.96983256</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC224" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD224" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409194632_dh_0.5_ctax_200_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>-25188201.0456662</v>
+      </c>
+      <c r="B225" t="n">
+        <v>31845651.81514538</v>
+      </c>
+      <c r="C225" t="n">
+        <v>4458987.607501581</v>
+      </c>
+      <c r="D225" t="n">
+        <v>22820313.98211749</v>
+      </c>
+      <c r="E225" t="n">
+        <v>0</v>
+      </c>
+      <c r="F225" t="n">
+        <v>54665965.79726287</v>
+      </c>
+      <c r="G225" t="n">
+        <v>4458987.607501581</v>
+      </c>
+      <c r="H225" t="n">
+        <v>4554513.398503194</v>
+      </c>
+      <c r="I225" t="n">
+        <v>-98445168.44109029</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" t="n">
+        <v>0</v>
+      </c>
+      <c r="L225" t="n">
+        <v>9577500.592156438</v>
+      </c>
+      <c r="M225" t="n">
+        <v>-25188201.0456662</v>
+      </c>
+      <c r="N225" t="n">
+        <v>47892.37219713123</v>
+      </c>
+      <c r="O225" t="n">
+        <v>0</v>
+      </c>
+      <c r="P225" t="n">
+        <v>47892.37219713123</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>47887.50296078217</v>
+      </c>
+      <c r="R225" t="n">
+        <v>0</v>
+      </c>
+      <c r="S225" t="n">
+        <v>0</v>
+      </c>
+      <c r="T225" t="n">
+        <v>0</v>
+      </c>
+      <c r="U225" t="n">
+        <v>4.869236349029795</v>
+      </c>
+      <c r="V225" t="n">
+        <v>18.84599995613098</v>
+      </c>
+      <c r="W225" t="n">
+        <v>-25188201.0456662</v>
+      </c>
+      <c r="X225" t="n">
+        <v>-25188201.0456662</v>
+      </c>
+      <c r="Y225" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC225" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD225" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409195043_dh_0.5_ctax_200_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>14028308.17080783</v>
+      </c>
+      <c r="B226" t="n">
+        <v>4038158.974886176</v>
+      </c>
+      <c r="C226" t="n">
+        <v>3322784.532894418</v>
+      </c>
+      <c r="D226" t="n">
+        <v>3735732.345036694</v>
+      </c>
+      <c r="E226" t="n">
+        <v>0</v>
+      </c>
+      <c r="F226" t="n">
+        <v>7773891.31992287</v>
+      </c>
+      <c r="G226" t="n">
+        <v>3322784.532894418</v>
+      </c>
+      <c r="H226" t="n">
+        <v>37234.21128322011</v>
+      </c>
+      <c r="I226" t="n">
+        <v>-2578207.152988558</v>
+      </c>
+      <c r="J226" t="n">
+        <v>0</v>
+      </c>
+      <c r="K226" t="n">
+        <v>0</v>
+      </c>
+      <c r="L226" t="n">
+        <v>5472605.259695878</v>
+      </c>
+      <c r="M226" t="n">
+        <v>14028308.17080783</v>
+      </c>
+      <c r="N226" t="n">
+        <v>21892.81235692455</v>
+      </c>
+      <c r="O226" t="n">
+        <v>0</v>
+      </c>
+      <c r="P226" t="n">
+        <v>21892.81235692455</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>21890.42103878348</v>
+      </c>
+      <c r="R226" t="n">
+        <v>0</v>
+      </c>
+      <c r="S226" t="n">
+        <v>0</v>
+      </c>
+      <c r="T226" t="n">
+        <v>0</v>
+      </c>
+      <c r="U226" t="n">
+        <v>2.391318141082842</v>
+      </c>
+      <c r="V226" t="n">
+        <v>11.89299988746643</v>
+      </c>
+      <c r="W226" t="n">
+        <v>14028308.17080783</v>
+      </c>
+      <c r="X226" t="n">
+        <v>14028308.17080783</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC226" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD226" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409195301_dh_0.5_ctax_250_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>11449408.70283424</v>
+      </c>
+      <c r="B227" t="n">
+        <v>4031628.269264671</v>
+      </c>
+      <c r="C227" t="n">
+        <v>3319716.447537475</v>
+      </c>
+      <c r="D227" t="n">
+        <v>3732204.264567942</v>
+      </c>
+      <c r="E227" t="n">
+        <v>0</v>
+      </c>
+      <c r="F227" t="n">
+        <v>7763832.533832613</v>
+      </c>
+      <c r="G227" t="n">
+        <v>3319716.447537475</v>
+      </c>
+      <c r="H227" t="n">
+        <v>37234.21128322011</v>
+      </c>
+      <c r="I227" t="n">
+        <v>-5159379.237650293</v>
+      </c>
+      <c r="J227" t="n">
+        <v>0</v>
+      </c>
+      <c r="K227" t="n">
+        <v>0</v>
+      </c>
+      <c r="L227" t="n">
+        <v>5488004.747831225</v>
+      </c>
+      <c r="M227" t="n">
+        <v>11449408.70283424</v>
+      </c>
+      <c r="N227" t="n">
+        <v>21954.40953949162</v>
+      </c>
+      <c r="O227" t="n">
+        <v>0</v>
+      </c>
+      <c r="P227" t="n">
+        <v>21954.40953949162</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>21952.01899132496</v>
+      </c>
+      <c r="R227" t="n">
+        <v>0</v>
+      </c>
+      <c r="S227" t="n">
+        <v>0</v>
+      </c>
+      <c r="T227" t="n">
+        <v>0</v>
+      </c>
+      <c r="U227" t="n">
+        <v>2.390548166676074</v>
+      </c>
+      <c r="V227" t="n">
+        <v>16.1340000629425</v>
+      </c>
+      <c r="W227" t="n">
+        <v>11449408.70283424</v>
+      </c>
+      <c r="X227" t="n">
+        <v>11449408.70283424</v>
+      </c>
+      <c r="Y227" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC227" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD227" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409195512_dh_0.5_ctax_250_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>8860294.492579622</v>
+      </c>
+      <c r="B228" t="n">
+        <v>4024025.55113682</v>
+      </c>
+      <c r="C228" t="n">
+        <v>3316144.419378072</v>
+      </c>
+      <c r="D228" t="n">
+        <v>3728026.042897742</v>
+      </c>
+      <c r="E228" t="n">
+        <v>0</v>
+      </c>
+      <c r="F228" t="n">
+        <v>7752051.594034562</v>
+      </c>
+      <c r="G228" t="n">
+        <v>3316144.419378072</v>
+      </c>
+      <c r="H228" t="n">
+        <v>67290.74461011283</v>
+      </c>
+      <c r="I228" t="n">
+        <v>-7818317.017906344</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0</v>
+      </c>
+      <c r="K228" t="n">
+        <v>0</v>
+      </c>
+      <c r="L228" t="n">
+        <v>5543124.752463221</v>
+      </c>
+      <c r="M228" t="n">
+        <v>8860294.492579622</v>
+      </c>
+      <c r="N228" t="n">
+        <v>22174.88853966262</v>
+      </c>
+      <c r="O228" t="n">
+        <v>0</v>
+      </c>
+      <c r="P228" t="n">
+        <v>22174.88853966262</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>22172.49900985289</v>
+      </c>
+      <c r="R228" t="n">
+        <v>0</v>
+      </c>
+      <c r="S228" t="n">
+        <v>0</v>
+      </c>
+      <c r="T228" t="n">
+        <v>0</v>
+      </c>
+      <c r="U228" t="n">
+        <v>2.389529809777435</v>
+      </c>
+      <c r="V228" t="n">
+        <v>26.94700002670288</v>
+      </c>
+      <c r="W228" t="n">
+        <v>8860294.492579622</v>
+      </c>
+      <c r="X228" t="n">
+        <v>8860294.492579622</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC228" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD228" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409195729_dh_0.5_ctax_250_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>6183674.066166247</v>
+      </c>
+      <c r="B229" t="n">
+        <v>4012973.72175279</v>
+      </c>
+      <c r="C229" t="n">
+        <v>3310952.10059789</v>
+      </c>
+      <c r="D229" t="n">
+        <v>3721817.334584343</v>
+      </c>
+      <c r="E229" t="n">
+        <v>0</v>
+      </c>
+      <c r="F229" t="n">
+        <v>7734791.056337133</v>
+      </c>
+      <c r="G229" t="n">
+        <v>3310952.10059789</v>
+      </c>
+      <c r="H229" t="n">
+        <v>429214.1989452876</v>
+      </c>
+      <c r="I229" t="n">
+        <v>-11287105.42265883</v>
+      </c>
+      <c r="J229" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" t="n">
+        <v>0</v>
+      </c>
+      <c r="L229" t="n">
+        <v>5995822.132944769</v>
+      </c>
+      <c r="M229" t="n">
+        <v>6183674.066166247</v>
+      </c>
+      <c r="N229" t="n">
+        <v>23985.67635041946</v>
+      </c>
+      <c r="O229" t="n">
+        <v>0</v>
+      </c>
+      <c r="P229" t="n">
+        <v>23985.67635041946</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>23983.28853177899</v>
+      </c>
+      <c r="R229" t="n">
+        <v>0</v>
+      </c>
+      <c r="S229" t="n">
+        <v>0</v>
+      </c>
+      <c r="T229" t="n">
+        <v>0</v>
+      </c>
+      <c r="U229" t="n">
+        <v>2.387818640457112</v>
+      </c>
+      <c r="V229" t="n">
+        <v>29.72300004959106</v>
+      </c>
+      <c r="W229" t="n">
+        <v>6183674.066166247</v>
+      </c>
+      <c r="X229" t="n">
+        <v>6183674.066166247</v>
+      </c>
+      <c r="Y229" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC229" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD229" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409195957_dh_0.5_ctax_250_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>3030976.976496851</v>
+      </c>
+      <c r="B230" t="n">
+        <v>4000990.6588833</v>
+      </c>
+      <c r="C230" t="n">
+        <v>3305322.113930779</v>
+      </c>
+      <c r="D230" t="n">
+        <v>3714899.039353397</v>
+      </c>
+      <c r="E230" t="n">
+        <v>0</v>
+      </c>
+      <c r="F230" t="n">
+        <v>7715889.698236696</v>
+      </c>
+      <c r="G230" t="n">
+        <v>3305322.113930779</v>
+      </c>
+      <c r="H230" t="n">
+        <v>1890187.726186975</v>
+      </c>
+      <c r="I230" t="n">
+        <v>-17608991.36679493</v>
+      </c>
+      <c r="J230" t="n">
+        <v>0</v>
+      </c>
+      <c r="K230" t="n">
+        <v>0</v>
+      </c>
+      <c r="L230" t="n">
+        <v>7728568.804937335</v>
+      </c>
+      <c r="M230" t="n">
+        <v>3030976.976496851</v>
+      </c>
+      <c r="N230" t="n">
+        <v>30916.66086358813</v>
+      </c>
+      <c r="O230" t="n">
+        <v>0</v>
+      </c>
+      <c r="P230" t="n">
+        <v>30916.66086358813</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>30914.2752197493</v>
+      </c>
+      <c r="R230" t="n">
+        <v>0</v>
+      </c>
+      <c r="S230" t="n">
+        <v>0</v>
+      </c>
+      <c r="T230" t="n">
+        <v>0</v>
+      </c>
+      <c r="U230" t="n">
+        <v>2.385643838901143</v>
+      </c>
+      <c r="V230" t="n">
+        <v>38.76300001144409</v>
+      </c>
+      <c r="W230" t="n">
+        <v>3030976.976496851</v>
+      </c>
+      <c r="X230" t="n">
+        <v>3030976.976496851</v>
+      </c>
+      <c r="Y230" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD230" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409200443_dh_0.5_ctax_250_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>-1031150.961156504</v>
+      </c>
+      <c r="B231" t="n">
+        <v>3988604.781811651</v>
+      </c>
+      <c r="C231" t="n">
+        <v>3299502.787088084</v>
+      </c>
+      <c r="D231" t="n">
+        <v>3707523.889737644</v>
+      </c>
+      <c r="E231" t="n">
+        <v>0</v>
+      </c>
+      <c r="F231" t="n">
+        <v>7696128.671549295</v>
+      </c>
+      <c r="G231" t="n">
+        <v>3299502.787088084</v>
+      </c>
+      <c r="H231" t="n">
+        <v>4771792.963630504</v>
+      </c>
+      <c r="I231" t="n">
+        <v>-27911641.97848226</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0</v>
+      </c>
+      <c r="K231" t="n">
+        <v>0</v>
+      </c>
+      <c r="L231" t="n">
+        <v>11113066.59505787</v>
+      </c>
+      <c r="M231" t="n">
+        <v>-1031150.961156504</v>
+      </c>
+      <c r="N231" t="n">
+        <v>44454.64939198364</v>
+      </c>
+      <c r="O231" t="n">
+        <v>0</v>
+      </c>
+      <c r="P231" t="n">
+        <v>44454.64939198364</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>44452.26638023145</v>
+      </c>
+      <c r="R231" t="n">
+        <v>0</v>
+      </c>
+      <c r="S231" t="n">
+        <v>0</v>
+      </c>
+      <c r="T231" t="n">
+        <v>0</v>
+      </c>
+      <c r="U231" t="n">
+        <v>2.38301175218482</v>
+      </c>
+      <c r="V231" t="n">
+        <v>27.23199987411499</v>
+      </c>
+      <c r="W231" t="n">
+        <v>-1031150.961156504</v>
+      </c>
+      <c r="X231" t="n">
+        <v>-1031150.961156504</v>
+      </c>
+      <c r="Y231" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC231" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD231" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409200723_dh_0.5_ctax_250_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>-10585969.16492157</v>
+      </c>
+      <c r="B232" t="n">
+        <v>32022539.03271046</v>
+      </c>
+      <c r="C232" t="n">
+        <v>4475795.730429249</v>
+      </c>
+      <c r="D232" t="n">
+        <v>22940355.14542694</v>
+      </c>
+      <c r="E232" t="n">
+        <v>0</v>
+      </c>
+      <c r="F232" t="n">
+        <v>54962894.17813741</v>
+      </c>
+      <c r="G232" t="n">
+        <v>4475795.730429249</v>
+      </c>
+      <c r="H232" t="n">
+        <v>4131091.726744702</v>
+      </c>
+      <c r="I232" t="n">
+        <v>-85435081.46908544</v>
+      </c>
+      <c r="J232" t="n">
+        <v>0</v>
+      </c>
+      <c r="K232" t="n">
+        <v>0</v>
+      </c>
+      <c r="L232" t="n">
+        <v>11279330.66885251</v>
+      </c>
+      <c r="M232" t="n">
+        <v>-10585969.16492157</v>
+      </c>
+      <c r="N232" t="n">
+        <v>45122.21314214281</v>
+      </c>
+      <c r="O232" t="n">
+        <v>0</v>
+      </c>
+      <c r="P232" t="n">
+        <v>45122.21314214281</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>45117.32267541003</v>
+      </c>
+      <c r="R232" t="n">
+        <v>0</v>
+      </c>
+      <c r="S232" t="n">
+        <v>0</v>
+      </c>
+      <c r="T232" t="n">
+        <v>0</v>
+      </c>
+      <c r="U232" t="n">
+        <v>4.89046673279933</v>
+      </c>
+      <c r="V232" t="n">
+        <v>22.91300010681152</v>
+      </c>
+      <c r="W232" t="n">
+        <v>-10585969.16492157</v>
+      </c>
+      <c r="X232" t="n">
+        <v>-10585969.16492157</v>
+      </c>
+      <c r="Y232" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD232" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409200950_dh_0.5_ctax_250_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>-22847000.82855792</v>
+      </c>
+      <c r="B233" t="n">
+        <v>32192029.80639485</v>
+      </c>
+      <c r="C233" t="n">
+        <v>4491901.030735329</v>
+      </c>
+      <c r="D233" t="n">
+        <v>23054399.83895468</v>
+      </c>
+      <c r="E233" t="n">
+        <v>0</v>
+      </c>
+      <c r="F233" t="n">
+        <v>55246429.64534953</v>
+      </c>
+      <c r="G233" t="n">
+        <v>4491901.030735329</v>
+      </c>
+      <c r="H233" t="n">
+        <v>4449520.488528318</v>
+      </c>
+      <c r="I233" t="n">
+        <v>-98500538.48356315</v>
+      </c>
+      <c r="J233" t="n">
+        <v>0</v>
+      </c>
+      <c r="K233" t="n">
+        <v>0</v>
+      </c>
+      <c r="L233" t="n">
+        <v>11465686.49039206</v>
+      </c>
+      <c r="M233" t="n">
+        <v>-22847000.82855792</v>
+      </c>
+      <c r="N233" t="n">
+        <v>45867.65544778584</v>
+      </c>
+      <c r="O233" t="n">
+        <v>0</v>
+      </c>
+      <c r="P233" t="n">
+        <v>45867.65544778584</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>45862.74596156717</v>
+      </c>
+      <c r="R233" t="n">
+        <v>0</v>
+      </c>
+      <c r="S233" t="n">
+        <v>0</v>
+      </c>
+      <c r="T233" t="n">
+        <v>0</v>
+      </c>
+      <c r="U233" t="n">
+        <v>4.909486217584692</v>
+      </c>
+      <c r="V233" t="n">
+        <v>17.40499997138977</v>
+      </c>
+      <c r="W233" t="n">
+        <v>-22847000.82855792</v>
+      </c>
+      <c r="X233" t="n">
+        <v>-22847000.82855792</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC233" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD233" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409201214_dh_0.5_ctax_250_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>12495140.26418298</v>
+      </c>
+      <c r="B234" t="n">
+        <v>3910637.318171366</v>
+      </c>
+      <c r="C234" t="n">
+        <v>3262875.396373267</v>
+      </c>
+      <c r="D234" t="n">
+        <v>3544295.099405051</v>
+      </c>
+      <c r="E234" t="n">
+        <v>0</v>
+      </c>
+      <c r="F234" t="n">
+        <v>7454932.417576417</v>
+      </c>
+      <c r="G234" t="n">
+        <v>3262875.396373267</v>
+      </c>
+      <c r="H234" t="n">
+        <v>35446.35724911594</v>
+      </c>
+      <c r="I234" t="n">
+        <v>-2245347.736689426</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0</v>
+      </c>
+      <c r="K234" t="n">
+        <v>0</v>
+      </c>
+      <c r="L234" t="n">
+        <v>3987233.829673608</v>
+      </c>
+      <c r="M234" t="n">
+        <v>12495140.26418298</v>
+      </c>
+      <c r="N234" t="n">
+        <v>39874.50473755127</v>
+      </c>
+      <c r="O234" t="n">
+        <v>0</v>
+      </c>
+      <c r="P234" t="n">
+        <v>39874.50473755127</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>39872.33829673625</v>
+      </c>
+      <c r="R234" t="n">
+        <v>0</v>
+      </c>
+      <c r="S234" t="n">
+        <v>0</v>
+      </c>
+      <c r="T234" t="n">
+        <v>0</v>
+      </c>
+      <c r="U234" t="n">
+        <v>2.166440815047086</v>
+      </c>
+      <c r="V234" t="n">
+        <v>14.36199998855591</v>
+      </c>
+      <c r="W234" t="n">
+        <v>12495140.26418298</v>
+      </c>
+      <c r="X234" t="n">
+        <v>12495140.26418298</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC234" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD234" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409201439_dh_1_ctax_100_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>9240876.844967514</v>
+      </c>
+      <c r="B235" t="n">
+        <v>0</v>
+      </c>
+      <c r="C235" t="n">
+        <v>0</v>
+      </c>
+      <c r="D235" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E235" t="n">
+        <v>0</v>
+      </c>
+      <c r="F235" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" t="n">
+        <v>60502.1733419845</v>
+      </c>
+      <c r="I235" t="n">
+        <v>-12585702.76516321</v>
+      </c>
+      <c r="J235" t="n">
+        <v>0</v>
+      </c>
+      <c r="K235" t="n">
+        <v>0</v>
+      </c>
+      <c r="L235" t="n">
+        <v>21330348.66499327</v>
+      </c>
+      <c r="M235" t="n">
+        <v>9240876.844967514</v>
+      </c>
+      <c r="N235" t="n">
+        <v>213303.4866499327</v>
+      </c>
+      <c r="O235" t="n">
+        <v>0</v>
+      </c>
+      <c r="P235" t="n">
+        <v>213303.4866499327</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>213303.4866499327</v>
+      </c>
+      <c r="R235" t="n">
+        <v>0</v>
+      </c>
+      <c r="S235" t="n">
+        <v>0</v>
+      </c>
+      <c r="T235" t="n">
+        <v>0</v>
+      </c>
+      <c r="U235" t="n">
+        <v>0</v>
+      </c>
+      <c r="V235" t="n">
+        <v>17.28600001335144</v>
+      </c>
+      <c r="W235" t="n">
+        <v>9240876.844967514</v>
+      </c>
+      <c r="X235" t="n">
+        <v>9240876.844967514</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC235" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD235" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409201655_dh_1_ctax_100_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>2867571.495318737</v>
+      </c>
+      <c r="B236" t="n">
+        <v>0</v>
+      </c>
+      <c r="C236" t="n">
+        <v>0</v>
+      </c>
+      <c r="D236" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E236" t="n">
+        <v>0</v>
+      </c>
+      <c r="F236" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" t="n">
+        <v>517059.0226530747</v>
+      </c>
+      <c r="I236" t="n">
+        <v>-19626722.50692945</v>
+      </c>
+      <c r="J236" t="n">
+        <v>0</v>
+      </c>
+      <c r="K236" t="n">
+        <v>0</v>
+      </c>
+      <c r="L236" t="n">
+        <v>21541506.20779965</v>
+      </c>
+      <c r="M236" t="n">
+        <v>2867571.495318737</v>
+      </c>
+      <c r="N236" t="n">
+        <v>215415.0620779964</v>
+      </c>
+      <c r="O236" t="n">
+        <v>0</v>
+      </c>
+      <c r="P236" t="n">
+        <v>215415.0620779964</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>215415.0620779964</v>
+      </c>
+      <c r="R236" t="n">
+        <v>0</v>
+      </c>
+      <c r="S236" t="n">
+        <v>0</v>
+      </c>
+      <c r="T236" t="n">
+        <v>0</v>
+      </c>
+      <c r="U236" t="n">
+        <v>0</v>
+      </c>
+      <c r="V236" t="n">
+        <v>9.170000076293945</v>
+      </c>
+      <c r="W236" t="n">
+        <v>2867571.495318647</v>
+      </c>
+      <c r="X236" t="n">
+        <v>2867571.495318737</v>
+      </c>
+      <c r="Y236" t="n">
+        <v>9.033828973770142e-08</v>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC236" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD236" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE236" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409202201_dh_1_ctax_100_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>-3907956.459950909</v>
+      </c>
+      <c r="B237" t="n">
+        <v>0</v>
+      </c>
+      <c r="C237" t="n">
+        <v>0</v>
+      </c>
+      <c r="D237" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E237" t="n">
+        <v>0</v>
+      </c>
+      <c r="F237" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
+      <c r="H237" t="n">
+        <v>1744785.219608191</v>
+      </c>
+      <c r="I237" t="n">
+        <v>-28197800.02524595</v>
+      </c>
+      <c r="J237" t="n">
+        <v>0</v>
+      </c>
+      <c r="K237" t="n">
+        <v>0</v>
+      </c>
+      <c r="L237" t="n">
+        <v>22109329.57389139</v>
+      </c>
+      <c r="M237" t="n">
+        <v>-3907956.459950909</v>
+      </c>
+      <c r="N237" t="n">
+        <v>221093.2957389139</v>
+      </c>
+      <c r="O237" t="n">
+        <v>0</v>
+      </c>
+      <c r="P237" t="n">
+        <v>221093.2957389139</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>221093.2957389138</v>
+      </c>
+      <c r="R237" t="n">
+        <v>0</v>
+      </c>
+      <c r="S237" t="n">
+        <v>0</v>
+      </c>
+      <c r="T237" t="n">
+        <v>0</v>
+      </c>
+      <c r="U237" t="n">
+        <v>0</v>
+      </c>
+      <c r="V237" t="n">
+        <v>6.290999889373779</v>
+      </c>
+      <c r="W237" t="n">
+        <v>-3907956.459950909</v>
+      </c>
+      <c r="X237" t="n">
+        <v>-3907956.459950909</v>
+      </c>
+      <c r="Y237" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC237" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD237" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE237" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409202414_dh_1_ctax_100_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>-11236309.91853718</v>
+      </c>
+      <c r="B238" t="n">
+        <v>0</v>
+      </c>
+      <c r="C238" t="n">
+        <v>0</v>
+      </c>
+      <c r="D238" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E238" t="n">
+        <v>0</v>
+      </c>
+      <c r="F238" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" t="n">
+        <v>3274721.082435129</v>
+      </c>
+      <c r="I238" t="n">
+        <v>-37763684.68321662</v>
+      </c>
+      <c r="J238" t="n">
+        <v>0</v>
+      </c>
+      <c r="K238" t="n">
+        <v>0</v>
+      </c>
+      <c r="L238" t="n">
+        <v>22816924.91044885</v>
+      </c>
+      <c r="M238" t="n">
+        <v>-11236309.91853718</v>
+      </c>
+      <c r="N238" t="n">
+        <v>228169.2491044884</v>
+      </c>
+      <c r="O238" t="n">
+        <v>0</v>
+      </c>
+      <c r="P238" t="n">
+        <v>228169.2491044884</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>228169.2491044884</v>
+      </c>
+      <c r="R238" t="n">
+        <v>0</v>
+      </c>
+      <c r="S238" t="n">
+        <v>0</v>
+      </c>
+      <c r="T238" t="n">
+        <v>0</v>
+      </c>
+      <c r="U238" t="n">
+        <v>0</v>
+      </c>
+      <c r="V238" t="n">
+        <v>6.300999879837036</v>
+      </c>
+      <c r="W238" t="n">
+        <v>-11236309.91853718</v>
+      </c>
+      <c r="X238" t="n">
+        <v>-11236309.91853718</v>
+      </c>
+      <c r="Y238" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC238" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD238" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409202624_dh_1_ctax_100_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>-18885483.653923</v>
+      </c>
+      <c r="B239" t="n">
+        <v>0</v>
+      </c>
+      <c r="C239" t="n">
+        <v>0</v>
+      </c>
+      <c r="D239" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E239" t="n">
+        <v>0</v>
+      </c>
+      <c r="F239" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" t="n">
+        <v>3864155.607518862</v>
+      </c>
+      <c r="I239" t="n">
+        <v>-46274906.4115374</v>
+      </c>
+      <c r="J239" t="n">
+        <v>0</v>
+      </c>
+      <c r="K239" t="n">
+        <v>0</v>
+      </c>
+      <c r="L239" t="n">
+        <v>23089538.37830008</v>
+      </c>
+      <c r="M239" t="n">
+        <v>-18885483.653923</v>
+      </c>
+      <c r="N239" t="n">
+        <v>230895.3837830007</v>
+      </c>
+      <c r="O239" t="n">
+        <v>0</v>
+      </c>
+      <c r="P239" t="n">
+        <v>230895.3837830007</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>230895.3837830007</v>
+      </c>
+      <c r="R239" t="n">
+        <v>0</v>
+      </c>
+      <c r="S239" t="n">
+        <v>0</v>
+      </c>
+      <c r="T239" t="n">
+        <v>0</v>
+      </c>
+      <c r="U239" t="n">
+        <v>0</v>
+      </c>
+      <c r="V239" t="n">
+        <v>6.430999994277954</v>
+      </c>
+      <c r="W239" t="n">
+        <v>-18885483.653923</v>
+      </c>
+      <c r="X239" t="n">
+        <v>-18885483.653923</v>
+      </c>
+      <c r="Y239" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC239" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD239" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE239" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409202833_dh_1_ctax_100_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>-26627309.3052735</v>
+      </c>
+      <c r="B240" t="n">
+        <v>0</v>
+      </c>
+      <c r="C240" t="n">
+        <v>0</v>
+      </c>
+      <c r="D240" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E240" t="n">
+        <v>0</v>
+      </c>
+      <c r="F240" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" t="n">
+        <v>4098614.410903892</v>
+      </c>
+      <c r="I240" t="n">
+        <v>-54359628.06283851</v>
+      </c>
+      <c r="J240" t="n">
+        <v>0</v>
+      </c>
+      <c r="K240" t="n">
+        <v>0</v>
+      </c>
+      <c r="L240" t="n">
+        <v>23197975.57486565</v>
+      </c>
+      <c r="M240" t="n">
+        <v>-26627309.3052735</v>
+      </c>
+      <c r="N240" t="n">
+        <v>231979.7557486565</v>
+      </c>
+      <c r="O240" t="n">
+        <v>0</v>
+      </c>
+      <c r="P240" t="n">
+        <v>231979.7557486565</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>231979.7557486565</v>
+      </c>
+      <c r="R240" t="n">
+        <v>0</v>
+      </c>
+      <c r="S240" t="n">
+        <v>0</v>
+      </c>
+      <c r="T240" t="n">
+        <v>0</v>
+      </c>
+      <c r="U240" t="n">
+        <v>0</v>
+      </c>
+      <c r="V240" t="n">
+        <v>9.509000062942505</v>
+      </c>
+      <c r="W240" t="n">
+        <v>-26627309.3052735</v>
+      </c>
+      <c r="X240" t="n">
+        <v>-26627309.3052735</v>
+      </c>
+      <c r="Y240" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC240" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD240" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE240" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409203047_dh_1_ctax_100_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>-34400959.54221863</v>
+      </c>
+      <c r="B241" t="n">
+        <v>0</v>
+      </c>
+      <c r="C241" t="n">
+        <v>0</v>
+      </c>
+      <c r="D241" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E241" t="n">
+        <v>0</v>
+      </c>
+      <c r="F241" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" t="n">
+        <v>4162735.064657771</v>
+      </c>
+      <c r="I241" t="n">
+        <v>-62227054.75589869</v>
+      </c>
+      <c r="J241" t="n">
+        <v>0</v>
+      </c>
+      <c r="K241" t="n">
+        <v>0</v>
+      </c>
+      <c r="L241" t="n">
+        <v>23227631.37722682</v>
+      </c>
+      <c r="M241" t="n">
+        <v>-34400959.54221863</v>
+      </c>
+      <c r="N241" t="n">
+        <v>232276.3137722682</v>
+      </c>
+      <c r="O241" t="n">
+        <v>0</v>
+      </c>
+      <c r="P241" t="n">
+        <v>232276.3137722682</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>232276.3137722682</v>
+      </c>
+      <c r="R241" t="n">
+        <v>0</v>
+      </c>
+      <c r="S241" t="n">
+        <v>0</v>
+      </c>
+      <c r="T241" t="n">
+        <v>0</v>
+      </c>
+      <c r="U241" t="n">
+        <v>0</v>
+      </c>
+      <c r="V241" t="n">
+        <v>9.965999841690063</v>
+      </c>
+      <c r="W241" t="n">
+        <v>-34400959.54221863</v>
+      </c>
+      <c r="X241" t="n">
+        <v>-34400959.54221863</v>
+      </c>
+      <c r="Y241" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC241" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD241" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE241" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409203302_dh_1_ctax_100_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>13954319.85580568</v>
+      </c>
+      <c r="B242" t="n">
+        <v>3994216.800843018</v>
+      </c>
+      <c r="C242" t="n">
+        <v>3302139.513805298</v>
+      </c>
+      <c r="D242" t="n">
+        <v>3710894.116939222</v>
+      </c>
+      <c r="E242" t="n">
+        <v>0</v>
+      </c>
+      <c r="F242" t="n">
+        <v>7705110.91778224</v>
+      </c>
+      <c r="G242" t="n">
+        <v>3302139.513805298</v>
+      </c>
+      <c r="H242" t="n">
+        <v>1064531.802006756</v>
+      </c>
+      <c r="I242" t="n">
+        <v>-2198491.922548403</v>
+      </c>
+      <c r="J242" t="n">
+        <v>0</v>
+      </c>
+      <c r="K242" t="n">
+        <v>0</v>
+      </c>
+      <c r="L242" t="n">
+        <v>4081029.544759787</v>
+      </c>
+      <c r="M242" t="n">
+        <v>13954319.85580568</v>
+      </c>
+      <c r="N242" t="n">
+        <v>27209.24788498246</v>
+      </c>
+      <c r="O242" t="n">
+        <v>0</v>
+      </c>
+      <c r="P242" t="n">
+        <v>27209.24788498246</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>27206.86363173174</v>
+      </c>
+      <c r="R242" t="n">
+        <v>0</v>
+      </c>
+      <c r="S242" t="n">
+        <v>0</v>
+      </c>
+      <c r="T242" t="n">
+        <v>0</v>
+      </c>
+      <c r="U242" t="n">
+        <v>2.384253250634693</v>
+      </c>
+      <c r="V242" t="n">
+        <v>12.73099994659424</v>
+      </c>
+      <c r="W242" t="n">
+        <v>13954319.85580568</v>
+      </c>
+      <c r="X242" t="n">
+        <v>13954319.85580568</v>
+      </c>
+      <c r="Y242" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC242" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD242" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409203517_dh_1_ctax_150_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>11750899.30181929</v>
+      </c>
+      <c r="B243" t="n">
+        <v>3971362.856961959</v>
+      </c>
+      <c r="C243" t="n">
+        <v>3291402.626360988</v>
+      </c>
+      <c r="D243" t="n">
+        <v>3696879.451015595</v>
+      </c>
+      <c r="E243" t="n">
+        <v>0</v>
+      </c>
+      <c r="F243" t="n">
+        <v>7668242.307977553</v>
+      </c>
+      <c r="G243" t="n">
+        <v>3291402.626360988</v>
+      </c>
+      <c r="H243" t="n">
+        <v>1072286.209907711</v>
+      </c>
+      <c r="I243" t="n">
+        <v>-4434058.988704775</v>
+      </c>
+      <c r="J243" t="n">
+        <v>0</v>
+      </c>
+      <c r="K243" t="n">
+        <v>0</v>
+      </c>
+      <c r="L243" t="n">
+        <v>4153027.146277816</v>
+      </c>
+      <c r="M243" t="n">
+        <v>11750899.30181929</v>
+      </c>
+      <c r="N243" t="n">
+        <v>27689.2263436044</v>
+      </c>
+      <c r="O243" t="n">
+        <v>0</v>
+      </c>
+      <c r="P243" t="n">
+        <v>27689.2263436044</v>
+      </c>
+      <c r="Q243" t="n">
+        <v>27686.84764185222</v>
+      </c>
+      <c r="R243" t="n">
+        <v>0</v>
+      </c>
+      <c r="S243" t="n">
+        <v>0</v>
+      </c>
+      <c r="T243" t="n">
+        <v>0</v>
+      </c>
+      <c r="U243" t="n">
+        <v>2.378701752214961</v>
+      </c>
+      <c r="V243" t="n">
+        <v>12.75300002098083</v>
+      </c>
+      <c r="W243" t="n">
+        <v>11750899.30181929</v>
+      </c>
+      <c r="X243" t="n">
+        <v>11750899.30181929</v>
+      </c>
+      <c r="Y243" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC243" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD243" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE243" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409204059_dh_1_ctax_150_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>9477570.883508692</v>
+      </c>
+      <c r="B244" t="n">
+        <v>3924578.217032834</v>
+      </c>
+      <c r="C244" t="n">
+        <v>3269424.415683485</v>
+      </c>
+      <c r="D244" t="n">
+        <v>3666032.726498528</v>
+      </c>
+      <c r="E244" t="n">
+        <v>0</v>
+      </c>
+      <c r="F244" t="n">
+        <v>7590610.943531362</v>
+      </c>
+      <c r="G244" t="n">
+        <v>3269424.415683485</v>
+      </c>
+      <c r="H244" t="n">
+        <v>1333454.770729136</v>
+      </c>
+      <c r="I244" t="n">
+        <v>-7230809.64356482</v>
+      </c>
+      <c r="J244" t="n">
+        <v>0</v>
+      </c>
+      <c r="K244" t="n">
+        <v>0</v>
+      </c>
+      <c r="L244" t="n">
+        <v>4514890.39712953</v>
+      </c>
+      <c r="M244" t="n">
+        <v>9477570.883508692</v>
+      </c>
+      <c r="N244" t="n">
+        <v>30101.63295948533</v>
+      </c>
+      <c r="O244" t="n">
+        <v>0</v>
+      </c>
+      <c r="P244" t="n">
+        <v>30101.63295948533</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>30099.2693141967</v>
+      </c>
+      <c r="R244" t="n">
+        <v>0</v>
+      </c>
+      <c r="S244" t="n">
+        <v>0</v>
+      </c>
+      <c r="T244" t="n">
+        <v>0</v>
+      </c>
+      <c r="U244" t="n">
+        <v>2.363645288733144</v>
+      </c>
+      <c r="V244" t="n">
+        <v>14.22800016403198</v>
+      </c>
+      <c r="W244" t="n">
+        <v>9477570.883508692</v>
+      </c>
+      <c r="X244" t="n">
+        <v>9477570.883508692</v>
+      </c>
+      <c r="Y244" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC244" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD244" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE244" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409204314_dh_1_ctax_150_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>6611536.374500076</v>
+      </c>
+      <c r="B245" t="n">
+        <v>3859334.57278088</v>
+      </c>
+      <c r="C245" t="n">
+        <v>3238773.500788544</v>
+      </c>
+      <c r="D245" t="n">
+        <v>3617467.604186256</v>
+      </c>
+      <c r="E245" t="n">
+        <v>0</v>
+      </c>
+      <c r="F245" t="n">
+        <v>7476802.176967137</v>
+      </c>
+      <c r="G245" t="n">
+        <v>3238773.500788544</v>
+      </c>
+      <c r="H245" t="n">
+        <v>3352841.246855168</v>
+      </c>
+      <c r="I245" t="n">
+        <v>-13738698.05225685</v>
+      </c>
+      <c r="J245" t="n">
+        <v>0</v>
+      </c>
+      <c r="K245" t="n">
+        <v>0</v>
+      </c>
+      <c r="L245" t="n">
+        <v>6281817.502146081</v>
+      </c>
+      <c r="M245" t="n">
+        <v>6611536.374500076</v>
+      </c>
+      <c r="N245" t="n">
+        <v>41881.1164947842</v>
+      </c>
+      <c r="O245" t="n">
+        <v>0</v>
+      </c>
+      <c r="P245" t="n">
+        <v>41881.1164947842</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>41878.78334764023</v>
+      </c>
+      <c r="R245" t="n">
+        <v>0</v>
+      </c>
+      <c r="S245" t="n">
+        <v>0</v>
+      </c>
+      <c r="T245" t="n">
+        <v>0</v>
+      </c>
+      <c r="U245" t="n">
+        <v>2.333147143966136</v>
+      </c>
+      <c r="V245" t="n">
+        <v>22.2480001449585</v>
+      </c>
+      <c r="W245" t="n">
+        <v>6611536.374500076</v>
+      </c>
+      <c r="X245" t="n">
+        <v>6611536.374500076</v>
+      </c>
+      <c r="Y245" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB245" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC245" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD245" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409204536_dh_1_ctax_150_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>62478.0002864562</v>
+      </c>
+      <c r="B246" t="n">
+        <v>0</v>
+      </c>
+      <c r="C246" t="n">
+        <v>0</v>
+      </c>
+      <c r="D246" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E246" t="n">
+        <v>0</v>
+      </c>
+      <c r="F246" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" t="n">
+        <v>2275717.794954614</v>
+      </c>
+      <c r="I246" t="n">
+        <v>-36181297.4014473</v>
+      </c>
+      <c r="J246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K246" t="n">
+        <v>0</v>
+      </c>
+      <c r="L246" t="n">
+        <v>33532328.83498367</v>
+      </c>
+      <c r="M246" t="n">
+        <v>62478.0002864562</v>
+      </c>
+      <c r="N246" t="n">
+        <v>223548.8588998911</v>
+      </c>
+      <c r="O246" t="n">
+        <v>0</v>
+      </c>
+      <c r="P246" t="n">
+        <v>223548.8588998911</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>223548.8588998911</v>
+      </c>
+      <c r="R246" t="n">
+        <v>0</v>
+      </c>
+      <c r="S246" t="n">
+        <v>0</v>
+      </c>
+      <c r="T246" t="n">
+        <v>0</v>
+      </c>
+      <c r="U246" t="n">
+        <v>0</v>
+      </c>
+      <c r="V246" t="n">
+        <v>24.17900013923645</v>
+      </c>
+      <c r="W246" t="n">
+        <v>62478.0002864562</v>
+      </c>
+      <c r="X246" t="n">
+        <v>62478.0002864562</v>
+      </c>
+      <c r="Y246" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD246" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409204806_dh_1_ctax_150_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>-7384589.217097677</v>
+      </c>
+      <c r="B247" t="n">
+        <v>0</v>
+      </c>
+      <c r="C247" t="n">
+        <v>0</v>
+      </c>
+      <c r="D247" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E247" t="n">
+        <v>0</v>
+      </c>
+      <c r="F247" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" t="n">
+        <v>3398482.612366882</v>
+      </c>
+      <c r="I247" t="n">
+        <v>-45530047.52832346</v>
+      </c>
+      <c r="J247" t="n">
+        <v>0</v>
+      </c>
+      <c r="K247" t="n">
+        <v>0</v>
+      </c>
+      <c r="L247" t="n">
+        <v>34311246.92706344</v>
+      </c>
+      <c r="M247" t="n">
+        <v>-7384589.217097677</v>
+      </c>
+      <c r="N247" t="n">
+        <v>228741.6461804228</v>
+      </c>
+      <c r="O247" t="n">
+        <v>0</v>
+      </c>
+      <c r="P247" t="n">
+        <v>228741.6461804228</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>228741.6461804228</v>
+      </c>
+      <c r="R247" t="n">
+        <v>0</v>
+      </c>
+      <c r="S247" t="n">
+        <v>0</v>
+      </c>
+      <c r="T247" t="n">
+        <v>0</v>
+      </c>
+      <c r="U247" t="n">
+        <v>0</v>
+      </c>
+      <c r="V247" t="n">
+        <v>11.94400000572205</v>
+      </c>
+      <c r="W247" t="n">
+        <v>-7384589.217097677</v>
+      </c>
+      <c r="X247" t="n">
+        <v>-7384589.217097677</v>
+      </c>
+      <c r="Y247" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC247" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD247" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE247" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409205053_dh_1_ctax_150_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>-15053248.70991591</v>
+      </c>
+      <c r="B248" t="n">
+        <v>0</v>
+      </c>
+      <c r="C248" t="n">
+        <v>0</v>
+      </c>
+      <c r="D248" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E248" t="n">
+        <v>0</v>
+      </c>
+      <c r="F248" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" t="n">
+        <v>3875514.618392541</v>
+      </c>
+      <c r="I248" t="n">
+        <v>-54006679.98134765</v>
+      </c>
+      <c r="J248" t="n">
+        <v>0</v>
+      </c>
+      <c r="K248" t="n">
+        <v>0</v>
+      </c>
+      <c r="L248" t="n">
+        <v>34642187.88124374</v>
+      </c>
+      <c r="M248" t="n">
+        <v>-15053248.70991591</v>
+      </c>
+      <c r="N248" t="n">
+        <v>230947.9192082915</v>
+      </c>
+      <c r="O248" t="n">
+        <v>0</v>
+      </c>
+      <c r="P248" t="n">
+        <v>230947.9192082915</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>230947.9192082915</v>
+      </c>
+      <c r="R248" t="n">
+        <v>0</v>
+      </c>
+      <c r="S248" t="n">
+        <v>0</v>
+      </c>
+      <c r="T248" t="n">
+        <v>0</v>
+      </c>
+      <c r="U248" t="n">
+        <v>0</v>
+      </c>
+      <c r="V248" t="n">
+        <v>12.1710000038147</v>
+      </c>
+      <c r="W248" t="n">
+        <v>-15053248.70991591</v>
+      </c>
+      <c r="X248" t="n">
+        <v>-15053248.70991591</v>
+      </c>
+      <c r="Y248" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC248" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD248" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409205326_dh_1_ctax_150_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>-24091377.66414457</v>
+      </c>
+      <c r="B249" t="n">
+        <v>31226380.04370679</v>
+      </c>
+      <c r="C249" t="n">
+        <v>4400143.355196329</v>
+      </c>
+      <c r="D249" t="n">
+        <v>22393383.94098206</v>
+      </c>
+      <c r="E249" t="n">
+        <v>0</v>
+      </c>
+      <c r="F249" t="n">
+        <v>53619763.98468886</v>
+      </c>
+      <c r="G249" t="n">
+        <v>4400143.355196329</v>
+      </c>
+      <c r="H249" t="n">
+        <v>6658779.769069648</v>
+      </c>
+      <c r="I249" t="n">
+        <v>-97891201.01177154</v>
+      </c>
+      <c r="J249" t="n">
+        <v>0</v>
+      </c>
+      <c r="K249" t="n">
+        <v>0</v>
+      </c>
+      <c r="L249" t="n">
+        <v>9121136.238672147</v>
+      </c>
+      <c r="M249" t="n">
+        <v>-24091377.66414457</v>
+      </c>
+      <c r="N249" t="n">
+        <v>60812.36079734494</v>
+      </c>
+      <c r="O249" t="n">
+        <v>0</v>
+      </c>
+      <c r="P249" t="n">
+        <v>60812.36079734494</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>60807.57492447986</v>
+      </c>
+      <c r="R249" t="n">
+        <v>0</v>
+      </c>
+      <c r="S249" t="n">
+        <v>0</v>
+      </c>
+      <c r="T249" t="n">
+        <v>0</v>
+      </c>
+      <c r="U249" t="n">
+        <v>4.785872864007006</v>
+      </c>
+      <c r="V249" t="n">
+        <v>15.03999996185303</v>
+      </c>
+      <c r="W249" t="n">
+        <v>-24091377.66414457</v>
+      </c>
+      <c r="X249" t="n">
+        <v>-24091377.66414457</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC249" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD249" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE249" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409205600_dh_1_ctax_150_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>15303532.06789121</v>
+      </c>
+      <c r="B250" t="n">
+        <v>4021759.637968136</v>
+      </c>
+      <c r="C250" t="n">
+        <v>3315079.812548094</v>
+      </c>
+      <c r="D250" t="n">
+        <v>3726765.870120138</v>
+      </c>
+      <c r="E250" t="n">
+        <v>0</v>
+      </c>
+      <c r="F250" t="n">
+        <v>7748525.508088274</v>
+      </c>
+      <c r="G250" t="n">
+        <v>3315079.812548094</v>
+      </c>
+      <c r="H250" t="n">
+        <v>1065818.406851869</v>
+      </c>
+      <c r="I250" t="n">
+        <v>-2189293.842234393</v>
+      </c>
+      <c r="J250" t="n">
+        <v>0</v>
+      </c>
+      <c r="K250" t="n">
+        <v>0</v>
+      </c>
+      <c r="L250" t="n">
+        <v>5363402.182637366</v>
+      </c>
+      <c r="M250" t="n">
+        <v>15303532.06789121</v>
+      </c>
+      <c r="N250" t="n">
+        <v>26819.4001139784</v>
+      </c>
+      <c r="O250" t="n">
+        <v>0</v>
+      </c>
+      <c r="P250" t="n">
+        <v>26819.4001139784</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>26817.0109131869</v>
+      </c>
+      <c r="R250" t="n">
+        <v>0</v>
+      </c>
+      <c r="S250" t="n">
+        <v>0</v>
+      </c>
+      <c r="T250" t="n">
+        <v>0</v>
+      </c>
+      <c r="U250" t="n">
+        <v>2.389200791459112</v>
+      </c>
+      <c r="V250" t="n">
+        <v>18.43400001525879</v>
+      </c>
+      <c r="W250" t="n">
+        <v>15303532.06789121</v>
+      </c>
+      <c r="X250" t="n">
+        <v>15303532.06789121</v>
+      </c>
+      <c r="Y250" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC250" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD250" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409205837_dh_1_ctax_200_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>13112576.23413161</v>
+      </c>
+      <c r="B251" t="n">
+        <v>4010171.755731796</v>
+      </c>
+      <c r="C251" t="n">
+        <v>3309635.720712662</v>
+      </c>
+      <c r="D251" t="n">
+        <v>3720218.83319391</v>
+      </c>
+      <c r="E251" t="n">
+        <v>0</v>
+      </c>
+      <c r="F251" t="n">
+        <v>7730390.588925706</v>
+      </c>
+      <c r="G251" t="n">
+        <v>3309635.720712662</v>
+      </c>
+      <c r="H251" t="n">
+        <v>1065353.221567235</v>
+      </c>
+      <c r="I251" t="n">
+        <v>-4385499.150017253</v>
+      </c>
+      <c r="J251" t="n">
+        <v>0</v>
+      </c>
+      <c r="K251" t="n">
+        <v>0</v>
+      </c>
+      <c r="L251" t="n">
+        <v>5392695.852943263</v>
+      </c>
+      <c r="M251" t="n">
+        <v>13112576.23413161</v>
+      </c>
+      <c r="N251" t="n">
+        <v>26965.86660775985</v>
+      </c>
+      <c r="O251" t="n">
+        <v>0</v>
+      </c>
+      <c r="P251" t="n">
+        <v>26965.86660775985</v>
+      </c>
+      <c r="Q251" t="n">
+        <v>26963.47926471628</v>
+      </c>
+      <c r="R251" t="n">
+        <v>0</v>
+      </c>
+      <c r="S251" t="n">
+        <v>0</v>
+      </c>
+      <c r="T251" t="n">
+        <v>0</v>
+      </c>
+      <c r="U251" t="n">
+        <v>2.387343043540727</v>
+      </c>
+      <c r="V251" t="n">
+        <v>19.70799994468689</v>
+      </c>
+      <c r="W251" t="n">
+        <v>13112576.23413161</v>
+      </c>
+      <c r="X251" t="n">
+        <v>13112576.23413161</v>
+      </c>
+      <c r="Y251" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC251" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD251" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409210117_dh_1_ctax_200_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>10897171.66731552</v>
+      </c>
+      <c r="B252" t="n">
+        <v>3996327.685210792</v>
+      </c>
+      <c r="C252" t="n">
+        <v>3303131.282574854</v>
+      </c>
+      <c r="D252" t="n">
+        <v>3712148.983041775</v>
+      </c>
+      <c r="E252" t="n">
+        <v>0</v>
+      </c>
+      <c r="F252" t="n">
+        <v>7708476.668252568</v>
+      </c>
+      <c r="G252" t="n">
+        <v>3303131.282574854</v>
+      </c>
+      <c r="H252" t="n">
+        <v>1137680.85705842</v>
+      </c>
+      <c r="I252" t="n">
+        <v>-6754031.837846552</v>
+      </c>
+      <c r="J252" t="n">
+        <v>0</v>
+      </c>
+      <c r="K252" t="n">
+        <v>0</v>
+      </c>
+      <c r="L252" t="n">
+        <v>5501914.697276236</v>
+      </c>
+      <c r="M252" t="n">
+        <v>10897171.66731552</v>
+      </c>
+      <c r="N252" t="n">
+        <v>27511.95818468827</v>
+      </c>
+      <c r="O252" t="n">
+        <v>0</v>
+      </c>
+      <c r="P252" t="n">
+        <v>27511.95818468827</v>
+      </c>
+      <c r="Q252" t="n">
+        <v>27509.57348638117</v>
+      </c>
+      <c r="R252" t="n">
+        <v>0</v>
+      </c>
+      <c r="S252" t="n">
+        <v>0</v>
+      </c>
+      <c r="T252" t="n">
+        <v>0</v>
+      </c>
+      <c r="U252" t="n">
+        <v>2.38469830719675</v>
+      </c>
+      <c r="V252" t="n">
+        <v>33.91299986839294</v>
+      </c>
+      <c r="W252" t="n">
+        <v>10897171.66731552</v>
+      </c>
+      <c r="X252" t="n">
+        <v>10897171.66731552</v>
+      </c>
+      <c r="Y252" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC252" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD252" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409210401_dh_1_ctax_200_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>8431159.805459101</v>
+      </c>
+      <c r="B253" t="n">
+        <v>3976586.81130441</v>
+      </c>
+      <c r="C253" t="n">
+        <v>3293856.684982591</v>
+      </c>
+      <c r="D253" t="n">
+        <v>3700087.936445781</v>
+      </c>
+      <c r="E253" t="n">
+        <v>0</v>
+      </c>
+      <c r="F253" t="n">
+        <v>7676674.747750191</v>
+      </c>
+      <c r="G253" t="n">
+        <v>3293856.684982591</v>
+      </c>
+      <c r="H253" t="n">
+        <v>2173941.482569549</v>
+      </c>
+      <c r="I253" t="n">
+        <v>-11249276.64068091</v>
+      </c>
+      <c r="J253" t="n">
+        <v>0</v>
+      </c>
+      <c r="K253" t="n">
+        <v>0</v>
+      </c>
+      <c r="L253" t="n">
+        <v>6535963.530837682</v>
+      </c>
+      <c r="M253" t="n">
+        <v>8431159.805459101</v>
+      </c>
+      <c r="N253" t="n">
+        <v>32682.19763326064</v>
+      </c>
+      <c r="O253" t="n">
+        <v>0</v>
+      </c>
+      <c r="P253" t="n">
+        <v>32682.19763326064</v>
+      </c>
+      <c r="Q253" t="n">
+        <v>32679.81765418823</v>
+      </c>
+      <c r="R253" t="n">
+        <v>0</v>
+      </c>
+      <c r="S253" t="n">
+        <v>0</v>
+      </c>
+      <c r="T253" t="n">
+        <v>0</v>
+      </c>
+      <c r="U253" t="n">
+        <v>2.379979072511524</v>
+      </c>
+      <c r="V253" t="n">
+        <v>42.44900012016296</v>
+      </c>
+      <c r="W253" t="n">
+        <v>8431159.805459101</v>
+      </c>
+      <c r="X253" t="n">
+        <v>8431159.805459101</v>
+      </c>
+      <c r="Y253" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC253" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD253" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE253" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409211130_dh_1_ctax_200_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>5104377.096970277</v>
+      </c>
+      <c r="B254" t="n">
+        <v>3944751.412615256</v>
+      </c>
+      <c r="C254" t="n">
+        <v>3278901.282302473</v>
+      </c>
+      <c r="D254" t="n">
+        <v>3679465.036767517</v>
+      </c>
+      <c r="E254" t="n">
+        <v>0</v>
+      </c>
+      <c r="F254" t="n">
+        <v>7624216.449382773</v>
+      </c>
+      <c r="G254" t="n">
+        <v>3278901.282302473</v>
+      </c>
+      <c r="H254" t="n">
+        <v>4879318.447686139</v>
+      </c>
+      <c r="I254" t="n">
+        <v>-19870359.79704779</v>
+      </c>
+      <c r="J254" t="n">
+        <v>0</v>
+      </c>
+      <c r="K254" t="n">
+        <v>0</v>
+      </c>
+      <c r="L254" t="n">
+        <v>9192300.714646682</v>
+      </c>
+      <c r="M254" t="n">
+        <v>5104377.096970277</v>
+      </c>
+      <c r="N254" t="n">
+        <v>45963.87393583735</v>
+      </c>
+      <c r="O254" t="n">
+        <v>0</v>
+      </c>
+      <c r="P254" t="n">
+        <v>45963.87393583735</v>
+      </c>
+      <c r="Q254" t="n">
+        <v>45961.50357323323</v>
+      </c>
+      <c r="R254" t="n">
+        <v>0</v>
+      </c>
+      <c r="S254" t="n">
+        <v>0</v>
+      </c>
+      <c r="T254" t="n">
+        <v>0</v>
+      </c>
+      <c r="U254" t="n">
+        <v>2.370362604319264</v>
+      </c>
+      <c r="V254" t="n">
+        <v>33.80199980735779</v>
+      </c>
+      <c r="W254" t="n">
+        <v>5104377.096970277</v>
+      </c>
+      <c r="X254" t="n">
+        <v>5104377.096970277</v>
+      </c>
+      <c r="Y254" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC254" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD254" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409211437_dh_1_ctax_200_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>384301.5889070705</v>
+      </c>
+      <c r="B255" t="n">
+        <v>3912521.630760927</v>
+      </c>
+      <c r="C255" t="n">
+        <v>3263760.590338029</v>
+      </c>
+      <c r="D255" t="n">
+        <v>3656675.275057851</v>
+      </c>
+      <c r="E255" t="n">
+        <v>0</v>
+      </c>
+      <c r="F255" t="n">
+        <v>7569196.905818779</v>
+      </c>
+      <c r="G255" t="n">
+        <v>3263760.590338029</v>
+      </c>
+      <c r="H255" t="n">
+        <v>8962806.777790256</v>
+      </c>
+      <c r="I255" t="n">
+        <v>-32589127.33766071</v>
+      </c>
+      <c r="J255" t="n">
+        <v>0</v>
+      </c>
+      <c r="K255" t="n">
+        <v>0</v>
+      </c>
+      <c r="L255" t="n">
+        <v>13177664.65262072</v>
+      </c>
+      <c r="M255" t="n">
+        <v>384301.5889070705</v>
+      </c>
+      <c r="N255" t="n">
+        <v>65890.68061713089</v>
+      </c>
+      <c r="O255" t="n">
+        <v>0</v>
+      </c>
+      <c r="P255" t="n">
+        <v>65890.68061713089</v>
+      </c>
+      <c r="Q255" t="n">
+        <v>65888.32326310361</v>
+      </c>
+      <c r="R255" t="n">
+        <v>0</v>
+      </c>
+      <c r="S255" t="n">
+        <v>0</v>
+      </c>
+      <c r="T255" t="n">
+        <v>0</v>
+      </c>
+      <c r="U255" t="n">
+        <v>2.357354027280028</v>
+      </c>
+      <c r="V255" t="n">
+        <v>29.65599989891052</v>
+      </c>
+      <c r="W255" t="n">
+        <v>384301.5889070705</v>
+      </c>
+      <c r="X255" t="n">
+        <v>384301.5889070705</v>
+      </c>
+      <c r="Y255" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC255" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD255" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE255" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409211737_dh_1_ctax_200_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>-8942627.72777753</v>
+      </c>
+      <c r="B256" t="n">
+        <v>31572859.92774187</v>
+      </c>
+      <c r="C256" t="n">
+        <v>4433066.460455095</v>
+      </c>
+      <c r="D256" t="n">
+        <v>22633399.01066497</v>
+      </c>
+      <c r="E256" t="n">
+        <v>0</v>
+      </c>
+      <c r="F256" t="n">
+        <v>54206258.93840684</v>
+      </c>
+      <c r="G256" t="n">
+        <v>4433066.460455095</v>
+      </c>
+      <c r="H256" t="n">
+        <v>6143855.308541361</v>
+      </c>
+      <c r="I256" t="n">
+        <v>-85042395.01753746</v>
+      </c>
+      <c r="J256" t="n">
+        <v>0</v>
+      </c>
+      <c r="K256" t="n">
+        <v>0</v>
+      </c>
+      <c r="L256" t="n">
+        <v>11316586.58235663</v>
+      </c>
+      <c r="M256" t="n">
+        <v>-8942627.72777753</v>
+      </c>
+      <c r="N256" t="n">
+        <v>56587.76698298996</v>
+      </c>
+      <c r="O256" t="n">
+        <v>0</v>
+      </c>
+      <c r="P256" t="n">
+        <v>56587.76698298996</v>
+      </c>
+      <c r="Q256" t="n">
+        <v>56582.9329117821</v>
+      </c>
+      <c r="R256" t="n">
+        <v>0</v>
+      </c>
+      <c r="S256" t="n">
+        <v>0</v>
+      </c>
+      <c r="T256" t="n">
+        <v>0</v>
+      </c>
+      <c r="U256" t="n">
+        <v>4.834071206764877</v>
+      </c>
+      <c r="V256" t="n">
+        <v>30.86800003051758</v>
+      </c>
+      <c r="W256" t="n">
+        <v>-8942627.72777753</v>
+      </c>
+      <c r="X256" t="n">
+        <v>-8942627.72777753</v>
+      </c>
+      <c r="Y256" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC256" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD256" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE256" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409212032_dh_1_ctax_200_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>-21160679.92385862</v>
+      </c>
+      <c r="B257" t="n">
+        <v>31845651.81514538</v>
+      </c>
+      <c r="C257" t="n">
+        <v>4458987.607501581</v>
+      </c>
+      <c r="D257" t="n">
+        <v>22820313.98211749</v>
+      </c>
+      <c r="E257" t="n">
+        <v>0</v>
+      </c>
+      <c r="F257" t="n">
+        <v>54665965.79726287</v>
+      </c>
+      <c r="G257" t="n">
+        <v>4458987.607501581</v>
+      </c>
+      <c r="H257" t="n">
+        <v>6496561.063224415</v>
+      </c>
+      <c r="I257" t="n">
+        <v>-98156089.07387105</v>
+      </c>
+      <c r="J257" t="n">
+        <v>0</v>
+      </c>
+      <c r="K257" t="n">
+        <v>0</v>
+      </c>
+      <c r="L257" t="n">
+        <v>11373894.68202357</v>
+      </c>
+      <c r="M257" t="n">
+        <v>-21160679.92385862</v>
+      </c>
+      <c r="N257" t="n">
+        <v>56874.34264646687</v>
+      </c>
+      <c r="O257" t="n">
+        <v>0</v>
+      </c>
+      <c r="P257" t="n">
+        <v>56874.34264646687</v>
+      </c>
+      <c r="Q257" t="n">
+        <v>56869.47341011782</v>
+      </c>
+      <c r="R257" t="n">
+        <v>0</v>
+      </c>
+      <c r="S257" t="n">
+        <v>0</v>
+      </c>
+      <c r="T257" t="n">
+        <v>0</v>
+      </c>
+      <c r="U257" t="n">
+        <v>4.869236349029795</v>
+      </c>
+      <c r="V257" t="n">
+        <v>27.34700012207031</v>
+      </c>
+      <c r="W257" t="n">
+        <v>-21160679.92385862</v>
+      </c>
+      <c r="X257" t="n">
+        <v>-21160679.92385862</v>
+      </c>
+      <c r="Y257" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC257" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD257" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE257" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409212329_dh_1_ctax_200_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>16639997.0668359</v>
+      </c>
+      <c r="B258" t="n">
+        <v>4036624.974126604</v>
+      </c>
+      <c r="C258" t="n">
+        <v>3322063.903070181</v>
+      </c>
+      <c r="D258" t="n">
+        <v>3734908.582965364</v>
+      </c>
+      <c r="E258" t="n">
+        <v>0</v>
+      </c>
+      <c r="F258" t="n">
+        <v>7771533.557091968</v>
+      </c>
+      <c r="G258" t="n">
+        <v>3322063.903070181</v>
+      </c>
+      <c r="H258" t="n">
+        <v>1066227.470191716</v>
+      </c>
+      <c r="I258" t="n">
+        <v>-2185653.367093981</v>
+      </c>
+      <c r="J258" t="n">
+        <v>0</v>
+      </c>
+      <c r="K258" t="n">
+        <v>0</v>
+      </c>
+      <c r="L258" t="n">
+        <v>6665825.503576017</v>
+      </c>
+      <c r="M258" t="n">
+        <v>16639997.0668359</v>
+      </c>
+      <c r="N258" t="n">
+        <v>26665.69316010576</v>
+      </c>
+      <c r="O258" t="n">
+        <v>0</v>
+      </c>
+      <c r="P258" t="n">
+        <v>26665.69316010576</v>
+      </c>
+      <c r="Q258" t="n">
+        <v>26663.30201430412</v>
+      </c>
+      <c r="R258" t="n">
+        <v>0</v>
+      </c>
+      <c r="S258" t="n">
+        <v>0</v>
+      </c>
+      <c r="T258" t="n">
+        <v>0</v>
+      </c>
+      <c r="U258" t="n">
+        <v>2.391145801669481</v>
+      </c>
+      <c r="V258" t="n">
+        <v>27.49399995803833</v>
+      </c>
+      <c r="W258" t="n">
+        <v>16639997.0668359</v>
+      </c>
+      <c r="X258" t="n">
+        <v>16639997.0668359</v>
+      </c>
+      <c r="Y258" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC258" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD258" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE258" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409212624_dh_1_ctax_250_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>14453735.03800246</v>
+      </c>
+      <c r="B259" t="n">
+        <v>4030919.040461549</v>
+      </c>
+      <c r="C259" t="n">
+        <v>3319383.226548138</v>
+      </c>
+      <c r="D259" t="n">
+        <v>3731817.680510193</v>
+      </c>
+      <c r="E259" t="n">
+        <v>0</v>
+      </c>
+      <c r="F259" t="n">
+        <v>7762736.720971742</v>
+      </c>
+      <c r="G259" t="n">
+        <v>3319383.226548138</v>
+      </c>
+      <c r="H259" t="n">
+        <v>1066083.409134711</v>
+      </c>
+      <c r="I259" t="n">
+        <v>-4373870.79903931</v>
+      </c>
+      <c r="J259" t="n">
+        <v>0</v>
+      </c>
+      <c r="K259" t="n">
+        <v>0</v>
+      </c>
+      <c r="L259" t="n">
+        <v>6679402.480387182</v>
+      </c>
+      <c r="M259" t="n">
+        <v>14453735.03800246</v>
+      </c>
+      <c r="N259" t="n">
+        <v>26720.00038017293</v>
+      </c>
+      <c r="O259" t="n">
+        <v>0</v>
+      </c>
+      <c r="P259" t="n">
+        <v>26720.00038017293</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>26717.60992154868</v>
+      </c>
+      <c r="R259" t="n">
+        <v>0</v>
+      </c>
+      <c r="S259" t="n">
+        <v>0</v>
+      </c>
+      <c r="T259" t="n">
+        <v>0</v>
+      </c>
+      <c r="U259" t="n">
+        <v>2.390458624299066</v>
+      </c>
+      <c r="V259" t="n">
+        <v>38.21300005912781</v>
+      </c>
+      <c r="W259" t="n">
+        <v>14453735.03800246</v>
+      </c>
+      <c r="X259" t="n">
+        <v>14453735.03800246</v>
+      </c>
+      <c r="Y259" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC259" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD259" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE259" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409212919_dh_1_ctax_250_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>12257325.43294577</v>
+      </c>
+      <c r="B260" t="n">
+        <v>4022615.451018038</v>
+      </c>
+      <c r="C260" t="n">
+        <v>3315481.904045112</v>
+      </c>
+      <c r="D260" t="n">
+        <v>3727242.584967434</v>
+      </c>
+      <c r="E260" t="n">
+        <v>0</v>
+      </c>
+      <c r="F260" t="n">
+        <v>7749858.035985473</v>
+      </c>
+      <c r="G260" t="n">
+        <v>3315481.904045112</v>
+      </c>
+      <c r="H260" t="n">
+        <v>1096289.820328449</v>
+      </c>
+      <c r="I260" t="n">
+        <v>-6641278.259634858</v>
+      </c>
+      <c r="J260" t="n">
+        <v>0</v>
+      </c>
+      <c r="K260" t="n">
+        <v>0</v>
+      </c>
+      <c r="L260" t="n">
+        <v>6736973.932221589</v>
+      </c>
+      <c r="M260" t="n">
+        <v>12257325.43294577</v>
+      </c>
+      <c r="N260" t="n">
+        <v>26950.28505524618</v>
+      </c>
+      <c r="O260" t="n">
+        <v>0</v>
+      </c>
+      <c r="P260" t="n">
+        <v>26950.28505524618</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>26947.89572888641</v>
+      </c>
+      <c r="R260" t="n">
+        <v>0</v>
+      </c>
+      <c r="S260" t="n">
+        <v>0</v>
+      </c>
+      <c r="T260" t="n">
+        <v>0</v>
+      </c>
+      <c r="U260" t="n">
+        <v>2.389326359854483</v>
+      </c>
+      <c r="V260" t="n">
+        <v>39.3050000667572</v>
+      </c>
+      <c r="W260" t="n">
+        <v>12257325.43294577</v>
+      </c>
+      <c r="X260" t="n">
+        <v>12257325.43294577</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC260" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD260" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE260" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409213224_dh_1_ctax_250_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>9966655.689191142</v>
+      </c>
+      <c r="B261" t="n">
+        <v>4011563.850009988</v>
+      </c>
+      <c r="C261" t="n">
+        <v>3310289.776259458</v>
+      </c>
+      <c r="D261" t="n">
+        <v>3721014.415072524</v>
+      </c>
+      <c r="E261" t="n">
+        <v>0</v>
+      </c>
+      <c r="F261" t="n">
+        <v>7732578.265082512</v>
+      </c>
+      <c r="G261" t="n">
+        <v>3310289.776259458</v>
+      </c>
+      <c r="H261" t="n">
+        <v>1498594.495543832</v>
+      </c>
+      <c r="I261" t="n">
+        <v>-9811837.026055846</v>
+      </c>
+      <c r="J261" t="n">
+        <v>0</v>
+      </c>
+      <c r="K261" t="n">
+        <v>0</v>
+      </c>
+      <c r="L261" t="n">
+        <v>7237030.178361187</v>
+      </c>
+      <c r="M261" t="n">
+        <v>9966655.689191142</v>
+      </c>
+      <c r="N261" t="n">
+        <v>28950.50829523134</v>
+      </c>
+      <c r="O261" t="n">
+        <v>0</v>
+      </c>
+      <c r="P261" t="n">
+        <v>28950.50829523134</v>
+      </c>
+      <c r="Q261" t="n">
+        <v>28948.12071344485</v>
+      </c>
+      <c r="R261" t="n">
+        <v>0</v>
+      </c>
+      <c r="S261" t="n">
+        <v>0</v>
+      </c>
+      <c r="T261" t="n">
+        <v>0</v>
+      </c>
+      <c r="U261" t="n">
+        <v>2.387581786583392</v>
+      </c>
+      <c r="V261" t="n">
+        <v>39.65700006484985</v>
+      </c>
+      <c r="W261" t="n">
+        <v>9966655.689191142</v>
+      </c>
+      <c r="X261" t="n">
+        <v>9966655.689191142</v>
+      </c>
+      <c r="Y261" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC261" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD261" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE261" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409213533_dh_1_ctax_250_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>7136245.687074631</v>
+      </c>
+      <c r="B262" t="n">
+        <v>3999975.12223014</v>
+      </c>
+      <c r="C262" t="n">
+        <v>3304844.978587735</v>
+      </c>
+      <c r="D262" t="n">
+        <v>3714242.97417877</v>
+      </c>
+      <c r="E262" t="n">
+        <v>0</v>
+      </c>
+      <c r="F262" t="n">
+        <v>7714218.09640891</v>
+      </c>
+      <c r="G262" t="n">
+        <v>3304844.978587735</v>
+      </c>
+      <c r="H262" t="n">
+        <v>3149098.471467149</v>
+      </c>
+      <c r="I262" t="n">
+        <v>-16222175.50580761</v>
+      </c>
+      <c r="J262" t="n">
+        <v>0</v>
+      </c>
+      <c r="K262" t="n">
+        <v>0</v>
+      </c>
+      <c r="L262" t="n">
+        <v>9190259.646418449</v>
+      </c>
+      <c r="M262" t="n">
+        <v>7136245.687074631</v>
+      </c>
+      <c r="N262" t="n">
+        <v>36763.42392574815</v>
+      </c>
+      <c r="O262" t="n">
+        <v>0</v>
+      </c>
+      <c r="P262" t="n">
+        <v>36763.42392574815</v>
+      </c>
+      <c r="Q262" t="n">
+        <v>36761.03858567389</v>
+      </c>
+      <c r="R262" t="n">
+        <v>0</v>
+      </c>
+      <c r="S262" t="n">
+        <v>0</v>
+      </c>
+      <c r="T262" t="n">
+        <v>0</v>
+      </c>
+      <c r="U262" t="n">
+        <v>2.385340074288595</v>
+      </c>
+      <c r="V262" t="n">
+        <v>50.06800007820129</v>
+      </c>
+      <c r="W262" t="n">
+        <v>7136245.687074631</v>
+      </c>
+      <c r="X262" t="n">
+        <v>7136245.687074631</v>
+      </c>
+      <c r="Y262" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC262" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD262" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE262" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409213842_dh_1_ctax_250_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>3305685.75627007</v>
+      </c>
+      <c r="B263" t="n">
+        <v>3987597.262628307</v>
+      </c>
+      <c r="C263" t="n">
+        <v>3299029.418638337</v>
+      </c>
+      <c r="D263" t="n">
+        <v>3706787.901126604</v>
+      </c>
+      <c r="E263" t="n">
+        <v>0</v>
+      </c>
+      <c r="F263" t="n">
+        <v>7694385.16375491</v>
+      </c>
+      <c r="G263" t="n">
+        <v>3299029.418638337</v>
+      </c>
+      <c r="H263" t="n">
+        <v>6251334.825022924</v>
+      </c>
+      <c r="I263" t="n">
+        <v>-26771792.37332096</v>
+      </c>
+      <c r="J263" t="n">
+        <v>0</v>
+      </c>
+      <c r="K263" t="n">
+        <v>0</v>
+      </c>
+      <c r="L263" t="n">
+        <v>12832728.72217485</v>
+      </c>
+      <c r="M263" t="n">
+        <v>3305685.75627007</v>
+      </c>
+      <c r="N263" t="n">
+        <v>51333.29745335915</v>
+      </c>
+      <c r="O263" t="n">
+        <v>0</v>
+      </c>
+      <c r="P263" t="n">
+        <v>51333.29745335915</v>
+      </c>
+      <c r="Q263" t="n">
+        <v>51330.91488869942</v>
+      </c>
+      <c r="R263" t="n">
+        <v>0</v>
+      </c>
+      <c r="S263" t="n">
+        <v>0</v>
+      </c>
+      <c r="T263" t="n">
+        <v>0</v>
+      </c>
+      <c r="U263" t="n">
+        <v>2.382564659690719</v>
+      </c>
+      <c r="V263" t="n">
+        <v>39.98000001907349</v>
+      </c>
+      <c r="W263" t="n">
+        <v>3305685.75627007</v>
+      </c>
+      <c r="X263" t="n">
+        <v>3305685.75627007</v>
+      </c>
+      <c r="Y263" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC263" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD263" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE263" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409214202_dh_1_ctax_250_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>-6234021.569075886</v>
+      </c>
+      <c r="B264" t="n">
+        <v>32022539.03271046</v>
+      </c>
+      <c r="C264" t="n">
+        <v>4475795.730429249</v>
+      </c>
+      <c r="D264" t="n">
+        <v>22940355.14542694</v>
+      </c>
+      <c r="E264" t="n">
+        <v>0</v>
+      </c>
+      <c r="F264" t="n">
+        <v>54962894.17813741</v>
+      </c>
+      <c r="G264" t="n">
+        <v>4475795.730429249</v>
+      </c>
+      <c r="H264" t="n">
+        <v>5638664.602735557</v>
+      </c>
+      <c r="I264" t="n">
+        <v>-84333837.88709503</v>
+      </c>
+      <c r="J264" t="n">
+        <v>0</v>
+      </c>
+      <c r="K264" t="n">
+        <v>0</v>
+      </c>
+      <c r="L264" t="n">
+        <v>13022461.80671694</v>
+      </c>
+      <c r="M264" t="n">
+        <v>-6234021.569075886</v>
+      </c>
+      <c r="N264" t="n">
+        <v>52094.73769360053</v>
+      </c>
+      <c r="O264" t="n">
+        <v>0</v>
+      </c>
+      <c r="P264" t="n">
+        <v>52094.73769360053</v>
+      </c>
+      <c r="Q264" t="n">
+        <v>52089.84722686773</v>
+      </c>
+      <c r="R264" t="n">
+        <v>0</v>
+      </c>
+      <c r="S264" t="n">
+        <v>0</v>
+      </c>
+      <c r="T264" t="n">
+        <v>0</v>
+      </c>
+      <c r="U264" t="n">
+        <v>4.89046673279933</v>
+      </c>
+      <c r="V264" t="n">
+        <v>34.90400004386902</v>
+      </c>
+      <c r="W264" t="n">
+        <v>-6234021.569075886</v>
+      </c>
+      <c r="X264" t="n">
+        <v>-6234021.569075886</v>
+      </c>
+      <c r="Y264" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC264" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD264" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE264" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409215113_dh_1_ctax_250_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>-18384469.71401452</v>
+      </c>
+      <c r="B265" t="n">
+        <v>32192029.80639485</v>
+      </c>
+      <c r="C265" t="n">
+        <v>4491901.030735329</v>
+      </c>
+      <c r="D265" t="n">
+        <v>23054399.83895468</v>
+      </c>
+      <c r="E265" t="n">
+        <v>0</v>
+      </c>
+      <c r="F265" t="n">
+        <v>55246429.64534953</v>
+      </c>
+      <c r="G265" t="n">
+        <v>4491901.030735329</v>
+      </c>
+      <c r="H265" t="n">
+        <v>6264977.752830625</v>
+      </c>
+      <c r="I265" t="n">
+        <v>-97952587.0951716</v>
+      </c>
+      <c r="J265" t="n">
+        <v>0</v>
+      </c>
+      <c r="K265" t="n">
+        <v>0</v>
+      </c>
+      <c r="L265" t="n">
+        <v>13564808.9522416</v>
+      </c>
+      <c r="M265" t="n">
+        <v>-18384469.71401452</v>
+      </c>
+      <c r="N265" t="n">
+        <v>54264.145295184</v>
+      </c>
+      <c r="O265" t="n">
+        <v>0</v>
+      </c>
+      <c r="P265" t="n">
+        <v>54264.145295184</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>54259.2358089664</v>
+      </c>
+      <c r="R265" t="n">
+        <v>0</v>
+      </c>
+      <c r="S265" t="n">
+        <v>0</v>
+      </c>
+      <c r="T265" t="n">
+        <v>0</v>
+      </c>
+      <c r="U265" t="n">
+        <v>4.909486217584692</v>
+      </c>
+      <c r="V265" t="n">
+        <v>30.12599992752075</v>
+      </c>
+      <c r="W265" t="n">
+        <v>-18384469.71401452</v>
+      </c>
+      <c r="X265" t="n">
+        <v>-18384469.71401452</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC265" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD265" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE265" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260409215419_dh_1_ctax_250_el_price_400</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_WtE/raw_results/technology_selection/Summary.xlsx
+++ b/dataCaseStudy_WtE/raw_results/technology_selection/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE130"/>
+  <dimension ref="A1:AE194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13869,6 +13869,6598 @@
       <c r="AE130" t="inlineStr">
         <is>
           <t>dataCaseStudy_WtE\raw_results\tech_sel_CaL\20260416223127_dh_1_ctax_250_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>11848649.15001597</v>
+      </c>
+      <c r="B131" t="n">
+        <v>4496791.901331041</v>
+      </c>
+      <c r="C131" t="n">
+        <v>3254895.4035373</v>
+      </c>
+      <c r="D131" t="n">
+        <v>3922233.632322108</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" t="n">
+        <v>8419025.533653149</v>
+      </c>
+      <c r="G131" t="n">
+        <v>3254895.4035373</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>-2403520.371525242</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
+        <v>2578248.584350756</v>
+      </c>
+      <c r="M131" t="n">
+        <v>11848649.15001597</v>
+      </c>
+      <c r="N131" t="n">
+        <v>25784.82635823535</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>25784.82635823535</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>25782.48584350741</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0</v>
+      </c>
+      <c r="U131" t="n">
+        <v>2.340514728183982</v>
+      </c>
+      <c r="V131" t="n">
+        <v>17.83699989318848</v>
+      </c>
+      <c r="W131" t="n">
+        <v>11848649.15001597</v>
+      </c>
+      <c r="X131" t="n">
+        <v>11848649.15001597</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417164302_dh_0.5_ctax_100_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>7692927.423242366</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>16087.92112087848</v>
+      </c>
+      <c r="I132" t="n">
+        <v>-14068696.34301499</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>21309807.07334101</v>
+      </c>
+      <c r="M132" t="n">
+        <v>7692927.423242366</v>
+      </c>
+      <c r="N132" t="n">
+        <v>213098.07073341</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>213098.07073341</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>213098.07073341</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0</v>
+      </c>
+      <c r="V132" t="n">
+        <v>15.8970000743866</v>
+      </c>
+      <c r="W132" t="n">
+        <v>7692927.423242366</v>
+      </c>
+      <c r="X132" t="n">
+        <v>7692927.423242366</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417164543_dh_0.5_ctax_100_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>616427.8433460556</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>250352.7371741842</v>
+      </c>
+      <c r="I133" t="n">
+        <v>-21487808.21638926</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
+        <v>21418154.55076566</v>
+      </c>
+      <c r="M133" t="n">
+        <v>616427.8433460556</v>
+      </c>
+      <c r="N133" t="n">
+        <v>214181.5455076566</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>214181.5455076566</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>214181.5455076566</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0</v>
+      </c>
+      <c r="V133" t="n">
+        <v>6.777999877929688</v>
+      </c>
+      <c r="W133" t="n">
+        <v>616427.8433459736</v>
+      </c>
+      <c r="X133" t="n">
+        <v>616427.8433460556</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>8.195638656616211e-08</v>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417164813_dh_0.5_ctax_100_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>-6664264.485831395</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>871463.3829878251</v>
+      </c>
+      <c r="I134" t="n">
+        <v>-29676874.86506916</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="n">
+        <v>21705418.22445447</v>
+      </c>
+      <c r="M134" t="n">
+        <v>-6664264.485831395</v>
+      </c>
+      <c r="N134" t="n">
+        <v>217054.1822445446</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>217054.1822445446</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>217054.1822445447</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0</v>
+      </c>
+      <c r="V134" t="n">
+        <v>5.07699990272522</v>
+      </c>
+      <c r="W134" t="n">
+        <v>-6664264.485831395</v>
+      </c>
+      <c r="X134" t="n">
+        <v>-6664264.485831395</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417165043_dh_0.5_ctax_100_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>-14223105.46445471</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>1637043.526087382</v>
+      </c>
+      <c r="I135" t="n">
+        <v>-38355376.80297558</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
+        <v>22059499.04063802</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-14223105.46445471</v>
+      </c>
+      <c r="N135" t="n">
+        <v>220594.9904063801</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>220594.9904063801</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>220594.9904063801</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" t="n">
+        <v>4.51800012588501</v>
+      </c>
+      <c r="W135" t="n">
+        <v>-14223105.46445471</v>
+      </c>
+      <c r="X135" t="n">
+        <v>-14223105.46445471</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417165303_dh_0.5_ctax_100_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>-21942439.48836367</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>1931930.186764378</v>
+      </c>
+      <c r="I136" t="n">
+        <v>-46505982.56812464</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
+        <v>22195884.12120113</v>
+      </c>
+      <c r="M136" t="n">
+        <v>-21942439.48836367</v>
+      </c>
+      <c r="N136" t="n">
+        <v>221958.8412120113</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>221958.8412120113</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>221958.8412120112</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0</v>
+      </c>
+      <c r="V136" t="n">
+        <v>4.496999979019165</v>
+      </c>
+      <c r="W136" t="n">
+        <v>-21942439.48836367</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-21942439.48836367</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417165527_dh_0.5_ctax_100_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>-29708118.43058869</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" t="n">
+        <v>435728.7717954647</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" t="n">
+        <v>435728.7717954658</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>2049307.205451946</v>
+      </c>
+      <c r="I137" t="n">
+        <v>-54443325.40018023</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
+        <v>22250170.99234413</v>
+      </c>
+      <c r="M137" t="n">
+        <v>-29708118.43058869</v>
+      </c>
+      <c r="N137" t="n">
+        <v>222501.7099234413</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>222501.7099234413</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>222501.7099234412</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0</v>
+      </c>
+      <c r="V137" t="n">
+        <v>6.610000133514404</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-29708118.43058869</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-29708118.43058869</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417165755_dh_0.5_ctax_100_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>-37489730.88745569</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>2081367.532328885</v>
+      </c>
+      <c r="I138" t="n">
+        <v>-62271826.08510476</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>22264998.89352471</v>
+      </c>
+      <c r="M138" t="n">
+        <v>-37489730.88745569</v>
+      </c>
+      <c r="N138" t="n">
+        <v>222649.9889352471</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>222649.9889352471</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>222649.9889352471</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0</v>
+      </c>
+      <c r="V138" t="n">
+        <v>5.461999893188477</v>
+      </c>
+      <c r="W138" t="n">
+        <v>-37489730.88745569</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-37489730.88745569</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD138" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417170029_dh_0.5_ctax_100_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>13040862.50238379</v>
+      </c>
+      <c r="B139" t="n">
+        <v>4606697.01508003</v>
+      </c>
+      <c r="C139" t="n">
+        <v>3296311.782785068</v>
+      </c>
+      <c r="D139" t="n">
+        <v>3997918.753663895</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" t="n">
+        <v>8604615.768743925</v>
+      </c>
+      <c r="G139" t="n">
+        <v>3296311.782785068</v>
+      </c>
+      <c r="H139" t="n">
+        <v>61649.79858812681</v>
+      </c>
+      <c r="I139" t="n">
+        <v>-2341213.361767607</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
+        <v>3419498.514034279</v>
+      </c>
+      <c r="M139" t="n">
+        <v>13040862.50238379</v>
+      </c>
+      <c r="N139" t="n">
+        <v>22799.03816194926</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>22799.03816194926</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>22796.65676022858</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0</v>
+      </c>
+      <c r="U139" t="n">
+        <v>2.381401720705843</v>
+      </c>
+      <c r="V139" t="n">
+        <v>11.72100019454956</v>
+      </c>
+      <c r="W139" t="n">
+        <v>13040862.50238379</v>
+      </c>
+      <c r="X139" t="n">
+        <v>13040862.50238379</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417170310_dh_0.5_ctax_150_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>10690839.24273433</v>
+      </c>
+      <c r="B140" t="n">
+        <v>4566176.867306454</v>
+      </c>
+      <c r="C140" t="n">
+        <v>3281042.319004511</v>
+      </c>
+      <c r="D140" t="n">
+        <v>3973447.188271914</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" t="n">
+        <v>8539624.055578368</v>
+      </c>
+      <c r="G140" t="n">
+        <v>3281042.319004511</v>
+      </c>
+      <c r="H140" t="n">
+        <v>71057.05106035015</v>
+      </c>
+      <c r="I140" t="n">
+        <v>-4737273.459144993</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>3536389.276236091</v>
+      </c>
+      <c r="M140" t="n">
+        <v>10690839.24273433</v>
+      </c>
+      <c r="N140" t="n">
+        <v>23578.30071292132</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>23578.30071292132</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>23575.92850824055</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" t="n">
+        <v>2.372204680639244</v>
+      </c>
+      <c r="V140" t="n">
+        <v>11.95000004768372</v>
+      </c>
+      <c r="W140" t="n">
+        <v>10690839.24273433</v>
+      </c>
+      <c r="X140" t="n">
+        <v>10690839.24273433</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417170520_dh_0.5_ctax_150_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>8256593.6895591</v>
+      </c>
+      <c r="B141" t="n">
+        <v>4490419.675538186</v>
+      </c>
+      <c r="C141" t="n">
+        <v>3252494.092406618</v>
+      </c>
+      <c r="D141" t="n">
+        <v>3924290.074034605</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" t="n">
+        <v>8414709.749572791</v>
+      </c>
+      <c r="G141" t="n">
+        <v>3252494.092406618</v>
+      </c>
+      <c r="H141" t="n">
+        <v>332190.6098252513</v>
+      </c>
+      <c r="I141" t="n">
+        <v>-7736653.150511968</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="n">
+        <v>3993852.388266406</v>
+      </c>
+      <c r="M141" t="n">
+        <v>8256593.6895591</v>
+      </c>
+      <c r="N141" t="n">
+        <v>26628.03176798092</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
+        <v>26628.03176798092</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>26625.68258844255</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0</v>
+      </c>
+      <c r="U141" t="n">
+        <v>2.349179538502815</v>
+      </c>
+      <c r="V141" t="n">
+        <v>12.44400000572205</v>
+      </c>
+      <c r="W141" t="n">
+        <v>8256593.6895591</v>
+      </c>
+      <c r="X141" t="n">
+        <v>8256593.6895591</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417170818_dh_0.5_ctax_150_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>4139887.773123667</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>472568.2005307369</v>
+      </c>
+      <c r="I142" t="n">
+        <v>-29049803.00305464</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
+        <v>32281393.80385211</v>
+      </c>
+      <c r="M142" t="n">
+        <v>4139887.773123667</v>
+      </c>
+      <c r="N142" t="n">
+        <v>215209.2920256807</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>215209.2920256807</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>215209.2920256806</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0</v>
+      </c>
+      <c r="V142" t="n">
+        <v>12.69700002670288</v>
+      </c>
+      <c r="W142" t="n">
+        <v>4139887.773123667</v>
+      </c>
+      <c r="X142" t="n">
+        <v>4139887.773123667</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417171028_dh_0.5_ctax_150_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>-3248202.711602185</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>1137429.25938166</v>
+      </c>
+      <c r="I143" t="n">
+        <v>-37564001.90620925</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" t="n">
+        <v>32742641.16342994</v>
+      </c>
+      <c r="M143" t="n">
+        <v>-3248202.711602185</v>
+      </c>
+      <c r="N143" t="n">
+        <v>218284.2744228661</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>218284.2744228661</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>218284.2744228661</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0</v>
+      </c>
+      <c r="V143" t="n">
+        <v>7.552000045776367</v>
+      </c>
+      <c r="W143" t="n">
+        <v>-3248202.711602185</v>
+      </c>
+      <c r="X143" t="n">
+        <v>-3248202.711602185</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417171237_dh_0.5_ctax_150_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>-10866436.25968079</v>
+      </c>
+      <c r="B144" t="n">
+        <v>0</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>1698977.295211495</v>
+      </c>
+      <c r="I144" t="n">
+        <v>-46133357.43997464</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="n">
+        <v>33132215.11328689</v>
+      </c>
+      <c r="M144" t="n">
+        <v>-10866436.25968079</v>
+      </c>
+      <c r="N144" t="n">
+        <v>220881.4340885791</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" t="n">
+        <v>220881.4340885791</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>220881.4340885791</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" t="n">
+        <v>0</v>
+      </c>
+      <c r="T144" t="n">
+        <v>0</v>
+      </c>
+      <c r="U144" t="n">
+        <v>0</v>
+      </c>
+      <c r="V144" t="n">
+        <v>8.86299991607666</v>
+      </c>
+      <c r="W144" t="n">
+        <v>-10866436.25968079</v>
+      </c>
+      <c r="X144" t="n">
+        <v>-10866436.25968079</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417171541_dh_0.5_ctax_150_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>-18595519.44406056</v>
+      </c>
+      <c r="B145" t="n">
+        <v>0</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>1937609.692201218</v>
+      </c>
+      <c r="I145" t="n">
+        <v>-54266624.24675574</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="n">
+        <v>33297766.33869851</v>
+      </c>
+      <c r="M145" t="n">
+        <v>-18595519.44406056</v>
+      </c>
+      <c r="N145" t="n">
+        <v>221985.1089246566</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" t="n">
+        <v>221985.1089246566</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>221985.1089246566</v>
+      </c>
+      <c r="R145" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" t="n">
+        <v>0</v>
+      </c>
+      <c r="T145" t="n">
+        <v>0</v>
+      </c>
+      <c r="U145" t="n">
+        <v>0</v>
+      </c>
+      <c r="V145" t="n">
+        <v>8.157000064849854</v>
+      </c>
+      <c r="W145" t="n">
+        <v>-18595519.44406056</v>
+      </c>
+      <c r="X145" t="n">
+        <v>-18595519.44406056</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417171747_dh_0.5_ctax_150_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>-28107429.62501524</v>
+      </c>
+      <c r="B146" t="n">
+        <v>30925520.59477416</v>
+      </c>
+      <c r="C146" t="n">
+        <v>4401617.220603922</v>
+      </c>
+      <c r="D146" t="n">
+        <v>22215864.24309056</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" t="n">
+        <v>53141384.83786473</v>
+      </c>
+      <c r="G146" t="n">
+        <v>4401617.220603922</v>
+      </c>
+      <c r="H146" t="n">
+        <v>4613397.044162707</v>
+      </c>
+      <c r="I146" t="n">
+        <v>-97966060.99482425</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" t="n">
+        <v>7702232.26717765</v>
+      </c>
+      <c r="M146" t="n">
+        <v>-28107429.62501524</v>
+      </c>
+      <c r="N146" t="n">
+        <v>51353.00097338344</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" t="n">
+        <v>51353.00097338344</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>51348.21511451765</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0</v>
+      </c>
+      <c r="S146" t="n">
+        <v>0</v>
+      </c>
+      <c r="T146" t="n">
+        <v>0</v>
+      </c>
+      <c r="U146" t="n">
+        <v>4.785858865855401</v>
+      </c>
+      <c r="V146" t="n">
+        <v>10.47500014305115</v>
+      </c>
+      <c r="W146" t="n">
+        <v>-28107429.62501524</v>
+      </c>
+      <c r="X146" t="n">
+        <v>-28107429.62501524</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417172106_dh_0.5_ctax_150_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>14166758.54410403</v>
+      </c>
+      <c r="B147" t="n">
+        <v>4642318.04535487</v>
+      </c>
+      <c r="C147" t="n">
+        <v>3309736.557256324</v>
+      </c>
+      <c r="D147" t="n">
+        <v>4018199.967996317</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" t="n">
+        <v>8660518.013351187</v>
+      </c>
+      <c r="G147" t="n">
+        <v>3309736.557256324</v>
+      </c>
+      <c r="H147" t="n">
+        <v>61662.36207718177</v>
+      </c>
+      <c r="I147" t="n">
+        <v>-2328846.088867476</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" t="n">
+        <v>4463687.700286811</v>
+      </c>
+      <c r="M147" t="n">
+        <v>14166758.54410403</v>
+      </c>
+      <c r="N147" t="n">
+        <v>22320.82588160943</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" t="n">
+        <v>22320.82588160943</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>22318.43850143416</v>
+      </c>
+      <c r="R147" t="n">
+        <v>0</v>
+      </c>
+      <c r="S147" t="n">
+        <v>0</v>
+      </c>
+      <c r="T147" t="n">
+        <v>0</v>
+      </c>
+      <c r="U147" t="n">
+        <v>2.387380175267484</v>
+      </c>
+      <c r="V147" t="n">
+        <v>8.931999921798706</v>
+      </c>
+      <c r="W147" t="n">
+        <v>14166758.54410403</v>
+      </c>
+      <c r="X147" t="n">
+        <v>14166758.54410403</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD147" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417172315_dh_0.5_ctax_200_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>11835747.11314649</v>
+      </c>
+      <c r="B148" t="n">
+        <v>4627169.776723255</v>
+      </c>
+      <c r="C148" t="n">
+        <v>3304027.502166309</v>
+      </c>
+      <c r="D148" t="n">
+        <v>4009723.435701016</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" t="n">
+        <v>8636893.212424271</v>
+      </c>
+      <c r="G148" t="n">
+        <v>3304027.502166309</v>
+      </c>
+      <c r="H148" t="n">
+        <v>61654.05822728113</v>
+      </c>
+      <c r="I148" t="n">
+        <v>-4667123.497132756</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="n">
+        <v>4500295.837461386</v>
+      </c>
+      <c r="M148" t="n">
+        <v>11835747.11314649</v>
+      </c>
+      <c r="N148" t="n">
+        <v>22503.86427899349</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" t="n">
+        <v>22503.86427899349</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>22501.47918730695</v>
+      </c>
+      <c r="R148" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" t="n">
+        <v>0</v>
+      </c>
+      <c r="T148" t="n">
+        <v>0</v>
+      </c>
+      <c r="U148" t="n">
+        <v>2.385091686627753</v>
+      </c>
+      <c r="V148" t="n">
+        <v>11.14900016784668</v>
+      </c>
+      <c r="W148" t="n">
+        <v>11835747.11314649</v>
+      </c>
+      <c r="X148" t="n">
+        <v>11835747.11314649</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417172522_dh_0.5_ctax_200_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>9477138.164523251</v>
+      </c>
+      <c r="B149" t="n">
+        <v>4604583.296346824</v>
+      </c>
+      <c r="C149" t="n">
+        <v>3295515.256774864</v>
+      </c>
+      <c r="D149" t="n">
+        <v>3996676.512226075</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" t="n">
+        <v>8601259.8085729</v>
+      </c>
+      <c r="G149" t="n">
+        <v>3295515.256774864</v>
+      </c>
+      <c r="H149" t="n">
+        <v>135493.902903906</v>
+      </c>
+      <c r="I149" t="n">
+        <v>-7189504.135956261</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="n">
+        <v>4634373.332227846</v>
+      </c>
+      <c r="M149" t="n">
+        <v>9477138.164523251</v>
+      </c>
+      <c r="N149" t="n">
+        <v>23174.24764184825</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" t="n">
+        <v>23174.24764184825</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>23171.86666113914</v>
+      </c>
+      <c r="R149" t="n">
+        <v>0</v>
+      </c>
+      <c r="S149" t="n">
+        <v>0</v>
+      </c>
+      <c r="T149" t="n">
+        <v>0</v>
+      </c>
+      <c r="U149" t="n">
+        <v>2.380980709225217</v>
+      </c>
+      <c r="V149" t="n">
+        <v>19.61299991607666</v>
+      </c>
+      <c r="W149" t="n">
+        <v>9477138.164523251</v>
+      </c>
+      <c r="X149" t="n">
+        <v>9477138.164523251</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417172732_dh_0.5_ctax_200_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>6871416.133773591</v>
+      </c>
+      <c r="B150" t="n">
+        <v>4564400.08812881</v>
+      </c>
+      <c r="C150" t="n">
+        <v>3280372.764059877</v>
+      </c>
+      <c r="D150" t="n">
+        <v>3972343.710548659</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" t="n">
+        <v>8536743.798677469</v>
+      </c>
+      <c r="G150" t="n">
+        <v>3280372.764059877</v>
+      </c>
+      <c r="H150" t="n">
+        <v>1119185.52067141</v>
+      </c>
+      <c r="I150" t="n">
+        <v>-11756876.38305586</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" t="n">
+        <v>5691990.433420699</v>
+      </c>
+      <c r="M150" t="n">
+        <v>6871416.133773591</v>
+      </c>
+      <c r="N150" t="n">
+        <v>28462.32391641501</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" t="n">
+        <v>28462.32391641501</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>28459.95216710323</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" t="n">
+        <v>0</v>
+      </c>
+      <c r="T150" t="n">
+        <v>0</v>
+      </c>
+      <c r="U150" t="n">
+        <v>2.37174931205285</v>
+      </c>
+      <c r="V150" t="n">
+        <v>33.24599981307983</v>
+      </c>
+      <c r="W150" t="n">
+        <v>6871416.133773591</v>
+      </c>
+      <c r="X150" t="n">
+        <v>6871416.133773591</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417173119_dh_0.5_ctax_200_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>3423906.207601314</v>
+      </c>
+      <c r="B151" t="n">
+        <v>4506512.66346193</v>
+      </c>
+      <c r="C151" t="n">
+        <v>3258558.539419242</v>
+      </c>
+      <c r="D151" t="n">
+        <v>3935107.176450228</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" t="n">
+        <v>8441619.839912158</v>
+      </c>
+      <c r="G151" t="n">
+        <v>3258558.539419242</v>
+      </c>
+      <c r="H151" t="n">
+        <v>3776909.146758025</v>
+      </c>
+      <c r="I151" t="n">
+        <v>-20476156.90554141</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" t="n">
+        <v>8422975.587053295</v>
+      </c>
+      <c r="M151" t="n">
+        <v>3423906.207601314</v>
+      </c>
+      <c r="N151" t="n">
+        <v>42117.23264765362</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" t="n">
+        <v>42117.23264765362</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>42114.87793526654</v>
+      </c>
+      <c r="R151" t="n">
+        <v>0</v>
+      </c>
+      <c r="S151" t="n">
+        <v>0</v>
+      </c>
+      <c r="T151" t="n">
+        <v>0</v>
+      </c>
+      <c r="U151" t="n">
+        <v>2.354712387083941</v>
+      </c>
+      <c r="V151" t="n">
+        <v>28.11800003051758</v>
+      </c>
+      <c r="W151" t="n">
+        <v>3423906.207601314</v>
+      </c>
+      <c r="X151" t="n">
+        <v>3423906.207601314</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417173350_dh_0.5_ctax_200_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>-1433164.151404953</v>
+      </c>
+      <c r="B152" t="n">
+        <v>4465442.171120796</v>
+      </c>
+      <c r="C152" t="n">
+        <v>3243080.610760778</v>
+      </c>
+      <c r="D152" t="n">
+        <v>3907042.435369417</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" t="n">
+        <v>8372484.606490213</v>
+      </c>
+      <c r="G152" t="n">
+        <v>3243080.610760778</v>
+      </c>
+      <c r="H152" t="n">
+        <v>7938930.891909698</v>
+      </c>
+      <c r="I152" t="n">
+        <v>-33499022.42168859</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" t="n">
+        <v>12511362.16112295</v>
+      </c>
+      <c r="M152" t="n">
+        <v>-1433164.151404953</v>
+      </c>
+      <c r="N152" t="n">
+        <v>62559.15061072303</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" t="n">
+        <v>62559.15061072303</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>62556.81080561471</v>
+      </c>
+      <c r="R152" t="n">
+        <v>0</v>
+      </c>
+      <c r="S152" t="n">
+        <v>0</v>
+      </c>
+      <c r="T152" t="n">
+        <v>0</v>
+      </c>
+      <c r="U152" t="n">
+        <v>2.33980510834617</v>
+      </c>
+      <c r="V152" t="n">
+        <v>23.39300012588501</v>
+      </c>
+      <c r="W152" t="n">
+        <v>-1433164.151404953</v>
+      </c>
+      <c r="X152" t="n">
+        <v>-1433164.151404953</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417173618_dh_0.5_ctax_200_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>-13368399.38271082</v>
+      </c>
+      <c r="B153" t="n">
+        <v>31256936.19164934</v>
+      </c>
+      <c r="C153" t="n">
+        <v>4433512.990636175</v>
+      </c>
+      <c r="D153" t="n">
+        <v>22445490.82275625</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" t="n">
+        <v>53702427.01440558</v>
+      </c>
+      <c r="G153" t="n">
+        <v>4433512.990636175</v>
+      </c>
+      <c r="H153" t="n">
+        <v>4367628.094789819</v>
+      </c>
+      <c r="I153" t="n">
+        <v>-85561192.11853638</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
+        <v>9689224.635993993</v>
+      </c>
+      <c r="M153" t="n">
+        <v>-13368399.38271082</v>
+      </c>
+      <c r="N153" t="n">
+        <v>48450.95520513508</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" t="n">
+        <v>48450.95520513508</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>48446.12317996996</v>
+      </c>
+      <c r="R153" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" t="n">
+        <v>0</v>
+      </c>
+      <c r="T153" t="n">
+        <v>0</v>
+      </c>
+      <c r="U153" t="n">
+        <v>4.83202516511338</v>
+      </c>
+      <c r="V153" t="n">
+        <v>23.67999982833862</v>
+      </c>
+      <c r="W153" t="n">
+        <v>-13368399.38271082</v>
+      </c>
+      <c r="X153" t="n">
+        <v>-13368399.38271082</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417173840_dh_0.5_ctax_200_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>-25633824.64073544</v>
+      </c>
+      <c r="B154" t="n">
+        <v>31511866.04814287</v>
+      </c>
+      <c r="C154" t="n">
+        <v>4458047.696165243</v>
+      </c>
+      <c r="D154" t="n">
+        <v>22620186.08415221</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" t="n">
+        <v>54132052.13229508</v>
+      </c>
+      <c r="G154" t="n">
+        <v>4458047.696165243</v>
+      </c>
+      <c r="H154" t="n">
+        <v>4552193.967694725</v>
+      </c>
+      <c r="I154" t="n">
+        <v>-98384532.82457685</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" t="n">
+        <v>9608414.387686372</v>
+      </c>
+      <c r="M154" t="n">
+        <v>-25633824.64073544</v>
+      </c>
+      <c r="N154" t="n">
+        <v>48046.93685220528</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" t="n">
+        <v>48046.93685220528</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>48042.07193843184</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" t="n">
+        <v>0</v>
+      </c>
+      <c r="T154" t="n">
+        <v>0</v>
+      </c>
+      <c r="U154" t="n">
+        <v>4.864913773432199</v>
+      </c>
+      <c r="V154" t="n">
+        <v>15.86400008201599</v>
+      </c>
+      <c r="W154" t="n">
+        <v>-25633824.64073544</v>
+      </c>
+      <c r="X154" t="n">
+        <v>-25633824.64073544</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD154" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417174251_dh_0.5_ctax_200_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>15276445.83654195</v>
+      </c>
+      <c r="B155" t="n">
+        <v>4664830.678978589</v>
+      </c>
+      <c r="C155" t="n">
+        <v>3318220.834847338</v>
+      </c>
+      <c r="D155" t="n">
+        <v>4030420.999154678</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" t="n">
+        <v>8695251.678133268</v>
+      </c>
+      <c r="G155" t="n">
+        <v>3318220.834847338</v>
+      </c>
+      <c r="H155" t="n">
+        <v>61666.5612650128</v>
+      </c>
+      <c r="I155" t="n">
+        <v>-2323184.748177929</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" t="n">
+        <v>5524491.510474265</v>
+      </c>
+      <c r="M155" t="n">
+        <v>15276445.83654195</v>
+      </c>
+      <c r="N155" t="n">
+        <v>22100.35617822076</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" t="n">
+        <v>22100.35617822076</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>22097.966041897</v>
+      </c>
+      <c r="R155" t="n">
+        <v>0</v>
+      </c>
+      <c r="S155" t="n">
+        <v>0</v>
+      </c>
+      <c r="T155" t="n">
+        <v>0</v>
+      </c>
+      <c r="U155" t="n">
+        <v>2.390136323777245</v>
+      </c>
+      <c r="V155" t="n">
+        <v>15.13300013542175</v>
+      </c>
+      <c r="W155" t="n">
+        <v>15276445.83654195</v>
+      </c>
+      <c r="X155" t="n">
+        <v>15276445.83654195</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417174507_dh_0.5_ctax_250_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>12952153.71258856</v>
+      </c>
+      <c r="B156" t="n">
+        <v>4655056.495507496</v>
+      </c>
+      <c r="C156" t="n">
+        <v>3314537.156319223</v>
+      </c>
+      <c r="D156" t="n">
+        <v>4025166.997872301</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" t="n">
+        <v>8680223.493379798</v>
+      </c>
+      <c r="G156" t="n">
+        <v>3314537.156319223</v>
+      </c>
+      <c r="H156" t="n">
+        <v>61666.56126501285</v>
+      </c>
+      <c r="I156" t="n">
+        <v>-4650922.193487093</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" t="n">
+        <v>5546648.695111616</v>
+      </c>
+      <c r="M156" t="n">
+        <v>12952153.71258856</v>
+      </c>
+      <c r="N156" t="n">
+        <v>22188.98380891108</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" t="n">
+        <v>22188.98380891108</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>22186.59478044647</v>
+      </c>
+      <c r="R156" t="n">
+        <v>0</v>
+      </c>
+      <c r="S156" t="n">
+        <v>0</v>
+      </c>
+      <c r="T156" t="n">
+        <v>0</v>
+      </c>
+      <c r="U156" t="n">
+        <v>2.389028464545377</v>
+      </c>
+      <c r="V156" t="n">
+        <v>19.68700003623962</v>
+      </c>
+      <c r="W156" t="n">
+        <v>12952153.71258856</v>
+      </c>
+      <c r="X156" t="n">
+        <v>12952153.71258856</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD156" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417174722_dh_0.5_ctax_250_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>10616205.42052932</v>
+      </c>
+      <c r="B157" t="n">
+        <v>4641668.897790302</v>
+      </c>
+      <c r="C157" t="n">
+        <v>3309491.907567453</v>
+      </c>
+      <c r="D157" t="n">
+        <v>4017841.262892848</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" t="n">
+        <v>8659510.160683149</v>
+      </c>
+      <c r="G157" t="n">
+        <v>3309491.907567453</v>
+      </c>
+      <c r="H157" t="n">
+        <v>92920.77819241522</v>
+      </c>
+      <c r="I157" t="n">
+        <v>-7063275.513886054</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" t="n">
+        <v>5617558.087972356</v>
+      </c>
+      <c r="M157" t="n">
+        <v>10616205.42052932</v>
+      </c>
+      <c r="N157" t="n">
+        <v>22472.61964176868</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="n">
+        <v>22472.61964176868</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>22470.23235188934</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0</v>
+      </c>
+      <c r="S157" t="n">
+        <v>0</v>
+      </c>
+      <c r="T157" t="n">
+        <v>0</v>
+      </c>
+      <c r="U157" t="n">
+        <v>2.387289879318457</v>
+      </c>
+      <c r="V157" t="n">
+        <v>25.21699976921082</v>
+      </c>
+      <c r="W157" t="n">
+        <v>10616205.42052932</v>
+      </c>
+      <c r="X157" t="n">
+        <v>10616205.42052932</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417174942_dh_0.5_ctax_250_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>8185551.863647556</v>
+      </c>
+      <c r="B158" t="n">
+        <v>4625843.394039859</v>
+      </c>
+      <c r="C158" t="n">
+        <v>3303527.617196344</v>
+      </c>
+      <c r="D158" t="n">
+        <v>4008970.65780279</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" t="n">
+        <v>8634814.051842649</v>
+      </c>
+      <c r="G158" t="n">
+        <v>3303527.617196344</v>
+      </c>
+      <c r="H158" t="n">
+        <v>481658.4088778297</v>
+      </c>
+      <c r="I158" t="n">
+        <v>-10349817.72262519</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
+        <v>6115369.508355927</v>
+      </c>
+      <c r="M158" t="n">
+        <v>8185551.863647556</v>
+      </c>
+      <c r="N158" t="n">
+        <v>24463.86290662627</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="n">
+        <v>24463.86290662627</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>24461.47803342369</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" t="n">
+        <v>0</v>
+      </c>
+      <c r="T158" t="n">
+        <v>0</v>
+      </c>
+      <c r="U158" t="n">
+        <v>2.384873202573278</v>
+      </c>
+      <c r="V158" t="n">
+        <v>27.75500011444092</v>
+      </c>
+      <c r="W158" t="n">
+        <v>8185551.863647556</v>
+      </c>
+      <c r="X158" t="n">
+        <v>8185551.863647556</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD158" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417175208_dh_0.5_ctax_250_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>5237895.4880572</v>
+      </c>
+      <c r="B159" t="n">
+        <v>4605441.009884761</v>
+      </c>
+      <c r="C159" t="n">
+        <v>3295838.474396744</v>
+      </c>
+      <c r="D159" t="n">
+        <v>3997180.994087991</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" t="n">
+        <v>8602622.003972752</v>
+      </c>
+      <c r="G159" t="n">
+        <v>3295838.474396744</v>
+      </c>
+      <c r="H159" t="n">
+        <v>2066201.930817454</v>
+      </c>
+      <c r="I159" t="n">
+        <v>-16748684.24964689</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
+        <v>8021917.328517143</v>
+      </c>
+      <c r="M159" t="n">
+        <v>5237895.4880572</v>
+      </c>
+      <c r="N159" t="n">
+        <v>32090.05046630251</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="n">
+        <v>32090.05046630251</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>32087.66931406857</v>
+      </c>
+      <c r="R159" t="n">
+        <v>0</v>
+      </c>
+      <c r="S159" t="n">
+        <v>0</v>
+      </c>
+      <c r="T159" t="n">
+        <v>0</v>
+      </c>
+      <c r="U159" t="n">
+        <v>2.381152233927351</v>
+      </c>
+      <c r="V159" t="n">
+        <v>43.25799989700317</v>
+      </c>
+      <c r="W159" t="n">
+        <v>5237895.4880572</v>
+      </c>
+      <c r="X159" t="n">
+        <v>5237895.4880572</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417175650_dh_0.5_ctax_250_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>1060402.734726978</v>
+      </c>
+      <c r="B160" t="n">
+        <v>31475976.17174264</v>
+      </c>
+      <c r="C160" t="n">
+        <v>4454593.618400224</v>
+      </c>
+      <c r="D160" t="n">
+        <v>22595709.69279263</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" t="n">
+        <v>54071685.86453527</v>
+      </c>
+      <c r="G160" t="n">
+        <v>4454593.618400224</v>
+      </c>
+      <c r="H160" t="n">
+        <v>3527963.701534422</v>
+      </c>
+      <c r="I160" t="n">
+        <v>-71862831.82590297</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" t="n">
+        <v>10868991.37616003</v>
+      </c>
+      <c r="M160" t="n">
+        <v>1060402.734726978</v>
+      </c>
+      <c r="N160" t="n">
+        <v>43480.82594776877</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" t="n">
+        <v>43480.82594776877</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>43475.96550464014</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" t="n">
+        <v>0</v>
+      </c>
+      <c r="T160" t="n">
+        <v>0</v>
+      </c>
+      <c r="U160" t="n">
+        <v>4.860443128641434</v>
+      </c>
+      <c r="V160" t="n">
+        <v>23.87199997901917</v>
+      </c>
+      <c r="W160" t="n">
+        <v>1060402.734726978</v>
+      </c>
+      <c r="X160" t="n">
+        <v>1060402.734726978</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417175936_dh_0.5_ctax_250_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>-11031060.47567807</v>
+      </c>
+      <c r="B161" t="n">
+        <v>31677578.71586813</v>
+      </c>
+      <c r="C161" t="n">
+        <v>4473996.049806509</v>
+      </c>
+      <c r="D161" t="n">
+        <v>22732670.9539523</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" t="n">
+        <v>54410249.66982044</v>
+      </c>
+      <c r="G161" t="n">
+        <v>4473996.049806509</v>
+      </c>
+      <c r="H161" t="n">
+        <v>4128072.326948888</v>
+      </c>
+      <c r="I161" t="n">
+        <v>-85373013.07793203</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" t="n">
+        <v>11329634.55567813</v>
+      </c>
+      <c r="M161" t="n">
+        <v>-11031060.47567807</v>
+      </c>
+      <c r="N161" t="n">
+        <v>45323.42306238208</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" t="n">
+        <v>45323.42306238208</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>45318.53822271253</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" t="n">
+        <v>0</v>
+      </c>
+      <c r="T161" t="n">
+        <v>0</v>
+      </c>
+      <c r="U161" t="n">
+        <v>4.884839669543479</v>
+      </c>
+      <c r="V161" t="n">
+        <v>22.56899976730347</v>
+      </c>
+      <c r="W161" t="n">
+        <v>-11031060.47567807</v>
+      </c>
+      <c r="X161" t="n">
+        <v>-11031060.47567807</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417180202_dh_0.5_ctax_250_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>-23283402.20346651</v>
+      </c>
+      <c r="B162" t="n">
+        <v>31847832.37810468</v>
+      </c>
+      <c r="C162" t="n">
+        <v>4490381.433322094</v>
+      </c>
+      <c r="D162" t="n">
+        <v>22847254.13138406</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" t="n">
+        <v>54695086.50948874</v>
+      </c>
+      <c r="G162" t="n">
+        <v>4490381.433322094</v>
+      </c>
+      <c r="H162" t="n">
+        <v>4446565.30946459</v>
+      </c>
+      <c r="I162" t="n">
+        <v>-98430355.90096943</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="n">
+        <v>11514920.44522749</v>
+      </c>
+      <c r="M162" t="n">
+        <v>-23283402.20346651</v>
+      </c>
+      <c r="N162" t="n">
+        <v>46064.58575974841</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" t="n">
+        <v>46064.58575974841</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>46059.68178090997</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="n">
+        <v>0</v>
+      </c>
+      <c r="T162" t="n">
+        <v>0</v>
+      </c>
+      <c r="U162" t="n">
+        <v>4.903978838420235</v>
+      </c>
+      <c r="V162" t="n">
+        <v>21.32299995422363</v>
+      </c>
+      <c r="W162" t="n">
+        <v>-23283402.20346651</v>
+      </c>
+      <c r="X162" t="n">
+        <v>-23283402.20346651</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417180425_dh_0.5_ctax_250_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>13709888.75963045</v>
+      </c>
+      <c r="B163" t="n">
+        <v>4463843.831386548</v>
+      </c>
+      <c r="C163" t="n">
+        <v>3242478.25427367</v>
+      </c>
+      <c r="D163" t="n">
+        <v>3785395.256626775</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" t="n">
+        <v>8249239.088013323</v>
+      </c>
+      <c r="G163" t="n">
+        <v>3242478.25427367</v>
+      </c>
+      <c r="H163" t="n">
+        <v>35446.35724911593</v>
+      </c>
+      <c r="I163" t="n">
+        <v>-2073694.396406966</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" t="n">
+        <v>4256419.456501309</v>
+      </c>
+      <c r="M163" t="n">
+        <v>13709888.75963045</v>
+      </c>
+      <c r="N163" t="n">
+        <v>42566.32735762457</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" t="n">
+        <v>42566.32735762457</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>42564.19456501291</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0</v>
+      </c>
+      <c r="S163" t="n">
+        <v>0</v>
+      </c>
+      <c r="T163" t="n">
+        <v>0</v>
+      </c>
+      <c r="U163" t="n">
+        <v>2.132792611693628</v>
+      </c>
+      <c r="V163" t="n">
+        <v>17.57399988174438</v>
+      </c>
+      <c r="W163" t="n">
+        <v>13709888.75963045</v>
+      </c>
+      <c r="X163" t="n">
+        <v>13709888.75963045</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417180649_dh_1_ctax_100_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>9240876.844967514</v>
+      </c>
+      <c r="B164" t="n">
+        <v>0</v>
+      </c>
+      <c r="C164" t="n">
+        <v>0</v>
+      </c>
+      <c r="D164" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
+        <v>60502.1733419845</v>
+      </c>
+      <c r="I164" t="n">
+        <v>-12585702.76516321</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" t="n">
+        <v>21330348.66499327</v>
+      </c>
+      <c r="M164" t="n">
+        <v>9240876.844967514</v>
+      </c>
+      <c r="N164" t="n">
+        <v>213303.4866499327</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" t="n">
+        <v>213303.4866499327</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>213303.4866499327</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" t="n">
+        <v>0</v>
+      </c>
+      <c r="T164" t="n">
+        <v>0</v>
+      </c>
+      <c r="U164" t="n">
+        <v>0</v>
+      </c>
+      <c r="V164" t="n">
+        <v>21.87399983406067</v>
+      </c>
+      <c r="W164" t="n">
+        <v>9240876.844967514</v>
+      </c>
+      <c r="X164" t="n">
+        <v>9240876.844967514</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD164" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417180909_dh_1_ctax_100_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>2867571.495318737</v>
+      </c>
+      <c r="B165" t="n">
+        <v>0</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0</v>
+      </c>
+      <c r="D165" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0</v>
+      </c>
+      <c r="F165" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="n">
+        <v>517059.0226530748</v>
+      </c>
+      <c r="I165" t="n">
+        <v>-19626722.50692945</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" t="n">
+        <v>21541506.20779965</v>
+      </c>
+      <c r="M165" t="n">
+        <v>2867571.495318737</v>
+      </c>
+      <c r="N165" t="n">
+        <v>215415.0620779964</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" t="n">
+        <v>215415.0620779964</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>215415.0620779964</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0</v>
+      </c>
+      <c r="S165" t="n">
+        <v>0</v>
+      </c>
+      <c r="T165" t="n">
+        <v>0</v>
+      </c>
+      <c r="U165" t="n">
+        <v>0</v>
+      </c>
+      <c r="V165" t="n">
+        <v>9.365999937057495</v>
+      </c>
+      <c r="W165" t="n">
+        <v>2867571.495318647</v>
+      </c>
+      <c r="X165" t="n">
+        <v>2867571.495318737</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>9.033828973770142e-08</v>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417181414_dh_1_ctax_100_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>-3907956.459950909</v>
+      </c>
+      <c r="B166" t="n">
+        <v>0</v>
+      </c>
+      <c r="C166" t="n">
+        <v>0</v>
+      </c>
+      <c r="D166" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" t="n">
+        <v>1744785.219608191</v>
+      </c>
+      <c r="I166" t="n">
+        <v>-28197800.02524595</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" t="n">
+        <v>22109329.57389139</v>
+      </c>
+      <c r="M166" t="n">
+        <v>-3907956.459950909</v>
+      </c>
+      <c r="N166" t="n">
+        <v>221093.2957389139</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" t="n">
+        <v>221093.2957389139</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>221093.2957389138</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" t="n">
+        <v>0</v>
+      </c>
+      <c r="T166" t="n">
+        <v>0</v>
+      </c>
+      <c r="U166" t="n">
+        <v>0</v>
+      </c>
+      <c r="V166" t="n">
+        <v>6.389999866485596</v>
+      </c>
+      <c r="W166" t="n">
+        <v>-3907956.459950909</v>
+      </c>
+      <c r="X166" t="n">
+        <v>-3907956.459950909</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD166" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417181626_dh_1_ctax_100_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>-11236309.91853718</v>
+      </c>
+      <c r="B167" t="n">
+        <v>0</v>
+      </c>
+      <c r="C167" t="n">
+        <v>0</v>
+      </c>
+      <c r="D167" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="n">
+        <v>3274721.082435129</v>
+      </c>
+      <c r="I167" t="n">
+        <v>-37763684.68321662</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" t="n">
+        <v>22816924.91044885</v>
+      </c>
+      <c r="M167" t="n">
+        <v>-11236309.91853718</v>
+      </c>
+      <c r="N167" t="n">
+        <v>228169.2491044884</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" t="n">
+        <v>228169.2491044884</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>228169.2491044884</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0</v>
+      </c>
+      <c r="S167" t="n">
+        <v>0</v>
+      </c>
+      <c r="T167" t="n">
+        <v>0</v>
+      </c>
+      <c r="U167" t="n">
+        <v>0</v>
+      </c>
+      <c r="V167" t="n">
+        <v>6.348000049591064</v>
+      </c>
+      <c r="W167" t="n">
+        <v>-11236309.91853718</v>
+      </c>
+      <c r="X167" t="n">
+        <v>-11236309.91853718</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417181834_dh_1_ctax_100_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>-18885483.653923</v>
+      </c>
+      <c r="B168" t="n">
+        <v>0</v>
+      </c>
+      <c r="C168" t="n">
+        <v>0</v>
+      </c>
+      <c r="D168" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="n">
+        <v>3864155.607518862</v>
+      </c>
+      <c r="I168" t="n">
+        <v>-46274906.4115374</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" t="n">
+        <v>23089538.37830008</v>
+      </c>
+      <c r="M168" t="n">
+        <v>-18885483.653923</v>
+      </c>
+      <c r="N168" t="n">
+        <v>230895.3837830007</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
+        <v>230895.3837830007</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>230895.3837830007</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0</v>
+      </c>
+      <c r="S168" t="n">
+        <v>0</v>
+      </c>
+      <c r="T168" t="n">
+        <v>0</v>
+      </c>
+      <c r="U168" t="n">
+        <v>0</v>
+      </c>
+      <c r="V168" t="n">
+        <v>6.265000104904175</v>
+      </c>
+      <c r="W168" t="n">
+        <v>-18885483.653923</v>
+      </c>
+      <c r="X168" t="n">
+        <v>-18885483.653923</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD168" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417182043_dh_1_ctax_100_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>-26627309.3052735</v>
+      </c>
+      <c r="B169" t="n">
+        <v>0</v>
+      </c>
+      <c r="C169" t="n">
+        <v>0</v>
+      </c>
+      <c r="D169" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="n">
+        <v>4098614.410903892</v>
+      </c>
+      <c r="I169" t="n">
+        <v>-54359628.06283851</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" t="n">
+        <v>23197975.57486565</v>
+      </c>
+      <c r="M169" t="n">
+        <v>-26627309.3052735</v>
+      </c>
+      <c r="N169" t="n">
+        <v>231979.7557486565</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" t="n">
+        <v>231979.7557486565</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>231979.7557486565</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0</v>
+      </c>
+      <c r="S169" t="n">
+        <v>0</v>
+      </c>
+      <c r="T169" t="n">
+        <v>0</v>
+      </c>
+      <c r="U169" t="n">
+        <v>0</v>
+      </c>
+      <c r="V169" t="n">
+        <v>9.644999980926514</v>
+      </c>
+      <c r="W169" t="n">
+        <v>-26627309.3052735</v>
+      </c>
+      <c r="X169" t="n">
+        <v>-26627309.3052735</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417182252_dh_1_ctax_100_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>-34400959.54221863</v>
+      </c>
+      <c r="B170" t="n">
+        <v>0</v>
+      </c>
+      <c r="C170" t="n">
+        <v>0</v>
+      </c>
+      <c r="D170" t="n">
+        <v>435728.771795464</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" t="n">
+        <v>435728.7717954641</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>4162735.064657771</v>
+      </c>
+      <c r="I170" t="n">
+        <v>-62227054.75589869</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L170" t="n">
+        <v>23227631.37722682</v>
+      </c>
+      <c r="M170" t="n">
+        <v>-34400959.54221863</v>
+      </c>
+      <c r="N170" t="n">
+        <v>232276.3137722682</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" t="n">
+        <v>232276.3137722682</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>232276.3137722682</v>
+      </c>
+      <c r="R170" t="n">
+        <v>0</v>
+      </c>
+      <c r="S170" t="n">
+        <v>0</v>
+      </c>
+      <c r="T170" t="n">
+        <v>0</v>
+      </c>
+      <c r="U170" t="n">
+        <v>0</v>
+      </c>
+      <c r="V170" t="n">
+        <v>10.89499998092651</v>
+      </c>
+      <c r="W170" t="n">
+        <v>-34400959.54221863</v>
+      </c>
+      <c r="X170" t="n">
+        <v>-34400959.54221863</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417182505_dh_1_ctax_100_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>15351539.32508947</v>
+      </c>
+      <c r="B171" t="n">
+        <v>4599542.624500888</v>
+      </c>
+      <c r="C171" t="n">
+        <v>3293615.748495395</v>
+      </c>
+      <c r="D171" t="n">
+        <v>3993697.852002246</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" t="n">
+        <v>8593240.476503134</v>
+      </c>
+      <c r="G171" t="n">
+        <v>3293615.748495395</v>
+      </c>
+      <c r="H171" t="n">
+        <v>1221964.892626518</v>
+      </c>
+      <c r="I171" t="n">
+        <v>-1999182.703117302</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="n">
+        <v>0</v>
+      </c>
+      <c r="L171" t="n">
+        <v>4241900.910581727</v>
+      </c>
+      <c r="M171" t="n">
+        <v>15351539.32508947</v>
+      </c>
+      <c r="N171" t="n">
+        <v>28281.71935278201</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" t="n">
+        <v>28281.71935278201</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>28279.3394038782</v>
+      </c>
+      <c r="R171" t="n">
+        <v>0</v>
+      </c>
+      <c r="S171" t="n">
+        <v>0</v>
+      </c>
+      <c r="T171" t="n">
+        <v>0</v>
+      </c>
+      <c r="U171" t="n">
+        <v>2.379948904034318</v>
+      </c>
+      <c r="V171" t="n">
+        <v>15.4060001373291</v>
+      </c>
+      <c r="W171" t="n">
+        <v>15351539.32508947</v>
+      </c>
+      <c r="X171" t="n">
+        <v>15351539.32508947</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417182721_dh_1_ctax_150_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>13342444.52352396</v>
+      </c>
+      <c r="B172" t="n">
+        <v>4551378.219191149</v>
+      </c>
+      <c r="C172" t="n">
+        <v>3275465.50873317</v>
+      </c>
+      <c r="D172" t="n">
+        <v>3964186.655272894</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" t="n">
+        <v>8515564.874464042</v>
+      </c>
+      <c r="G172" t="n">
+        <v>3275465.50873317</v>
+      </c>
+      <c r="H172" t="n">
+        <v>1226215.707994437</v>
+      </c>
+      <c r="I172" t="n">
+        <v>-4059530.960983664</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="n">
+        <v>0</v>
+      </c>
+      <c r="L172" t="n">
+        <v>4384729.393315976</v>
+      </c>
+      <c r="M172" t="n">
+        <v>13342444.52352396</v>
+      </c>
+      <c r="N172" t="n">
+        <v>29233.89758105405</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="P172" t="n">
+        <v>29233.89758105405</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>29231.5292887731</v>
+      </c>
+      <c r="R172" t="n">
+        <v>0</v>
+      </c>
+      <c r="S172" t="n">
+        <v>0</v>
+      </c>
+      <c r="T172" t="n">
+        <v>0</v>
+      </c>
+      <c r="U172" t="n">
+        <v>2.368292280736589</v>
+      </c>
+      <c r="V172" t="n">
+        <v>15.53799986839294</v>
+      </c>
+      <c r="W172" t="n">
+        <v>13342444.52352396</v>
+      </c>
+      <c r="X172" t="n">
+        <v>13342444.52352396</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD172" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417183301_dh_1_ctax_150_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>11244750.39534782</v>
+      </c>
+      <c r="B173" t="n">
+        <v>4474342.377421819</v>
+      </c>
+      <c r="C173" t="n">
+        <v>3246434.906180321</v>
+      </c>
+      <c r="D173" t="n">
+        <v>3913145.59025656</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" t="n">
+        <v>8387487.967678379</v>
+      </c>
+      <c r="G173" t="n">
+        <v>3246434.906180321</v>
+      </c>
+      <c r="H173" t="n">
+        <v>1486104.41581778</v>
+      </c>
+      <c r="I173" t="n">
+        <v>-6742942.51940487</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L173" t="n">
+        <v>4867665.625076213</v>
+      </c>
+      <c r="M173" t="n">
+        <v>11244750.39534782</v>
+      </c>
+      <c r="N173" t="n">
+        <v>32453.44723958582</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0</v>
+      </c>
+      <c r="P173" t="n">
+        <v>32453.44723958582</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>32451.10416717469</v>
+      </c>
+      <c r="R173" t="n">
+        <v>0</v>
+      </c>
+      <c r="S173" t="n">
+        <v>0</v>
+      </c>
+      <c r="T173" t="n">
+        <v>0</v>
+      </c>
+      <c r="U173" t="n">
+        <v>2.343072410677606</v>
+      </c>
+      <c r="V173" t="n">
+        <v>20.05200004577637</v>
+      </c>
+      <c r="W173" t="n">
+        <v>11244750.39534782</v>
+      </c>
+      <c r="X173" t="n">
+        <v>11244750.39534782</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417183520_dh_1_ctax_150_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>7050699.147829827</v>
+      </c>
+      <c r="B174" t="n">
+        <v>0</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0</v>
+      </c>
+      <c r="D174" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" t="n">
+        <v>955403.0045410157</v>
+      </c>
+      <c r="I174" t="n">
+        <v>-26956793.07764089</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" t="n">
+        <v>0</v>
+      </c>
+      <c r="L174" t="n">
+        <v>32616360.44913424</v>
+      </c>
+      <c r="M174" t="n">
+        <v>7050699.147829827</v>
+      </c>
+      <c r="N174" t="n">
+        <v>217442.4029942281</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" t="n">
+        <v>217442.4029942281</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>217442.4029942282</v>
+      </c>
+      <c r="R174" t="n">
+        <v>0</v>
+      </c>
+      <c r="S174" t="n">
+        <v>0</v>
+      </c>
+      <c r="T174" t="n">
+        <v>0</v>
+      </c>
+      <c r="U174" t="n">
+        <v>0</v>
+      </c>
+      <c r="V174" t="n">
+        <v>19.15499997138977</v>
+      </c>
+      <c r="W174" t="n">
+        <v>6951519.272699739</v>
+      </c>
+      <c r="X174" t="n">
+        <v>7050699.147829827</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>99179.87513008807</v>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC174" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD174" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE174" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417183746_dh_1_ctax_150_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>62478.0002864562</v>
+      </c>
+      <c r="B175" t="n">
+        <v>0</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0</v>
+      </c>
+      <c r="D175" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" t="n">
+        <v>2275717.794954614</v>
+      </c>
+      <c r="I175" t="n">
+        <v>-36181297.4014473</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" t="n">
+        <v>0</v>
+      </c>
+      <c r="L175" t="n">
+        <v>33532328.83498367</v>
+      </c>
+      <c r="M175" t="n">
+        <v>62478.0002864562</v>
+      </c>
+      <c r="N175" t="n">
+        <v>223548.8588998911</v>
+      </c>
+      <c r="O175" t="n">
+        <v>0</v>
+      </c>
+      <c r="P175" t="n">
+        <v>223548.8588998911</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>223548.8588998911</v>
+      </c>
+      <c r="R175" t="n">
+        <v>0</v>
+      </c>
+      <c r="S175" t="n">
+        <v>0</v>
+      </c>
+      <c r="T175" t="n">
+        <v>0</v>
+      </c>
+      <c r="U175" t="n">
+        <v>0</v>
+      </c>
+      <c r="V175" t="n">
+        <v>12.60199999809265</v>
+      </c>
+      <c r="W175" t="n">
+        <v>62478.0002864562</v>
+      </c>
+      <c r="X175" t="n">
+        <v>62478.0002864562</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD175" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417184010_dh_1_ctax_150_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>-7384589.217097677</v>
+      </c>
+      <c r="B176" t="n">
+        <v>0</v>
+      </c>
+      <c r="C176" t="n">
+        <v>0</v>
+      </c>
+      <c r="D176" t="n">
+        <v>435728.771795464</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" t="n">
+        <v>435728.771795464</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" t="n">
+        <v>3398482.612366882</v>
+      </c>
+      <c r="I176" t="n">
+        <v>-45530047.52832346</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" t="n">
+        <v>0</v>
+      </c>
+      <c r="L176" t="n">
+        <v>34311246.92706344</v>
+      </c>
+      <c r="M176" t="n">
+        <v>-7384589.217097677</v>
+      </c>
+      <c r="N176" t="n">
+        <v>228741.6461804228</v>
+      </c>
+      <c r="O176" t="n">
+        <v>0</v>
+      </c>
+      <c r="P176" t="n">
+        <v>228741.6461804228</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>228741.6461804228</v>
+      </c>
+      <c r="R176" t="n">
+        <v>0</v>
+      </c>
+      <c r="S176" t="n">
+        <v>0</v>
+      </c>
+      <c r="T176" t="n">
+        <v>0</v>
+      </c>
+      <c r="U176" t="n">
+        <v>0</v>
+      </c>
+      <c r="V176" t="n">
+        <v>10.83699989318848</v>
+      </c>
+      <c r="W176" t="n">
+        <v>-7384589.217097677</v>
+      </c>
+      <c r="X176" t="n">
+        <v>-7384589.217097677</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD176" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417184233_dh_1_ctax_150_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>-15053248.70991591</v>
+      </c>
+      <c r="B177" t="n">
+        <v>0</v>
+      </c>
+      <c r="C177" t="n">
+        <v>0</v>
+      </c>
+      <c r="D177" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E177" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="n">
+        <v>3875514.618392541</v>
+      </c>
+      <c r="I177" t="n">
+        <v>-54006679.98134765</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="n">
+        <v>0</v>
+      </c>
+      <c r="L177" t="n">
+        <v>34642187.88124374</v>
+      </c>
+      <c r="M177" t="n">
+        <v>-15053248.70991591</v>
+      </c>
+      <c r="N177" t="n">
+        <v>230947.9192082915</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" t="n">
+        <v>230947.9192082915</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>230947.9192082915</v>
+      </c>
+      <c r="R177" t="n">
+        <v>0</v>
+      </c>
+      <c r="S177" t="n">
+        <v>0</v>
+      </c>
+      <c r="T177" t="n">
+        <v>0</v>
+      </c>
+      <c r="U177" t="n">
+        <v>0</v>
+      </c>
+      <c r="V177" t="n">
+        <v>14.03399991989136</v>
+      </c>
+      <c r="W177" t="n">
+        <v>-15053248.70991591</v>
+      </c>
+      <c r="X177" t="n">
+        <v>-15053248.70991591</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD177" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417184504_dh_1_ctax_150_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>-24540806.65989729</v>
+      </c>
+      <c r="B178" t="n">
+        <v>30925520.59477416</v>
+      </c>
+      <c r="C178" t="n">
+        <v>4401617.220603922</v>
+      </c>
+      <c r="D178" t="n">
+        <v>22215864.24309057</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" t="n">
+        <v>53141384.83786473</v>
+      </c>
+      <c r="G178" t="n">
+        <v>4401617.220603922</v>
+      </c>
+      <c r="H178" t="n">
+        <v>6658772.2578664</v>
+      </c>
+      <c r="I178" t="n">
+        <v>-97863792.29791692</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" t="n">
+        <v>0</v>
+      </c>
+      <c r="L178" t="n">
+        <v>9121211.321684588</v>
+      </c>
+      <c r="M178" t="n">
+        <v>-24540806.65989729</v>
+      </c>
+      <c r="N178" t="n">
+        <v>60812.86133676305</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" t="n">
+        <v>60812.86133676305</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>60808.07547789723</v>
+      </c>
+      <c r="R178" t="n">
+        <v>0</v>
+      </c>
+      <c r="S178" t="n">
+        <v>0</v>
+      </c>
+      <c r="T178" t="n">
+        <v>0</v>
+      </c>
+      <c r="U178" t="n">
+        <v>4.785858865855401</v>
+      </c>
+      <c r="V178" t="n">
+        <v>17.52699995040894</v>
+      </c>
+      <c r="W178" t="n">
+        <v>-24540806.65989729</v>
+      </c>
+      <c r="X178" t="n">
+        <v>-24540806.65989729</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD178" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE178" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417184741_dh_1_ctax_150_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>16748983.3251502</v>
+      </c>
+      <c r="B179" t="n">
+        <v>4639402.637478655</v>
+      </c>
+      <c r="C179" t="n">
+        <v>3308637.803030351</v>
+      </c>
+      <c r="D179" t="n">
+        <v>4016586.287431212</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0</v>
+      </c>
+      <c r="F179" t="n">
+        <v>8655988.924909867</v>
+      </c>
+      <c r="G179" t="n">
+        <v>3308637.803030351</v>
+      </c>
+      <c r="H179" t="n">
+        <v>1224187.398177296</v>
+      </c>
+      <c r="I179" t="n">
+        <v>-1985416.311011272</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="n">
+        <v>0</v>
+      </c>
+      <c r="L179" t="n">
+        <v>5545585.510043955</v>
+      </c>
+      <c r="M179" t="n">
+        <v>16748983.3251502</v>
+      </c>
+      <c r="N179" t="n">
+        <v>27730.31452026049</v>
+      </c>
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
+      <c r="P179" t="n">
+        <v>27730.31452026049</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>27727.92755021981</v>
+      </c>
+      <c r="R179" t="n">
+        <v>0</v>
+      </c>
+      <c r="S179" t="n">
+        <v>0</v>
+      </c>
+      <c r="T179" t="n">
+        <v>0</v>
+      </c>
+      <c r="U179" t="n">
+        <v>2.386970040807202</v>
+      </c>
+      <c r="V179" t="n">
+        <v>14.49000000953674</v>
+      </c>
+      <c r="W179" t="n">
+        <v>16748983.3251502</v>
+      </c>
+      <c r="X179" t="n">
+        <v>16748983.3251502</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC179" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD179" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417185022_dh_1_ctax_200_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>14761348.63360327</v>
+      </c>
+      <c r="B180" t="n">
+        <v>4623032.230384513</v>
+      </c>
+      <c r="C180" t="n">
+        <v>3302468.150364476</v>
+      </c>
+      <c r="D180" t="n">
+        <v>4007370.354880523</v>
+      </c>
+      <c r="E180" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" t="n">
+        <v>8630402.585265037</v>
+      </c>
+      <c r="G180" t="n">
+        <v>3302468.150364476</v>
+      </c>
+      <c r="H180" t="n">
+        <v>1223427.694481949</v>
+      </c>
+      <c r="I180" t="n">
+        <v>-3980923.811463071</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L180" t="n">
+        <v>5585974.014954882</v>
+      </c>
+      <c r="M180" t="n">
+        <v>14761348.63360327</v>
+      </c>
+      <c r="N180" t="n">
+        <v>27932.25447661326</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" t="n">
+        <v>27932.25447661326</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>27929.87007477451</v>
+      </c>
+      <c r="R180" t="n">
+        <v>0</v>
+      </c>
+      <c r="S180" t="n">
+        <v>0</v>
+      </c>
+      <c r="T180" t="n">
+        <v>0</v>
+      </c>
+      <c r="U180" t="n">
+        <v>2.384401838880381</v>
+      </c>
+      <c r="V180" t="n">
+        <v>25.01200008392334</v>
+      </c>
+      <c r="W180" t="n">
+        <v>14761348.63360327</v>
+      </c>
+      <c r="X180" t="n">
+        <v>14761348.63360327</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD180" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417185301_dh_1_ctax_200_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>12746129.93566353</v>
+      </c>
+      <c r="B181" t="n">
+        <v>4600013.165219379</v>
+      </c>
+      <c r="C181" t="n">
+        <v>3293793.065332895</v>
+      </c>
+      <c r="D181" t="n">
+        <v>3993976.874504026</v>
+      </c>
+      <c r="E181" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" t="n">
+        <v>8593990.039723406</v>
+      </c>
+      <c r="G181" t="n">
+        <v>3293793.065332895</v>
+      </c>
+      <c r="H181" t="n">
+        <v>1297379.865548342</v>
+      </c>
+      <c r="I181" t="n">
+        <v>-6163092.157066563</v>
+      </c>
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
+      <c r="K181" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" t="n">
+        <v>5724059.122125454</v>
+      </c>
+      <c r="M181" t="n">
+        <v>12746129.93566353</v>
+      </c>
+      <c r="N181" t="n">
+        <v>28622.67565750697</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" t="n">
+        <v>28622.67565750697</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>28620.29561062738</v>
+      </c>
+      <c r="R181" t="n">
+        <v>0</v>
+      </c>
+      <c r="S181" t="n">
+        <v>0</v>
+      </c>
+      <c r="T181" t="n">
+        <v>0</v>
+      </c>
+      <c r="U181" t="n">
+        <v>2.380046879571996</v>
+      </c>
+      <c r="V181" t="n">
+        <v>35.41299986839294</v>
+      </c>
+      <c r="W181" t="n">
+        <v>12746129.93566353</v>
+      </c>
+      <c r="X181" t="n">
+        <v>12746129.93566353</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC181" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD181" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417185550_dh_1_ctax_200_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>10463087.23150969</v>
+      </c>
+      <c r="B182" t="n">
+        <v>4557714.109590459</v>
+      </c>
+      <c r="C182" t="n">
+        <v>3277853.10212896</v>
+      </c>
+      <c r="D182" t="n">
+        <v>3968049.451993026</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" t="n">
+        <v>8525763.561583485</v>
+      </c>
+      <c r="G182" t="n">
+        <v>3277853.10212896</v>
+      </c>
+      <c r="H182" t="n">
+        <v>2380163.834754401</v>
+      </c>
+      <c r="I182" t="n">
+        <v>-10610396.53368326</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" t="n">
+        <v>0</v>
+      </c>
+      <c r="L182" t="n">
+        <v>6889703.266726107</v>
+      </c>
+      <c r="M182" t="n">
+        <v>10463087.23150969</v>
+      </c>
+      <c r="N182" t="n">
+        <v>34450.88612619901</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" t="n">
+        <v>34450.88612619901</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>34448.51633363035</v>
+      </c>
+      <c r="R182" t="n">
+        <v>0</v>
+      </c>
+      <c r="S182" t="n">
+        <v>0</v>
+      </c>
+      <c r="T182" t="n">
+        <v>0</v>
+      </c>
+      <c r="U182" t="n">
+        <v>2.369792568754184</v>
+      </c>
+      <c r="V182" t="n">
+        <v>39.71600008010864</v>
+      </c>
+      <c r="W182" t="n">
+        <v>10463087.23150969</v>
+      </c>
+      <c r="X182" t="n">
+        <v>10463087.23150969</v>
+      </c>
+      <c r="Y182" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC182" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD182" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417190315_dh_1_ctax_200_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>7258679.883857291</v>
+      </c>
+      <c r="B183" t="n">
+        <v>4499402.943274959</v>
+      </c>
+      <c r="C183" t="n">
+        <v>3255879.33888159</v>
+      </c>
+      <c r="D183" t="n">
+        <v>3929475.929699738</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0</v>
+      </c>
+      <c r="F183" t="n">
+        <v>8428878.872974698</v>
+      </c>
+      <c r="G183" t="n">
+        <v>3255879.33888159</v>
+      </c>
+      <c r="H183" t="n">
+        <v>5227546.576378906</v>
+      </c>
+      <c r="I183" t="n">
+        <v>-19480902.15603677</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" t="n">
+        <v>0</v>
+      </c>
+      <c r="L183" t="n">
+        <v>9827277.251658864</v>
+      </c>
+      <c r="M183" t="n">
+        <v>7258679.883857291</v>
+      </c>
+      <c r="N183" t="n">
+        <v>49138.73706680367</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+      <c r="P183" t="n">
+        <v>49138.73706680367</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>49136.38625829434</v>
+      </c>
+      <c r="R183" t="n">
+        <v>0</v>
+      </c>
+      <c r="S183" t="n">
+        <v>0</v>
+      </c>
+      <c r="T183" t="n">
+        <v>0</v>
+      </c>
+      <c r="U183" t="n">
+        <v>2.35080850944605</v>
+      </c>
+      <c r="V183" t="n">
+        <v>38.29000020027161</v>
+      </c>
+      <c r="W183" t="n">
+        <v>7258679.883857291</v>
+      </c>
+      <c r="X183" t="n">
+        <v>7258679.883857291</v>
+      </c>
+      <c r="Y183" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC183" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD183" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417190621_dh_1_ctax_200_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>2565915.895558203</v>
+      </c>
+      <c r="B184" t="n">
+        <v>4457388.248179838</v>
+      </c>
+      <c r="C184" t="n">
+        <v>3240045.558684655</v>
+      </c>
+      <c r="D184" t="n">
+        <v>3899298.910104576</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0</v>
+      </c>
+      <c r="F184" t="n">
+        <v>8356687.158284415</v>
+      </c>
+      <c r="G184" t="n">
+        <v>3240045.558684655</v>
+      </c>
+      <c r="H184" t="n">
+        <v>9554202.442659181</v>
+      </c>
+      <c r="I184" t="n">
+        <v>-32698647.87622739</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" t="n">
+        <v>0</v>
+      </c>
+      <c r="L184" t="n">
+        <v>14113628.61215735</v>
+      </c>
+      <c r="M184" t="n">
+        <v>2565915.895558203</v>
+      </c>
+      <c r="N184" t="n">
+        <v>70570.4761071285</v>
+      </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+      <c r="P184" t="n">
+        <v>70570.4761071285</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>70568.1430607868</v>
+      </c>
+      <c r="R184" t="n">
+        <v>0</v>
+      </c>
+      <c r="S184" t="n">
+        <v>0</v>
+      </c>
+      <c r="T184" t="n">
+        <v>0</v>
+      </c>
+      <c r="U184" t="n">
+        <v>2.333046341684223</v>
+      </c>
+      <c r="V184" t="n">
+        <v>32.51899981498718</v>
+      </c>
+      <c r="W184" t="n">
+        <v>2565915.895558203</v>
+      </c>
+      <c r="X184" t="n">
+        <v>2565915.895558203</v>
+      </c>
+      <c r="Y184" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC184" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD184" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417190926_dh_1_ctax_200_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>-9394885.140655778</v>
+      </c>
+      <c r="B185" t="n">
+        <v>31256936.19164934</v>
+      </c>
+      <c r="C185" t="n">
+        <v>4433512.990636175</v>
+      </c>
+      <c r="D185" t="n">
+        <v>22445490.82275625</v>
+      </c>
+      <c r="E185" t="n">
+        <v>0</v>
+      </c>
+      <c r="F185" t="n">
+        <v>53702427.01440559</v>
+      </c>
+      <c r="G185" t="n">
+        <v>4433512.990636175</v>
+      </c>
+      <c r="H185" t="n">
+        <v>6142757.432533278</v>
+      </c>
+      <c r="I185" t="n">
+        <v>-85004801.85163751</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0</v>
+      </c>
+      <c r="K185" t="n">
+        <v>0</v>
+      </c>
+      <c r="L185" t="n">
+        <v>11331219.27340668</v>
+      </c>
+      <c r="M185" t="n">
+        <v>-9394885.140655778</v>
+      </c>
+      <c r="N185" t="n">
+        <v>56660.92839219856</v>
+      </c>
+      <c r="O185" t="n">
+        <v>0</v>
+      </c>
+      <c r="P185" t="n">
+        <v>56660.92839219856</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>56656.09636703345</v>
+      </c>
+      <c r="R185" t="n">
+        <v>0</v>
+      </c>
+      <c r="S185" t="n">
+        <v>0</v>
+      </c>
+      <c r="T185" t="n">
+        <v>0</v>
+      </c>
+      <c r="U185" t="n">
+        <v>4.83202516511338</v>
+      </c>
+      <c r="V185" t="n">
+        <v>25.875</v>
+      </c>
+      <c r="W185" t="n">
+        <v>-9394885.140655778</v>
+      </c>
+      <c r="X185" t="n">
+        <v>-9394885.140655778</v>
+      </c>
+      <c r="Y185" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC185" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD185" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417191225_dh_1_ctax_200_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>-21606303.51892786</v>
+      </c>
+      <c r="B186" t="n">
+        <v>31511866.04814287</v>
+      </c>
+      <c r="C186" t="n">
+        <v>4458047.696165243</v>
+      </c>
+      <c r="D186" t="n">
+        <v>22620186.0841522</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" t="n">
+        <v>54132052.13229507</v>
+      </c>
+      <c r="G186" t="n">
+        <v>4458047.696165243</v>
+      </c>
+      <c r="H186" t="n">
+        <v>6494241.632415947</v>
+      </c>
+      <c r="I186" t="n">
+        <v>-98095453.45735762</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" t="n">
+        <v>0</v>
+      </c>
+      <c r="L186" t="n">
+        <v>11404808.47755349</v>
+      </c>
+      <c r="M186" t="n">
+        <v>-21606303.51892786</v>
+      </c>
+      <c r="N186" t="n">
+        <v>57028.90730154092</v>
+      </c>
+      <c r="O186" t="n">
+        <v>0</v>
+      </c>
+      <c r="P186" t="n">
+        <v>57028.90730154092</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>57024.04238776748</v>
+      </c>
+      <c r="R186" t="n">
+        <v>0</v>
+      </c>
+      <c r="S186" t="n">
+        <v>0</v>
+      </c>
+      <c r="T186" t="n">
+        <v>0</v>
+      </c>
+      <c r="U186" t="n">
+        <v>4.864913773432199</v>
+      </c>
+      <c r="V186" t="n">
+        <v>25.25600004196167</v>
+      </c>
+      <c r="W186" t="n">
+        <v>-21606303.51892786</v>
+      </c>
+      <c r="X186" t="n">
+        <v>-21606303.51892786</v>
+      </c>
+      <c r="Y186" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC186" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD186" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417191519_dh_1_ctax_200_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>18128927.13279833</v>
+      </c>
+      <c r="B187" t="n">
+        <v>4662935.717924869</v>
+      </c>
+      <c r="C187" t="n">
+        <v>3317506.664976693</v>
+      </c>
+      <c r="D187" t="n">
+        <v>4029408.601116285</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" t="n">
+        <v>8692344.319041153</v>
+      </c>
+      <c r="G187" t="n">
+        <v>3317506.664976693</v>
+      </c>
+      <c r="H187" t="n">
+        <v>1224991.05270989</v>
+      </c>
+      <c r="I187" t="n">
+        <v>-1979583.156952733</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" t="n">
+        <v>0</v>
+      </c>
+      <c r="L187" t="n">
+        <v>6873668.253023325</v>
+      </c>
+      <c r="M187" t="n">
+        <v>18128927.13279833</v>
+      </c>
+      <c r="N187" t="n">
+        <v>27497.06294427694</v>
+      </c>
+      <c r="O187" t="n">
+        <v>0</v>
+      </c>
+      <c r="P187" t="n">
+        <v>27497.06294427694</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>27494.67301209323</v>
+      </c>
+      <c r="R187" t="n">
+        <v>0</v>
+      </c>
+      <c r="S187" t="n">
+        <v>0</v>
+      </c>
+      <c r="T187" t="n">
+        <v>0</v>
+      </c>
+      <c r="U187" t="n">
+        <v>2.38993218381145</v>
+      </c>
+      <c r="V187" t="n">
+        <v>24.68799996376038</v>
+      </c>
+      <c r="W187" t="n">
+        <v>18128927.13279833</v>
+      </c>
+      <c r="X187" t="n">
+        <v>18128927.13279833</v>
+      </c>
+      <c r="Y187" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC187" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD187" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417191813_dh_1_ctax_250_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>16148209.55796553</v>
+      </c>
+      <c r="B188" t="n">
+        <v>4652253.754567728</v>
+      </c>
+      <c r="C188" t="n">
+        <v>3313480.86382684</v>
+      </c>
+      <c r="D188" t="n">
+        <v>4023645.362045859</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" t="n">
+        <v>8675899.116613587</v>
+      </c>
+      <c r="G188" t="n">
+        <v>3313480.86382684</v>
+      </c>
+      <c r="H188" t="n">
+        <v>1224678.631931261</v>
+      </c>
+      <c r="I188" t="n">
+        <v>-3964099.57876177</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" t="n">
+        <v>0</v>
+      </c>
+      <c r="L188" t="n">
+        <v>6898250.524355614</v>
+      </c>
+      <c r="M188" t="n">
+        <v>16148209.55796553</v>
+      </c>
+      <c r="N188" t="n">
+        <v>27595.39078243091</v>
+      </c>
+      <c r="O188" t="n">
+        <v>0</v>
+      </c>
+      <c r="P188" t="n">
+        <v>27595.39078243091</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>27593.00209742256</v>
+      </c>
+      <c r="R188" t="n">
+        <v>0</v>
+      </c>
+      <c r="S188" t="n">
+        <v>0</v>
+      </c>
+      <c r="T188" t="n">
+        <v>0</v>
+      </c>
+      <c r="U188" t="n">
+        <v>2.388685008418568</v>
+      </c>
+      <c r="V188" t="n">
+        <v>34.5699999332428</v>
+      </c>
+      <c r="W188" t="n">
+        <v>16148209.55796553</v>
+      </c>
+      <c r="X188" t="n">
+        <v>16148209.55796553</v>
+      </c>
+      <c r="Y188" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD188" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE188" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417192106_dh_1_ctax_250_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>14155918.72006492</v>
+      </c>
+      <c r="B189" t="n">
+        <v>4639448.926549187</v>
+      </c>
+      <c r="C189" t="n">
+        <v>3308655.248380717</v>
+      </c>
+      <c r="D189" t="n">
+        <v>4016611.977348081</v>
+      </c>
+      <c r="E189" t="n">
+        <v>0</v>
+      </c>
+      <c r="F189" t="n">
+        <v>8656060.903897267</v>
+      </c>
+      <c r="G189" t="n">
+        <v>3308655.248380717</v>
+      </c>
+      <c r="H189" t="n">
+        <v>1255393.360064316</v>
+      </c>
+      <c r="I189" t="n">
+        <v>-6032121.977036969</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0</v>
+      </c>
+      <c r="K189" t="n">
+        <v>0</v>
+      </c>
+      <c r="L189" t="n">
+        <v>6967931.184759591</v>
+      </c>
+      <c r="M189" t="n">
+        <v>14155918.72006492</v>
+      </c>
+      <c r="N189" t="n">
+        <v>27874.11171570889</v>
+      </c>
+      <c r="O189" t="n">
+        <v>0</v>
+      </c>
+      <c r="P189" t="n">
+        <v>27874.11171570889</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>27871.72473903837</v>
+      </c>
+      <c r="R189" t="n">
+        <v>0</v>
+      </c>
+      <c r="S189" t="n">
+        <v>0</v>
+      </c>
+      <c r="T189" t="n">
+        <v>0</v>
+      </c>
+      <c r="U189" t="n">
+        <v>2.386976670618563</v>
+      </c>
+      <c r="V189" t="n">
+        <v>36.27799987792969</v>
+      </c>
+      <c r="W189" t="n">
+        <v>14155918.72006492</v>
+      </c>
+      <c r="X189" t="n">
+        <v>14155918.72006492</v>
+      </c>
+      <c r="Y189" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC189" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD189" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417192409_dh_1_ctax_250_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>12064474.19830745</v>
+      </c>
+      <c r="B190" t="n">
+        <v>4623297.165055408</v>
+      </c>
+      <c r="C190" t="n">
+        <v>3302567.998516642</v>
+      </c>
+      <c r="D190" t="n">
+        <v>4007517.258083981</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="n">
+        <v>8630814.42313939</v>
+      </c>
+      <c r="G190" t="n">
+        <v>3302567.998516642</v>
+      </c>
+      <c r="H190" t="n">
+        <v>1673399.515739382</v>
+      </c>
+      <c r="I190" t="n">
+        <v>-9044300.804373378</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" t="n">
+        <v>0</v>
+      </c>
+      <c r="L190" t="n">
+        <v>7501993.065285411</v>
+      </c>
+      <c r="M190" t="n">
+        <v>12064474.19830745</v>
+      </c>
+      <c r="N190" t="n">
+        <v>30010.35670069948</v>
+      </c>
+      <c r="O190" t="n">
+        <v>0</v>
+      </c>
+      <c r="P190" t="n">
+        <v>30010.35670069948</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>30007.9722611418</v>
+      </c>
+      <c r="R190" t="n">
+        <v>0</v>
+      </c>
+      <c r="S190" t="n">
+        <v>0</v>
+      </c>
+      <c r="T190" t="n">
+        <v>0</v>
+      </c>
+      <c r="U190" t="n">
+        <v>2.384439557467235</v>
+      </c>
+      <c r="V190" t="n">
+        <v>59.08899998664856</v>
+      </c>
+      <c r="W190" t="n">
+        <v>12064474.19830745</v>
+      </c>
+      <c r="X190" t="n">
+        <v>12064474.19830745</v>
+      </c>
+      <c r="Y190" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC190" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD190" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417192719_dh_1_ctax_250_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>9403276.274473999</v>
+      </c>
+      <c r="B191" t="n">
+        <v>4603330.046329536</v>
+      </c>
+      <c r="C191" t="n">
+        <v>3295042.986637698</v>
+      </c>
+      <c r="D191" t="n">
+        <v>3995836.953633601</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" t="n">
+        <v>8599166.999963136</v>
+      </c>
+      <c r="G191" t="n">
+        <v>3295042.986637698</v>
+      </c>
+      <c r="H191" t="n">
+        <v>3418588.351336118</v>
+      </c>
+      <c r="I191" t="n">
+        <v>-15507087.20980049</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0</v>
+      </c>
+      <c r="K191" t="n">
+        <v>0</v>
+      </c>
+      <c r="L191" t="n">
+        <v>9597565.146337541</v>
+      </c>
+      <c r="M191" t="n">
+        <v>9403276.274473999</v>
+      </c>
+      <c r="N191" t="n">
+        <v>38392.64114003311</v>
+      </c>
+      <c r="O191" t="n">
+        <v>0</v>
+      </c>
+      <c r="P191" t="n">
+        <v>38392.64114003311</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>38390.26058535012</v>
+      </c>
+      <c r="R191" t="n">
+        <v>0</v>
+      </c>
+      <c r="S191" t="n">
+        <v>0</v>
+      </c>
+      <c r="T191" t="n">
+        <v>0</v>
+      </c>
+      <c r="U191" t="n">
+        <v>2.380554682972567</v>
+      </c>
+      <c r="V191" t="n">
+        <v>50.38000011444092</v>
+      </c>
+      <c r="W191" t="n">
+        <v>9403276.274473999</v>
+      </c>
+      <c r="X191" t="n">
+        <v>9403276.274473999</v>
+      </c>
+      <c r="Y191" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB191" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC191" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD191" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417193054_dh_1_ctax_250_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>5161275.771872403</v>
+      </c>
+      <c r="B192" t="n">
+        <v>31475976.17174264</v>
+      </c>
+      <c r="C192" t="n">
+        <v>4454593.618400224</v>
+      </c>
+      <c r="D192" t="n">
+        <v>22595709.69279263</v>
+      </c>
+      <c r="E192" t="n">
+        <v>0</v>
+      </c>
+      <c r="F192" t="n">
+        <v>54071685.86453527</v>
+      </c>
+      <c r="G192" t="n">
+        <v>4454593.618400224</v>
+      </c>
+      <c r="H192" t="n">
+        <v>4449684.874718445</v>
+      </c>
+      <c r="I192" t="n">
+        <v>-69749420.06843559</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" t="n">
+        <v>11934731.48265406</v>
+      </c>
+      <c r="M192" t="n">
+        <v>5161275.771872403</v>
+      </c>
+      <c r="N192" t="n">
+        <v>47743.78637374489</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0</v>
+      </c>
+      <c r="P192" t="n">
+        <v>47743.78637374489</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>47738.92593061625</v>
+      </c>
+      <c r="R192" t="n">
+        <v>0</v>
+      </c>
+      <c r="S192" t="n">
+        <v>0</v>
+      </c>
+      <c r="T192" t="n">
+        <v>0</v>
+      </c>
+      <c r="U192" t="n">
+        <v>4.860443128641434</v>
+      </c>
+      <c r="V192" t="n">
+        <v>34.01699995994568</v>
+      </c>
+      <c r="W192" t="n">
+        <v>5161275.771872403</v>
+      </c>
+      <c r="X192" t="n">
+        <v>5161275.771872403</v>
+      </c>
+      <c r="Y192" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC192" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD192" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417193415_dh_1_ctax_250_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>-6679112.879832441</v>
+      </c>
+      <c r="B193" t="n">
+        <v>31677578.71586811</v>
+      </c>
+      <c r="C193" t="n">
+        <v>4473996.049806509</v>
+      </c>
+      <c r="D193" t="n">
+        <v>22732670.95395229</v>
+      </c>
+      <c r="E193" t="n">
+        <v>0</v>
+      </c>
+      <c r="F193" t="n">
+        <v>54410249.6698204</v>
+      </c>
+      <c r="G193" t="n">
+        <v>4473996.049806509</v>
+      </c>
+      <c r="H193" t="n">
+        <v>5635645.202939743</v>
+      </c>
+      <c r="I193" t="n">
+        <v>-84271769.49594164</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" t="n">
+        <v>13072765.69354255</v>
+      </c>
+      <c r="M193" t="n">
+        <v>-6679112.879832441</v>
+      </c>
+      <c r="N193" t="n">
+        <v>52295.94761383977</v>
+      </c>
+      <c r="O193" t="n">
+        <v>0</v>
+      </c>
+      <c r="P193" t="n">
+        <v>52295.94761383977</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>52291.06277417023</v>
+      </c>
+      <c r="R193" t="n">
+        <v>0</v>
+      </c>
+      <c r="S193" t="n">
+        <v>0</v>
+      </c>
+      <c r="T193" t="n">
+        <v>0</v>
+      </c>
+      <c r="U193" t="n">
+        <v>4.884839669543479</v>
+      </c>
+      <c r="V193" t="n">
+        <v>30.4980001449585</v>
+      </c>
+      <c r="W193" t="n">
+        <v>-6679112.879832441</v>
+      </c>
+      <c r="X193" t="n">
+        <v>-6679112.879832441</v>
+      </c>
+      <c r="Y193" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC193" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417194318_dh_1_ctax_250_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>-18820871.08892307</v>
+      </c>
+      <c r="B194" t="n">
+        <v>31847832.37810471</v>
+      </c>
+      <c r="C194" t="n">
+        <v>4490381.433322094</v>
+      </c>
+      <c r="D194" t="n">
+        <v>22847254.13138408</v>
+      </c>
+      <c r="E194" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" t="n">
+        <v>54695086.50948879</v>
+      </c>
+      <c r="G194" t="n">
+        <v>4490381.433322094</v>
+      </c>
+      <c r="H194" t="n">
+        <v>6262022.573766897</v>
+      </c>
+      <c r="I194" t="n">
+        <v>-97882404.51257789</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" t="n">
+        <v>13614042.90707704</v>
+      </c>
+      <c r="M194" t="n">
+        <v>-18820871.08892307</v>
+      </c>
+      <c r="N194" t="n">
+        <v>54461.07560714655</v>
+      </c>
+      <c r="O194" t="n">
+        <v>0</v>
+      </c>
+      <c r="P194" t="n">
+        <v>54461.07560714655</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>54456.17162830814</v>
+      </c>
+      <c r="R194" t="n">
+        <v>0</v>
+      </c>
+      <c r="S194" t="n">
+        <v>0</v>
+      </c>
+      <c r="T194" t="n">
+        <v>0</v>
+      </c>
+      <c r="U194" t="n">
+        <v>4.903978838420235</v>
+      </c>
+      <c r="V194" t="n">
+        <v>30.94000005722046</v>
+      </c>
+      <c r="W194" t="n">
+        <v>-18820871.08892307</v>
+      </c>
+      <c r="X194" t="n">
+        <v>-18820871.08892307</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD194" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417194623_dh_1_ctax_250_el_price_400</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_WtE/raw_results/technology_selection/Summary.xlsx
+++ b/dataCaseStudy_WtE/raw_results/technology_selection/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE194"/>
+  <dimension ref="A1:AE258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20461,6 +20461,6598 @@
       <c r="AE194" t="inlineStr">
         <is>
           <t>dataCaseStudy_WtE\raw_results\technology_selection\20260417194623_dh_1_ctax_250_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>11848649.15001597</v>
+      </c>
+      <c r="B195" t="n">
+        <v>4496791.901331041</v>
+      </c>
+      <c r="C195" t="n">
+        <v>3254895.4035373</v>
+      </c>
+      <c r="D195" t="n">
+        <v>3922233.632322108</v>
+      </c>
+      <c r="E195" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" t="n">
+        <v>8419025.533653149</v>
+      </c>
+      <c r="G195" t="n">
+        <v>3254895.4035373</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0</v>
+      </c>
+      <c r="I195" t="n">
+        <v>-2403520.371525242</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K195" t="n">
+        <v>0</v>
+      </c>
+      <c r="L195" t="n">
+        <v>2578248.584350756</v>
+      </c>
+      <c r="M195" t="n">
+        <v>11848649.15001597</v>
+      </c>
+      <c r="N195" t="n">
+        <v>25784.82635823535</v>
+      </c>
+      <c r="O195" t="n">
+        <v>0</v>
+      </c>
+      <c r="P195" t="n">
+        <v>25784.82635823535</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>25782.48584350741</v>
+      </c>
+      <c r="R195" t="n">
+        <v>0</v>
+      </c>
+      <c r="S195" t="n">
+        <v>0</v>
+      </c>
+      <c r="T195" t="n">
+        <v>0</v>
+      </c>
+      <c r="U195" t="n">
+        <v>2.340514728183982</v>
+      </c>
+      <c r="V195" t="n">
+        <v>19.75300002098083</v>
+      </c>
+      <c r="W195" t="n">
+        <v>11848649.15001597</v>
+      </c>
+      <c r="X195" t="n">
+        <v>11848649.15001597</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD195" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260425232713_dh_0.5_ctax_100_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>7692927.423242366</v>
+      </c>
+      <c r="B196" t="n">
+        <v>0</v>
+      </c>
+      <c r="C196" t="n">
+        <v>0</v>
+      </c>
+      <c r="D196" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E196" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="n">
+        <v>16087.92112087848</v>
+      </c>
+      <c r="I196" t="n">
+        <v>-14068696.34301499</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" t="n">
+        <v>0</v>
+      </c>
+      <c r="L196" t="n">
+        <v>21309807.07334101</v>
+      </c>
+      <c r="M196" t="n">
+        <v>7692927.423242366</v>
+      </c>
+      <c r="N196" t="n">
+        <v>213098.07073341</v>
+      </c>
+      <c r="O196" t="n">
+        <v>0</v>
+      </c>
+      <c r="P196" t="n">
+        <v>213098.07073341</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>213098.07073341</v>
+      </c>
+      <c r="R196" t="n">
+        <v>0</v>
+      </c>
+      <c r="S196" t="n">
+        <v>0</v>
+      </c>
+      <c r="T196" t="n">
+        <v>0</v>
+      </c>
+      <c r="U196" t="n">
+        <v>0</v>
+      </c>
+      <c r="V196" t="n">
+        <v>17.69899988174438</v>
+      </c>
+      <c r="W196" t="n">
+        <v>7692927.423242366</v>
+      </c>
+      <c r="X196" t="n">
+        <v>7692927.423242366</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC196" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD196" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260425233009_dh_0.5_ctax_100_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>616427.8433460556</v>
+      </c>
+      <c r="B197" t="n">
+        <v>0</v>
+      </c>
+      <c r="C197" t="n">
+        <v>0</v>
+      </c>
+      <c r="D197" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E197" t="n">
+        <v>0</v>
+      </c>
+      <c r="F197" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" t="n">
+        <v>250352.7371741842</v>
+      </c>
+      <c r="I197" t="n">
+        <v>-21487808.21638926</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" t="n">
+        <v>21418154.55076566</v>
+      </c>
+      <c r="M197" t="n">
+        <v>616427.8433460556</v>
+      </c>
+      <c r="N197" t="n">
+        <v>214181.5455076566</v>
+      </c>
+      <c r="O197" t="n">
+        <v>0</v>
+      </c>
+      <c r="P197" t="n">
+        <v>214181.5455076566</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>214181.5455076566</v>
+      </c>
+      <c r="R197" t="n">
+        <v>0</v>
+      </c>
+      <c r="S197" t="n">
+        <v>0</v>
+      </c>
+      <c r="T197" t="n">
+        <v>0</v>
+      </c>
+      <c r="U197" t="n">
+        <v>0</v>
+      </c>
+      <c r="V197" t="n">
+        <v>7.788000106811523</v>
+      </c>
+      <c r="W197" t="n">
+        <v>616427.8433459736</v>
+      </c>
+      <c r="X197" t="n">
+        <v>616427.8433460556</v>
+      </c>
+      <c r="Y197" t="n">
+        <v>8.195638656616211e-08</v>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC197" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD197" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260425233254_dh_0.5_ctax_100_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>-6664264.485831395</v>
+      </c>
+      <c r="B198" t="n">
+        <v>0</v>
+      </c>
+      <c r="C198" t="n">
+        <v>0</v>
+      </c>
+      <c r="D198" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E198" t="n">
+        <v>0</v>
+      </c>
+      <c r="F198" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="n">
+        <v>871463.3829878251</v>
+      </c>
+      <c r="I198" t="n">
+        <v>-29676874.86506916</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" t="n">
+        <v>0</v>
+      </c>
+      <c r="L198" t="n">
+        <v>21705418.22445447</v>
+      </c>
+      <c r="M198" t="n">
+        <v>-6664264.485831395</v>
+      </c>
+      <c r="N198" t="n">
+        <v>217054.1822445446</v>
+      </c>
+      <c r="O198" t="n">
+        <v>0</v>
+      </c>
+      <c r="P198" t="n">
+        <v>217054.1822445446</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>217054.1822445447</v>
+      </c>
+      <c r="R198" t="n">
+        <v>0</v>
+      </c>
+      <c r="S198" t="n">
+        <v>0</v>
+      </c>
+      <c r="T198" t="n">
+        <v>0</v>
+      </c>
+      <c r="U198" t="n">
+        <v>0</v>
+      </c>
+      <c r="V198" t="n">
+        <v>5.894000053405762</v>
+      </c>
+      <c r="W198" t="n">
+        <v>-6664264.485831395</v>
+      </c>
+      <c r="X198" t="n">
+        <v>-6664264.485831395</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC198" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD198" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260425233540_dh_0.5_ctax_100_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>-14223105.46445471</v>
+      </c>
+      <c r="B199" t="n">
+        <v>0</v>
+      </c>
+      <c r="C199" t="n">
+        <v>0</v>
+      </c>
+      <c r="D199" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E199" t="n">
+        <v>0</v>
+      </c>
+      <c r="F199" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="n">
+        <v>1637043.526087382</v>
+      </c>
+      <c r="I199" t="n">
+        <v>-38355376.80297558</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" t="n">
+        <v>22059499.04063802</v>
+      </c>
+      <c r="M199" t="n">
+        <v>-14223105.46445471</v>
+      </c>
+      <c r="N199" t="n">
+        <v>220594.9904063801</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0</v>
+      </c>
+      <c r="P199" t="n">
+        <v>220594.9904063801</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>220594.9904063801</v>
+      </c>
+      <c r="R199" t="n">
+        <v>0</v>
+      </c>
+      <c r="S199" t="n">
+        <v>0</v>
+      </c>
+      <c r="T199" t="n">
+        <v>0</v>
+      </c>
+      <c r="U199" t="n">
+        <v>0</v>
+      </c>
+      <c r="V199" t="n">
+        <v>5.376999855041504</v>
+      </c>
+      <c r="W199" t="n">
+        <v>-14223105.46445471</v>
+      </c>
+      <c r="X199" t="n">
+        <v>-14223105.46445471</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC199" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260425233812_dh_0.5_ctax_100_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>-21942439.48836367</v>
+      </c>
+      <c r="B200" t="n">
+        <v>0</v>
+      </c>
+      <c r="C200" t="n">
+        <v>0</v>
+      </c>
+      <c r="D200" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E200" t="n">
+        <v>0</v>
+      </c>
+      <c r="F200" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="n">
+        <v>1931930.186764378</v>
+      </c>
+      <c r="I200" t="n">
+        <v>-46505982.56812464</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" t="n">
+        <v>0</v>
+      </c>
+      <c r="L200" t="n">
+        <v>22195884.12120113</v>
+      </c>
+      <c r="M200" t="n">
+        <v>-21942439.48836367</v>
+      </c>
+      <c r="N200" t="n">
+        <v>221958.8412120113</v>
+      </c>
+      <c r="O200" t="n">
+        <v>0</v>
+      </c>
+      <c r="P200" t="n">
+        <v>221958.8412120113</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>221958.8412120112</v>
+      </c>
+      <c r="R200" t="n">
+        <v>0</v>
+      </c>
+      <c r="S200" t="n">
+        <v>0</v>
+      </c>
+      <c r="T200" t="n">
+        <v>0</v>
+      </c>
+      <c r="U200" t="n">
+        <v>0</v>
+      </c>
+      <c r="V200" t="n">
+        <v>5.384999990463257</v>
+      </c>
+      <c r="W200" t="n">
+        <v>-21942439.48836367</v>
+      </c>
+      <c r="X200" t="n">
+        <v>-21942439.48836367</v>
+      </c>
+      <c r="Y200" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC200" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD200" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260425234050_dh_0.5_ctax_100_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>-29708118.43058869</v>
+      </c>
+      <c r="B201" t="n">
+        <v>0</v>
+      </c>
+      <c r="C201" t="n">
+        <v>0</v>
+      </c>
+      <c r="D201" t="n">
+        <v>435728.7717954647</v>
+      </c>
+      <c r="E201" t="n">
+        <v>0</v>
+      </c>
+      <c r="F201" t="n">
+        <v>435728.7717954658</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" t="n">
+        <v>2049307.205451946</v>
+      </c>
+      <c r="I201" t="n">
+        <v>-54443325.40018023</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" t="n">
+        <v>0</v>
+      </c>
+      <c r="L201" t="n">
+        <v>22250170.99234413</v>
+      </c>
+      <c r="M201" t="n">
+        <v>-29708118.43058869</v>
+      </c>
+      <c r="N201" t="n">
+        <v>222501.7099234413</v>
+      </c>
+      <c r="O201" t="n">
+        <v>0</v>
+      </c>
+      <c r="P201" t="n">
+        <v>222501.7099234413</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>222501.7099234412</v>
+      </c>
+      <c r="R201" t="n">
+        <v>0</v>
+      </c>
+      <c r="S201" t="n">
+        <v>0</v>
+      </c>
+      <c r="T201" t="n">
+        <v>0</v>
+      </c>
+      <c r="U201" t="n">
+        <v>0</v>
+      </c>
+      <c r="V201" t="n">
+        <v>7.650000095367432</v>
+      </c>
+      <c r="W201" t="n">
+        <v>-29708118.43058869</v>
+      </c>
+      <c r="X201" t="n">
+        <v>-29708118.43058869</v>
+      </c>
+      <c r="Y201" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC201" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD201" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260425234336_dh_0.5_ctax_100_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>-37489730.88745569</v>
+      </c>
+      <c r="B202" t="n">
+        <v>0</v>
+      </c>
+      <c r="C202" t="n">
+        <v>0</v>
+      </c>
+      <c r="D202" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E202" t="n">
+        <v>0</v>
+      </c>
+      <c r="F202" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" t="n">
+        <v>2081367.532328885</v>
+      </c>
+      <c r="I202" t="n">
+        <v>-62271826.08510476</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0</v>
+      </c>
+      <c r="K202" t="n">
+        <v>0</v>
+      </c>
+      <c r="L202" t="n">
+        <v>22264998.89352471</v>
+      </c>
+      <c r="M202" t="n">
+        <v>-37489730.88745569</v>
+      </c>
+      <c r="N202" t="n">
+        <v>222649.9889352471</v>
+      </c>
+      <c r="O202" t="n">
+        <v>0</v>
+      </c>
+      <c r="P202" t="n">
+        <v>222649.9889352471</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>222649.9889352471</v>
+      </c>
+      <c r="R202" t="n">
+        <v>0</v>
+      </c>
+      <c r="S202" t="n">
+        <v>0</v>
+      </c>
+      <c r="T202" t="n">
+        <v>0</v>
+      </c>
+      <c r="U202" t="n">
+        <v>0</v>
+      </c>
+      <c r="V202" t="n">
+        <v>6.203999996185303</v>
+      </c>
+      <c r="W202" t="n">
+        <v>-37489730.88745569</v>
+      </c>
+      <c r="X202" t="n">
+        <v>-37489730.88745569</v>
+      </c>
+      <c r="Y202" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC202" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260425234631_dh_0.5_ctax_100_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>13040862.50238379</v>
+      </c>
+      <c r="B203" t="n">
+        <v>4606697.01508003</v>
+      </c>
+      <c r="C203" t="n">
+        <v>3296311.782785068</v>
+      </c>
+      <c r="D203" t="n">
+        <v>3997918.753663895</v>
+      </c>
+      <c r="E203" t="n">
+        <v>0</v>
+      </c>
+      <c r="F203" t="n">
+        <v>8604615.768743925</v>
+      </c>
+      <c r="G203" t="n">
+        <v>3296311.782785068</v>
+      </c>
+      <c r="H203" t="n">
+        <v>61649.79858812681</v>
+      </c>
+      <c r="I203" t="n">
+        <v>-2341213.361767607</v>
+      </c>
+      <c r="J203" t="n">
+        <v>0</v>
+      </c>
+      <c r="K203" t="n">
+        <v>0</v>
+      </c>
+      <c r="L203" t="n">
+        <v>3419498.514034279</v>
+      </c>
+      <c r="M203" t="n">
+        <v>13040862.50238379</v>
+      </c>
+      <c r="N203" t="n">
+        <v>22799.03816194926</v>
+      </c>
+      <c r="O203" t="n">
+        <v>0</v>
+      </c>
+      <c r="P203" t="n">
+        <v>22799.03816194926</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>22796.65676022858</v>
+      </c>
+      <c r="R203" t="n">
+        <v>0</v>
+      </c>
+      <c r="S203" t="n">
+        <v>0</v>
+      </c>
+      <c r="T203" t="n">
+        <v>0</v>
+      </c>
+      <c r="U203" t="n">
+        <v>2.381401720705843</v>
+      </c>
+      <c r="V203" t="n">
+        <v>12.68799996376038</v>
+      </c>
+      <c r="W203" t="n">
+        <v>13040862.50238379</v>
+      </c>
+      <c r="X203" t="n">
+        <v>13040862.50238379</v>
+      </c>
+      <c r="Y203" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC203" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260425234936_dh_0.5_ctax_150_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>10690839.24273433</v>
+      </c>
+      <c r="B204" t="n">
+        <v>4566176.867306454</v>
+      </c>
+      <c r="C204" t="n">
+        <v>3281042.319004511</v>
+      </c>
+      <c r="D204" t="n">
+        <v>3973447.188271914</v>
+      </c>
+      <c r="E204" t="n">
+        <v>0</v>
+      </c>
+      <c r="F204" t="n">
+        <v>8539624.055578368</v>
+      </c>
+      <c r="G204" t="n">
+        <v>3281042.319004511</v>
+      </c>
+      <c r="H204" t="n">
+        <v>71057.05106035015</v>
+      </c>
+      <c r="I204" t="n">
+        <v>-4737273.459144993</v>
+      </c>
+      <c r="J204" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" t="n">
+        <v>0</v>
+      </c>
+      <c r="L204" t="n">
+        <v>3536389.276236091</v>
+      </c>
+      <c r="M204" t="n">
+        <v>10690839.24273433</v>
+      </c>
+      <c r="N204" t="n">
+        <v>23578.30071292132</v>
+      </c>
+      <c r="O204" t="n">
+        <v>0</v>
+      </c>
+      <c r="P204" t="n">
+        <v>23578.30071292132</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>23575.92850824055</v>
+      </c>
+      <c r="R204" t="n">
+        <v>0</v>
+      </c>
+      <c r="S204" t="n">
+        <v>0</v>
+      </c>
+      <c r="T204" t="n">
+        <v>0</v>
+      </c>
+      <c r="U204" t="n">
+        <v>2.372204680639244</v>
+      </c>
+      <c r="V204" t="n">
+        <v>13.00699996948242</v>
+      </c>
+      <c r="W204" t="n">
+        <v>10690839.24273433</v>
+      </c>
+      <c r="X204" t="n">
+        <v>10690839.24273433</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC204" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD204" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260425235154_dh_0.5_ctax_150_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>8256593.6895591</v>
+      </c>
+      <c r="B205" t="n">
+        <v>4490419.675538186</v>
+      </c>
+      <c r="C205" t="n">
+        <v>3252494.092406618</v>
+      </c>
+      <c r="D205" t="n">
+        <v>3924290.074034605</v>
+      </c>
+      <c r="E205" t="n">
+        <v>0</v>
+      </c>
+      <c r="F205" t="n">
+        <v>8414709.749572791</v>
+      </c>
+      <c r="G205" t="n">
+        <v>3252494.092406618</v>
+      </c>
+      <c r="H205" t="n">
+        <v>332190.6098252513</v>
+      </c>
+      <c r="I205" t="n">
+        <v>-7736653.150511968</v>
+      </c>
+      <c r="J205" t="n">
+        <v>0</v>
+      </c>
+      <c r="K205" t="n">
+        <v>0</v>
+      </c>
+      <c r="L205" t="n">
+        <v>3993852.388266406</v>
+      </c>
+      <c r="M205" t="n">
+        <v>8256593.6895591</v>
+      </c>
+      <c r="N205" t="n">
+        <v>26628.03176798092</v>
+      </c>
+      <c r="O205" t="n">
+        <v>0</v>
+      </c>
+      <c r="P205" t="n">
+        <v>26628.03176798092</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>26625.68258844255</v>
+      </c>
+      <c r="R205" t="n">
+        <v>0</v>
+      </c>
+      <c r="S205" t="n">
+        <v>0</v>
+      </c>
+      <c r="T205" t="n">
+        <v>0</v>
+      </c>
+      <c r="U205" t="n">
+        <v>2.349179538502815</v>
+      </c>
+      <c r="V205" t="n">
+        <v>13.74000000953674</v>
+      </c>
+      <c r="W205" t="n">
+        <v>8256593.6895591</v>
+      </c>
+      <c r="X205" t="n">
+        <v>8256593.6895591</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC205" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260425235516_dh_0.5_ctax_150_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>4139887.773123667</v>
+      </c>
+      <c r="B206" t="n">
+        <v>0</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0</v>
+      </c>
+      <c r="D206" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E206" t="n">
+        <v>0</v>
+      </c>
+      <c r="F206" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0</v>
+      </c>
+      <c r="H206" t="n">
+        <v>472568.2005307369</v>
+      </c>
+      <c r="I206" t="n">
+        <v>-29049803.00305464</v>
+      </c>
+      <c r="J206" t="n">
+        <v>0</v>
+      </c>
+      <c r="K206" t="n">
+        <v>0</v>
+      </c>
+      <c r="L206" t="n">
+        <v>32281393.80385211</v>
+      </c>
+      <c r="M206" t="n">
+        <v>4139887.773123667</v>
+      </c>
+      <c r="N206" t="n">
+        <v>215209.2920256807</v>
+      </c>
+      <c r="O206" t="n">
+        <v>0</v>
+      </c>
+      <c r="P206" t="n">
+        <v>215209.2920256807</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>215209.2920256806</v>
+      </c>
+      <c r="R206" t="n">
+        <v>0</v>
+      </c>
+      <c r="S206" t="n">
+        <v>0</v>
+      </c>
+      <c r="T206" t="n">
+        <v>0</v>
+      </c>
+      <c r="U206" t="n">
+        <v>0</v>
+      </c>
+      <c r="V206" t="n">
+        <v>14.20000004768372</v>
+      </c>
+      <c r="W206" t="n">
+        <v>4139887.773123667</v>
+      </c>
+      <c r="X206" t="n">
+        <v>4139887.773123667</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260425235735_dh_0.5_ctax_150_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>-3248202.711602185</v>
+      </c>
+      <c r="B207" t="n">
+        <v>0</v>
+      </c>
+      <c r="C207" t="n">
+        <v>0</v>
+      </c>
+      <c r="D207" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E207" t="n">
+        <v>0</v>
+      </c>
+      <c r="F207" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" t="n">
+        <v>1137429.25938166</v>
+      </c>
+      <c r="I207" t="n">
+        <v>-37564001.90620925</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" t="n">
+        <v>0</v>
+      </c>
+      <c r="L207" t="n">
+        <v>32742641.16342994</v>
+      </c>
+      <c r="M207" t="n">
+        <v>-3248202.711602185</v>
+      </c>
+      <c r="N207" t="n">
+        <v>218284.2744228661</v>
+      </c>
+      <c r="O207" t="n">
+        <v>0</v>
+      </c>
+      <c r="P207" t="n">
+        <v>218284.2744228661</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>218284.2744228661</v>
+      </c>
+      <c r="R207" t="n">
+        <v>0</v>
+      </c>
+      <c r="S207" t="n">
+        <v>0</v>
+      </c>
+      <c r="T207" t="n">
+        <v>0</v>
+      </c>
+      <c r="U207" t="n">
+        <v>0</v>
+      </c>
+      <c r="V207" t="n">
+        <v>9.134999990463257</v>
+      </c>
+      <c r="W207" t="n">
+        <v>-3248202.711602185</v>
+      </c>
+      <c r="X207" t="n">
+        <v>-3248202.711602185</v>
+      </c>
+      <c r="Y207" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260425235955_dh_0.5_ctax_150_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>-10866436.25968079</v>
+      </c>
+      <c r="B208" t="n">
+        <v>0</v>
+      </c>
+      <c r="C208" t="n">
+        <v>0</v>
+      </c>
+      <c r="D208" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="n">
+        <v>1698977.295211495</v>
+      </c>
+      <c r="I208" t="n">
+        <v>-46133357.43997464</v>
+      </c>
+      <c r="J208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" t="n">
+        <v>0</v>
+      </c>
+      <c r="L208" t="n">
+        <v>33132215.11328689</v>
+      </c>
+      <c r="M208" t="n">
+        <v>-10866436.25968079</v>
+      </c>
+      <c r="N208" t="n">
+        <v>220881.4340885791</v>
+      </c>
+      <c r="O208" t="n">
+        <v>0</v>
+      </c>
+      <c r="P208" t="n">
+        <v>220881.4340885791</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>220881.4340885791</v>
+      </c>
+      <c r="R208" t="n">
+        <v>0</v>
+      </c>
+      <c r="S208" t="n">
+        <v>0</v>
+      </c>
+      <c r="T208" t="n">
+        <v>0</v>
+      </c>
+      <c r="U208" t="n">
+        <v>0</v>
+      </c>
+      <c r="V208" t="n">
+        <v>10.08800005912781</v>
+      </c>
+      <c r="W208" t="n">
+        <v>-10866436.25968079</v>
+      </c>
+      <c r="X208" t="n">
+        <v>-10866436.25968079</v>
+      </c>
+      <c r="Y208" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC208" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426000329_dh_0.5_ctax_150_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>-18595519.44406056</v>
+      </c>
+      <c r="B209" t="n">
+        <v>0</v>
+      </c>
+      <c r="C209" t="n">
+        <v>0</v>
+      </c>
+      <c r="D209" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E209" t="n">
+        <v>0</v>
+      </c>
+      <c r="F209" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" t="n">
+        <v>1937609.692201218</v>
+      </c>
+      <c r="I209" t="n">
+        <v>-54266624.24675574</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0</v>
+      </c>
+      <c r="L209" t="n">
+        <v>33297766.33869851</v>
+      </c>
+      <c r="M209" t="n">
+        <v>-18595519.44406056</v>
+      </c>
+      <c r="N209" t="n">
+        <v>221985.1089246566</v>
+      </c>
+      <c r="O209" t="n">
+        <v>0</v>
+      </c>
+      <c r="P209" t="n">
+        <v>221985.1089246566</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>221985.1089246566</v>
+      </c>
+      <c r="R209" t="n">
+        <v>0</v>
+      </c>
+      <c r="S209" t="n">
+        <v>0</v>
+      </c>
+      <c r="T209" t="n">
+        <v>0</v>
+      </c>
+      <c r="U209" t="n">
+        <v>0</v>
+      </c>
+      <c r="V209" t="n">
+        <v>9.726000070571899</v>
+      </c>
+      <c r="W209" t="n">
+        <v>-18595519.44406056</v>
+      </c>
+      <c r="X209" t="n">
+        <v>-18595519.44406056</v>
+      </c>
+      <c r="Y209" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC209" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426000548_dh_0.5_ctax_150_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>-28107429.62501524</v>
+      </c>
+      <c r="B210" t="n">
+        <v>30925520.59477416</v>
+      </c>
+      <c r="C210" t="n">
+        <v>4401617.220603922</v>
+      </c>
+      <c r="D210" t="n">
+        <v>22215864.24309056</v>
+      </c>
+      <c r="E210" t="n">
+        <v>0</v>
+      </c>
+      <c r="F210" t="n">
+        <v>53141384.83786473</v>
+      </c>
+      <c r="G210" t="n">
+        <v>4401617.220603922</v>
+      </c>
+      <c r="H210" t="n">
+        <v>4613397.044162707</v>
+      </c>
+      <c r="I210" t="n">
+        <v>-97966060.99482425</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" t="n">
+        <v>0</v>
+      </c>
+      <c r="L210" t="n">
+        <v>7702232.26717765</v>
+      </c>
+      <c r="M210" t="n">
+        <v>-28107429.62501524</v>
+      </c>
+      <c r="N210" t="n">
+        <v>51353.00097338344</v>
+      </c>
+      <c r="O210" t="n">
+        <v>0</v>
+      </c>
+      <c r="P210" t="n">
+        <v>51353.00097338344</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>51348.21511451765</v>
+      </c>
+      <c r="R210" t="n">
+        <v>0</v>
+      </c>
+      <c r="S210" t="n">
+        <v>0</v>
+      </c>
+      <c r="T210" t="n">
+        <v>0</v>
+      </c>
+      <c r="U210" t="n">
+        <v>4.785858865855401</v>
+      </c>
+      <c r="V210" t="n">
+        <v>12.25099992752075</v>
+      </c>
+      <c r="W210" t="n">
+        <v>-28107429.62501524</v>
+      </c>
+      <c r="X210" t="n">
+        <v>-28107429.62501524</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426000940_dh_0.5_ctax_150_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>14166758.54410403</v>
+      </c>
+      <c r="B211" t="n">
+        <v>4642318.04535487</v>
+      </c>
+      <c r="C211" t="n">
+        <v>3309736.557256324</v>
+      </c>
+      <c r="D211" t="n">
+        <v>4018199.967996317</v>
+      </c>
+      <c r="E211" t="n">
+        <v>0</v>
+      </c>
+      <c r="F211" t="n">
+        <v>8660518.013351187</v>
+      </c>
+      <c r="G211" t="n">
+        <v>3309736.557256324</v>
+      </c>
+      <c r="H211" t="n">
+        <v>61662.36207718177</v>
+      </c>
+      <c r="I211" t="n">
+        <v>-2328846.088867476</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" t="n">
+        <v>0</v>
+      </c>
+      <c r="L211" t="n">
+        <v>4463687.700286811</v>
+      </c>
+      <c r="M211" t="n">
+        <v>14166758.54410403</v>
+      </c>
+      <c r="N211" t="n">
+        <v>22320.82588160943</v>
+      </c>
+      <c r="O211" t="n">
+        <v>0</v>
+      </c>
+      <c r="P211" t="n">
+        <v>22320.82588160943</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>22318.43850143416</v>
+      </c>
+      <c r="R211" t="n">
+        <v>0</v>
+      </c>
+      <c r="S211" t="n">
+        <v>0</v>
+      </c>
+      <c r="T211" t="n">
+        <v>0</v>
+      </c>
+      <c r="U211" t="n">
+        <v>2.387380175267484</v>
+      </c>
+      <c r="V211" t="n">
+        <v>10.64399981498718</v>
+      </c>
+      <c r="W211" t="n">
+        <v>14166758.54410403</v>
+      </c>
+      <c r="X211" t="n">
+        <v>14166758.54410403</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426001203_dh_0.5_ctax_200_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>11835747.11314649</v>
+      </c>
+      <c r="B212" t="n">
+        <v>4627169.776723255</v>
+      </c>
+      <c r="C212" t="n">
+        <v>3304027.502166309</v>
+      </c>
+      <c r="D212" t="n">
+        <v>4009723.435701016</v>
+      </c>
+      <c r="E212" t="n">
+        <v>0</v>
+      </c>
+      <c r="F212" t="n">
+        <v>8636893.212424271</v>
+      </c>
+      <c r="G212" t="n">
+        <v>3304027.502166309</v>
+      </c>
+      <c r="H212" t="n">
+        <v>61654.05822728113</v>
+      </c>
+      <c r="I212" t="n">
+        <v>-4667123.497132756</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" t="n">
+        <v>0</v>
+      </c>
+      <c r="L212" t="n">
+        <v>4500295.837461386</v>
+      </c>
+      <c r="M212" t="n">
+        <v>11835747.11314649</v>
+      </c>
+      <c r="N212" t="n">
+        <v>22503.86427899349</v>
+      </c>
+      <c r="O212" t="n">
+        <v>0</v>
+      </c>
+      <c r="P212" t="n">
+        <v>22503.86427899349</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>22501.47918730695</v>
+      </c>
+      <c r="R212" t="n">
+        <v>0</v>
+      </c>
+      <c r="S212" t="n">
+        <v>0</v>
+      </c>
+      <c r="T212" t="n">
+        <v>0</v>
+      </c>
+      <c r="U212" t="n">
+        <v>2.385091686627753</v>
+      </c>
+      <c r="V212" t="n">
+        <v>12.89900016784668</v>
+      </c>
+      <c r="W212" t="n">
+        <v>11835747.11314649</v>
+      </c>
+      <c r="X212" t="n">
+        <v>11835747.11314649</v>
+      </c>
+      <c r="Y212" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC212" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD212" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426001424_dh_0.5_ctax_200_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>9477138.164523251</v>
+      </c>
+      <c r="B213" t="n">
+        <v>4604583.296346824</v>
+      </c>
+      <c r="C213" t="n">
+        <v>3295515.256774864</v>
+      </c>
+      <c r="D213" t="n">
+        <v>3996676.512226075</v>
+      </c>
+      <c r="E213" t="n">
+        <v>0</v>
+      </c>
+      <c r="F213" t="n">
+        <v>8601259.8085729</v>
+      </c>
+      <c r="G213" t="n">
+        <v>3295515.256774864</v>
+      </c>
+      <c r="H213" t="n">
+        <v>135493.902903906</v>
+      </c>
+      <c r="I213" t="n">
+        <v>-7189504.135956261</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="n">
+        <v>0</v>
+      </c>
+      <c r="L213" t="n">
+        <v>4634373.332227846</v>
+      </c>
+      <c r="M213" t="n">
+        <v>9477138.164523251</v>
+      </c>
+      <c r="N213" t="n">
+        <v>23174.24764184825</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0</v>
+      </c>
+      <c r="P213" t="n">
+        <v>23174.24764184825</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>23171.86666113914</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0</v>
+      </c>
+      <c r="S213" t="n">
+        <v>0</v>
+      </c>
+      <c r="T213" t="n">
+        <v>0</v>
+      </c>
+      <c r="U213" t="n">
+        <v>2.380980709225217</v>
+      </c>
+      <c r="V213" t="n">
+        <v>21.99499988555908</v>
+      </c>
+      <c r="W213" t="n">
+        <v>9477138.164523251</v>
+      </c>
+      <c r="X213" t="n">
+        <v>9477138.164523251</v>
+      </c>
+      <c r="Y213" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD213" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426001647_dh_0.5_ctax_200_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>6871416.133773591</v>
+      </c>
+      <c r="B214" t="n">
+        <v>4564400.08812881</v>
+      </c>
+      <c r="C214" t="n">
+        <v>3280372.764059877</v>
+      </c>
+      <c r="D214" t="n">
+        <v>3972343.710548659</v>
+      </c>
+      <c r="E214" t="n">
+        <v>0</v>
+      </c>
+      <c r="F214" t="n">
+        <v>8536743.798677469</v>
+      </c>
+      <c r="G214" t="n">
+        <v>3280372.764059877</v>
+      </c>
+      <c r="H214" t="n">
+        <v>1119185.52067141</v>
+      </c>
+      <c r="I214" t="n">
+        <v>-11756876.38305586</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" t="n">
+        <v>0</v>
+      </c>
+      <c r="L214" t="n">
+        <v>5691990.433420699</v>
+      </c>
+      <c r="M214" t="n">
+        <v>6871416.133773591</v>
+      </c>
+      <c r="N214" t="n">
+        <v>28462.32391641501</v>
+      </c>
+      <c r="O214" t="n">
+        <v>0</v>
+      </c>
+      <c r="P214" t="n">
+        <v>28462.32391641501</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>28459.95216710323</v>
+      </c>
+      <c r="R214" t="n">
+        <v>0</v>
+      </c>
+      <c r="S214" t="n">
+        <v>0</v>
+      </c>
+      <c r="T214" t="n">
+        <v>0</v>
+      </c>
+      <c r="U214" t="n">
+        <v>2.37174931205285</v>
+      </c>
+      <c r="V214" t="n">
+        <v>36.18600010871887</v>
+      </c>
+      <c r="W214" t="n">
+        <v>6871416.133773591</v>
+      </c>
+      <c r="X214" t="n">
+        <v>6871416.133773591</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD214" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426002112_dh_0.5_ctax_200_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>3423906.207601314</v>
+      </c>
+      <c r="B215" t="n">
+        <v>4506512.66346193</v>
+      </c>
+      <c r="C215" t="n">
+        <v>3258558.539419242</v>
+      </c>
+      <c r="D215" t="n">
+        <v>3935107.176450228</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0</v>
+      </c>
+      <c r="F215" t="n">
+        <v>8441619.839912158</v>
+      </c>
+      <c r="G215" t="n">
+        <v>3258558.539419242</v>
+      </c>
+      <c r="H215" t="n">
+        <v>3776909.146758025</v>
+      </c>
+      <c r="I215" t="n">
+        <v>-20476156.90554141</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" t="n">
+        <v>0</v>
+      </c>
+      <c r="L215" t="n">
+        <v>8422975.587053295</v>
+      </c>
+      <c r="M215" t="n">
+        <v>3423906.207601314</v>
+      </c>
+      <c r="N215" t="n">
+        <v>42117.23264765362</v>
+      </c>
+      <c r="O215" t="n">
+        <v>0</v>
+      </c>
+      <c r="P215" t="n">
+        <v>42117.23264765362</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>42114.87793526654</v>
+      </c>
+      <c r="R215" t="n">
+        <v>0</v>
+      </c>
+      <c r="S215" t="n">
+        <v>0</v>
+      </c>
+      <c r="T215" t="n">
+        <v>0</v>
+      </c>
+      <c r="U215" t="n">
+        <v>2.354712387083941</v>
+      </c>
+      <c r="V215" t="n">
+        <v>31.03499984741211</v>
+      </c>
+      <c r="W215" t="n">
+        <v>3423906.207601314</v>
+      </c>
+      <c r="X215" t="n">
+        <v>3423906.207601314</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD215" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426002358_dh_0.5_ctax_200_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>-1433164.151404953</v>
+      </c>
+      <c r="B216" t="n">
+        <v>4465442.171120796</v>
+      </c>
+      <c r="C216" t="n">
+        <v>3243080.610760778</v>
+      </c>
+      <c r="D216" t="n">
+        <v>3907042.435369417</v>
+      </c>
+      <c r="E216" t="n">
+        <v>0</v>
+      </c>
+      <c r="F216" t="n">
+        <v>8372484.606490213</v>
+      </c>
+      <c r="G216" t="n">
+        <v>3243080.610760778</v>
+      </c>
+      <c r="H216" t="n">
+        <v>7938930.891909698</v>
+      </c>
+      <c r="I216" t="n">
+        <v>-33499022.42168859</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" t="n">
+        <v>0</v>
+      </c>
+      <c r="L216" t="n">
+        <v>12511362.16112295</v>
+      </c>
+      <c r="M216" t="n">
+        <v>-1433164.151404953</v>
+      </c>
+      <c r="N216" t="n">
+        <v>62559.15061072303</v>
+      </c>
+      <c r="O216" t="n">
+        <v>0</v>
+      </c>
+      <c r="P216" t="n">
+        <v>62559.15061072303</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>62556.81080561471</v>
+      </c>
+      <c r="R216" t="n">
+        <v>0</v>
+      </c>
+      <c r="S216" t="n">
+        <v>0</v>
+      </c>
+      <c r="T216" t="n">
+        <v>0</v>
+      </c>
+      <c r="U216" t="n">
+        <v>2.33980510834617</v>
+      </c>
+      <c r="V216" t="n">
+        <v>25.89100003242493</v>
+      </c>
+      <c r="W216" t="n">
+        <v>-1433164.151404953</v>
+      </c>
+      <c r="X216" t="n">
+        <v>-1433164.151404953</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC216" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD216" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426002638_dh_0.5_ctax_200_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>-13368399.38271082</v>
+      </c>
+      <c r="B217" t="n">
+        <v>31256936.19164934</v>
+      </c>
+      <c r="C217" t="n">
+        <v>4433512.990636175</v>
+      </c>
+      <c r="D217" t="n">
+        <v>22445490.82275625</v>
+      </c>
+      <c r="E217" t="n">
+        <v>0</v>
+      </c>
+      <c r="F217" t="n">
+        <v>53702427.01440558</v>
+      </c>
+      <c r="G217" t="n">
+        <v>4433512.990636175</v>
+      </c>
+      <c r="H217" t="n">
+        <v>4367628.094789819</v>
+      </c>
+      <c r="I217" t="n">
+        <v>-85561192.11853638</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" t="n">
+        <v>0</v>
+      </c>
+      <c r="L217" t="n">
+        <v>9689224.635993993</v>
+      </c>
+      <c r="M217" t="n">
+        <v>-13368399.38271082</v>
+      </c>
+      <c r="N217" t="n">
+        <v>48450.95520513508</v>
+      </c>
+      <c r="O217" t="n">
+        <v>0</v>
+      </c>
+      <c r="P217" t="n">
+        <v>48450.95520513508</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>48446.12317996996</v>
+      </c>
+      <c r="R217" t="n">
+        <v>0</v>
+      </c>
+      <c r="S217" t="n">
+        <v>0</v>
+      </c>
+      <c r="T217" t="n">
+        <v>0</v>
+      </c>
+      <c r="U217" t="n">
+        <v>4.83202516511338</v>
+      </c>
+      <c r="V217" t="n">
+        <v>27.50100016593933</v>
+      </c>
+      <c r="W217" t="n">
+        <v>-13368399.38271082</v>
+      </c>
+      <c r="X217" t="n">
+        <v>-13368399.38271082</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC217" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD217" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426002913_dh_0.5_ctax_200_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>-25633824.64073544</v>
+      </c>
+      <c r="B218" t="n">
+        <v>31511866.04814287</v>
+      </c>
+      <c r="C218" t="n">
+        <v>4458047.696165243</v>
+      </c>
+      <c r="D218" t="n">
+        <v>22620186.08415221</v>
+      </c>
+      <c r="E218" t="n">
+        <v>0</v>
+      </c>
+      <c r="F218" t="n">
+        <v>54132052.13229508</v>
+      </c>
+      <c r="G218" t="n">
+        <v>4458047.696165243</v>
+      </c>
+      <c r="H218" t="n">
+        <v>4552193.967694725</v>
+      </c>
+      <c r="I218" t="n">
+        <v>-98384532.82457685</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" t="n">
+        <v>0</v>
+      </c>
+      <c r="L218" t="n">
+        <v>9608414.387686372</v>
+      </c>
+      <c r="M218" t="n">
+        <v>-25633824.64073544</v>
+      </c>
+      <c r="N218" t="n">
+        <v>48046.93685220528</v>
+      </c>
+      <c r="O218" t="n">
+        <v>0</v>
+      </c>
+      <c r="P218" t="n">
+        <v>48046.93685220528</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>48042.07193843184</v>
+      </c>
+      <c r="R218" t="n">
+        <v>0</v>
+      </c>
+      <c r="S218" t="n">
+        <v>0</v>
+      </c>
+      <c r="T218" t="n">
+        <v>0</v>
+      </c>
+      <c r="U218" t="n">
+        <v>4.864913773432199</v>
+      </c>
+      <c r="V218" t="n">
+        <v>18.17199993133545</v>
+      </c>
+      <c r="W218" t="n">
+        <v>-25633824.64073544</v>
+      </c>
+      <c r="X218" t="n">
+        <v>-25633824.64073544</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC218" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD218" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426003408_dh_0.5_ctax_200_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>15276445.83654195</v>
+      </c>
+      <c r="B219" t="n">
+        <v>4664830.678978589</v>
+      </c>
+      <c r="C219" t="n">
+        <v>3318220.834847338</v>
+      </c>
+      <c r="D219" t="n">
+        <v>4030420.999154678</v>
+      </c>
+      <c r="E219" t="n">
+        <v>0</v>
+      </c>
+      <c r="F219" t="n">
+        <v>8695251.678133268</v>
+      </c>
+      <c r="G219" t="n">
+        <v>3318220.834847338</v>
+      </c>
+      <c r="H219" t="n">
+        <v>61666.5612650128</v>
+      </c>
+      <c r="I219" t="n">
+        <v>-2323184.748177929</v>
+      </c>
+      <c r="J219" t="n">
+        <v>0</v>
+      </c>
+      <c r="K219" t="n">
+        <v>0</v>
+      </c>
+      <c r="L219" t="n">
+        <v>5524491.510474265</v>
+      </c>
+      <c r="M219" t="n">
+        <v>15276445.83654195</v>
+      </c>
+      <c r="N219" t="n">
+        <v>22100.35617822076</v>
+      </c>
+      <c r="O219" t="n">
+        <v>0</v>
+      </c>
+      <c r="P219" t="n">
+        <v>22100.35617822076</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>22097.966041897</v>
+      </c>
+      <c r="R219" t="n">
+        <v>0</v>
+      </c>
+      <c r="S219" t="n">
+        <v>0</v>
+      </c>
+      <c r="T219" t="n">
+        <v>0</v>
+      </c>
+      <c r="U219" t="n">
+        <v>2.390136323777245</v>
+      </c>
+      <c r="V219" t="n">
+        <v>17.48600006103516</v>
+      </c>
+      <c r="W219" t="n">
+        <v>15276445.83654195</v>
+      </c>
+      <c r="X219" t="n">
+        <v>15276445.83654195</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC219" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD219" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426003638_dh_0.5_ctax_250_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>12952153.71258856</v>
+      </c>
+      <c r="B220" t="n">
+        <v>4655056.495507496</v>
+      </c>
+      <c r="C220" t="n">
+        <v>3314537.156319223</v>
+      </c>
+      <c r="D220" t="n">
+        <v>4025166.997872301</v>
+      </c>
+      <c r="E220" t="n">
+        <v>0</v>
+      </c>
+      <c r="F220" t="n">
+        <v>8680223.493379798</v>
+      </c>
+      <c r="G220" t="n">
+        <v>3314537.156319223</v>
+      </c>
+      <c r="H220" t="n">
+        <v>61666.56126501285</v>
+      </c>
+      <c r="I220" t="n">
+        <v>-4650922.193487093</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" t="n">
+        <v>0</v>
+      </c>
+      <c r="L220" t="n">
+        <v>5546648.695111616</v>
+      </c>
+      <c r="M220" t="n">
+        <v>12952153.71258856</v>
+      </c>
+      <c r="N220" t="n">
+        <v>22188.98380891108</v>
+      </c>
+      <c r="O220" t="n">
+        <v>0</v>
+      </c>
+      <c r="P220" t="n">
+        <v>22188.98380891108</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>22186.59478044647</v>
+      </c>
+      <c r="R220" t="n">
+        <v>0</v>
+      </c>
+      <c r="S220" t="n">
+        <v>0</v>
+      </c>
+      <c r="T220" t="n">
+        <v>0</v>
+      </c>
+      <c r="U220" t="n">
+        <v>2.389028464545377</v>
+      </c>
+      <c r="V220" t="n">
+        <v>22.52499985694885</v>
+      </c>
+      <c r="W220" t="n">
+        <v>12952153.71258856</v>
+      </c>
+      <c r="X220" t="n">
+        <v>12952153.71258856</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC220" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD220" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE220" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426003907_dh_0.5_ctax_250_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>10616205.42052932</v>
+      </c>
+      <c r="B221" t="n">
+        <v>4641668.897790302</v>
+      </c>
+      <c r="C221" t="n">
+        <v>3309491.907567453</v>
+      </c>
+      <c r="D221" t="n">
+        <v>4017841.262892848</v>
+      </c>
+      <c r="E221" t="n">
+        <v>0</v>
+      </c>
+      <c r="F221" t="n">
+        <v>8659510.160683149</v>
+      </c>
+      <c r="G221" t="n">
+        <v>3309491.907567453</v>
+      </c>
+      <c r="H221" t="n">
+        <v>92920.77819241522</v>
+      </c>
+      <c r="I221" t="n">
+        <v>-7063275.513886054</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" t="n">
+        <v>0</v>
+      </c>
+      <c r="L221" t="n">
+        <v>5617558.087972356</v>
+      </c>
+      <c r="M221" t="n">
+        <v>10616205.42052932</v>
+      </c>
+      <c r="N221" t="n">
+        <v>22472.61964176868</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
+      <c r="P221" t="n">
+        <v>22472.61964176868</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>22470.23235188934</v>
+      </c>
+      <c r="R221" t="n">
+        <v>0</v>
+      </c>
+      <c r="S221" t="n">
+        <v>0</v>
+      </c>
+      <c r="T221" t="n">
+        <v>0</v>
+      </c>
+      <c r="U221" t="n">
+        <v>2.387289879318457</v>
+      </c>
+      <c r="V221" t="n">
+        <v>27.81500005722046</v>
+      </c>
+      <c r="W221" t="n">
+        <v>10616205.42052932</v>
+      </c>
+      <c r="X221" t="n">
+        <v>10616205.42052932</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC221" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD221" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426004143_dh_0.5_ctax_250_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>8185551.863647556</v>
+      </c>
+      <c r="B222" t="n">
+        <v>4625843.394039859</v>
+      </c>
+      <c r="C222" t="n">
+        <v>3303527.617196344</v>
+      </c>
+      <c r="D222" t="n">
+        <v>4008970.65780279</v>
+      </c>
+      <c r="E222" t="n">
+        <v>0</v>
+      </c>
+      <c r="F222" t="n">
+        <v>8634814.051842649</v>
+      </c>
+      <c r="G222" t="n">
+        <v>3303527.617196344</v>
+      </c>
+      <c r="H222" t="n">
+        <v>481658.4088778297</v>
+      </c>
+      <c r="I222" t="n">
+        <v>-10349817.72262519</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" t="n">
+        <v>0</v>
+      </c>
+      <c r="L222" t="n">
+        <v>6115369.508355927</v>
+      </c>
+      <c r="M222" t="n">
+        <v>8185551.863647556</v>
+      </c>
+      <c r="N222" t="n">
+        <v>24463.86290662627</v>
+      </c>
+      <c r="O222" t="n">
+        <v>0</v>
+      </c>
+      <c r="P222" t="n">
+        <v>24463.86290662627</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>24461.47803342369</v>
+      </c>
+      <c r="R222" t="n">
+        <v>0</v>
+      </c>
+      <c r="S222" t="n">
+        <v>0</v>
+      </c>
+      <c r="T222" t="n">
+        <v>0</v>
+      </c>
+      <c r="U222" t="n">
+        <v>2.384873202573278</v>
+      </c>
+      <c r="V222" t="n">
+        <v>31.66899991035461</v>
+      </c>
+      <c r="W222" t="n">
+        <v>8185551.863647556</v>
+      </c>
+      <c r="X222" t="n">
+        <v>8185551.863647556</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC222" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD222" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426004424_dh_0.5_ctax_250_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>5237895.4880572</v>
+      </c>
+      <c r="B223" t="n">
+        <v>4605441.009884761</v>
+      </c>
+      <c r="C223" t="n">
+        <v>3295838.474396744</v>
+      </c>
+      <c r="D223" t="n">
+        <v>3997180.994087991</v>
+      </c>
+      <c r="E223" t="n">
+        <v>0</v>
+      </c>
+      <c r="F223" t="n">
+        <v>8602622.003972752</v>
+      </c>
+      <c r="G223" t="n">
+        <v>3295838.474396744</v>
+      </c>
+      <c r="H223" t="n">
+        <v>2066201.930817454</v>
+      </c>
+      <c r="I223" t="n">
+        <v>-16748684.24964689</v>
+      </c>
+      <c r="J223" t="n">
+        <v>0</v>
+      </c>
+      <c r="K223" t="n">
+        <v>0</v>
+      </c>
+      <c r="L223" t="n">
+        <v>8021917.328517143</v>
+      </c>
+      <c r="M223" t="n">
+        <v>5237895.4880572</v>
+      </c>
+      <c r="N223" t="n">
+        <v>32090.05046630251</v>
+      </c>
+      <c r="O223" t="n">
+        <v>0</v>
+      </c>
+      <c r="P223" t="n">
+        <v>32090.05046630251</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>32087.66931406857</v>
+      </c>
+      <c r="R223" t="n">
+        <v>0</v>
+      </c>
+      <c r="S223" t="n">
+        <v>0</v>
+      </c>
+      <c r="T223" t="n">
+        <v>0</v>
+      </c>
+      <c r="U223" t="n">
+        <v>2.381152233927351</v>
+      </c>
+      <c r="V223" t="n">
+        <v>46.33500003814697</v>
+      </c>
+      <c r="W223" t="n">
+        <v>5237895.4880572</v>
+      </c>
+      <c r="X223" t="n">
+        <v>5237895.4880572</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC223" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD223" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426004959_dh_0.5_ctax_250_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>1060402.734726978</v>
+      </c>
+      <c r="B224" t="n">
+        <v>31475976.17174264</v>
+      </c>
+      <c r="C224" t="n">
+        <v>4454593.618400224</v>
+      </c>
+      <c r="D224" t="n">
+        <v>22595709.69279263</v>
+      </c>
+      <c r="E224" t="n">
+        <v>0</v>
+      </c>
+      <c r="F224" t="n">
+        <v>54071685.86453527</v>
+      </c>
+      <c r="G224" t="n">
+        <v>4454593.618400224</v>
+      </c>
+      <c r="H224" t="n">
+        <v>3527963.701534422</v>
+      </c>
+      <c r="I224" t="n">
+        <v>-71862831.82590297</v>
+      </c>
+      <c r="J224" t="n">
+        <v>0</v>
+      </c>
+      <c r="K224" t="n">
+        <v>0</v>
+      </c>
+      <c r="L224" t="n">
+        <v>10868991.37616003</v>
+      </c>
+      <c r="M224" t="n">
+        <v>1060402.734726978</v>
+      </c>
+      <c r="N224" t="n">
+        <v>43480.82594776877</v>
+      </c>
+      <c r="O224" t="n">
+        <v>0</v>
+      </c>
+      <c r="P224" t="n">
+        <v>43480.82594776877</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>43475.96550464014</v>
+      </c>
+      <c r="R224" t="n">
+        <v>0</v>
+      </c>
+      <c r="S224" t="n">
+        <v>0</v>
+      </c>
+      <c r="T224" t="n">
+        <v>0</v>
+      </c>
+      <c r="U224" t="n">
+        <v>4.860443128641434</v>
+      </c>
+      <c r="V224" t="n">
+        <v>27.87800002098083</v>
+      </c>
+      <c r="W224" t="n">
+        <v>1060402.734726978</v>
+      </c>
+      <c r="X224" t="n">
+        <v>1060402.734726978</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC224" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD224" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426005259_dh_0.5_ctax_250_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>-11031060.47567807</v>
+      </c>
+      <c r="B225" t="n">
+        <v>31677578.71586813</v>
+      </c>
+      <c r="C225" t="n">
+        <v>4473996.049806509</v>
+      </c>
+      <c r="D225" t="n">
+        <v>22732670.9539523</v>
+      </c>
+      <c r="E225" t="n">
+        <v>0</v>
+      </c>
+      <c r="F225" t="n">
+        <v>54410249.66982044</v>
+      </c>
+      <c r="G225" t="n">
+        <v>4473996.049806509</v>
+      </c>
+      <c r="H225" t="n">
+        <v>4128072.326948888</v>
+      </c>
+      <c r="I225" t="n">
+        <v>-85373013.07793203</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" t="n">
+        <v>0</v>
+      </c>
+      <c r="L225" t="n">
+        <v>11329634.55567813</v>
+      </c>
+      <c r="M225" t="n">
+        <v>-11031060.47567807</v>
+      </c>
+      <c r="N225" t="n">
+        <v>45323.42306238208</v>
+      </c>
+      <c r="O225" t="n">
+        <v>0</v>
+      </c>
+      <c r="P225" t="n">
+        <v>45323.42306238208</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>45318.53822271253</v>
+      </c>
+      <c r="R225" t="n">
+        <v>0</v>
+      </c>
+      <c r="S225" t="n">
+        <v>0</v>
+      </c>
+      <c r="T225" t="n">
+        <v>0</v>
+      </c>
+      <c r="U225" t="n">
+        <v>4.884839669543479</v>
+      </c>
+      <c r="V225" t="n">
+        <v>27.0460000038147</v>
+      </c>
+      <c r="W225" t="n">
+        <v>-11031060.47567807</v>
+      </c>
+      <c r="X225" t="n">
+        <v>-11031060.47567807</v>
+      </c>
+      <c r="Y225" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC225" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD225" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426005538_dh_0.5_ctax_250_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>-23283402.20346651</v>
+      </c>
+      <c r="B226" t="n">
+        <v>31847832.37810468</v>
+      </c>
+      <c r="C226" t="n">
+        <v>4490381.433322094</v>
+      </c>
+      <c r="D226" t="n">
+        <v>22847254.13138406</v>
+      </c>
+      <c r="E226" t="n">
+        <v>0</v>
+      </c>
+      <c r="F226" t="n">
+        <v>54695086.50948874</v>
+      </c>
+      <c r="G226" t="n">
+        <v>4490381.433322094</v>
+      </c>
+      <c r="H226" t="n">
+        <v>4446565.30946459</v>
+      </c>
+      <c r="I226" t="n">
+        <v>-98430355.90096943</v>
+      </c>
+      <c r="J226" t="n">
+        <v>0</v>
+      </c>
+      <c r="K226" t="n">
+        <v>0</v>
+      </c>
+      <c r="L226" t="n">
+        <v>11514920.44522749</v>
+      </c>
+      <c r="M226" t="n">
+        <v>-23283402.20346651</v>
+      </c>
+      <c r="N226" t="n">
+        <v>46064.58575974841</v>
+      </c>
+      <c r="O226" t="n">
+        <v>0</v>
+      </c>
+      <c r="P226" t="n">
+        <v>46064.58575974841</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>46059.68178090997</v>
+      </c>
+      <c r="R226" t="n">
+        <v>0</v>
+      </c>
+      <c r="S226" t="n">
+        <v>0</v>
+      </c>
+      <c r="T226" t="n">
+        <v>0</v>
+      </c>
+      <c r="U226" t="n">
+        <v>4.903978838420235</v>
+      </c>
+      <c r="V226" t="n">
+        <v>25.28400015830994</v>
+      </c>
+      <c r="W226" t="n">
+        <v>-23283402.20346651</v>
+      </c>
+      <c r="X226" t="n">
+        <v>-23283402.20346651</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC226" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD226" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426005823_dh_0.5_ctax_250_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>13709888.75963045</v>
+      </c>
+      <c r="B227" t="n">
+        <v>4463843.831386548</v>
+      </c>
+      <c r="C227" t="n">
+        <v>3242478.25427367</v>
+      </c>
+      <c r="D227" t="n">
+        <v>3785395.256626775</v>
+      </c>
+      <c r="E227" t="n">
+        <v>0</v>
+      </c>
+      <c r="F227" t="n">
+        <v>8249239.088013323</v>
+      </c>
+      <c r="G227" t="n">
+        <v>3242478.25427367</v>
+      </c>
+      <c r="H227" t="n">
+        <v>35446.35724911593</v>
+      </c>
+      <c r="I227" t="n">
+        <v>-2073694.396406966</v>
+      </c>
+      <c r="J227" t="n">
+        <v>0</v>
+      </c>
+      <c r="K227" t="n">
+        <v>0</v>
+      </c>
+      <c r="L227" t="n">
+        <v>4256419.456501309</v>
+      </c>
+      <c r="M227" t="n">
+        <v>13709888.75963045</v>
+      </c>
+      <c r="N227" t="n">
+        <v>42566.32735762457</v>
+      </c>
+      <c r="O227" t="n">
+        <v>0</v>
+      </c>
+      <c r="P227" t="n">
+        <v>42566.32735762457</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>42564.19456501291</v>
+      </c>
+      <c r="R227" t="n">
+        <v>0</v>
+      </c>
+      <c r="S227" t="n">
+        <v>0</v>
+      </c>
+      <c r="T227" t="n">
+        <v>0</v>
+      </c>
+      <c r="U227" t="n">
+        <v>2.132792611693628</v>
+      </c>
+      <c r="V227" t="n">
+        <v>20.69099998474121</v>
+      </c>
+      <c r="W227" t="n">
+        <v>13709888.75963045</v>
+      </c>
+      <c r="X227" t="n">
+        <v>13709888.75963045</v>
+      </c>
+      <c r="Y227" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC227" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD227" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426010101_dh_1_ctax_100_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>9240876.844967514</v>
+      </c>
+      <c r="B228" t="n">
+        <v>0</v>
+      </c>
+      <c r="C228" t="n">
+        <v>0</v>
+      </c>
+      <c r="D228" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E228" t="n">
+        <v>0</v>
+      </c>
+      <c r="F228" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="n">
+        <v>60502.1733419845</v>
+      </c>
+      <c r="I228" t="n">
+        <v>-12585702.76516321</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0</v>
+      </c>
+      <c r="K228" t="n">
+        <v>0</v>
+      </c>
+      <c r="L228" t="n">
+        <v>21330348.66499327</v>
+      </c>
+      <c r="M228" t="n">
+        <v>9240876.844967514</v>
+      </c>
+      <c r="N228" t="n">
+        <v>213303.4866499327</v>
+      </c>
+      <c r="O228" t="n">
+        <v>0</v>
+      </c>
+      <c r="P228" t="n">
+        <v>213303.4866499327</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>213303.4866499327</v>
+      </c>
+      <c r="R228" t="n">
+        <v>0</v>
+      </c>
+      <c r="S228" t="n">
+        <v>0</v>
+      </c>
+      <c r="T228" t="n">
+        <v>0</v>
+      </c>
+      <c r="U228" t="n">
+        <v>0</v>
+      </c>
+      <c r="V228" t="n">
+        <v>25.17200016975403</v>
+      </c>
+      <c r="W228" t="n">
+        <v>9240876.844967514</v>
+      </c>
+      <c r="X228" t="n">
+        <v>9240876.844967514</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC228" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD228" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426010335_dh_1_ctax_100_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>2867571.495318737</v>
+      </c>
+      <c r="B229" t="n">
+        <v>0</v>
+      </c>
+      <c r="C229" t="n">
+        <v>0</v>
+      </c>
+      <c r="D229" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E229" t="n">
+        <v>0</v>
+      </c>
+      <c r="F229" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+      <c r="H229" t="n">
+        <v>517059.0226530748</v>
+      </c>
+      <c r="I229" t="n">
+        <v>-19626722.50692945</v>
+      </c>
+      <c r="J229" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" t="n">
+        <v>0</v>
+      </c>
+      <c r="L229" t="n">
+        <v>21541506.20779965</v>
+      </c>
+      <c r="M229" t="n">
+        <v>2867571.495318737</v>
+      </c>
+      <c r="N229" t="n">
+        <v>215415.0620779964</v>
+      </c>
+      <c r="O229" t="n">
+        <v>0</v>
+      </c>
+      <c r="P229" t="n">
+        <v>215415.0620779964</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>215415.0620779964</v>
+      </c>
+      <c r="R229" t="n">
+        <v>0</v>
+      </c>
+      <c r="S229" t="n">
+        <v>0</v>
+      </c>
+      <c r="T229" t="n">
+        <v>0</v>
+      </c>
+      <c r="U229" t="n">
+        <v>0</v>
+      </c>
+      <c r="V229" t="n">
+        <v>11.3490002155304</v>
+      </c>
+      <c r="W229" t="n">
+        <v>2867571.495318647</v>
+      </c>
+      <c r="X229" t="n">
+        <v>2867571.495318737</v>
+      </c>
+      <c r="Y229" t="n">
+        <v>9.033828973770142e-08</v>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC229" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD229" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426010940_dh_1_ctax_100_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>-3907956.459950909</v>
+      </c>
+      <c r="B230" t="n">
+        <v>0</v>
+      </c>
+      <c r="C230" t="n">
+        <v>0</v>
+      </c>
+      <c r="D230" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E230" t="n">
+        <v>0</v>
+      </c>
+      <c r="F230" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="n">
+        <v>1744785.219608191</v>
+      </c>
+      <c r="I230" t="n">
+        <v>-28197800.02524595</v>
+      </c>
+      <c r="J230" t="n">
+        <v>0</v>
+      </c>
+      <c r="K230" t="n">
+        <v>0</v>
+      </c>
+      <c r="L230" t="n">
+        <v>22109329.57389139</v>
+      </c>
+      <c r="M230" t="n">
+        <v>-3907956.459950909</v>
+      </c>
+      <c r="N230" t="n">
+        <v>221093.2957389139</v>
+      </c>
+      <c r="O230" t="n">
+        <v>0</v>
+      </c>
+      <c r="P230" t="n">
+        <v>221093.2957389139</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>221093.2957389138</v>
+      </c>
+      <c r="R230" t="n">
+        <v>0</v>
+      </c>
+      <c r="S230" t="n">
+        <v>0</v>
+      </c>
+      <c r="T230" t="n">
+        <v>0</v>
+      </c>
+      <c r="U230" t="n">
+        <v>0</v>
+      </c>
+      <c r="V230" t="n">
+        <v>8.466000080108643</v>
+      </c>
+      <c r="W230" t="n">
+        <v>-3907956.459950909</v>
+      </c>
+      <c r="X230" t="n">
+        <v>-3907956.459950909</v>
+      </c>
+      <c r="Y230" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD230" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426011204_dh_1_ctax_100_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>-11236309.91853718</v>
+      </c>
+      <c r="B231" t="n">
+        <v>0</v>
+      </c>
+      <c r="C231" t="n">
+        <v>0</v>
+      </c>
+      <c r="D231" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E231" t="n">
+        <v>0</v>
+      </c>
+      <c r="F231" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" t="n">
+        <v>3274721.082435129</v>
+      </c>
+      <c r="I231" t="n">
+        <v>-37763684.68321662</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0</v>
+      </c>
+      <c r="K231" t="n">
+        <v>0</v>
+      </c>
+      <c r="L231" t="n">
+        <v>22816924.91044885</v>
+      </c>
+      <c r="M231" t="n">
+        <v>-11236309.91853718</v>
+      </c>
+      <c r="N231" t="n">
+        <v>228169.2491044884</v>
+      </c>
+      <c r="O231" t="n">
+        <v>0</v>
+      </c>
+      <c r="P231" t="n">
+        <v>228169.2491044884</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>228169.2491044884</v>
+      </c>
+      <c r="R231" t="n">
+        <v>0</v>
+      </c>
+      <c r="S231" t="n">
+        <v>0</v>
+      </c>
+      <c r="T231" t="n">
+        <v>0</v>
+      </c>
+      <c r="U231" t="n">
+        <v>0</v>
+      </c>
+      <c r="V231" t="n">
+        <v>8.694999933242798</v>
+      </c>
+      <c r="W231" t="n">
+        <v>-11236309.91853718</v>
+      </c>
+      <c r="X231" t="n">
+        <v>-11236309.91853718</v>
+      </c>
+      <c r="Y231" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC231" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD231" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426011424_dh_1_ctax_100_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>-18885483.653923</v>
+      </c>
+      <c r="B232" t="n">
+        <v>0</v>
+      </c>
+      <c r="C232" t="n">
+        <v>0</v>
+      </c>
+      <c r="D232" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E232" t="n">
+        <v>0</v>
+      </c>
+      <c r="F232" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" t="n">
+        <v>3864155.607518862</v>
+      </c>
+      <c r="I232" t="n">
+        <v>-46274906.4115374</v>
+      </c>
+      <c r="J232" t="n">
+        <v>0</v>
+      </c>
+      <c r="K232" t="n">
+        <v>0</v>
+      </c>
+      <c r="L232" t="n">
+        <v>23089538.37830008</v>
+      </c>
+      <c r="M232" t="n">
+        <v>-18885483.653923</v>
+      </c>
+      <c r="N232" t="n">
+        <v>230895.3837830007</v>
+      </c>
+      <c r="O232" t="n">
+        <v>0</v>
+      </c>
+      <c r="P232" t="n">
+        <v>230895.3837830007</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>230895.3837830007</v>
+      </c>
+      <c r="R232" t="n">
+        <v>0</v>
+      </c>
+      <c r="S232" t="n">
+        <v>0</v>
+      </c>
+      <c r="T232" t="n">
+        <v>0</v>
+      </c>
+      <c r="U232" t="n">
+        <v>0</v>
+      </c>
+      <c r="V232" t="n">
+        <v>8.586999893188477</v>
+      </c>
+      <c r="W232" t="n">
+        <v>-18885483.653923</v>
+      </c>
+      <c r="X232" t="n">
+        <v>-18885483.653923</v>
+      </c>
+      <c r="Y232" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD232" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426011647_dh_1_ctax_100_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>-26627309.3052735</v>
+      </c>
+      <c r="B233" t="n">
+        <v>0</v>
+      </c>
+      <c r="C233" t="n">
+        <v>0</v>
+      </c>
+      <c r="D233" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E233" t="n">
+        <v>0</v>
+      </c>
+      <c r="F233" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="n">
+        <v>4098614.410903892</v>
+      </c>
+      <c r="I233" t="n">
+        <v>-54359628.06283851</v>
+      </c>
+      <c r="J233" t="n">
+        <v>0</v>
+      </c>
+      <c r="K233" t="n">
+        <v>0</v>
+      </c>
+      <c r="L233" t="n">
+        <v>23197975.57486565</v>
+      </c>
+      <c r="M233" t="n">
+        <v>-26627309.3052735</v>
+      </c>
+      <c r="N233" t="n">
+        <v>231979.7557486565</v>
+      </c>
+      <c r="O233" t="n">
+        <v>0</v>
+      </c>
+      <c r="P233" t="n">
+        <v>231979.7557486565</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>231979.7557486565</v>
+      </c>
+      <c r="R233" t="n">
+        <v>0</v>
+      </c>
+      <c r="S233" t="n">
+        <v>0</v>
+      </c>
+      <c r="T233" t="n">
+        <v>0</v>
+      </c>
+      <c r="U233" t="n">
+        <v>0</v>
+      </c>
+      <c r="V233" t="n">
+        <v>14.15100002288818</v>
+      </c>
+      <c r="W233" t="n">
+        <v>-26627309.3052735</v>
+      </c>
+      <c r="X233" t="n">
+        <v>-26627309.3052735</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC233" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD233" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426011911_dh_1_ctax_100_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>-34400959.54221863</v>
+      </c>
+      <c r="B234" t="n">
+        <v>0</v>
+      </c>
+      <c r="C234" t="n">
+        <v>0</v>
+      </c>
+      <c r="D234" t="n">
+        <v>435728.771795464</v>
+      </c>
+      <c r="E234" t="n">
+        <v>0</v>
+      </c>
+      <c r="F234" t="n">
+        <v>435728.7717954641</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" t="n">
+        <v>4162735.064657771</v>
+      </c>
+      <c r="I234" t="n">
+        <v>-62227054.75589869</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0</v>
+      </c>
+      <c r="K234" t="n">
+        <v>0</v>
+      </c>
+      <c r="L234" t="n">
+        <v>23227631.37722682</v>
+      </c>
+      <c r="M234" t="n">
+        <v>-34400959.54221863</v>
+      </c>
+      <c r="N234" t="n">
+        <v>232276.3137722682</v>
+      </c>
+      <c r="O234" t="n">
+        <v>0</v>
+      </c>
+      <c r="P234" t="n">
+        <v>232276.3137722682</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>232276.3137722682</v>
+      </c>
+      <c r="R234" t="n">
+        <v>0</v>
+      </c>
+      <c r="S234" t="n">
+        <v>0</v>
+      </c>
+      <c r="T234" t="n">
+        <v>0</v>
+      </c>
+      <c r="U234" t="n">
+        <v>0</v>
+      </c>
+      <c r="V234" t="n">
+        <v>16.54800009727478</v>
+      </c>
+      <c r="W234" t="n">
+        <v>-34400959.54221863</v>
+      </c>
+      <c r="X234" t="n">
+        <v>-34400959.54221863</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC234" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD234" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426012140_dh_1_ctax_100_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>15351539.32508947</v>
+      </c>
+      <c r="B235" t="n">
+        <v>4599542.624500888</v>
+      </c>
+      <c r="C235" t="n">
+        <v>3293615.748495395</v>
+      </c>
+      <c r="D235" t="n">
+        <v>3993697.852002246</v>
+      </c>
+      <c r="E235" t="n">
+        <v>0</v>
+      </c>
+      <c r="F235" t="n">
+        <v>8593240.476503134</v>
+      </c>
+      <c r="G235" t="n">
+        <v>3293615.748495395</v>
+      </c>
+      <c r="H235" t="n">
+        <v>1221964.892626518</v>
+      </c>
+      <c r="I235" t="n">
+        <v>-1999182.703117302</v>
+      </c>
+      <c r="J235" t="n">
+        <v>0</v>
+      </c>
+      <c r="K235" t="n">
+        <v>0</v>
+      </c>
+      <c r="L235" t="n">
+        <v>4241900.910581727</v>
+      </c>
+      <c r="M235" t="n">
+        <v>15351539.32508947</v>
+      </c>
+      <c r="N235" t="n">
+        <v>28281.71935278201</v>
+      </c>
+      <c r="O235" t="n">
+        <v>0</v>
+      </c>
+      <c r="P235" t="n">
+        <v>28281.71935278201</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>28279.3394038782</v>
+      </c>
+      <c r="R235" t="n">
+        <v>0</v>
+      </c>
+      <c r="S235" t="n">
+        <v>0</v>
+      </c>
+      <c r="T235" t="n">
+        <v>0</v>
+      </c>
+      <c r="U235" t="n">
+        <v>2.379948904034318</v>
+      </c>
+      <c r="V235" t="n">
+        <v>18.98300004005432</v>
+      </c>
+      <c r="W235" t="n">
+        <v>15351539.32508947</v>
+      </c>
+      <c r="X235" t="n">
+        <v>15351539.32508947</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC235" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD235" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426012414_dh_1_ctax_150_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>13342444.52352396</v>
+      </c>
+      <c r="B236" t="n">
+        <v>4551378.219191149</v>
+      </c>
+      <c r="C236" t="n">
+        <v>3275465.50873317</v>
+      </c>
+      <c r="D236" t="n">
+        <v>3964186.655272894</v>
+      </c>
+      <c r="E236" t="n">
+        <v>0</v>
+      </c>
+      <c r="F236" t="n">
+        <v>8515564.874464042</v>
+      </c>
+      <c r="G236" t="n">
+        <v>3275465.50873317</v>
+      </c>
+      <c r="H236" t="n">
+        <v>1226215.707994437</v>
+      </c>
+      <c r="I236" t="n">
+        <v>-4059530.960983664</v>
+      </c>
+      <c r="J236" t="n">
+        <v>0</v>
+      </c>
+      <c r="K236" t="n">
+        <v>0</v>
+      </c>
+      <c r="L236" t="n">
+        <v>4384729.393315976</v>
+      </c>
+      <c r="M236" t="n">
+        <v>13342444.52352396</v>
+      </c>
+      <c r="N236" t="n">
+        <v>29233.89758105405</v>
+      </c>
+      <c r="O236" t="n">
+        <v>0</v>
+      </c>
+      <c r="P236" t="n">
+        <v>29233.89758105405</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>29231.5292887731</v>
+      </c>
+      <c r="R236" t="n">
+        <v>0</v>
+      </c>
+      <c r="S236" t="n">
+        <v>0</v>
+      </c>
+      <c r="T236" t="n">
+        <v>0</v>
+      </c>
+      <c r="U236" t="n">
+        <v>2.368292280736589</v>
+      </c>
+      <c r="V236" t="n">
+        <v>18.86299991607666</v>
+      </c>
+      <c r="W236" t="n">
+        <v>13342444.52352396</v>
+      </c>
+      <c r="X236" t="n">
+        <v>13342444.52352396</v>
+      </c>
+      <c r="Y236" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC236" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD236" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE236" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426013053_dh_1_ctax_150_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>11244750.39534782</v>
+      </c>
+      <c r="B237" t="n">
+        <v>4474342.377421819</v>
+      </c>
+      <c r="C237" t="n">
+        <v>3246434.906180321</v>
+      </c>
+      <c r="D237" t="n">
+        <v>3913145.59025656</v>
+      </c>
+      <c r="E237" t="n">
+        <v>0</v>
+      </c>
+      <c r="F237" t="n">
+        <v>8387487.967678379</v>
+      </c>
+      <c r="G237" t="n">
+        <v>3246434.906180321</v>
+      </c>
+      <c r="H237" t="n">
+        <v>1486104.41581778</v>
+      </c>
+      <c r="I237" t="n">
+        <v>-6742942.51940487</v>
+      </c>
+      <c r="J237" t="n">
+        <v>0</v>
+      </c>
+      <c r="K237" t="n">
+        <v>0</v>
+      </c>
+      <c r="L237" t="n">
+        <v>4867665.625076213</v>
+      </c>
+      <c r="M237" t="n">
+        <v>11244750.39534782</v>
+      </c>
+      <c r="N237" t="n">
+        <v>32453.44723958582</v>
+      </c>
+      <c r="O237" t="n">
+        <v>0</v>
+      </c>
+      <c r="P237" t="n">
+        <v>32453.44723958582</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>32451.10416717469</v>
+      </c>
+      <c r="R237" t="n">
+        <v>0</v>
+      </c>
+      <c r="S237" t="n">
+        <v>0</v>
+      </c>
+      <c r="T237" t="n">
+        <v>0</v>
+      </c>
+      <c r="U237" t="n">
+        <v>2.343072410677606</v>
+      </c>
+      <c r="V237" t="n">
+        <v>23.93200016021729</v>
+      </c>
+      <c r="W237" t="n">
+        <v>11244750.39534782</v>
+      </c>
+      <c r="X237" t="n">
+        <v>11244750.39534782</v>
+      </c>
+      <c r="Y237" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC237" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD237" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE237" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426013327_dh_1_ctax_150_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>7050699.147829827</v>
+      </c>
+      <c r="B238" t="n">
+        <v>0</v>
+      </c>
+      <c r="C238" t="n">
+        <v>0</v>
+      </c>
+      <c r="D238" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E238" t="n">
+        <v>0</v>
+      </c>
+      <c r="F238" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" t="n">
+        <v>955403.0045410157</v>
+      </c>
+      <c r="I238" t="n">
+        <v>-26956793.07764089</v>
+      </c>
+      <c r="J238" t="n">
+        <v>0</v>
+      </c>
+      <c r="K238" t="n">
+        <v>0</v>
+      </c>
+      <c r="L238" t="n">
+        <v>32616360.44913424</v>
+      </c>
+      <c r="M238" t="n">
+        <v>7050699.147829827</v>
+      </c>
+      <c r="N238" t="n">
+        <v>217442.4029942281</v>
+      </c>
+      <c r="O238" t="n">
+        <v>0</v>
+      </c>
+      <c r="P238" t="n">
+        <v>217442.4029942281</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>217442.4029942282</v>
+      </c>
+      <c r="R238" t="n">
+        <v>0</v>
+      </c>
+      <c r="S238" t="n">
+        <v>0</v>
+      </c>
+      <c r="T238" t="n">
+        <v>0</v>
+      </c>
+      <c r="U238" t="n">
+        <v>0</v>
+      </c>
+      <c r="V238" t="n">
+        <v>23.4760000705719</v>
+      </c>
+      <c r="W238" t="n">
+        <v>6951519.272699739</v>
+      </c>
+      <c r="X238" t="n">
+        <v>7050699.147829827</v>
+      </c>
+      <c r="Y238" t="n">
+        <v>99179.87513008807</v>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC238" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD238" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426013609_dh_1_ctax_150_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>62478.0002864562</v>
+      </c>
+      <c r="B239" t="n">
+        <v>0</v>
+      </c>
+      <c r="C239" t="n">
+        <v>0</v>
+      </c>
+      <c r="D239" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E239" t="n">
+        <v>0</v>
+      </c>
+      <c r="F239" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" t="n">
+        <v>2275717.794954614</v>
+      </c>
+      <c r="I239" t="n">
+        <v>-36181297.4014473</v>
+      </c>
+      <c r="J239" t="n">
+        <v>0</v>
+      </c>
+      <c r="K239" t="n">
+        <v>0</v>
+      </c>
+      <c r="L239" t="n">
+        <v>33532328.83498367</v>
+      </c>
+      <c r="M239" t="n">
+        <v>62478.0002864562</v>
+      </c>
+      <c r="N239" t="n">
+        <v>223548.8588998911</v>
+      </c>
+      <c r="O239" t="n">
+        <v>0</v>
+      </c>
+      <c r="P239" t="n">
+        <v>223548.8588998911</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>223548.8588998911</v>
+      </c>
+      <c r="R239" t="n">
+        <v>0</v>
+      </c>
+      <c r="S239" t="n">
+        <v>0</v>
+      </c>
+      <c r="T239" t="n">
+        <v>0</v>
+      </c>
+      <c r="U239" t="n">
+        <v>0</v>
+      </c>
+      <c r="V239" t="n">
+        <v>14.55999994277954</v>
+      </c>
+      <c r="W239" t="n">
+        <v>62478.0002864562</v>
+      </c>
+      <c r="X239" t="n">
+        <v>62478.0002864562</v>
+      </c>
+      <c r="Y239" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC239" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD239" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE239" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426013851_dh_1_ctax_150_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>-7384589.217097677</v>
+      </c>
+      <c r="B240" t="n">
+        <v>0</v>
+      </c>
+      <c r="C240" t="n">
+        <v>0</v>
+      </c>
+      <c r="D240" t="n">
+        <v>435728.771795464</v>
+      </c>
+      <c r="E240" t="n">
+        <v>0</v>
+      </c>
+      <c r="F240" t="n">
+        <v>435728.771795464</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" t="n">
+        <v>3398482.612366882</v>
+      </c>
+      <c r="I240" t="n">
+        <v>-45530047.52832346</v>
+      </c>
+      <c r="J240" t="n">
+        <v>0</v>
+      </c>
+      <c r="K240" t="n">
+        <v>0</v>
+      </c>
+      <c r="L240" t="n">
+        <v>34311246.92706344</v>
+      </c>
+      <c r="M240" t="n">
+        <v>-7384589.217097677</v>
+      </c>
+      <c r="N240" t="n">
+        <v>228741.6461804228</v>
+      </c>
+      <c r="O240" t="n">
+        <v>0</v>
+      </c>
+      <c r="P240" t="n">
+        <v>228741.6461804228</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>228741.6461804228</v>
+      </c>
+      <c r="R240" t="n">
+        <v>0</v>
+      </c>
+      <c r="S240" t="n">
+        <v>0</v>
+      </c>
+      <c r="T240" t="n">
+        <v>0</v>
+      </c>
+      <c r="U240" t="n">
+        <v>0</v>
+      </c>
+      <c r="V240" t="n">
+        <v>15.51900005340576</v>
+      </c>
+      <c r="W240" t="n">
+        <v>-7384589.217097677</v>
+      </c>
+      <c r="X240" t="n">
+        <v>-7384589.217097677</v>
+      </c>
+      <c r="Y240" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC240" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD240" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE240" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426014125_dh_1_ctax_150_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>-15053248.70991591</v>
+      </c>
+      <c r="B241" t="n">
+        <v>0</v>
+      </c>
+      <c r="C241" t="n">
+        <v>0</v>
+      </c>
+      <c r="D241" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E241" t="n">
+        <v>0</v>
+      </c>
+      <c r="F241" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" t="n">
+        <v>3875514.618392541</v>
+      </c>
+      <c r="I241" t="n">
+        <v>-54006679.98134765</v>
+      </c>
+      <c r="J241" t="n">
+        <v>0</v>
+      </c>
+      <c r="K241" t="n">
+        <v>0</v>
+      </c>
+      <c r="L241" t="n">
+        <v>34642187.88124374</v>
+      </c>
+      <c r="M241" t="n">
+        <v>-15053248.70991591</v>
+      </c>
+      <c r="N241" t="n">
+        <v>230947.9192082915</v>
+      </c>
+      <c r="O241" t="n">
+        <v>0</v>
+      </c>
+      <c r="P241" t="n">
+        <v>230947.9192082915</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>230947.9192082915</v>
+      </c>
+      <c r="R241" t="n">
+        <v>0</v>
+      </c>
+      <c r="S241" t="n">
+        <v>0</v>
+      </c>
+      <c r="T241" t="n">
+        <v>0</v>
+      </c>
+      <c r="U241" t="n">
+        <v>0</v>
+      </c>
+      <c r="V241" t="n">
+        <v>16.52600002288818</v>
+      </c>
+      <c r="W241" t="n">
+        <v>-15053248.70991591</v>
+      </c>
+      <c r="X241" t="n">
+        <v>-15053248.70991591</v>
+      </c>
+      <c r="Y241" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC241" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD241" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE241" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426014400_dh_1_ctax_150_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>-24540806.65989729</v>
+      </c>
+      <c r="B242" t="n">
+        <v>30925520.59477416</v>
+      </c>
+      <c r="C242" t="n">
+        <v>4401617.220603922</v>
+      </c>
+      <c r="D242" t="n">
+        <v>22215864.24309057</v>
+      </c>
+      <c r="E242" t="n">
+        <v>0</v>
+      </c>
+      <c r="F242" t="n">
+        <v>53141384.83786473</v>
+      </c>
+      <c r="G242" t="n">
+        <v>4401617.220603922</v>
+      </c>
+      <c r="H242" t="n">
+        <v>6658772.2578664</v>
+      </c>
+      <c r="I242" t="n">
+        <v>-97863792.29791692</v>
+      </c>
+      <c r="J242" t="n">
+        <v>0</v>
+      </c>
+      <c r="K242" t="n">
+        <v>0</v>
+      </c>
+      <c r="L242" t="n">
+        <v>9121211.321684588</v>
+      </c>
+      <c r="M242" t="n">
+        <v>-24540806.65989729</v>
+      </c>
+      <c r="N242" t="n">
+        <v>60812.86133676305</v>
+      </c>
+      <c r="O242" t="n">
+        <v>0</v>
+      </c>
+      <c r="P242" t="n">
+        <v>60812.86133676305</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>60808.07547789723</v>
+      </c>
+      <c r="R242" t="n">
+        <v>0</v>
+      </c>
+      <c r="S242" t="n">
+        <v>0</v>
+      </c>
+      <c r="T242" t="n">
+        <v>0</v>
+      </c>
+      <c r="U242" t="n">
+        <v>4.785858865855401</v>
+      </c>
+      <c r="V242" t="n">
+        <v>21.10400009155273</v>
+      </c>
+      <c r="W242" t="n">
+        <v>-24540806.65989729</v>
+      </c>
+      <c r="X242" t="n">
+        <v>-24540806.65989729</v>
+      </c>
+      <c r="Y242" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC242" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD242" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426014639_dh_1_ctax_150_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>16748983.3251502</v>
+      </c>
+      <c r="B243" t="n">
+        <v>4639402.637478655</v>
+      </c>
+      <c r="C243" t="n">
+        <v>3308637.803030351</v>
+      </c>
+      <c r="D243" t="n">
+        <v>4016586.287431212</v>
+      </c>
+      <c r="E243" t="n">
+        <v>0</v>
+      </c>
+      <c r="F243" t="n">
+        <v>8655988.924909867</v>
+      </c>
+      <c r="G243" t="n">
+        <v>3308637.803030351</v>
+      </c>
+      <c r="H243" t="n">
+        <v>1224187.398177296</v>
+      </c>
+      <c r="I243" t="n">
+        <v>-1985416.311011272</v>
+      </c>
+      <c r="J243" t="n">
+        <v>0</v>
+      </c>
+      <c r="K243" t="n">
+        <v>0</v>
+      </c>
+      <c r="L243" t="n">
+        <v>5545585.510043955</v>
+      </c>
+      <c r="M243" t="n">
+        <v>16748983.3251502</v>
+      </c>
+      <c r="N243" t="n">
+        <v>27730.31452026049</v>
+      </c>
+      <c r="O243" t="n">
+        <v>0</v>
+      </c>
+      <c r="P243" t="n">
+        <v>27730.31452026049</v>
+      </c>
+      <c r="Q243" t="n">
+        <v>27727.92755021981</v>
+      </c>
+      <c r="R243" t="n">
+        <v>0</v>
+      </c>
+      <c r="S243" t="n">
+        <v>0</v>
+      </c>
+      <c r="T243" t="n">
+        <v>0</v>
+      </c>
+      <c r="U243" t="n">
+        <v>2.386970040807202</v>
+      </c>
+      <c r="V243" t="n">
+        <v>15.67000007629395</v>
+      </c>
+      <c r="W243" t="n">
+        <v>16748983.3251502</v>
+      </c>
+      <c r="X243" t="n">
+        <v>16748983.3251502</v>
+      </c>
+      <c r="Y243" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC243" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD243" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE243" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426014924_dh_1_ctax_200_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>14761348.63360327</v>
+      </c>
+      <c r="B244" t="n">
+        <v>4623032.230384513</v>
+      </c>
+      <c r="C244" t="n">
+        <v>3302468.150364476</v>
+      </c>
+      <c r="D244" t="n">
+        <v>4007370.354880523</v>
+      </c>
+      <c r="E244" t="n">
+        <v>0</v>
+      </c>
+      <c r="F244" t="n">
+        <v>8630402.585265037</v>
+      </c>
+      <c r="G244" t="n">
+        <v>3302468.150364476</v>
+      </c>
+      <c r="H244" t="n">
+        <v>1223427.694481949</v>
+      </c>
+      <c r="I244" t="n">
+        <v>-3980923.811463071</v>
+      </c>
+      <c r="J244" t="n">
+        <v>0</v>
+      </c>
+      <c r="K244" t="n">
+        <v>0</v>
+      </c>
+      <c r="L244" t="n">
+        <v>5585974.014954882</v>
+      </c>
+      <c r="M244" t="n">
+        <v>14761348.63360327</v>
+      </c>
+      <c r="N244" t="n">
+        <v>27932.25447661326</v>
+      </c>
+      <c r="O244" t="n">
+        <v>0</v>
+      </c>
+      <c r="P244" t="n">
+        <v>27932.25447661326</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>27929.87007477451</v>
+      </c>
+      <c r="R244" t="n">
+        <v>0</v>
+      </c>
+      <c r="S244" t="n">
+        <v>0</v>
+      </c>
+      <c r="T244" t="n">
+        <v>0</v>
+      </c>
+      <c r="U244" t="n">
+        <v>2.384401838880381</v>
+      </c>
+      <c r="V244" t="n">
+        <v>26.87999987602234</v>
+      </c>
+      <c r="W244" t="n">
+        <v>14761348.63360327</v>
+      </c>
+      <c r="X244" t="n">
+        <v>14761348.63360327</v>
+      </c>
+      <c r="Y244" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC244" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD244" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE244" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426015203_dh_1_ctax_200_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>12746129.93566353</v>
+      </c>
+      <c r="B245" t="n">
+        <v>4600013.165219379</v>
+      </c>
+      <c r="C245" t="n">
+        <v>3293793.065332895</v>
+      </c>
+      <c r="D245" t="n">
+        <v>3993976.874504026</v>
+      </c>
+      <c r="E245" t="n">
+        <v>0</v>
+      </c>
+      <c r="F245" t="n">
+        <v>8593990.039723406</v>
+      </c>
+      <c r="G245" t="n">
+        <v>3293793.065332895</v>
+      </c>
+      <c r="H245" t="n">
+        <v>1297379.865548342</v>
+      </c>
+      <c r="I245" t="n">
+        <v>-6163092.157066563</v>
+      </c>
+      <c r="J245" t="n">
+        <v>0</v>
+      </c>
+      <c r="K245" t="n">
+        <v>0</v>
+      </c>
+      <c r="L245" t="n">
+        <v>5724059.122125454</v>
+      </c>
+      <c r="M245" t="n">
+        <v>12746129.93566353</v>
+      </c>
+      <c r="N245" t="n">
+        <v>28622.67565750697</v>
+      </c>
+      <c r="O245" t="n">
+        <v>0</v>
+      </c>
+      <c r="P245" t="n">
+        <v>28622.67565750697</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>28620.29561062738</v>
+      </c>
+      <c r="R245" t="n">
+        <v>0</v>
+      </c>
+      <c r="S245" t="n">
+        <v>0</v>
+      </c>
+      <c r="T245" t="n">
+        <v>0</v>
+      </c>
+      <c r="U245" t="n">
+        <v>2.380046879571996</v>
+      </c>
+      <c r="V245" t="n">
+        <v>35.38199996948242</v>
+      </c>
+      <c r="W245" t="n">
+        <v>12746129.93566353</v>
+      </c>
+      <c r="X245" t="n">
+        <v>12746129.93566353</v>
+      </c>
+      <c r="Y245" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB245" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC245" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD245" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426015452_dh_1_ctax_200_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>10463087.23150969</v>
+      </c>
+      <c r="B246" t="n">
+        <v>4557714.109590459</v>
+      </c>
+      <c r="C246" t="n">
+        <v>3277853.10212896</v>
+      </c>
+      <c r="D246" t="n">
+        <v>3968049.451993026</v>
+      </c>
+      <c r="E246" t="n">
+        <v>0</v>
+      </c>
+      <c r="F246" t="n">
+        <v>8525763.561583485</v>
+      </c>
+      <c r="G246" t="n">
+        <v>3277853.10212896</v>
+      </c>
+      <c r="H246" t="n">
+        <v>2380163.834754401</v>
+      </c>
+      <c r="I246" t="n">
+        <v>-10610396.53368326</v>
+      </c>
+      <c r="J246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K246" t="n">
+        <v>0</v>
+      </c>
+      <c r="L246" t="n">
+        <v>6889703.266726107</v>
+      </c>
+      <c r="M246" t="n">
+        <v>10463087.23150969</v>
+      </c>
+      <c r="N246" t="n">
+        <v>34450.88612619901</v>
+      </c>
+      <c r="O246" t="n">
+        <v>0</v>
+      </c>
+      <c r="P246" t="n">
+        <v>34450.88612619901</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>34448.51633363035</v>
+      </c>
+      <c r="R246" t="n">
+        <v>0</v>
+      </c>
+      <c r="S246" t="n">
+        <v>0</v>
+      </c>
+      <c r="T246" t="n">
+        <v>0</v>
+      </c>
+      <c r="U246" t="n">
+        <v>2.369792568754184</v>
+      </c>
+      <c r="V246" t="n">
+        <v>41.59800004959106</v>
+      </c>
+      <c r="W246" t="n">
+        <v>10463087.23150969</v>
+      </c>
+      <c r="X246" t="n">
+        <v>10463087.23150969</v>
+      </c>
+      <c r="Y246" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD246" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426020251_dh_1_ctax_200_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>7258679.883857291</v>
+      </c>
+      <c r="B247" t="n">
+        <v>4499402.943274959</v>
+      </c>
+      <c r="C247" t="n">
+        <v>3255879.33888159</v>
+      </c>
+      <c r="D247" t="n">
+        <v>3929475.929699738</v>
+      </c>
+      <c r="E247" t="n">
+        <v>0</v>
+      </c>
+      <c r="F247" t="n">
+        <v>8428878.872974698</v>
+      </c>
+      <c r="G247" t="n">
+        <v>3255879.33888159</v>
+      </c>
+      <c r="H247" t="n">
+        <v>5227546.576378906</v>
+      </c>
+      <c r="I247" t="n">
+        <v>-19480902.15603677</v>
+      </c>
+      <c r="J247" t="n">
+        <v>0</v>
+      </c>
+      <c r="K247" t="n">
+        <v>0</v>
+      </c>
+      <c r="L247" t="n">
+        <v>9827277.251658864</v>
+      </c>
+      <c r="M247" t="n">
+        <v>7258679.883857291</v>
+      </c>
+      <c r="N247" t="n">
+        <v>49138.73706680367</v>
+      </c>
+      <c r="O247" t="n">
+        <v>0</v>
+      </c>
+      <c r="P247" t="n">
+        <v>49138.73706680367</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>49136.38625829434</v>
+      </c>
+      <c r="R247" t="n">
+        <v>0</v>
+      </c>
+      <c r="S247" t="n">
+        <v>0</v>
+      </c>
+      <c r="T247" t="n">
+        <v>0</v>
+      </c>
+      <c r="U247" t="n">
+        <v>2.35080850944605</v>
+      </c>
+      <c r="V247" t="n">
+        <v>40.29500007629395</v>
+      </c>
+      <c r="W247" t="n">
+        <v>7258679.883857291</v>
+      </c>
+      <c r="X247" t="n">
+        <v>7258679.883857291</v>
+      </c>
+      <c r="Y247" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC247" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD247" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE247" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426020559_dh_1_ctax_200_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>2565915.895558203</v>
+      </c>
+      <c r="B248" t="n">
+        <v>4457388.248179838</v>
+      </c>
+      <c r="C248" t="n">
+        <v>3240045.558684655</v>
+      </c>
+      <c r="D248" t="n">
+        <v>3899298.910104576</v>
+      </c>
+      <c r="E248" t="n">
+        <v>0</v>
+      </c>
+      <c r="F248" t="n">
+        <v>8356687.158284415</v>
+      </c>
+      <c r="G248" t="n">
+        <v>3240045.558684655</v>
+      </c>
+      <c r="H248" t="n">
+        <v>9554202.442659181</v>
+      </c>
+      <c r="I248" t="n">
+        <v>-32698647.87622739</v>
+      </c>
+      <c r="J248" t="n">
+        <v>0</v>
+      </c>
+      <c r="K248" t="n">
+        <v>0</v>
+      </c>
+      <c r="L248" t="n">
+        <v>14113628.61215735</v>
+      </c>
+      <c r="M248" t="n">
+        <v>2565915.895558203</v>
+      </c>
+      <c r="N248" t="n">
+        <v>70570.4761071285</v>
+      </c>
+      <c r="O248" t="n">
+        <v>0</v>
+      </c>
+      <c r="P248" t="n">
+        <v>70570.4761071285</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>70568.1430607868</v>
+      </c>
+      <c r="R248" t="n">
+        <v>0</v>
+      </c>
+      <c r="S248" t="n">
+        <v>0</v>
+      </c>
+      <c r="T248" t="n">
+        <v>0</v>
+      </c>
+      <c r="U248" t="n">
+        <v>2.333046341684223</v>
+      </c>
+      <c r="V248" t="n">
+        <v>36.08899998664856</v>
+      </c>
+      <c r="W248" t="n">
+        <v>2565915.895558203</v>
+      </c>
+      <c r="X248" t="n">
+        <v>2565915.895558203</v>
+      </c>
+      <c r="Y248" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC248" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD248" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426020906_dh_1_ctax_200_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>-9394885.140655778</v>
+      </c>
+      <c r="B249" t="n">
+        <v>31256936.19164934</v>
+      </c>
+      <c r="C249" t="n">
+        <v>4433512.990636175</v>
+      </c>
+      <c r="D249" t="n">
+        <v>22445490.82275625</v>
+      </c>
+      <c r="E249" t="n">
+        <v>0</v>
+      </c>
+      <c r="F249" t="n">
+        <v>53702427.01440559</v>
+      </c>
+      <c r="G249" t="n">
+        <v>4433512.990636175</v>
+      </c>
+      <c r="H249" t="n">
+        <v>6142757.432533278</v>
+      </c>
+      <c r="I249" t="n">
+        <v>-85004801.85163751</v>
+      </c>
+      <c r="J249" t="n">
+        <v>0</v>
+      </c>
+      <c r="K249" t="n">
+        <v>0</v>
+      </c>
+      <c r="L249" t="n">
+        <v>11331219.27340668</v>
+      </c>
+      <c r="M249" t="n">
+        <v>-9394885.140655778</v>
+      </c>
+      <c r="N249" t="n">
+        <v>56660.92839219856</v>
+      </c>
+      <c r="O249" t="n">
+        <v>0</v>
+      </c>
+      <c r="P249" t="n">
+        <v>56660.92839219856</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>56656.09636703345</v>
+      </c>
+      <c r="R249" t="n">
+        <v>0</v>
+      </c>
+      <c r="S249" t="n">
+        <v>0</v>
+      </c>
+      <c r="T249" t="n">
+        <v>0</v>
+      </c>
+      <c r="U249" t="n">
+        <v>4.83202516511338</v>
+      </c>
+      <c r="V249" t="n">
+        <v>28.62400007247925</v>
+      </c>
+      <c r="W249" t="n">
+        <v>-9394885.140655778</v>
+      </c>
+      <c r="X249" t="n">
+        <v>-9394885.140655778</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC249" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD249" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE249" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426021213_dh_1_ctax_200_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>-21606303.51892786</v>
+      </c>
+      <c r="B250" t="n">
+        <v>31511866.04814287</v>
+      </c>
+      <c r="C250" t="n">
+        <v>4458047.696165243</v>
+      </c>
+      <c r="D250" t="n">
+        <v>22620186.0841522</v>
+      </c>
+      <c r="E250" t="n">
+        <v>0</v>
+      </c>
+      <c r="F250" t="n">
+        <v>54132052.13229507</v>
+      </c>
+      <c r="G250" t="n">
+        <v>4458047.696165243</v>
+      </c>
+      <c r="H250" t="n">
+        <v>6494241.632415947</v>
+      </c>
+      <c r="I250" t="n">
+        <v>-98095453.45735762</v>
+      </c>
+      <c r="J250" t="n">
+        <v>0</v>
+      </c>
+      <c r="K250" t="n">
+        <v>0</v>
+      </c>
+      <c r="L250" t="n">
+        <v>11404808.47755349</v>
+      </c>
+      <c r="M250" t="n">
+        <v>-21606303.51892786</v>
+      </c>
+      <c r="N250" t="n">
+        <v>57028.90730154092</v>
+      </c>
+      <c r="O250" t="n">
+        <v>0</v>
+      </c>
+      <c r="P250" t="n">
+        <v>57028.90730154092</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>57024.04238776748</v>
+      </c>
+      <c r="R250" t="n">
+        <v>0</v>
+      </c>
+      <c r="S250" t="n">
+        <v>0</v>
+      </c>
+      <c r="T250" t="n">
+        <v>0</v>
+      </c>
+      <c r="U250" t="n">
+        <v>4.864913773432199</v>
+      </c>
+      <c r="V250" t="n">
+        <v>27.73900008201599</v>
+      </c>
+      <c r="W250" t="n">
+        <v>-21606303.51892786</v>
+      </c>
+      <c r="X250" t="n">
+        <v>-21606303.51892786</v>
+      </c>
+      <c r="Y250" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC250" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD250" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426021514_dh_1_ctax_200_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>18128927.13279833</v>
+      </c>
+      <c r="B251" t="n">
+        <v>4662935.717924869</v>
+      </c>
+      <c r="C251" t="n">
+        <v>3317506.664976693</v>
+      </c>
+      <c r="D251" t="n">
+        <v>4029408.601116285</v>
+      </c>
+      <c r="E251" t="n">
+        <v>0</v>
+      </c>
+      <c r="F251" t="n">
+        <v>8692344.319041153</v>
+      </c>
+      <c r="G251" t="n">
+        <v>3317506.664976693</v>
+      </c>
+      <c r="H251" t="n">
+        <v>1224991.05270989</v>
+      </c>
+      <c r="I251" t="n">
+        <v>-1979583.156952733</v>
+      </c>
+      <c r="J251" t="n">
+        <v>0</v>
+      </c>
+      <c r="K251" t="n">
+        <v>0</v>
+      </c>
+      <c r="L251" t="n">
+        <v>6873668.253023325</v>
+      </c>
+      <c r="M251" t="n">
+        <v>18128927.13279833</v>
+      </c>
+      <c r="N251" t="n">
+        <v>27497.06294427694</v>
+      </c>
+      <c r="O251" t="n">
+        <v>0</v>
+      </c>
+      <c r="P251" t="n">
+        <v>27497.06294427694</v>
+      </c>
+      <c r="Q251" t="n">
+        <v>27494.67301209323</v>
+      </c>
+      <c r="R251" t="n">
+        <v>0</v>
+      </c>
+      <c r="S251" t="n">
+        <v>0</v>
+      </c>
+      <c r="T251" t="n">
+        <v>0</v>
+      </c>
+      <c r="U251" t="n">
+        <v>2.38993218381145</v>
+      </c>
+      <c r="V251" t="n">
+        <v>26.91000008583069</v>
+      </c>
+      <c r="W251" t="n">
+        <v>18128927.13279833</v>
+      </c>
+      <c r="X251" t="n">
+        <v>18128927.13279833</v>
+      </c>
+      <c r="Y251" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC251" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD251" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426021813_dh_1_ctax_250_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>16148209.55796553</v>
+      </c>
+      <c r="B252" t="n">
+        <v>4652253.754567728</v>
+      </c>
+      <c r="C252" t="n">
+        <v>3313480.86382684</v>
+      </c>
+      <c r="D252" t="n">
+        <v>4023645.362045859</v>
+      </c>
+      <c r="E252" t="n">
+        <v>0</v>
+      </c>
+      <c r="F252" t="n">
+        <v>8675899.116613587</v>
+      </c>
+      <c r="G252" t="n">
+        <v>3313480.86382684</v>
+      </c>
+      <c r="H252" t="n">
+        <v>1224678.631931261</v>
+      </c>
+      <c r="I252" t="n">
+        <v>-3964099.57876177</v>
+      </c>
+      <c r="J252" t="n">
+        <v>0</v>
+      </c>
+      <c r="K252" t="n">
+        <v>0</v>
+      </c>
+      <c r="L252" t="n">
+        <v>6898250.524355614</v>
+      </c>
+      <c r="M252" t="n">
+        <v>16148209.55796553</v>
+      </c>
+      <c r="N252" t="n">
+        <v>27595.39078243091</v>
+      </c>
+      <c r="O252" t="n">
+        <v>0</v>
+      </c>
+      <c r="P252" t="n">
+        <v>27595.39078243091</v>
+      </c>
+      <c r="Q252" t="n">
+        <v>27593.00209742256</v>
+      </c>
+      <c r="R252" t="n">
+        <v>0</v>
+      </c>
+      <c r="S252" t="n">
+        <v>0</v>
+      </c>
+      <c r="T252" t="n">
+        <v>0</v>
+      </c>
+      <c r="U252" t="n">
+        <v>2.388685008418568</v>
+      </c>
+      <c r="V252" t="n">
+        <v>37.02300000190735</v>
+      </c>
+      <c r="W252" t="n">
+        <v>16148209.55796553</v>
+      </c>
+      <c r="X252" t="n">
+        <v>16148209.55796553</v>
+      </c>
+      <c r="Y252" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC252" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD252" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426022115_dh_1_ctax_250_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>14155918.72006492</v>
+      </c>
+      <c r="B253" t="n">
+        <v>4639448.926549187</v>
+      </c>
+      <c r="C253" t="n">
+        <v>3308655.248380717</v>
+      </c>
+      <c r="D253" t="n">
+        <v>4016611.977348081</v>
+      </c>
+      <c r="E253" t="n">
+        <v>0</v>
+      </c>
+      <c r="F253" t="n">
+        <v>8656060.903897267</v>
+      </c>
+      <c r="G253" t="n">
+        <v>3308655.248380717</v>
+      </c>
+      <c r="H253" t="n">
+        <v>1255393.360064316</v>
+      </c>
+      <c r="I253" t="n">
+        <v>-6032121.977036969</v>
+      </c>
+      <c r="J253" t="n">
+        <v>0</v>
+      </c>
+      <c r="K253" t="n">
+        <v>0</v>
+      </c>
+      <c r="L253" t="n">
+        <v>6967931.184759591</v>
+      </c>
+      <c r="M253" t="n">
+        <v>14155918.72006492</v>
+      </c>
+      <c r="N253" t="n">
+        <v>27874.11171570889</v>
+      </c>
+      <c r="O253" t="n">
+        <v>0</v>
+      </c>
+      <c r="P253" t="n">
+        <v>27874.11171570889</v>
+      </c>
+      <c r="Q253" t="n">
+        <v>27871.72473903837</v>
+      </c>
+      <c r="R253" t="n">
+        <v>0</v>
+      </c>
+      <c r="S253" t="n">
+        <v>0</v>
+      </c>
+      <c r="T253" t="n">
+        <v>0</v>
+      </c>
+      <c r="U253" t="n">
+        <v>2.386976670618563</v>
+      </c>
+      <c r="V253" t="n">
+        <v>35.74000000953674</v>
+      </c>
+      <c r="W253" t="n">
+        <v>14155918.72006492</v>
+      </c>
+      <c r="X253" t="n">
+        <v>14155918.72006492</v>
+      </c>
+      <c r="Y253" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC253" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD253" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE253" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426022426_dh_1_ctax_250_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>12064474.19830745</v>
+      </c>
+      <c r="B254" t="n">
+        <v>4623297.165055408</v>
+      </c>
+      <c r="C254" t="n">
+        <v>3302567.998516642</v>
+      </c>
+      <c r="D254" t="n">
+        <v>4007517.258083981</v>
+      </c>
+      <c r="E254" t="n">
+        <v>0</v>
+      </c>
+      <c r="F254" t="n">
+        <v>8630814.42313939</v>
+      </c>
+      <c r="G254" t="n">
+        <v>3302567.998516642</v>
+      </c>
+      <c r="H254" t="n">
+        <v>1673399.515739382</v>
+      </c>
+      <c r="I254" t="n">
+        <v>-9044300.804373378</v>
+      </c>
+      <c r="J254" t="n">
+        <v>0</v>
+      </c>
+      <c r="K254" t="n">
+        <v>0</v>
+      </c>
+      <c r="L254" t="n">
+        <v>7501993.065285411</v>
+      </c>
+      <c r="M254" t="n">
+        <v>12064474.19830745</v>
+      </c>
+      <c r="N254" t="n">
+        <v>30010.35670069948</v>
+      </c>
+      <c r="O254" t="n">
+        <v>0</v>
+      </c>
+      <c r="P254" t="n">
+        <v>30010.35670069948</v>
+      </c>
+      <c r="Q254" t="n">
+        <v>30007.9722611418</v>
+      </c>
+      <c r="R254" t="n">
+        <v>0</v>
+      </c>
+      <c r="S254" t="n">
+        <v>0</v>
+      </c>
+      <c r="T254" t="n">
+        <v>0</v>
+      </c>
+      <c r="U254" t="n">
+        <v>2.384439557467235</v>
+      </c>
+      <c r="V254" t="n">
+        <v>59.07999992370605</v>
+      </c>
+      <c r="W254" t="n">
+        <v>12064474.19830745</v>
+      </c>
+      <c r="X254" t="n">
+        <v>12064474.19830745</v>
+      </c>
+      <c r="Y254" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC254" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD254" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426022735_dh_1_ctax_250_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>9403276.274473999</v>
+      </c>
+      <c r="B255" t="n">
+        <v>4603330.046329536</v>
+      </c>
+      <c r="C255" t="n">
+        <v>3295042.986637698</v>
+      </c>
+      <c r="D255" t="n">
+        <v>3995836.953633601</v>
+      </c>
+      <c r="E255" t="n">
+        <v>0</v>
+      </c>
+      <c r="F255" t="n">
+        <v>8599166.999963136</v>
+      </c>
+      <c r="G255" t="n">
+        <v>3295042.986637698</v>
+      </c>
+      <c r="H255" t="n">
+        <v>3418588.351336118</v>
+      </c>
+      <c r="I255" t="n">
+        <v>-15507087.20980049</v>
+      </c>
+      <c r="J255" t="n">
+        <v>0</v>
+      </c>
+      <c r="K255" t="n">
+        <v>0</v>
+      </c>
+      <c r="L255" t="n">
+        <v>9597565.146337541</v>
+      </c>
+      <c r="M255" t="n">
+        <v>9403276.274473999</v>
+      </c>
+      <c r="N255" t="n">
+        <v>38392.64114003311</v>
+      </c>
+      <c r="O255" t="n">
+        <v>0</v>
+      </c>
+      <c r="P255" t="n">
+        <v>38392.64114003311</v>
+      </c>
+      <c r="Q255" t="n">
+        <v>38390.26058535012</v>
+      </c>
+      <c r="R255" t="n">
+        <v>0</v>
+      </c>
+      <c r="S255" t="n">
+        <v>0</v>
+      </c>
+      <c r="T255" t="n">
+        <v>0</v>
+      </c>
+      <c r="U255" t="n">
+        <v>2.380554682972567</v>
+      </c>
+      <c r="V255" t="n">
+        <v>52.47699999809265</v>
+      </c>
+      <c r="W255" t="n">
+        <v>9403276.274473999</v>
+      </c>
+      <c r="X255" t="n">
+        <v>9403276.274473999</v>
+      </c>
+      <c r="Y255" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC255" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD255" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE255" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426023108_dh_1_ctax_250_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>5161275.771872403</v>
+      </c>
+      <c r="B256" t="n">
+        <v>31475976.17174264</v>
+      </c>
+      <c r="C256" t="n">
+        <v>4454593.618400224</v>
+      </c>
+      <c r="D256" t="n">
+        <v>22595709.69279263</v>
+      </c>
+      <c r="E256" t="n">
+        <v>0</v>
+      </c>
+      <c r="F256" t="n">
+        <v>54071685.86453527</v>
+      </c>
+      <c r="G256" t="n">
+        <v>4454593.618400224</v>
+      </c>
+      <c r="H256" t="n">
+        <v>4449684.874718445</v>
+      </c>
+      <c r="I256" t="n">
+        <v>-69749420.06843559</v>
+      </c>
+      <c r="J256" t="n">
+        <v>0</v>
+      </c>
+      <c r="K256" t="n">
+        <v>0</v>
+      </c>
+      <c r="L256" t="n">
+        <v>11934731.48265406</v>
+      </c>
+      <c r="M256" t="n">
+        <v>5161275.771872403</v>
+      </c>
+      <c r="N256" t="n">
+        <v>47743.78637374489</v>
+      </c>
+      <c r="O256" t="n">
+        <v>0</v>
+      </c>
+      <c r="P256" t="n">
+        <v>47743.78637374489</v>
+      </c>
+      <c r="Q256" t="n">
+        <v>47738.92593061625</v>
+      </c>
+      <c r="R256" t="n">
+        <v>0</v>
+      </c>
+      <c r="S256" t="n">
+        <v>0</v>
+      </c>
+      <c r="T256" t="n">
+        <v>0</v>
+      </c>
+      <c r="U256" t="n">
+        <v>4.860443128641434</v>
+      </c>
+      <c r="V256" t="n">
+        <v>36.6780002117157</v>
+      </c>
+      <c r="W256" t="n">
+        <v>5161275.771872403</v>
+      </c>
+      <c r="X256" t="n">
+        <v>5161275.771872403</v>
+      </c>
+      <c r="Y256" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC256" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD256" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE256" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426023435_dh_1_ctax_250_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>-6679112.879832441</v>
+      </c>
+      <c r="B257" t="n">
+        <v>31677578.71586811</v>
+      </c>
+      <c r="C257" t="n">
+        <v>4473996.049806509</v>
+      </c>
+      <c r="D257" t="n">
+        <v>22732670.95395229</v>
+      </c>
+      <c r="E257" t="n">
+        <v>0</v>
+      </c>
+      <c r="F257" t="n">
+        <v>54410249.6698204</v>
+      </c>
+      <c r="G257" t="n">
+        <v>4473996.049806509</v>
+      </c>
+      <c r="H257" t="n">
+        <v>5635645.202939743</v>
+      </c>
+      <c r="I257" t="n">
+        <v>-84271769.49594164</v>
+      </c>
+      <c r="J257" t="n">
+        <v>0</v>
+      </c>
+      <c r="K257" t="n">
+        <v>0</v>
+      </c>
+      <c r="L257" t="n">
+        <v>13072765.69354255</v>
+      </c>
+      <c r="M257" t="n">
+        <v>-6679112.879832441</v>
+      </c>
+      <c r="N257" t="n">
+        <v>52295.94761383977</v>
+      </c>
+      <c r="O257" t="n">
+        <v>0</v>
+      </c>
+      <c r="P257" t="n">
+        <v>52295.94761383977</v>
+      </c>
+      <c r="Q257" t="n">
+        <v>52291.06277417023</v>
+      </c>
+      <c r="R257" t="n">
+        <v>0</v>
+      </c>
+      <c r="S257" t="n">
+        <v>0</v>
+      </c>
+      <c r="T257" t="n">
+        <v>0</v>
+      </c>
+      <c r="U257" t="n">
+        <v>4.884839669543479</v>
+      </c>
+      <c r="V257" t="n">
+        <v>34.63100004196167</v>
+      </c>
+      <c r="W257" t="n">
+        <v>-6679112.879832441</v>
+      </c>
+      <c r="X257" t="n">
+        <v>-6679112.879832441</v>
+      </c>
+      <c r="Y257" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC257" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD257" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE257" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426024403_dh_1_ctax_250_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>-18820871.08892307</v>
+      </c>
+      <c r="B258" t="n">
+        <v>31847832.37810471</v>
+      </c>
+      <c r="C258" t="n">
+        <v>4490381.433322094</v>
+      </c>
+      <c r="D258" t="n">
+        <v>22847254.13138408</v>
+      </c>
+      <c r="E258" t="n">
+        <v>0</v>
+      </c>
+      <c r="F258" t="n">
+        <v>54695086.50948879</v>
+      </c>
+      <c r="G258" t="n">
+        <v>4490381.433322094</v>
+      </c>
+      <c r="H258" t="n">
+        <v>6262022.573766897</v>
+      </c>
+      <c r="I258" t="n">
+        <v>-97882404.51257789</v>
+      </c>
+      <c r="J258" t="n">
+        <v>0</v>
+      </c>
+      <c r="K258" t="n">
+        <v>0</v>
+      </c>
+      <c r="L258" t="n">
+        <v>13614042.90707704</v>
+      </c>
+      <c r="M258" t="n">
+        <v>-18820871.08892307</v>
+      </c>
+      <c r="N258" t="n">
+        <v>54461.07560714655</v>
+      </c>
+      <c r="O258" t="n">
+        <v>0</v>
+      </c>
+      <c r="P258" t="n">
+        <v>54461.07560714655</v>
+      </c>
+      <c r="Q258" t="n">
+        <v>54456.17162830814</v>
+      </c>
+      <c r="R258" t="n">
+        <v>0</v>
+      </c>
+      <c r="S258" t="n">
+        <v>0</v>
+      </c>
+      <c r="T258" t="n">
+        <v>0</v>
+      </c>
+      <c r="U258" t="n">
+        <v>4.903978838420235</v>
+      </c>
+      <c r="V258" t="n">
+        <v>34.10700011253357</v>
+      </c>
+      <c r="W258" t="n">
+        <v>-18820871.08892307</v>
+      </c>
+      <c r="X258" t="n">
+        <v>-18820871.08892307</v>
+      </c>
+      <c r="Y258" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC258" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD258" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE258" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426024711_dh_1_ctax_250_el_price_400</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_WtE/raw_results/technology_selection/Summary.xlsx
+++ b/dataCaseStudy_WtE/raw_results/technology_selection/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE258"/>
+  <dimension ref="A1:AE322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27053,6 +27053,6598 @@
       <c r="AE258" t="inlineStr">
         <is>
           <t>dataCaseStudy_WtE\raw_results\technology_selection\20260426024711_dh_1_ctax_250_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>13212651.19193472</v>
+      </c>
+      <c r="B259" t="n">
+        <v>4470200.639116395</v>
+      </c>
+      <c r="C259" t="n">
+        <v>3244873.974516834</v>
+      </c>
+      <c r="D259" t="n">
+        <v>5265215.841826544</v>
+      </c>
+      <c r="E259" t="n">
+        <v>0</v>
+      </c>
+      <c r="F259" t="n">
+        <v>9735416.480942938</v>
+      </c>
+      <c r="G259" t="n">
+        <v>3244873.974516834</v>
+      </c>
+      <c r="H259" t="n">
+        <v>-2.181626322684247e-17</v>
+      </c>
+      <c r="I259" t="n">
+        <v>-2423590.327672481</v>
+      </c>
+      <c r="J259" t="n">
+        <v>0</v>
+      </c>
+      <c r="K259" t="n">
+        <v>0</v>
+      </c>
+      <c r="L259" t="n">
+        <v>2655951.06414743</v>
+      </c>
+      <c r="M259" t="n">
+        <v>13212651.19193472</v>
+      </c>
+      <c r="N259" t="n">
+        <v>26561.8414433927</v>
+      </c>
+      <c r="O259" t="n">
+        <v>0</v>
+      </c>
+      <c r="P259" t="n">
+        <v>26561.8414433927</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>26559.51064147439</v>
+      </c>
+      <c r="R259" t="n">
+        <v>0</v>
+      </c>
+      <c r="S259" t="n">
+        <v>0</v>
+      </c>
+      <c r="T259" t="n">
+        <v>0</v>
+      </c>
+      <c r="U259" t="n">
+        <v>2.330801918209394</v>
+      </c>
+      <c r="V259" t="n">
+        <v>20.19799995422363</v>
+      </c>
+      <c r="W259" t="n">
+        <v>13212651.19193472</v>
+      </c>
+      <c r="X259" t="n">
+        <v>13212651.19193472</v>
+      </c>
+      <c r="Y259" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC259" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD259" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE259" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427141848_dh_0.5_ctax_100_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>7692927.423242366</v>
+      </c>
+      <c r="B260" t="n">
+        <v>0</v>
+      </c>
+      <c r="C260" t="n">
+        <v>0</v>
+      </c>
+      <c r="D260" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E260" t="n">
+        <v>0</v>
+      </c>
+      <c r="F260" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G260" t="n">
+        <v>0</v>
+      </c>
+      <c r="H260" t="n">
+        <v>16087.92112087848</v>
+      </c>
+      <c r="I260" t="n">
+        <v>-14068696.34301499</v>
+      </c>
+      <c r="J260" t="n">
+        <v>0</v>
+      </c>
+      <c r="K260" t="n">
+        <v>0</v>
+      </c>
+      <c r="L260" t="n">
+        <v>21309807.07334101</v>
+      </c>
+      <c r="M260" t="n">
+        <v>7692927.423242366</v>
+      </c>
+      <c r="N260" t="n">
+        <v>213098.07073341</v>
+      </c>
+      <c r="O260" t="n">
+        <v>0</v>
+      </c>
+      <c r="P260" t="n">
+        <v>213098.07073341</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>213098.07073341</v>
+      </c>
+      <c r="R260" t="n">
+        <v>0</v>
+      </c>
+      <c r="S260" t="n">
+        <v>0</v>
+      </c>
+      <c r="T260" t="n">
+        <v>0</v>
+      </c>
+      <c r="U260" t="n">
+        <v>0</v>
+      </c>
+      <c r="V260" t="n">
+        <v>14.46700000762939</v>
+      </c>
+      <c r="W260" t="n">
+        <v>7692927.423242348</v>
+      </c>
+      <c r="X260" t="n">
+        <v>7692927.423242366</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>1.769512891769409e-08</v>
+      </c>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC260" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD260" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE260" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427142147_dh_0.5_ctax_100_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>616427.8433460556</v>
+      </c>
+      <c r="B261" t="n">
+        <v>0</v>
+      </c>
+      <c r="C261" t="n">
+        <v>0</v>
+      </c>
+      <c r="D261" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E261" t="n">
+        <v>0</v>
+      </c>
+      <c r="F261" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G261" t="n">
+        <v>0</v>
+      </c>
+      <c r="H261" t="n">
+        <v>250352.7371741842</v>
+      </c>
+      <c r="I261" t="n">
+        <v>-21487808.21638926</v>
+      </c>
+      <c r="J261" t="n">
+        <v>0</v>
+      </c>
+      <c r="K261" t="n">
+        <v>0</v>
+      </c>
+      <c r="L261" t="n">
+        <v>21418154.55076566</v>
+      </c>
+      <c r="M261" t="n">
+        <v>616427.8433460556</v>
+      </c>
+      <c r="N261" t="n">
+        <v>214181.5455076566</v>
+      </c>
+      <c r="O261" t="n">
+        <v>0</v>
+      </c>
+      <c r="P261" t="n">
+        <v>214181.5455076566</v>
+      </c>
+      <c r="Q261" t="n">
+        <v>214181.5455076566</v>
+      </c>
+      <c r="R261" t="n">
+        <v>0</v>
+      </c>
+      <c r="S261" t="n">
+        <v>0</v>
+      </c>
+      <c r="T261" t="n">
+        <v>0</v>
+      </c>
+      <c r="U261" t="n">
+        <v>0</v>
+      </c>
+      <c r="V261" t="n">
+        <v>7.128000020980835</v>
+      </c>
+      <c r="W261" t="n">
+        <v>616427.8433459736</v>
+      </c>
+      <c r="X261" t="n">
+        <v>616427.8433460556</v>
+      </c>
+      <c r="Y261" t="n">
+        <v>8.195638656616211e-08</v>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC261" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD261" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE261" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427142428_dh_0.5_ctax_100_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>-6664264.485831395</v>
+      </c>
+      <c r="B262" t="n">
+        <v>0</v>
+      </c>
+      <c r="C262" t="n">
+        <v>0</v>
+      </c>
+      <c r="D262" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E262" t="n">
+        <v>0</v>
+      </c>
+      <c r="F262" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G262" t="n">
+        <v>0</v>
+      </c>
+      <c r="H262" t="n">
+        <v>871463.3829878251</v>
+      </c>
+      <c r="I262" t="n">
+        <v>-29676874.86506916</v>
+      </c>
+      <c r="J262" t="n">
+        <v>0</v>
+      </c>
+      <c r="K262" t="n">
+        <v>0</v>
+      </c>
+      <c r="L262" t="n">
+        <v>21705418.22445447</v>
+      </c>
+      <c r="M262" t="n">
+        <v>-6664264.485831395</v>
+      </c>
+      <c r="N262" t="n">
+        <v>217054.1822445446</v>
+      </c>
+      <c r="O262" t="n">
+        <v>0</v>
+      </c>
+      <c r="P262" t="n">
+        <v>217054.1822445446</v>
+      </c>
+      <c r="Q262" t="n">
+        <v>217054.1822445447</v>
+      </c>
+      <c r="R262" t="n">
+        <v>0</v>
+      </c>
+      <c r="S262" t="n">
+        <v>0</v>
+      </c>
+      <c r="T262" t="n">
+        <v>0</v>
+      </c>
+      <c r="U262" t="n">
+        <v>0</v>
+      </c>
+      <c r="V262" t="n">
+        <v>5.680000066757202</v>
+      </c>
+      <c r="W262" t="n">
+        <v>-6664264.485831395</v>
+      </c>
+      <c r="X262" t="n">
+        <v>-6664264.485831395</v>
+      </c>
+      <c r="Y262" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC262" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD262" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE262" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427142715_dh_0.5_ctax_100_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>-14223105.46445471</v>
+      </c>
+      <c r="B263" t="n">
+        <v>0</v>
+      </c>
+      <c r="C263" t="n">
+        <v>0</v>
+      </c>
+      <c r="D263" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E263" t="n">
+        <v>0</v>
+      </c>
+      <c r="F263" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G263" t="n">
+        <v>0</v>
+      </c>
+      <c r="H263" t="n">
+        <v>1637043.526087382</v>
+      </c>
+      <c r="I263" t="n">
+        <v>-38355376.80297558</v>
+      </c>
+      <c r="J263" t="n">
+        <v>0</v>
+      </c>
+      <c r="K263" t="n">
+        <v>0</v>
+      </c>
+      <c r="L263" t="n">
+        <v>22059499.04063802</v>
+      </c>
+      <c r="M263" t="n">
+        <v>-14223105.46445471</v>
+      </c>
+      <c r="N263" t="n">
+        <v>220594.9904063801</v>
+      </c>
+      <c r="O263" t="n">
+        <v>0</v>
+      </c>
+      <c r="P263" t="n">
+        <v>220594.9904063801</v>
+      </c>
+      <c r="Q263" t="n">
+        <v>220594.9904063801</v>
+      </c>
+      <c r="R263" t="n">
+        <v>0</v>
+      </c>
+      <c r="S263" t="n">
+        <v>0</v>
+      </c>
+      <c r="T263" t="n">
+        <v>0</v>
+      </c>
+      <c r="U263" t="n">
+        <v>0</v>
+      </c>
+      <c r="V263" t="n">
+        <v>5.641999959945679</v>
+      </c>
+      <c r="W263" t="n">
+        <v>-14223105.46445471</v>
+      </c>
+      <c r="X263" t="n">
+        <v>-14223105.46445471</v>
+      </c>
+      <c r="Y263" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC263" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD263" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE263" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427142947_dh_0.5_ctax_100_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>-21942439.48836367</v>
+      </c>
+      <c r="B264" t="n">
+        <v>0</v>
+      </c>
+      <c r="C264" t="n">
+        <v>0</v>
+      </c>
+      <c r="D264" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E264" t="n">
+        <v>0</v>
+      </c>
+      <c r="F264" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G264" t="n">
+        <v>0</v>
+      </c>
+      <c r="H264" t="n">
+        <v>1931930.186764378</v>
+      </c>
+      <c r="I264" t="n">
+        <v>-46505982.56812464</v>
+      </c>
+      <c r="J264" t="n">
+        <v>0</v>
+      </c>
+      <c r="K264" t="n">
+        <v>0</v>
+      </c>
+      <c r="L264" t="n">
+        <v>22195884.12120113</v>
+      </c>
+      <c r="M264" t="n">
+        <v>-21942439.48836367</v>
+      </c>
+      <c r="N264" t="n">
+        <v>221958.8412120113</v>
+      </c>
+      <c r="O264" t="n">
+        <v>0</v>
+      </c>
+      <c r="P264" t="n">
+        <v>221958.8412120113</v>
+      </c>
+      <c r="Q264" t="n">
+        <v>221958.8412120112</v>
+      </c>
+      <c r="R264" t="n">
+        <v>0</v>
+      </c>
+      <c r="S264" t="n">
+        <v>0</v>
+      </c>
+      <c r="T264" t="n">
+        <v>0</v>
+      </c>
+      <c r="U264" t="n">
+        <v>0</v>
+      </c>
+      <c r="V264" t="n">
+        <v>5.753000020980835</v>
+      </c>
+      <c r="W264" t="n">
+        <v>-21942439.48836367</v>
+      </c>
+      <c r="X264" t="n">
+        <v>-21942439.48836367</v>
+      </c>
+      <c r="Y264" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC264" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD264" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE264" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427143226_dh_0.5_ctax_100_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>-29708118.43058869</v>
+      </c>
+      <c r="B265" t="n">
+        <v>0</v>
+      </c>
+      <c r="C265" t="n">
+        <v>0</v>
+      </c>
+      <c r="D265" t="n">
+        <v>435728.7717954647</v>
+      </c>
+      <c r="E265" t="n">
+        <v>0</v>
+      </c>
+      <c r="F265" t="n">
+        <v>435728.7717954658</v>
+      </c>
+      <c r="G265" t="n">
+        <v>0</v>
+      </c>
+      <c r="H265" t="n">
+        <v>2049307.205451946</v>
+      </c>
+      <c r="I265" t="n">
+        <v>-54443325.40018023</v>
+      </c>
+      <c r="J265" t="n">
+        <v>0</v>
+      </c>
+      <c r="K265" t="n">
+        <v>0</v>
+      </c>
+      <c r="L265" t="n">
+        <v>22250170.99234413</v>
+      </c>
+      <c r="M265" t="n">
+        <v>-29708118.43058869</v>
+      </c>
+      <c r="N265" t="n">
+        <v>222501.7099234413</v>
+      </c>
+      <c r="O265" t="n">
+        <v>0</v>
+      </c>
+      <c r="P265" t="n">
+        <v>222501.7099234413</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>222501.7099234412</v>
+      </c>
+      <c r="R265" t="n">
+        <v>0</v>
+      </c>
+      <c r="S265" t="n">
+        <v>0</v>
+      </c>
+      <c r="T265" t="n">
+        <v>0</v>
+      </c>
+      <c r="U265" t="n">
+        <v>0</v>
+      </c>
+      <c r="V265" t="n">
+        <v>7.49399995803833</v>
+      </c>
+      <c r="W265" t="n">
+        <v>-29708118.43058869</v>
+      </c>
+      <c r="X265" t="n">
+        <v>-29708118.43058869</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC265" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD265" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE265" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427143511_dh_0.5_ctax_100_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>-37489730.88745569</v>
+      </c>
+      <c r="B266" t="n">
+        <v>0</v>
+      </c>
+      <c r="C266" t="n">
+        <v>0</v>
+      </c>
+      <c r="D266" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E266" t="n">
+        <v>0</v>
+      </c>
+      <c r="F266" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G266" t="n">
+        <v>0</v>
+      </c>
+      <c r="H266" t="n">
+        <v>2081367.532328885</v>
+      </c>
+      <c r="I266" t="n">
+        <v>-62271826.08510476</v>
+      </c>
+      <c r="J266" t="n">
+        <v>0</v>
+      </c>
+      <c r="K266" t="n">
+        <v>0</v>
+      </c>
+      <c r="L266" t="n">
+        <v>22264998.89352471</v>
+      </c>
+      <c r="M266" t="n">
+        <v>-37489730.88745569</v>
+      </c>
+      <c r="N266" t="n">
+        <v>222649.9889352471</v>
+      </c>
+      <c r="O266" t="n">
+        <v>0</v>
+      </c>
+      <c r="P266" t="n">
+        <v>222649.9889352471</v>
+      </c>
+      <c r="Q266" t="n">
+        <v>222649.9889352471</v>
+      </c>
+      <c r="R266" t="n">
+        <v>0</v>
+      </c>
+      <c r="S266" t="n">
+        <v>0</v>
+      </c>
+      <c r="T266" t="n">
+        <v>0</v>
+      </c>
+      <c r="U266" t="n">
+        <v>0</v>
+      </c>
+      <c r="V266" t="n">
+        <v>6.662999868392944</v>
+      </c>
+      <c r="W266" t="n">
+        <v>-37489730.88745569</v>
+      </c>
+      <c r="X266" t="n">
+        <v>-37489730.88745569</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z266" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC266" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD266" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_100_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE266" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427143805_dh_0.5_ctax_100_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>14431071.78964609</v>
+      </c>
+      <c r="B267" t="n">
+        <v>4597296.635121451</v>
+      </c>
+      <c r="C267" t="n">
+        <v>3292769.37810029</v>
+      </c>
+      <c r="D267" t="n">
+        <v>5381978.745640699</v>
+      </c>
+      <c r="E267" t="n">
+        <v>0</v>
+      </c>
+      <c r="F267" t="n">
+        <v>9979275.380762149</v>
+      </c>
+      <c r="G267" t="n">
+        <v>3292769.37810029</v>
+      </c>
+      <c r="H267" t="n">
+        <v>61649.7985881268</v>
+      </c>
+      <c r="I267" t="n">
+        <v>-2345211.372792643</v>
+      </c>
+      <c r="J267" t="n">
+        <v>0</v>
+      </c>
+      <c r="K267" t="n">
+        <v>0</v>
+      </c>
+      <c r="L267" t="n">
+        <v>3442588.60498817</v>
+      </c>
+      <c r="M267" t="n">
+        <v>14431071.78964609</v>
+      </c>
+      <c r="N267" t="n">
+        <v>22952.9701774675</v>
+      </c>
+      <c r="O267" t="n">
+        <v>0</v>
+      </c>
+      <c r="P267" t="n">
+        <v>22952.9701774675</v>
+      </c>
+      <c r="Q267" t="n">
+        <v>22950.59069992108</v>
+      </c>
+      <c r="R267" t="n">
+        <v>0</v>
+      </c>
+      <c r="S267" t="n">
+        <v>0</v>
+      </c>
+      <c r="T267" t="n">
+        <v>0</v>
+      </c>
+      <c r="U267" t="n">
+        <v>2.379477546459687</v>
+      </c>
+      <c r="V267" t="n">
+        <v>13.00999999046326</v>
+      </c>
+      <c r="W267" t="n">
+        <v>14431071.78964609</v>
+      </c>
+      <c r="X267" t="n">
+        <v>14431071.78964609</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC267" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD267" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE267" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427144109_dh_0.5_ctax_150_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>12074880.56187627</v>
+      </c>
+      <c r="B268" t="n">
+        <v>4547623.293883766</v>
+      </c>
+      <c r="C268" t="n">
+        <v>3274050.516632522</v>
+      </c>
+      <c r="D268" t="n">
+        <v>5344290.869430327</v>
+      </c>
+      <c r="E268" t="n">
+        <v>0</v>
+      </c>
+      <c r="F268" t="n">
+        <v>9891914.163314093</v>
+      </c>
+      <c r="G268" t="n">
+        <v>3274050.516632522</v>
+      </c>
+      <c r="H268" t="n">
+        <v>71036.38152518011</v>
+      </c>
+      <c r="I268" t="n">
+        <v>-4757860.047339633</v>
+      </c>
+      <c r="J268" t="n">
+        <v>0</v>
+      </c>
+      <c r="K268" t="n">
+        <v>0</v>
+      </c>
+      <c r="L268" t="n">
+        <v>3595739.547744107</v>
+      </c>
+      <c r="M268" t="n">
+        <v>12074880.56187627</v>
+      </c>
+      <c r="N268" t="n">
+        <v>23973.96424259031</v>
+      </c>
+      <c r="O268" t="n">
+        <v>0</v>
+      </c>
+      <c r="P268" t="n">
+        <v>23973.96424259031</v>
+      </c>
+      <c r="Q268" t="n">
+        <v>23971.59698496072</v>
+      </c>
+      <c r="R268" t="n">
+        <v>0</v>
+      </c>
+      <c r="S268" t="n">
+        <v>0</v>
+      </c>
+      <c r="T268" t="n">
+        <v>0</v>
+      </c>
+      <c r="U268" t="n">
+        <v>2.36725762972274</v>
+      </c>
+      <c r="V268" t="n">
+        <v>14.22199988365173</v>
+      </c>
+      <c r="W268" t="n">
+        <v>12074880.56187627</v>
+      </c>
+      <c r="X268" t="n">
+        <v>12074880.56187627</v>
+      </c>
+      <c r="Y268" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z268" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC268" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD268" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE268" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427144329_dh_0.5_ctax_150_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>9625897.395910997</v>
+      </c>
+      <c r="B269" t="n">
+        <v>4466693.643837974</v>
+      </c>
+      <c r="C269" t="n">
+        <v>3243552.263783296</v>
+      </c>
+      <c r="D269" t="n">
+        <v>5273893.893527393</v>
+      </c>
+      <c r="E269" t="n">
+        <v>0</v>
+      </c>
+      <c r="F269" t="n">
+        <v>9740587.537365368</v>
+      </c>
+      <c r="G269" t="n">
+        <v>3243552.263783296</v>
+      </c>
+      <c r="H269" t="n">
+        <v>328237.5928031027</v>
+      </c>
+      <c r="I269" t="n">
+        <v>-7791979.744508686</v>
+      </c>
+      <c r="J269" t="n">
+        <v>0</v>
+      </c>
+      <c r="K269" t="n">
+        <v>0</v>
+      </c>
+      <c r="L269" t="n">
+        <v>4105499.746467917</v>
+      </c>
+      <c r="M269" t="n">
+        <v>9625897.395910997</v>
+      </c>
+      <c r="N269" t="n">
+        <v>27372.33795684397</v>
+      </c>
+      <c r="O269" t="n">
+        <v>0</v>
+      </c>
+      <c r="P269" t="n">
+        <v>27372.33795684397</v>
+      </c>
+      <c r="Q269" t="n">
+        <v>27369.99830978595</v>
+      </c>
+      <c r="R269" t="n">
+        <v>0</v>
+      </c>
+      <c r="S269" t="n">
+        <v>0</v>
+      </c>
+      <c r="T269" t="n">
+        <v>0</v>
+      </c>
+      <c r="U269" t="n">
+        <v>2.33964705818943</v>
+      </c>
+      <c r="V269" t="n">
+        <v>14.27999997138977</v>
+      </c>
+      <c r="W269" t="n">
+        <v>9625897.395910997</v>
+      </c>
+      <c r="X269" t="n">
+        <v>9625897.395910997</v>
+      </c>
+      <c r="Y269" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC269" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD269" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE269" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427144652_dh_0.5_ctax_150_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>4139887.773123667</v>
+      </c>
+      <c r="B270" t="n">
+        <v>0</v>
+      </c>
+      <c r="C270" t="n">
+        <v>0</v>
+      </c>
+      <c r="D270" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E270" t="n">
+        <v>0</v>
+      </c>
+      <c r="F270" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G270" t="n">
+        <v>0</v>
+      </c>
+      <c r="H270" t="n">
+        <v>472568.2005307369</v>
+      </c>
+      <c r="I270" t="n">
+        <v>-29049803.00305464</v>
+      </c>
+      <c r="J270" t="n">
+        <v>0</v>
+      </c>
+      <c r="K270" t="n">
+        <v>0</v>
+      </c>
+      <c r="L270" t="n">
+        <v>32281393.80385211</v>
+      </c>
+      <c r="M270" t="n">
+        <v>4139887.773123667</v>
+      </c>
+      <c r="N270" t="n">
+        <v>215209.2920256807</v>
+      </c>
+      <c r="O270" t="n">
+        <v>0</v>
+      </c>
+      <c r="P270" t="n">
+        <v>215209.2920256807</v>
+      </c>
+      <c r="Q270" t="n">
+        <v>215209.2920256806</v>
+      </c>
+      <c r="R270" t="n">
+        <v>0</v>
+      </c>
+      <c r="S270" t="n">
+        <v>0</v>
+      </c>
+      <c r="T270" t="n">
+        <v>0</v>
+      </c>
+      <c r="U270" t="n">
+        <v>0</v>
+      </c>
+      <c r="V270" t="n">
+        <v>13.25100016593933</v>
+      </c>
+      <c r="W270" t="n">
+        <v>4139887.773123667</v>
+      </c>
+      <c r="X270" t="n">
+        <v>4139887.773123667</v>
+      </c>
+      <c r="Y270" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC270" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD270" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE270" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427144911_dh_0.5_ctax_150_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>-3248202.711602185</v>
+      </c>
+      <c r="B271" t="n">
+        <v>0</v>
+      </c>
+      <c r="C271" t="n">
+        <v>0</v>
+      </c>
+      <c r="D271" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E271" t="n">
+        <v>0</v>
+      </c>
+      <c r="F271" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G271" t="n">
+        <v>0</v>
+      </c>
+      <c r="H271" t="n">
+        <v>1137429.25938166</v>
+      </c>
+      <c r="I271" t="n">
+        <v>-37564001.90620925</v>
+      </c>
+      <c r="J271" t="n">
+        <v>0</v>
+      </c>
+      <c r="K271" t="n">
+        <v>0</v>
+      </c>
+      <c r="L271" t="n">
+        <v>32742641.16342994</v>
+      </c>
+      <c r="M271" t="n">
+        <v>-3248202.711602185</v>
+      </c>
+      <c r="N271" t="n">
+        <v>218284.2744228661</v>
+      </c>
+      <c r="O271" t="n">
+        <v>0</v>
+      </c>
+      <c r="P271" t="n">
+        <v>218284.2744228661</v>
+      </c>
+      <c r="Q271" t="n">
+        <v>218284.2744228661</v>
+      </c>
+      <c r="R271" t="n">
+        <v>0</v>
+      </c>
+      <c r="S271" t="n">
+        <v>0</v>
+      </c>
+      <c r="T271" t="n">
+        <v>0</v>
+      </c>
+      <c r="U271" t="n">
+        <v>0</v>
+      </c>
+      <c r="V271" t="n">
+        <v>10.81299996376038</v>
+      </c>
+      <c r="W271" t="n">
+        <v>-3248202.711602185</v>
+      </c>
+      <c r="X271" t="n">
+        <v>-3248202.711602185</v>
+      </c>
+      <c r="Y271" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC271" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD271" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE271" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427145129_dh_0.5_ctax_150_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>-10866436.25968079</v>
+      </c>
+      <c r="B272" t="n">
+        <v>0</v>
+      </c>
+      <c r="C272" t="n">
+        <v>0</v>
+      </c>
+      <c r="D272" t="n">
+        <v>435728.771795464</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" t="n">
+        <v>435728.7717954642</v>
+      </c>
+      <c r="G272" t="n">
+        <v>0</v>
+      </c>
+      <c r="H272" t="n">
+        <v>1698977.295211495</v>
+      </c>
+      <c r="I272" t="n">
+        <v>-46133357.43997464</v>
+      </c>
+      <c r="J272" t="n">
+        <v>0</v>
+      </c>
+      <c r="K272" t="n">
+        <v>0</v>
+      </c>
+      <c r="L272" t="n">
+        <v>33132215.11328689</v>
+      </c>
+      <c r="M272" t="n">
+        <v>-10866436.25968079</v>
+      </c>
+      <c r="N272" t="n">
+        <v>220881.4340885791</v>
+      </c>
+      <c r="O272" t="n">
+        <v>0</v>
+      </c>
+      <c r="P272" t="n">
+        <v>220881.4340885791</v>
+      </c>
+      <c r="Q272" t="n">
+        <v>220881.4340885791</v>
+      </c>
+      <c r="R272" t="n">
+        <v>0</v>
+      </c>
+      <c r="S272" t="n">
+        <v>0</v>
+      </c>
+      <c r="T272" t="n">
+        <v>0</v>
+      </c>
+      <c r="U272" t="n">
+        <v>0</v>
+      </c>
+      <c r="V272" t="n">
+        <v>12.63000011444092</v>
+      </c>
+      <c r="W272" t="n">
+        <v>-10866436.25968079</v>
+      </c>
+      <c r="X272" t="n">
+        <v>-10866436.25968079</v>
+      </c>
+      <c r="Y272" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC272" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD272" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE272" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427145502_dh_0.5_ctax_150_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>-18595519.44406056</v>
+      </c>
+      <c r="B273" t="n">
+        <v>0</v>
+      </c>
+      <c r="C273" t="n">
+        <v>0</v>
+      </c>
+      <c r="D273" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G273" t="n">
+        <v>0</v>
+      </c>
+      <c r="H273" t="n">
+        <v>1937609.692201218</v>
+      </c>
+      <c r="I273" t="n">
+        <v>-54266624.24675574</v>
+      </c>
+      <c r="J273" t="n">
+        <v>0</v>
+      </c>
+      <c r="K273" t="n">
+        <v>0</v>
+      </c>
+      <c r="L273" t="n">
+        <v>33297766.33869851</v>
+      </c>
+      <c r="M273" t="n">
+        <v>-18595519.44406056</v>
+      </c>
+      <c r="N273" t="n">
+        <v>221985.1089246566</v>
+      </c>
+      <c r="O273" t="n">
+        <v>0</v>
+      </c>
+      <c r="P273" t="n">
+        <v>221985.1089246566</v>
+      </c>
+      <c r="Q273" t="n">
+        <v>221985.1089246566</v>
+      </c>
+      <c r="R273" t="n">
+        <v>0</v>
+      </c>
+      <c r="S273" t="n">
+        <v>0</v>
+      </c>
+      <c r="T273" t="n">
+        <v>0</v>
+      </c>
+      <c r="U273" t="n">
+        <v>0</v>
+      </c>
+      <c r="V273" t="n">
+        <v>9.818000078201294</v>
+      </c>
+      <c r="W273" t="n">
+        <v>-18595519.44406056</v>
+      </c>
+      <c r="X273" t="n">
+        <v>-18595519.44406056</v>
+      </c>
+      <c r="Y273" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD273" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427145722_dh_0.5_ctax_150_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>-28107429.62501524</v>
+      </c>
+      <c r="B274" t="n">
+        <v>30925520.59477416</v>
+      </c>
+      <c r="C274" t="n">
+        <v>4401617.220603922</v>
+      </c>
+      <c r="D274" t="n">
+        <v>22215864.24309056</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" t="n">
+        <v>53141384.83786473</v>
+      </c>
+      <c r="G274" t="n">
+        <v>4401617.220603922</v>
+      </c>
+      <c r="H274" t="n">
+        <v>4613397.044162707</v>
+      </c>
+      <c r="I274" t="n">
+        <v>-97966060.99482425</v>
+      </c>
+      <c r="J274" t="n">
+        <v>0</v>
+      </c>
+      <c r="K274" t="n">
+        <v>0</v>
+      </c>
+      <c r="L274" t="n">
+        <v>7702232.26717765</v>
+      </c>
+      <c r="M274" t="n">
+        <v>-28107429.62501524</v>
+      </c>
+      <c r="N274" t="n">
+        <v>51353.00097338344</v>
+      </c>
+      <c r="O274" t="n">
+        <v>0</v>
+      </c>
+      <c r="P274" t="n">
+        <v>51353.00097338344</v>
+      </c>
+      <c r="Q274" t="n">
+        <v>51348.21511451765</v>
+      </c>
+      <c r="R274" t="n">
+        <v>0</v>
+      </c>
+      <c r="S274" t="n">
+        <v>0</v>
+      </c>
+      <c r="T274" t="n">
+        <v>0</v>
+      </c>
+      <c r="U274" t="n">
+        <v>4.785858865855401</v>
+      </c>
+      <c r="V274" t="n">
+        <v>9.185999870300293</v>
+      </c>
+      <c r="W274" t="n">
+        <v>-28107429.62501524</v>
+      </c>
+      <c r="X274" t="n">
+        <v>-28107429.62501524</v>
+      </c>
+      <c r="Y274" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z274" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC274" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD274" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_150_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE274" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427150112_dh_0.5_ctax_150_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>15560833.01007283</v>
+      </c>
+      <c r="B275" t="n">
+        <v>4638797.828254792</v>
+      </c>
+      <c r="C275" t="n">
+        <v>3308409.86350393</v>
+      </c>
+      <c r="D275" t="n">
+        <v>5410189.842212491</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="n">
+        <v>10048987.67046728</v>
+      </c>
+      <c r="G275" t="n">
+        <v>3308409.86350393</v>
+      </c>
+      <c r="H275" t="n">
+        <v>61660.43239431651</v>
+      </c>
+      <c r="I275" t="n">
+        <v>-2329868.57703856</v>
+      </c>
+      <c r="J275" t="n">
+        <v>0</v>
+      </c>
+      <c r="K275" t="n">
+        <v>0</v>
+      </c>
+      <c r="L275" t="n">
+        <v>4471643.620745859</v>
+      </c>
+      <c r="M275" t="n">
+        <v>15560833.01007283</v>
+      </c>
+      <c r="N275" t="n">
+        <v>22360.6049865478</v>
+      </c>
+      <c r="O275" t="n">
+        <v>0</v>
+      </c>
+      <c r="P275" t="n">
+        <v>22360.6049865478</v>
+      </c>
+      <c r="Q275" t="n">
+        <v>22358.21810372924</v>
+      </c>
+      <c r="R275" t="n">
+        <v>0</v>
+      </c>
+      <c r="S275" t="n">
+        <v>0</v>
+      </c>
+      <c r="T275" t="n">
+        <v>0</v>
+      </c>
+      <c r="U275" t="n">
+        <v>2.386882818679005</v>
+      </c>
+      <c r="V275" t="n">
+        <v>11.20500016212463</v>
+      </c>
+      <c r="W275" t="n">
+        <v>15560833.01007283</v>
+      </c>
+      <c r="X275" t="n">
+        <v>15560833.01007283</v>
+      </c>
+      <c r="Y275" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC275" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD275" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE275" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427150329_dh_0.5_ctax_200_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>13228328.6145497</v>
+      </c>
+      <c r="B276" t="n">
+        <v>4620853.653073619</v>
+      </c>
+      <c r="C276" t="n">
+        <v>3301647.09165551</v>
+      </c>
+      <c r="D276" t="n">
+        <v>5398398.024687304</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="n">
+        <v>10019251.67776092</v>
+      </c>
+      <c r="G276" t="n">
+        <v>3301647.09165551</v>
+      </c>
+      <c r="H276" t="n">
+        <v>61650.59590798803</v>
+      </c>
+      <c r="I276" t="n">
+        <v>-4671525.521148328</v>
+      </c>
+      <c r="J276" t="n">
+        <v>0</v>
+      </c>
+      <c r="K276" t="n">
+        <v>0</v>
+      </c>
+      <c r="L276" t="n">
+        <v>4517304.770373611</v>
+      </c>
+      <c r="M276" t="n">
+        <v>13228328.6145497</v>
+      </c>
+      <c r="N276" t="n">
+        <v>22588.90788029622</v>
+      </c>
+      <c r="O276" t="n">
+        <v>0</v>
+      </c>
+      <c r="P276" t="n">
+        <v>22588.90788029622</v>
+      </c>
+      <c r="Q276" t="n">
+        <v>22586.52385186816</v>
+      </c>
+      <c r="R276" t="n">
+        <v>0</v>
+      </c>
+      <c r="S276" t="n">
+        <v>0</v>
+      </c>
+      <c r="T276" t="n">
+        <v>0</v>
+      </c>
+      <c r="U276" t="n">
+        <v>2.384028428155403</v>
+      </c>
+      <c r="V276" t="n">
+        <v>12.60799980163574</v>
+      </c>
+      <c r="W276" t="n">
+        <v>13228328.6145497</v>
+      </c>
+      <c r="X276" t="n">
+        <v>13228328.6145497</v>
+      </c>
+      <c r="Y276" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC276" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD276" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE276" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427150547_dh_0.5_ctax_200_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>10867061.90043734</v>
+      </c>
+      <c r="B277" t="n">
+        <v>4594896.715581829</v>
+      </c>
+      <c r="C277" t="n">
+        <v>3291865.001228536</v>
+      </c>
+      <c r="D277" t="n">
+        <v>5380250.398001506</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="n">
+        <v>9975147.113583334</v>
+      </c>
+      <c r="G277" t="n">
+        <v>3291865.001228536</v>
+      </c>
+      <c r="H277" t="n">
+        <v>135448.7360800252</v>
+      </c>
+      <c r="I277" t="n">
+        <v>-7201960.107620176</v>
+      </c>
+      <c r="J277" t="n">
+        <v>0</v>
+      </c>
+      <c r="K277" t="n">
+        <v>0</v>
+      </c>
+      <c r="L277" t="n">
+        <v>4666561.157165619</v>
+      </c>
+      <c r="M277" t="n">
+        <v>10867061.90043734</v>
+      </c>
+      <c r="N277" t="n">
+        <v>23335.18475218672</v>
+      </c>
+      <c r="O277" t="n">
+        <v>0</v>
+      </c>
+      <c r="P277" t="n">
+        <v>23335.18475218672</v>
+      </c>
+      <c r="Q277" t="n">
+        <v>23332.80578582791</v>
+      </c>
+      <c r="R277" t="n">
+        <v>0</v>
+      </c>
+      <c r="S277" t="n">
+        <v>0</v>
+      </c>
+      <c r="T277" t="n">
+        <v>0</v>
+      </c>
+      <c r="U277" t="n">
+        <v>2.378966358959602</v>
+      </c>
+      <c r="V277" t="n">
+        <v>21.12999987602234</v>
+      </c>
+      <c r="W277" t="n">
+        <v>10867061.90043734</v>
+      </c>
+      <c r="X277" t="n">
+        <v>10867061.90043734</v>
+      </c>
+      <c r="Y277" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB277" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC277" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD277" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE277" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427150806_dh_0.5_ctax_200_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>8255096.461942806</v>
+      </c>
+      <c r="B278" t="n">
+        <v>4544946.647989851</v>
+      </c>
+      <c r="C278" t="n">
+        <v>3273041.85933948</v>
+      </c>
+      <c r="D278" t="n">
+        <v>5342156.884541682</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="n">
+        <v>9887103.532531533</v>
+      </c>
+      <c r="G278" t="n">
+        <v>3273041.85933948</v>
+      </c>
+      <c r="H278" t="n">
+        <v>1117162.480921441</v>
+      </c>
+      <c r="I278" t="n">
+        <v>-11796146.23609653</v>
+      </c>
+      <c r="J278" t="n">
+        <v>0</v>
+      </c>
+      <c r="K278" t="n">
+        <v>0</v>
+      </c>
+      <c r="L278" t="n">
+        <v>5773934.825246884</v>
+      </c>
+      <c r="M278" t="n">
+        <v>8255096.461942806</v>
+      </c>
+      <c r="N278" t="n">
+        <v>28872.04063706473</v>
+      </c>
+      <c r="O278" t="n">
+        <v>0</v>
+      </c>
+      <c r="P278" t="n">
+        <v>28872.04063706473</v>
+      </c>
+      <c r="Q278" t="n">
+        <v>28869.67412623427</v>
+      </c>
+      <c r="R278" t="n">
+        <v>0</v>
+      </c>
+      <c r="S278" t="n">
+        <v>0</v>
+      </c>
+      <c r="T278" t="n">
+        <v>0</v>
+      </c>
+      <c r="U278" t="n">
+        <v>2.366510830578167</v>
+      </c>
+      <c r="V278" t="n">
+        <v>38.90799999237061</v>
+      </c>
+      <c r="W278" t="n">
+        <v>8255096.461942806</v>
+      </c>
+      <c r="X278" t="n">
+        <v>8255096.461942806</v>
+      </c>
+      <c r="Y278" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z278" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB278" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC278" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD278" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE278" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427151231_dh_0.5_ctax_200_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>4796651.667670144</v>
+      </c>
+      <c r="B279" t="n">
+        <v>4482240.804677189</v>
+      </c>
+      <c r="C279" t="n">
+        <v>3249411.652726212</v>
+      </c>
+      <c r="D279" t="n">
+        <v>5288908.911025819</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="n">
+        <v>9771149.715703009</v>
+      </c>
+      <c r="G279" t="n">
+        <v>3249411.652726212</v>
+      </c>
+      <c r="H279" t="n">
+        <v>3763389.148704876</v>
+      </c>
+      <c r="I279" t="n">
+        <v>-20533512.63528412</v>
+      </c>
+      <c r="J279" t="n">
+        <v>0</v>
+      </c>
+      <c r="K279" t="n">
+        <v>0</v>
+      </c>
+      <c r="L279" t="n">
+        <v>8546213.785820166</v>
+      </c>
+      <c r="M279" t="n">
+        <v>4796651.667670144</v>
+      </c>
+      <c r="N279" t="n">
+        <v>42733.41515747566</v>
+      </c>
+      <c r="O279" t="n">
+        <v>0</v>
+      </c>
+      <c r="P279" t="n">
+        <v>42733.41515747566</v>
+      </c>
+      <c r="Q279" t="n">
+        <v>42731.06892910085</v>
+      </c>
+      <c r="R279" t="n">
+        <v>0</v>
+      </c>
+      <c r="S279" t="n">
+        <v>0</v>
+      </c>
+      <c r="T279" t="n">
+        <v>0</v>
+      </c>
+      <c r="U279" t="n">
+        <v>2.346228374773565</v>
+      </c>
+      <c r="V279" t="n">
+        <v>33.26600003242493</v>
+      </c>
+      <c r="W279" t="n">
+        <v>4796651.667670144</v>
+      </c>
+      <c r="X279" t="n">
+        <v>4796651.667670144</v>
+      </c>
+      <c r="Y279" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z279" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB279" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC279" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD279" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE279" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427151520_dh_0.5_ctax_200_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>-1223149.738543009</v>
+      </c>
+      <c r="B280" t="n">
+        <v>30880088.53854011</v>
+      </c>
+      <c r="C280" t="n">
+        <v>4397244.793864213</v>
+      </c>
+      <c r="D280" t="n">
+        <v>22184191.95416573</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="n">
+        <v>53064280.49270584</v>
+      </c>
+      <c r="G280" t="n">
+        <v>4397244.793864213</v>
+      </c>
+      <c r="H280" t="n">
+        <v>3911671.930557681</v>
+      </c>
+      <c r="I280" t="n">
+        <v>-72267305.48086812</v>
+      </c>
+      <c r="J280" t="n">
+        <v>0</v>
+      </c>
+      <c r="K280" t="n">
+        <v>0</v>
+      </c>
+      <c r="L280" t="n">
+        <v>9670958.525197374</v>
+      </c>
+      <c r="M280" t="n">
+        <v>-1223149.738543009</v>
+      </c>
+      <c r="N280" t="n">
+        <v>48359.57189346793</v>
+      </c>
+      <c r="O280" t="n">
+        <v>0</v>
+      </c>
+      <c r="P280" t="n">
+        <v>48359.57189346793</v>
+      </c>
+      <c r="Q280" t="n">
+        <v>48354.79262598684</v>
+      </c>
+      <c r="R280" t="n">
+        <v>0</v>
+      </c>
+      <c r="S280" t="n">
+        <v>0</v>
+      </c>
+      <c r="T280" t="n">
+        <v>0</v>
+      </c>
+      <c r="U280" t="n">
+        <v>4.779267481068855</v>
+      </c>
+      <c r="V280" t="n">
+        <v>27.13599991798401</v>
+      </c>
+      <c r="W280" t="n">
+        <v>-1223149.738543009</v>
+      </c>
+      <c r="X280" t="n">
+        <v>-1223149.738543009</v>
+      </c>
+      <c r="Y280" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z280" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB280" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC280" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD280" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE280" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427151801_dh_0.5_ctax_200_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>-13368399.38271079</v>
+      </c>
+      <c r="B281" t="n">
+        <v>31256936.19164935</v>
+      </c>
+      <c r="C281" t="n">
+        <v>4433512.990636175</v>
+      </c>
+      <c r="D281" t="n">
+        <v>22445490.82275625</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="n">
+        <v>53702427.0144056</v>
+      </c>
+      <c r="G281" t="n">
+        <v>4433512.990636175</v>
+      </c>
+      <c r="H281" t="n">
+        <v>4367628.094789819</v>
+      </c>
+      <c r="I281" t="n">
+        <v>-85561192.11853638</v>
+      </c>
+      <c r="J281" t="n">
+        <v>0</v>
+      </c>
+      <c r="K281" t="n">
+        <v>0</v>
+      </c>
+      <c r="L281" t="n">
+        <v>9689224.635993993</v>
+      </c>
+      <c r="M281" t="n">
+        <v>-13368399.38271079</v>
+      </c>
+      <c r="N281" t="n">
+        <v>48450.95520513508</v>
+      </c>
+      <c r="O281" t="n">
+        <v>0</v>
+      </c>
+      <c r="P281" t="n">
+        <v>48450.95520513508</v>
+      </c>
+      <c r="Q281" t="n">
+        <v>48446.12317996996</v>
+      </c>
+      <c r="R281" t="n">
+        <v>0</v>
+      </c>
+      <c r="S281" t="n">
+        <v>0</v>
+      </c>
+      <c r="T281" t="n">
+        <v>0</v>
+      </c>
+      <c r="U281" t="n">
+        <v>4.83202516511338</v>
+      </c>
+      <c r="V281" t="n">
+        <v>18.61800003051758</v>
+      </c>
+      <c r="W281" t="n">
+        <v>-13368399.38271079</v>
+      </c>
+      <c r="X281" t="n">
+        <v>-13368399.38271079</v>
+      </c>
+      <c r="Y281" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z281" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB281" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC281" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD281" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE281" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427152039_dh_0.5_ctax_200_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>-25633824.64073545</v>
+      </c>
+      <c r="B282" t="n">
+        <v>31511866.04814287</v>
+      </c>
+      <c r="C282" t="n">
+        <v>4458047.696165243</v>
+      </c>
+      <c r="D282" t="n">
+        <v>22620186.0841522</v>
+      </c>
+      <c r="E282" t="n">
+        <v>0</v>
+      </c>
+      <c r="F282" t="n">
+        <v>54132052.13229507</v>
+      </c>
+      <c r="G282" t="n">
+        <v>4458047.696165243</v>
+      </c>
+      <c r="H282" t="n">
+        <v>4552193.967694725</v>
+      </c>
+      <c r="I282" t="n">
+        <v>-98384532.82457685</v>
+      </c>
+      <c r="J282" t="n">
+        <v>0</v>
+      </c>
+      <c r="K282" t="n">
+        <v>0</v>
+      </c>
+      <c r="L282" t="n">
+        <v>9608414.387686372</v>
+      </c>
+      <c r="M282" t="n">
+        <v>-25633824.64073545</v>
+      </c>
+      <c r="N282" t="n">
+        <v>48046.93685220528</v>
+      </c>
+      <c r="O282" t="n">
+        <v>0</v>
+      </c>
+      <c r="P282" t="n">
+        <v>48046.93685220528</v>
+      </c>
+      <c r="Q282" t="n">
+        <v>48042.07193843184</v>
+      </c>
+      <c r="R282" t="n">
+        <v>0</v>
+      </c>
+      <c r="S282" t="n">
+        <v>0</v>
+      </c>
+      <c r="T282" t="n">
+        <v>0</v>
+      </c>
+      <c r="U282" t="n">
+        <v>4.864913773432199</v>
+      </c>
+      <c r="V282" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="W282" t="n">
+        <v>-25633824.64073545</v>
+      </c>
+      <c r="X282" t="n">
+        <v>-25633824.64073545</v>
+      </c>
+      <c r="Y282" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z282" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC282" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD282" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_200_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE282" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427152525_dh_0.5_ctax_200_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>16672197.28829921</v>
+      </c>
+      <c r="B283" t="n">
+        <v>4661718.814893891</v>
+      </c>
+      <c r="C283" t="n">
+        <v>3317048.040521846</v>
+      </c>
+      <c r="D283" t="n">
+        <v>5424399.573123281</v>
+      </c>
+      <c r="E283" t="n">
+        <v>0</v>
+      </c>
+      <c r="F283" t="n">
+        <v>10086118.38801717</v>
+      </c>
+      <c r="G283" t="n">
+        <v>3317048.040521846</v>
+      </c>
+      <c r="H283" t="n">
+        <v>61666.5612650128</v>
+      </c>
+      <c r="I283" t="n">
+        <v>-2323878.543375981</v>
+      </c>
+      <c r="J283" t="n">
+        <v>0</v>
+      </c>
+      <c r="K283" t="n">
+        <v>0</v>
+      </c>
+      <c r="L283" t="n">
+        <v>5531242.84187116</v>
+      </c>
+      <c r="M283" t="n">
+        <v>16672197.28829921</v>
+      </c>
+      <c r="N283" t="n">
+        <v>22127.36116624189</v>
+      </c>
+      <c r="O283" t="n">
+        <v>0</v>
+      </c>
+      <c r="P283" t="n">
+        <v>22127.36116624189</v>
+      </c>
+      <c r="Q283" t="n">
+        <v>22124.9713674846</v>
+      </c>
+      <c r="R283" t="n">
+        <v>0</v>
+      </c>
+      <c r="S283" t="n">
+        <v>0</v>
+      </c>
+      <c r="T283" t="n">
+        <v>0</v>
+      </c>
+      <c r="U283" t="n">
+        <v>2.389798757207401</v>
+      </c>
+      <c r="V283" t="n">
+        <v>16.8840000629425</v>
+      </c>
+      <c r="W283" t="n">
+        <v>16672197.28829921</v>
+      </c>
+      <c r="X283" t="n">
+        <v>16672197.28829921</v>
+      </c>
+      <c r="Y283" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z283" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB283" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC283" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD283" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE283" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427152753_dh_0.5_ctax_250_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>14347211.39145043</v>
+      </c>
+      <c r="B284" t="n">
+        <v>4651290.989729667</v>
+      </c>
+      <c r="C284" t="n">
+        <v>3313118.018564924</v>
+      </c>
+      <c r="D284" t="n">
+        <v>5418043.277904866</v>
+      </c>
+      <c r="E284" t="n">
+        <v>0</v>
+      </c>
+      <c r="F284" t="n">
+        <v>10069334.26763453</v>
+      </c>
+      <c r="G284" t="n">
+        <v>3313118.018564924</v>
+      </c>
+      <c r="H284" t="n">
+        <v>61666.56126501279</v>
+      </c>
+      <c r="I284" t="n">
+        <v>-4652828.267591804</v>
+      </c>
+      <c r="J284" t="n">
+        <v>0</v>
+      </c>
+      <c r="K284" t="n">
+        <v>0</v>
+      </c>
+      <c r="L284" t="n">
+        <v>5555920.811577768</v>
+      </c>
+      <c r="M284" t="n">
+        <v>14347211.39145043</v>
+      </c>
+      <c r="N284" t="n">
+        <v>22226.07181116978</v>
+      </c>
+      <c r="O284" t="n">
+        <v>0</v>
+      </c>
+      <c r="P284" t="n">
+        <v>22226.07181116978</v>
+      </c>
+      <c r="Q284" t="n">
+        <v>22223.68324631104</v>
+      </c>
+      <c r="R284" t="n">
+        <v>0</v>
+      </c>
+      <c r="S284" t="n">
+        <v>0</v>
+      </c>
+      <c r="T284" t="n">
+        <v>0</v>
+      </c>
+      <c r="U284" t="n">
+        <v>2.38856485872207</v>
+      </c>
+      <c r="V284" t="n">
+        <v>23.12599992752075</v>
+      </c>
+      <c r="W284" t="n">
+        <v>14347211.39145043</v>
+      </c>
+      <c r="X284" t="n">
+        <v>14347211.39145043</v>
+      </c>
+      <c r="Y284" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z284" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC284" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD284" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE284" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427153023_dh_0.5_ctax_250_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>12010218.19038019</v>
+      </c>
+      <c r="B285" t="n">
+        <v>4637819.301709238</v>
+      </c>
+      <c r="C285" t="n">
+        <v>3308041.077995073</v>
+      </c>
+      <c r="D285" t="n">
+        <v>5409562.580803385</v>
+      </c>
+      <c r="E285" t="n">
+        <v>0</v>
+      </c>
+      <c r="F285" t="n">
+        <v>10047381.88251262</v>
+      </c>
+      <c r="G285" t="n">
+        <v>3308041.077995073</v>
+      </c>
+      <c r="H285" t="n">
+        <v>92912.13943179831</v>
+      </c>
+      <c r="I285" t="n">
+        <v>-7066649.340665001</v>
+      </c>
+      <c r="J285" t="n">
+        <v>0</v>
+      </c>
+      <c r="K285" t="n">
+        <v>0</v>
+      </c>
+      <c r="L285" t="n">
+        <v>5628532.431105698</v>
+      </c>
+      <c r="M285" t="n">
+        <v>12010218.19038019</v>
+      </c>
+      <c r="N285" t="n">
+        <v>22516.51646508551</v>
+      </c>
+      <c r="O285" t="n">
+        <v>0</v>
+      </c>
+      <c r="P285" t="n">
+        <v>22516.51646508551</v>
+      </c>
+      <c r="Q285" t="n">
+        <v>22514.12972442282</v>
+      </c>
+      <c r="R285" t="n">
+        <v>0</v>
+      </c>
+      <c r="S285" t="n">
+        <v>0</v>
+      </c>
+      <c r="T285" t="n">
+        <v>0</v>
+      </c>
+      <c r="U285" t="n">
+        <v>2.38674066273344</v>
+      </c>
+      <c r="V285" t="n">
+        <v>28.63000011444092</v>
+      </c>
+      <c r="W285" t="n">
+        <v>12010218.19038019</v>
+      </c>
+      <c r="X285" t="n">
+        <v>12010218.19038019</v>
+      </c>
+      <c r="Y285" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z285" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC285" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD285" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE285" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427153300_dh_0.5_ctax_250_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>9578019.450263601</v>
+      </c>
+      <c r="B286" t="n">
+        <v>4619889.601103422</v>
+      </c>
+      <c r="C286" t="n">
+        <v>3301283.761301307</v>
+      </c>
+      <c r="D286" t="n">
+        <v>5397747.723862983</v>
+      </c>
+      <c r="E286" t="n">
+        <v>0</v>
+      </c>
+      <c r="F286" t="n">
+        <v>10017637.3249664</v>
+      </c>
+      <c r="G286" t="n">
+        <v>3301283.761301307</v>
+      </c>
+      <c r="H286" t="n">
+        <v>481540.8754114619</v>
+      </c>
+      <c r="I286" t="n">
+        <v>-10357926.06683011</v>
+      </c>
+      <c r="J286" t="n">
+        <v>0</v>
+      </c>
+      <c r="K286" t="n">
+        <v>0</v>
+      </c>
+      <c r="L286" t="n">
+        <v>6135483.555414533</v>
+      </c>
+      <c r="M286" t="n">
+        <v>9578019.450263601</v>
+      </c>
+      <c r="N286" t="n">
+        <v>24544.31808236345</v>
+      </c>
+      <c r="O286" t="n">
+        <v>0</v>
+      </c>
+      <c r="P286" t="n">
+        <v>24544.31808236345</v>
+      </c>
+      <c r="Q286" t="n">
+        <v>24541.93422165813</v>
+      </c>
+      <c r="R286" t="n">
+        <v>0</v>
+      </c>
+      <c r="S286" t="n">
+        <v>0</v>
+      </c>
+      <c r="T286" t="n">
+        <v>0</v>
+      </c>
+      <c r="U286" t="n">
+        <v>2.383860705316823</v>
+      </c>
+      <c r="V286" t="n">
+        <v>38.23200011253357</v>
+      </c>
+      <c r="W286" t="n">
+        <v>9578019.450263601</v>
+      </c>
+      <c r="X286" t="n">
+        <v>9578019.450263601</v>
+      </c>
+      <c r="Y286" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z286" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC286" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD286" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE286" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427153542_dh_0.5_ctax_250_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>6627981.706571741</v>
+      </c>
+      <c r="B287" t="n">
+        <v>4596346.401187796</v>
+      </c>
+      <c r="C287" t="n">
+        <v>3292411.295432031</v>
+      </c>
+      <c r="D287" t="n">
+        <v>5381295.858198824</v>
+      </c>
+      <c r="E287" t="n">
+        <v>0</v>
+      </c>
+      <c r="F287" t="n">
+        <v>9977642.259386621</v>
+      </c>
+      <c r="G287" t="n">
+        <v>3292411.295432031</v>
+      </c>
+      <c r="H287" t="n">
+        <v>2064795.499578854</v>
+      </c>
+      <c r="I287" t="n">
+        <v>-16764675.58822798</v>
+      </c>
+      <c r="J287" t="n">
+        <v>0</v>
+      </c>
+      <c r="K287" t="n">
+        <v>0</v>
+      </c>
+      <c r="L287" t="n">
+        <v>8057808.240402218</v>
+      </c>
+      <c r="M287" t="n">
+        <v>6627981.706571741</v>
+      </c>
+      <c r="N287" t="n">
+        <v>32233.61223798793</v>
+      </c>
+      <c r="O287" t="n">
+        <v>0</v>
+      </c>
+      <c r="P287" t="n">
+        <v>32233.61223798793</v>
+      </c>
+      <c r="Q287" t="n">
+        <v>32231.23296160888</v>
+      </c>
+      <c r="R287" t="n">
+        <v>0</v>
+      </c>
+      <c r="S287" t="n">
+        <v>0</v>
+      </c>
+      <c r="T287" t="n">
+        <v>0</v>
+      </c>
+      <c r="U287" t="n">
+        <v>2.379276379027116</v>
+      </c>
+      <c r="V287" t="n">
+        <v>43.00500011444092</v>
+      </c>
+      <c r="W287" t="n">
+        <v>6627981.706571741</v>
+      </c>
+      <c r="X287" t="n">
+        <v>6627981.706571741</v>
+      </c>
+      <c r="Y287" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z287" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC287" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD287" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE287" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427154122_dh_0.5_ctax_250_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>1060402.734726964</v>
+      </c>
+      <c r="B288" t="n">
+        <v>31475976.17174264</v>
+      </c>
+      <c r="C288" t="n">
+        <v>4454593.618400224</v>
+      </c>
+      <c r="D288" t="n">
+        <v>22595709.69279262</v>
+      </c>
+      <c r="E288" t="n">
+        <v>0</v>
+      </c>
+      <c r="F288" t="n">
+        <v>54071685.86453526</v>
+      </c>
+      <c r="G288" t="n">
+        <v>4454593.618400224</v>
+      </c>
+      <c r="H288" t="n">
+        <v>3527963.701534422</v>
+      </c>
+      <c r="I288" t="n">
+        <v>-71862831.82590297</v>
+      </c>
+      <c r="J288" t="n">
+        <v>0</v>
+      </c>
+      <c r="K288" t="n">
+        <v>0</v>
+      </c>
+      <c r="L288" t="n">
+        <v>10868991.37616003</v>
+      </c>
+      <c r="M288" t="n">
+        <v>1060402.734726964</v>
+      </c>
+      <c r="N288" t="n">
+        <v>43480.82594776877</v>
+      </c>
+      <c r="O288" t="n">
+        <v>0</v>
+      </c>
+      <c r="P288" t="n">
+        <v>43480.82594776877</v>
+      </c>
+      <c r="Q288" t="n">
+        <v>43475.96550464014</v>
+      </c>
+      <c r="R288" t="n">
+        <v>0</v>
+      </c>
+      <c r="S288" t="n">
+        <v>0</v>
+      </c>
+      <c r="T288" t="n">
+        <v>0</v>
+      </c>
+      <c r="U288" t="n">
+        <v>4.860443128641434</v>
+      </c>
+      <c r="V288" t="n">
+        <v>27.71399998664856</v>
+      </c>
+      <c r="W288" t="n">
+        <v>1060402.734726964</v>
+      </c>
+      <c r="X288" t="n">
+        <v>1060402.734726964</v>
+      </c>
+      <c r="Y288" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z288" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC288" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD288" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE288" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427154421_dh_0.5_ctax_250_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>-11031060.47567805</v>
+      </c>
+      <c r="B289" t="n">
+        <v>31677578.71586814</v>
+      </c>
+      <c r="C289" t="n">
+        <v>4473996.049806509</v>
+      </c>
+      <c r="D289" t="n">
+        <v>22732670.95395231</v>
+      </c>
+      <c r="E289" t="n">
+        <v>0</v>
+      </c>
+      <c r="F289" t="n">
+        <v>54410249.66982045</v>
+      </c>
+      <c r="G289" t="n">
+        <v>4473996.049806509</v>
+      </c>
+      <c r="H289" t="n">
+        <v>4128072.326948888</v>
+      </c>
+      <c r="I289" t="n">
+        <v>-85373013.07793203</v>
+      </c>
+      <c r="J289" t="n">
+        <v>0</v>
+      </c>
+      <c r="K289" t="n">
+        <v>0</v>
+      </c>
+      <c r="L289" t="n">
+        <v>11329634.55567813</v>
+      </c>
+      <c r="M289" t="n">
+        <v>-11031060.47567805</v>
+      </c>
+      <c r="N289" t="n">
+        <v>45323.42306238208</v>
+      </c>
+      <c r="O289" t="n">
+        <v>0</v>
+      </c>
+      <c r="P289" t="n">
+        <v>45323.42306238208</v>
+      </c>
+      <c r="Q289" t="n">
+        <v>45318.53822271253</v>
+      </c>
+      <c r="R289" t="n">
+        <v>0</v>
+      </c>
+      <c r="S289" t="n">
+        <v>0</v>
+      </c>
+      <c r="T289" t="n">
+        <v>0</v>
+      </c>
+      <c r="U289" t="n">
+        <v>4.884839669543479</v>
+      </c>
+      <c r="V289" t="n">
+        <v>25.64099979400635</v>
+      </c>
+      <c r="W289" t="n">
+        <v>-11031060.47567805</v>
+      </c>
+      <c r="X289" t="n">
+        <v>-11031060.47567805</v>
+      </c>
+      <c r="Y289" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z289" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC289" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD289" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE289" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427154704_dh_0.5_ctax_250_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>-23283402.20346649</v>
+      </c>
+      <c r="B290" t="n">
+        <v>31847832.37810469</v>
+      </c>
+      <c r="C290" t="n">
+        <v>4490381.433322094</v>
+      </c>
+      <c r="D290" t="n">
+        <v>22847254.13138407</v>
+      </c>
+      <c r="E290" t="n">
+        <v>0</v>
+      </c>
+      <c r="F290" t="n">
+        <v>54695086.50948876</v>
+      </c>
+      <c r="G290" t="n">
+        <v>4490381.433322094</v>
+      </c>
+      <c r="H290" t="n">
+        <v>4446565.30946459</v>
+      </c>
+      <c r="I290" t="n">
+        <v>-98430355.90096943</v>
+      </c>
+      <c r="J290" t="n">
+        <v>0</v>
+      </c>
+      <c r="K290" t="n">
+        <v>0</v>
+      </c>
+      <c r="L290" t="n">
+        <v>11514920.44522749</v>
+      </c>
+      <c r="M290" t="n">
+        <v>-23283402.20346649</v>
+      </c>
+      <c r="N290" t="n">
+        <v>46064.58575974841</v>
+      </c>
+      <c r="O290" t="n">
+        <v>0</v>
+      </c>
+      <c r="P290" t="n">
+        <v>46064.58575974841</v>
+      </c>
+      <c r="Q290" t="n">
+        <v>46059.68178090997</v>
+      </c>
+      <c r="R290" t="n">
+        <v>0</v>
+      </c>
+      <c r="S290" t="n">
+        <v>0</v>
+      </c>
+      <c r="T290" t="n">
+        <v>0</v>
+      </c>
+      <c r="U290" t="n">
+        <v>4.903978838420235</v>
+      </c>
+      <c r="V290" t="n">
+        <v>24.59299993515015</v>
+      </c>
+      <c r="W290" t="n">
+        <v>-23283402.20346649</v>
+      </c>
+      <c r="X290" t="n">
+        <v>-23283402.20346649</v>
+      </c>
+      <c r="Y290" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z290" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC290" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD290" t="inlineStr">
+        <is>
+          <t>dh_0.5_ctax_250_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE290" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427154945_dh_0.5_ctax_250_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>14952641.51186063</v>
+      </c>
+      <c r="B291" t="n">
+        <v>4437315.609181606</v>
+      </c>
+      <c r="C291" t="n">
+        <v>3232481.467449621</v>
+      </c>
+      <c r="D291" t="n">
+        <v>5007230.758951237</v>
+      </c>
+      <c r="E291" t="n">
+        <v>0</v>
+      </c>
+      <c r="F291" t="n">
+        <v>9444546.368132845</v>
+      </c>
+      <c r="G291" t="n">
+        <v>3232481.467449621</v>
+      </c>
+      <c r="H291" t="n">
+        <v>35446.35724911594</v>
+      </c>
+      <c r="I291" t="n">
+        <v>-2093036.079923186</v>
+      </c>
+      <c r="J291" t="n">
+        <v>0</v>
+      </c>
+      <c r="K291" t="n">
+        <v>0</v>
+      </c>
+      <c r="L291" t="n">
+        <v>4333203.398952238</v>
+      </c>
+      <c r="M291" t="n">
+        <v>14952641.51186063</v>
+      </c>
+      <c r="N291" t="n">
+        <v>43334.15718414133</v>
+      </c>
+      <c r="O291" t="n">
+        <v>0</v>
+      </c>
+      <c r="P291" t="n">
+        <v>43334.15718414133</v>
+      </c>
+      <c r="Q291" t="n">
+        <v>43332.03398952241</v>
+      </c>
+      <c r="R291" t="n">
+        <v>0</v>
+      </c>
+      <c r="S291" t="n">
+        <v>0</v>
+      </c>
+      <c r="T291" t="n">
+        <v>0</v>
+      </c>
+      <c r="U291" t="n">
+        <v>2.123194618887259</v>
+      </c>
+      <c r="V291" t="n">
+        <v>21.7480001449585</v>
+      </c>
+      <c r="W291" t="n">
+        <v>14952641.51186063</v>
+      </c>
+      <c r="X291" t="n">
+        <v>14952641.51186063</v>
+      </c>
+      <c r="Y291" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z291" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC291" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD291" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE291" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427155225_dh_1_ctax_100_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>9240876.844967514</v>
+      </c>
+      <c r="B292" t="n">
+        <v>0</v>
+      </c>
+      <c r="C292" t="n">
+        <v>0</v>
+      </c>
+      <c r="D292" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E292" t="n">
+        <v>0</v>
+      </c>
+      <c r="F292" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G292" t="n">
+        <v>0</v>
+      </c>
+      <c r="H292" t="n">
+        <v>60502.1733419845</v>
+      </c>
+      <c r="I292" t="n">
+        <v>-12585702.76516321</v>
+      </c>
+      <c r="J292" t="n">
+        <v>0</v>
+      </c>
+      <c r="K292" t="n">
+        <v>0</v>
+      </c>
+      <c r="L292" t="n">
+        <v>21330348.66499327</v>
+      </c>
+      <c r="M292" t="n">
+        <v>9240876.844967514</v>
+      </c>
+      <c r="N292" t="n">
+        <v>213303.4866499327</v>
+      </c>
+      <c r="O292" t="n">
+        <v>0</v>
+      </c>
+      <c r="P292" t="n">
+        <v>213303.4866499327</v>
+      </c>
+      <c r="Q292" t="n">
+        <v>213303.4866499327</v>
+      </c>
+      <c r="R292" t="n">
+        <v>0</v>
+      </c>
+      <c r="S292" t="n">
+        <v>0</v>
+      </c>
+      <c r="T292" t="n">
+        <v>0</v>
+      </c>
+      <c r="U292" t="n">
+        <v>0</v>
+      </c>
+      <c r="V292" t="n">
+        <v>15.53900003433228</v>
+      </c>
+      <c r="W292" t="n">
+        <v>9240876.844967498</v>
+      </c>
+      <c r="X292" t="n">
+        <v>9240876.844967514</v>
+      </c>
+      <c r="Y292" t="n">
+        <v>1.676380634307861e-08</v>
+      </c>
+      <c r="Z292" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC292" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD292" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE292" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427155502_dh_1_ctax_100_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>2867571.495318737</v>
+      </c>
+      <c r="B293" t="n">
+        <v>0</v>
+      </c>
+      <c r="C293" t="n">
+        <v>0</v>
+      </c>
+      <c r="D293" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E293" t="n">
+        <v>0</v>
+      </c>
+      <c r="F293" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G293" t="n">
+        <v>0</v>
+      </c>
+      <c r="H293" t="n">
+        <v>517059.0226530747</v>
+      </c>
+      <c r="I293" t="n">
+        <v>-19626722.50692945</v>
+      </c>
+      <c r="J293" t="n">
+        <v>0</v>
+      </c>
+      <c r="K293" t="n">
+        <v>0</v>
+      </c>
+      <c r="L293" t="n">
+        <v>21541506.20779965</v>
+      </c>
+      <c r="M293" t="n">
+        <v>2867571.495318737</v>
+      </c>
+      <c r="N293" t="n">
+        <v>215415.0620779964</v>
+      </c>
+      <c r="O293" t="n">
+        <v>0</v>
+      </c>
+      <c r="P293" t="n">
+        <v>215415.0620779964</v>
+      </c>
+      <c r="Q293" t="n">
+        <v>215415.0620779964</v>
+      </c>
+      <c r="R293" t="n">
+        <v>0</v>
+      </c>
+      <c r="S293" t="n">
+        <v>0</v>
+      </c>
+      <c r="T293" t="n">
+        <v>0</v>
+      </c>
+      <c r="U293" t="n">
+        <v>0</v>
+      </c>
+      <c r="V293" t="n">
+        <v>10.0530002117157</v>
+      </c>
+      <c r="W293" t="n">
+        <v>2867571.495318647</v>
+      </c>
+      <c r="X293" t="n">
+        <v>2867571.495318737</v>
+      </c>
+      <c r="Y293" t="n">
+        <v>9.033828973770142e-08</v>
+      </c>
+      <c r="Z293" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC293" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD293" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE293" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427160058_dh_1_ctax_100_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>-3907956.459950909</v>
+      </c>
+      <c r="B294" t="n">
+        <v>0</v>
+      </c>
+      <c r="C294" t="n">
+        <v>0</v>
+      </c>
+      <c r="D294" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E294" t="n">
+        <v>0</v>
+      </c>
+      <c r="F294" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G294" t="n">
+        <v>0</v>
+      </c>
+      <c r="H294" t="n">
+        <v>1744785.219608191</v>
+      </c>
+      <c r="I294" t="n">
+        <v>-28197800.02524595</v>
+      </c>
+      <c r="J294" t="n">
+        <v>0</v>
+      </c>
+      <c r="K294" t="n">
+        <v>0</v>
+      </c>
+      <c r="L294" t="n">
+        <v>22109329.57389139</v>
+      </c>
+      <c r="M294" t="n">
+        <v>-3907956.459950909</v>
+      </c>
+      <c r="N294" t="n">
+        <v>221093.2957389139</v>
+      </c>
+      <c r="O294" t="n">
+        <v>0</v>
+      </c>
+      <c r="P294" t="n">
+        <v>221093.2957389139</v>
+      </c>
+      <c r="Q294" t="n">
+        <v>221093.2957389138</v>
+      </c>
+      <c r="R294" t="n">
+        <v>0</v>
+      </c>
+      <c r="S294" t="n">
+        <v>0</v>
+      </c>
+      <c r="T294" t="n">
+        <v>0</v>
+      </c>
+      <c r="U294" t="n">
+        <v>0</v>
+      </c>
+      <c r="V294" t="n">
+        <v>8.901999950408936</v>
+      </c>
+      <c r="W294" t="n">
+        <v>-3907956.459950909</v>
+      </c>
+      <c r="X294" t="n">
+        <v>-3907956.459950909</v>
+      </c>
+      <c r="Y294" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z294" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC294" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD294" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE294" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427160325_dh_1_ctax_100_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>-11236309.91853718</v>
+      </c>
+      <c r="B295" t="n">
+        <v>0</v>
+      </c>
+      <c r="C295" t="n">
+        <v>0</v>
+      </c>
+      <c r="D295" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E295" t="n">
+        <v>0</v>
+      </c>
+      <c r="F295" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G295" t="n">
+        <v>0</v>
+      </c>
+      <c r="H295" t="n">
+        <v>3274721.082435129</v>
+      </c>
+      <c r="I295" t="n">
+        <v>-37763684.68321662</v>
+      </c>
+      <c r="J295" t="n">
+        <v>0</v>
+      </c>
+      <c r="K295" t="n">
+        <v>0</v>
+      </c>
+      <c r="L295" t="n">
+        <v>22816924.91044885</v>
+      </c>
+      <c r="M295" t="n">
+        <v>-11236309.91853718</v>
+      </c>
+      <c r="N295" t="n">
+        <v>228169.2491044884</v>
+      </c>
+      <c r="O295" t="n">
+        <v>0</v>
+      </c>
+      <c r="P295" t="n">
+        <v>228169.2491044884</v>
+      </c>
+      <c r="Q295" t="n">
+        <v>228169.2491044884</v>
+      </c>
+      <c r="R295" t="n">
+        <v>0</v>
+      </c>
+      <c r="S295" t="n">
+        <v>0</v>
+      </c>
+      <c r="T295" t="n">
+        <v>0</v>
+      </c>
+      <c r="U295" t="n">
+        <v>0</v>
+      </c>
+      <c r="V295" t="n">
+        <v>9.375</v>
+      </c>
+      <c r="W295" t="n">
+        <v>-11236309.91853718</v>
+      </c>
+      <c r="X295" t="n">
+        <v>-11236309.91853718</v>
+      </c>
+      <c r="Y295" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z295" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB295" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC295" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD295" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE295" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427160550_dh_1_ctax_100_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>-18885483.653923</v>
+      </c>
+      <c r="B296" t="n">
+        <v>0</v>
+      </c>
+      <c r="C296" t="n">
+        <v>0</v>
+      </c>
+      <c r="D296" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E296" t="n">
+        <v>0</v>
+      </c>
+      <c r="F296" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G296" t="n">
+        <v>0</v>
+      </c>
+      <c r="H296" t="n">
+        <v>3864155.607518862</v>
+      </c>
+      <c r="I296" t="n">
+        <v>-46274906.4115374</v>
+      </c>
+      <c r="J296" t="n">
+        <v>0</v>
+      </c>
+      <c r="K296" t="n">
+        <v>0</v>
+      </c>
+      <c r="L296" t="n">
+        <v>23089538.37830008</v>
+      </c>
+      <c r="M296" t="n">
+        <v>-18885483.653923</v>
+      </c>
+      <c r="N296" t="n">
+        <v>230895.3837830007</v>
+      </c>
+      <c r="O296" t="n">
+        <v>0</v>
+      </c>
+      <c r="P296" t="n">
+        <v>230895.3837830007</v>
+      </c>
+      <c r="Q296" t="n">
+        <v>230895.3837830007</v>
+      </c>
+      <c r="R296" t="n">
+        <v>0</v>
+      </c>
+      <c r="S296" t="n">
+        <v>0</v>
+      </c>
+      <c r="T296" t="n">
+        <v>0</v>
+      </c>
+      <c r="U296" t="n">
+        <v>0</v>
+      </c>
+      <c r="V296" t="n">
+        <v>9.557000160217285</v>
+      </c>
+      <c r="W296" t="n">
+        <v>-18885483.653923</v>
+      </c>
+      <c r="X296" t="n">
+        <v>-18885483.653923</v>
+      </c>
+      <c r="Y296" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z296" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC296" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD296" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE296" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427160819_dh_1_ctax_100_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>-26627309.3052735</v>
+      </c>
+      <c r="B297" t="n">
+        <v>0</v>
+      </c>
+      <c r="C297" t="n">
+        <v>0</v>
+      </c>
+      <c r="D297" t="n">
+        <v>435728.7717954647</v>
+      </c>
+      <c r="E297" t="n">
+        <v>0</v>
+      </c>
+      <c r="F297" t="n">
+        <v>435728.7717954658</v>
+      </c>
+      <c r="G297" t="n">
+        <v>0</v>
+      </c>
+      <c r="H297" t="n">
+        <v>4098614.410903892</v>
+      </c>
+      <c r="I297" t="n">
+        <v>-54359628.06283851</v>
+      </c>
+      <c r="J297" t="n">
+        <v>0</v>
+      </c>
+      <c r="K297" t="n">
+        <v>0</v>
+      </c>
+      <c r="L297" t="n">
+        <v>23197975.57486565</v>
+      </c>
+      <c r="M297" t="n">
+        <v>-26627309.3052735</v>
+      </c>
+      <c r="N297" t="n">
+        <v>231979.7557486565</v>
+      </c>
+      <c r="O297" t="n">
+        <v>0</v>
+      </c>
+      <c r="P297" t="n">
+        <v>231979.7557486565</v>
+      </c>
+      <c r="Q297" t="n">
+        <v>231979.7557486565</v>
+      </c>
+      <c r="R297" t="n">
+        <v>0</v>
+      </c>
+      <c r="S297" t="n">
+        <v>0</v>
+      </c>
+      <c r="T297" t="n">
+        <v>0</v>
+      </c>
+      <c r="U297" t="n">
+        <v>0</v>
+      </c>
+      <c r="V297" t="n">
+        <v>16.20900011062622</v>
+      </c>
+      <c r="W297" t="n">
+        <v>-26627309.3052735</v>
+      </c>
+      <c r="X297" t="n">
+        <v>-26627309.3052735</v>
+      </c>
+      <c r="Y297" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z297" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB297" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC297" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD297" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE297" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427161050_dh_1_ctax_100_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>-34400959.54221863</v>
+      </c>
+      <c r="B298" t="n">
+        <v>0</v>
+      </c>
+      <c r="C298" t="n">
+        <v>0</v>
+      </c>
+      <c r="D298" t="n">
+        <v>435728.771795464</v>
+      </c>
+      <c r="E298" t="n">
+        <v>0</v>
+      </c>
+      <c r="F298" t="n">
+        <v>435728.7717954641</v>
+      </c>
+      <c r="G298" t="n">
+        <v>0</v>
+      </c>
+      <c r="H298" t="n">
+        <v>4162735.064657771</v>
+      </c>
+      <c r="I298" t="n">
+        <v>-62227054.75589869</v>
+      </c>
+      <c r="J298" t="n">
+        <v>0</v>
+      </c>
+      <c r="K298" t="n">
+        <v>0</v>
+      </c>
+      <c r="L298" t="n">
+        <v>23227631.37722682</v>
+      </c>
+      <c r="M298" t="n">
+        <v>-34400959.54221863</v>
+      </c>
+      <c r="N298" t="n">
+        <v>232276.3137722682</v>
+      </c>
+      <c r="O298" t="n">
+        <v>0</v>
+      </c>
+      <c r="P298" t="n">
+        <v>232276.3137722682</v>
+      </c>
+      <c r="Q298" t="n">
+        <v>232276.3137722682</v>
+      </c>
+      <c r="R298" t="n">
+        <v>0</v>
+      </c>
+      <c r="S298" t="n">
+        <v>0</v>
+      </c>
+      <c r="T298" t="n">
+        <v>0</v>
+      </c>
+      <c r="U298" t="n">
+        <v>0</v>
+      </c>
+      <c r="V298" t="n">
+        <v>17.65000009536743</v>
+      </c>
+      <c r="W298" t="n">
+        <v>-34400959.54221863</v>
+      </c>
+      <c r="X298" t="n">
+        <v>-34400959.54221863</v>
+      </c>
+      <c r="Y298" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z298" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB298" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC298" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD298" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_100_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE298" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427161327_dh_1_ctax_100_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>16740773.15634823</v>
+      </c>
+      <c r="B299" t="n">
+        <v>4589062.438050324</v>
+      </c>
+      <c r="C299" t="n">
+        <v>3289666.433495001</v>
+      </c>
+      <c r="D299" t="n">
+        <v>5376004.918874981</v>
+      </c>
+      <c r="E299" t="n">
+        <v>0</v>
+      </c>
+      <c r="F299" t="n">
+        <v>9965067.356925305</v>
+      </c>
+      <c r="G299" t="n">
+        <v>3289666.433495001</v>
+      </c>
+      <c r="H299" t="n">
+        <v>1221144.902067077</v>
+      </c>
+      <c r="I299" t="n">
+        <v>-2003590.807805891</v>
+      </c>
+      <c r="J299" t="n">
+        <v>0</v>
+      </c>
+      <c r="K299" t="n">
+        <v>0</v>
+      </c>
+      <c r="L299" t="n">
+        <v>4268485.271666744</v>
+      </c>
+      <c r="M299" t="n">
+        <v>16740773.15634823</v>
+      </c>
+      <c r="N299" t="n">
+        <v>28458.94616391315</v>
+      </c>
+      <c r="O299" t="n">
+        <v>0</v>
+      </c>
+      <c r="P299" t="n">
+        <v>28458.94616391315</v>
+      </c>
+      <c r="Q299" t="n">
+        <v>28456.56847777806</v>
+      </c>
+      <c r="R299" t="n">
+        <v>0</v>
+      </c>
+      <c r="S299" t="n">
+        <v>0</v>
+      </c>
+      <c r="T299" t="n">
+        <v>0</v>
+      </c>
+      <c r="U299" t="n">
+        <v>2.377686134906352</v>
+      </c>
+      <c r="V299" t="n">
+        <v>19.59800004959106</v>
+      </c>
+      <c r="W299" t="n">
+        <v>16740773.15634823</v>
+      </c>
+      <c r="X299" t="n">
+        <v>16740773.15634823</v>
+      </c>
+      <c r="Y299" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z299" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB299" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC299" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD299" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE299" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427161608_dh_1_ctax_150_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>14723646.72838559</v>
+      </c>
+      <c r="B300" t="n">
+        <v>4528150.622987017</v>
+      </c>
+      <c r="C300" t="n">
+        <v>3266712.507686449</v>
+      </c>
+      <c r="D300" t="n">
+        <v>5328499.289195199</v>
+      </c>
+      <c r="E300" t="n">
+        <v>0</v>
+      </c>
+      <c r="F300" t="n">
+        <v>9856649.912182216</v>
+      </c>
+      <c r="G300" t="n">
+        <v>3266712.507686449</v>
+      </c>
+      <c r="H300" t="n">
+        <v>1222274.263521704</v>
+      </c>
+      <c r="I300" t="n">
+        <v>-4084337.525650487</v>
+      </c>
+      <c r="J300" t="n">
+        <v>0</v>
+      </c>
+      <c r="K300" t="n">
+        <v>0</v>
+      </c>
+      <c r="L300" t="n">
+        <v>4462347.570645708</v>
+      </c>
+      <c r="M300" t="n">
+        <v>14723646.72838559</v>
+      </c>
+      <c r="N300" t="n">
+        <v>29751.34540053881</v>
+      </c>
+      <c r="O300" t="n">
+        <v>0</v>
+      </c>
+      <c r="P300" t="n">
+        <v>29751.34540053881</v>
+      </c>
+      <c r="Q300" t="n">
+        <v>29748.98380430444</v>
+      </c>
+      <c r="R300" t="n">
+        <v>0</v>
+      </c>
+      <c r="S300" t="n">
+        <v>0</v>
+      </c>
+      <c r="T300" t="n">
+        <v>0</v>
+      </c>
+      <c r="U300" t="n">
+        <v>2.361596234533867</v>
+      </c>
+      <c r="V300" t="n">
+        <v>19.8769998550415</v>
+      </c>
+      <c r="W300" t="n">
+        <v>14723646.72838559</v>
+      </c>
+      <c r="X300" t="n">
+        <v>14723646.72838559</v>
+      </c>
+      <c r="Y300" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z300" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB300" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC300" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD300" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE300" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427162305_dh_1_ctax_150_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>12609910.00236992</v>
+      </c>
+      <c r="B301" t="n">
+        <v>4446194.272671598</v>
+      </c>
+      <c r="C301" t="n">
+        <v>3235827.266708472</v>
+      </c>
+      <c r="D301" t="n">
+        <v>5254052.961785969</v>
+      </c>
+      <c r="E301" t="n">
+        <v>0</v>
+      </c>
+      <c r="F301" t="n">
+        <v>9700247.234457567</v>
+      </c>
+      <c r="G301" t="n">
+        <v>3235827.266708472</v>
+      </c>
+      <c r="H301" t="n">
+        <v>1473307.432100462</v>
+      </c>
+      <c r="I301" t="n">
+        <v>-6803932.327076292</v>
+      </c>
+      <c r="J301" t="n">
+        <v>0</v>
+      </c>
+      <c r="K301" t="n">
+        <v>0</v>
+      </c>
+      <c r="L301" t="n">
+        <v>5004460.396179708</v>
+      </c>
+      <c r="M301" t="n">
+        <v>12609910.00236992</v>
+      </c>
+      <c r="N301" t="n">
+        <v>33365.40024088492</v>
+      </c>
+      <c r="O301" t="n">
+        <v>0</v>
+      </c>
+      <c r="P301" t="n">
+        <v>33365.40024088492</v>
+      </c>
+      <c r="Q301" t="n">
+        <v>33363.06930786442</v>
+      </c>
+      <c r="R301" t="n">
+        <v>0</v>
+      </c>
+      <c r="S301" t="n">
+        <v>0</v>
+      </c>
+      <c r="T301" t="n">
+        <v>0</v>
+      </c>
+      <c r="U301" t="n">
+        <v>2.330933020797827</v>
+      </c>
+      <c r="V301" t="n">
+        <v>25.21799993515015</v>
+      </c>
+      <c r="W301" t="n">
+        <v>12609910.00236992</v>
+      </c>
+      <c r="X301" t="n">
+        <v>12609910.00236992</v>
+      </c>
+      <c r="Y301" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z301" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB301" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC301" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD301" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE301" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427162547_dh_1_ctax_150_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>7050699.147829827</v>
+      </c>
+      <c r="B302" t="n">
+        <v>0</v>
+      </c>
+      <c r="C302" t="n">
+        <v>0</v>
+      </c>
+      <c r="D302" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E302" t="n">
+        <v>0</v>
+      </c>
+      <c r="F302" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G302" t="n">
+        <v>0</v>
+      </c>
+      <c r="H302" t="n">
+        <v>955403.0045410157</v>
+      </c>
+      <c r="I302" t="n">
+        <v>-26956793.07764089</v>
+      </c>
+      <c r="J302" t="n">
+        <v>0</v>
+      </c>
+      <c r="K302" t="n">
+        <v>0</v>
+      </c>
+      <c r="L302" t="n">
+        <v>32616360.44913424</v>
+      </c>
+      <c r="M302" t="n">
+        <v>7050699.147829827</v>
+      </c>
+      <c r="N302" t="n">
+        <v>217442.4029942281</v>
+      </c>
+      <c r="O302" t="n">
+        <v>0</v>
+      </c>
+      <c r="P302" t="n">
+        <v>217442.4029942281</v>
+      </c>
+      <c r="Q302" t="n">
+        <v>217442.4029942282</v>
+      </c>
+      <c r="R302" t="n">
+        <v>0</v>
+      </c>
+      <c r="S302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U302" t="n">
+        <v>0</v>
+      </c>
+      <c r="V302" t="n">
+        <v>16.35699987411499</v>
+      </c>
+      <c r="W302" t="n">
+        <v>7050699.147829827</v>
+      </c>
+      <c r="X302" t="n">
+        <v>7050699.147829827</v>
+      </c>
+      <c r="Y302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z302" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB302" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC302" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD302" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE302" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427162837_dh_1_ctax_150_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>62478.0002864562</v>
+      </c>
+      <c r="B303" t="n">
+        <v>0</v>
+      </c>
+      <c r="C303" t="n">
+        <v>0</v>
+      </c>
+      <c r="D303" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E303" t="n">
+        <v>0</v>
+      </c>
+      <c r="F303" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G303" t="n">
+        <v>0</v>
+      </c>
+      <c r="H303" t="n">
+        <v>2275717.794954614</v>
+      </c>
+      <c r="I303" t="n">
+        <v>-36181297.4014473</v>
+      </c>
+      <c r="J303" t="n">
+        <v>0</v>
+      </c>
+      <c r="K303" t="n">
+        <v>0</v>
+      </c>
+      <c r="L303" t="n">
+        <v>33532328.83498367</v>
+      </c>
+      <c r="M303" t="n">
+        <v>62478.0002864562</v>
+      </c>
+      <c r="N303" t="n">
+        <v>223548.8588998911</v>
+      </c>
+      <c r="O303" t="n">
+        <v>0</v>
+      </c>
+      <c r="P303" t="n">
+        <v>223548.8588998911</v>
+      </c>
+      <c r="Q303" t="n">
+        <v>223548.8588998911</v>
+      </c>
+      <c r="R303" t="n">
+        <v>0</v>
+      </c>
+      <c r="S303" t="n">
+        <v>0</v>
+      </c>
+      <c r="T303" t="n">
+        <v>0</v>
+      </c>
+      <c r="U303" t="n">
+        <v>0</v>
+      </c>
+      <c r="V303" t="n">
+        <v>15.19799995422363</v>
+      </c>
+      <c r="W303" t="n">
+        <v>62478.0002864562</v>
+      </c>
+      <c r="X303" t="n">
+        <v>62478.0002864562</v>
+      </c>
+      <c r="Y303" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z303" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB303" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC303" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD303" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE303" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427163117_dh_1_ctax_150_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>-7384589.217097677</v>
+      </c>
+      <c r="B304" t="n">
+        <v>0</v>
+      </c>
+      <c r="C304" t="n">
+        <v>0</v>
+      </c>
+      <c r="D304" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="E304" t="n">
+        <v>0</v>
+      </c>
+      <c r="F304" t="n">
+        <v>435728.7717954639</v>
+      </c>
+      <c r="G304" t="n">
+        <v>0</v>
+      </c>
+      <c r="H304" t="n">
+        <v>3398482.612366882</v>
+      </c>
+      <c r="I304" t="n">
+        <v>-45530047.52832346</v>
+      </c>
+      <c r="J304" t="n">
+        <v>0</v>
+      </c>
+      <c r="K304" t="n">
+        <v>0</v>
+      </c>
+      <c r="L304" t="n">
+        <v>34311246.92706344</v>
+      </c>
+      <c r="M304" t="n">
+        <v>-7384589.217097677</v>
+      </c>
+      <c r="N304" t="n">
+        <v>228741.6461804228</v>
+      </c>
+      <c r="O304" t="n">
+        <v>0</v>
+      </c>
+      <c r="P304" t="n">
+        <v>228741.6461804228</v>
+      </c>
+      <c r="Q304" t="n">
+        <v>228741.6461804228</v>
+      </c>
+      <c r="R304" t="n">
+        <v>0</v>
+      </c>
+      <c r="S304" t="n">
+        <v>0</v>
+      </c>
+      <c r="T304" t="n">
+        <v>0</v>
+      </c>
+      <c r="U304" t="n">
+        <v>0</v>
+      </c>
+      <c r="V304" t="n">
+        <v>20.93899989128113</v>
+      </c>
+      <c r="W304" t="n">
+        <v>-7384589.217097677</v>
+      </c>
+      <c r="X304" t="n">
+        <v>-7384589.217097677</v>
+      </c>
+      <c r="Y304" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z304" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA304" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB304" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC304" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD304" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE304" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427163356_dh_1_ctax_150_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>-15053248.70991591</v>
+      </c>
+      <c r="B305" t="n">
+        <v>0</v>
+      </c>
+      <c r="C305" t="n">
+        <v>0</v>
+      </c>
+      <c r="D305" t="n">
+        <v>435728.7717954649</v>
+      </c>
+      <c r="E305" t="n">
+        <v>0</v>
+      </c>
+      <c r="F305" t="n">
+        <v>435728.7717954663</v>
+      </c>
+      <c r="G305" t="n">
+        <v>0</v>
+      </c>
+      <c r="H305" t="n">
+        <v>3875514.618392541</v>
+      </c>
+      <c r="I305" t="n">
+        <v>-54006679.98134765</v>
+      </c>
+      <c r="J305" t="n">
+        <v>0</v>
+      </c>
+      <c r="K305" t="n">
+        <v>0</v>
+      </c>
+      <c r="L305" t="n">
+        <v>34642187.88124374</v>
+      </c>
+      <c r="M305" t="n">
+        <v>-15053248.70991591</v>
+      </c>
+      <c r="N305" t="n">
+        <v>230947.9192082915</v>
+      </c>
+      <c r="O305" t="n">
+        <v>0</v>
+      </c>
+      <c r="P305" t="n">
+        <v>230947.9192082915</v>
+      </c>
+      <c r="Q305" t="n">
+        <v>230947.9192082915</v>
+      </c>
+      <c r="R305" t="n">
+        <v>0</v>
+      </c>
+      <c r="S305" t="n">
+        <v>0</v>
+      </c>
+      <c r="T305" t="n">
+        <v>0</v>
+      </c>
+      <c r="U305" t="n">
+        <v>0</v>
+      </c>
+      <c r="V305" t="n">
+        <v>21.01199984550476</v>
+      </c>
+      <c r="W305" t="n">
+        <v>-15053248.70991591</v>
+      </c>
+      <c r="X305" t="n">
+        <v>-15053248.70991591</v>
+      </c>
+      <c r="Y305" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z305" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB305" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC305" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD305" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE305" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427163641_dh_1_ctax_150_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>-24540806.65989729</v>
+      </c>
+      <c r="B306" t="n">
+        <v>30925520.59477416</v>
+      </c>
+      <c r="C306" t="n">
+        <v>4401617.220603922</v>
+      </c>
+      <c r="D306" t="n">
+        <v>22215864.24309056</v>
+      </c>
+      <c r="E306" t="n">
+        <v>0</v>
+      </c>
+      <c r="F306" t="n">
+        <v>53141384.83786473</v>
+      </c>
+      <c r="G306" t="n">
+        <v>4401617.220603922</v>
+      </c>
+      <c r="H306" t="n">
+        <v>6658772.2578664</v>
+      </c>
+      <c r="I306" t="n">
+        <v>-97863792.29791692</v>
+      </c>
+      <c r="J306" t="n">
+        <v>0</v>
+      </c>
+      <c r="K306" t="n">
+        <v>0</v>
+      </c>
+      <c r="L306" t="n">
+        <v>9121211.321684588</v>
+      </c>
+      <c r="M306" t="n">
+        <v>-24540806.65989729</v>
+      </c>
+      <c r="N306" t="n">
+        <v>60812.86133676305</v>
+      </c>
+      <c r="O306" t="n">
+        <v>0</v>
+      </c>
+      <c r="P306" t="n">
+        <v>60812.86133676305</v>
+      </c>
+      <c r="Q306" t="n">
+        <v>60808.07547789723</v>
+      </c>
+      <c r="R306" t="n">
+        <v>0</v>
+      </c>
+      <c r="S306" t="n">
+        <v>0</v>
+      </c>
+      <c r="T306" t="n">
+        <v>0</v>
+      </c>
+      <c r="U306" t="n">
+        <v>4.785858865855401</v>
+      </c>
+      <c r="V306" t="n">
+        <v>20.70199990272522</v>
+      </c>
+      <c r="W306" t="n">
+        <v>-24540806.65989729</v>
+      </c>
+      <c r="X306" t="n">
+        <v>-24540806.65989729</v>
+      </c>
+      <c r="Y306" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z306" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB306" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC306" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD306" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_150_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE306" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427163925_dh_1_ctax_150_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>18142820.83824053</v>
+      </c>
+      <c r="B307" t="n">
+        <v>4635761.67070828</v>
+      </c>
+      <c r="C307" t="n">
+        <v>3307265.601336647</v>
+      </c>
+      <c r="D307" t="n">
+        <v>5408236.799222299</v>
+      </c>
+      <c r="E307" t="n">
+        <v>0</v>
+      </c>
+      <c r="F307" t="n">
+        <v>10043998.46993058</v>
+      </c>
+      <c r="G307" t="n">
+        <v>3307265.601336647</v>
+      </c>
+      <c r="H307" t="n">
+        <v>1224034.151524042</v>
+      </c>
+      <c r="I307" t="n">
+        <v>-1986466.919841166</v>
+      </c>
+      <c r="J307" t="n">
+        <v>0</v>
+      </c>
+      <c r="K307" t="n">
+        <v>0</v>
+      </c>
+      <c r="L307" t="n">
+        <v>5553989.535290425</v>
+      </c>
+      <c r="M307" t="n">
+        <v>18142820.83824053</v>
+      </c>
+      <c r="N307" t="n">
+        <v>27772.33411238189</v>
+      </c>
+      <c r="O307" t="n">
+        <v>0</v>
+      </c>
+      <c r="P307" t="n">
+        <v>27772.33411238189</v>
+      </c>
+      <c r="Q307" t="n">
+        <v>27769.9476764522</v>
+      </c>
+      <c r="R307" t="n">
+        <v>0</v>
+      </c>
+      <c r="S307" t="n">
+        <v>0</v>
+      </c>
+      <c r="T307" t="n">
+        <v>0</v>
+      </c>
+      <c r="U307" t="n">
+        <v>2.386435929657156</v>
+      </c>
+      <c r="V307" t="n">
+        <v>17.43700003623962</v>
+      </c>
+      <c r="W307" t="n">
+        <v>18142820.83824053</v>
+      </c>
+      <c r="X307" t="n">
+        <v>18142820.83824053</v>
+      </c>
+      <c r="Y307" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z307" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB307" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC307" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD307" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE307" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427164209_dh_1_ctax_200_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>16153570.47421044</v>
+      </c>
+      <c r="B308" t="n">
+        <v>4617835.984290843</v>
+      </c>
+      <c r="C308" t="n">
+        <v>3300509.797503733</v>
+      </c>
+      <c r="D308" t="n">
+        <v>5396354.504859557</v>
+      </c>
+      <c r="E308" t="n">
+        <v>0</v>
+      </c>
+      <c r="F308" t="n">
+        <v>10014190.4891504</v>
+      </c>
+      <c r="G308" t="n">
+        <v>3300509.797503733</v>
+      </c>
+      <c r="H308" t="n">
+        <v>1223152.882896746</v>
+      </c>
+      <c r="I308" t="n">
+        <v>-3984486.100832636</v>
+      </c>
+      <c r="J308" t="n">
+        <v>0</v>
+      </c>
+      <c r="K308" t="n">
+        <v>0</v>
+      </c>
+      <c r="L308" t="n">
+        <v>5600203.405492198</v>
+      </c>
+      <c r="M308" t="n">
+        <v>16153570.47421044</v>
+      </c>
+      <c r="N308" t="n">
+        <v>28003.4005240755</v>
+      </c>
+      <c r="O308" t="n">
+        <v>0</v>
+      </c>
+      <c r="P308" t="n">
+        <v>28003.4005240755</v>
+      </c>
+      <c r="Q308" t="n">
+        <v>28001.01702746102</v>
+      </c>
+      <c r="R308" t="n">
+        <v>0</v>
+      </c>
+      <c r="S308" t="n">
+        <v>0</v>
+      </c>
+      <c r="T308" t="n">
+        <v>0</v>
+      </c>
+      <c r="U308" t="n">
+        <v>2.383496614427029</v>
+      </c>
+      <c r="V308" t="n">
+        <v>26.49600005149841</v>
+      </c>
+      <c r="W308" t="n">
+        <v>16153570.47421044</v>
+      </c>
+      <c r="X308" t="n">
+        <v>16153570.47421044</v>
+      </c>
+      <c r="Y308" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z308" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB308" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC308" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD308" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE308" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427164448_dh_1_ctax_200_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>14135421.24424726</v>
+      </c>
+      <c r="B309" t="n">
+        <v>4589770.640216956</v>
+      </c>
+      <c r="C309" t="n">
+        <v>3289933.309800418</v>
+      </c>
+      <c r="D309" t="n">
+        <v>5376515.253341858</v>
+      </c>
+      <c r="E309" t="n">
+        <v>0</v>
+      </c>
+      <c r="F309" t="n">
+        <v>9966285.893558815</v>
+      </c>
+      <c r="G309" t="n">
+        <v>3289933.309800418</v>
+      </c>
+      <c r="H309" t="n">
+        <v>1296537.165223991</v>
+      </c>
+      <c r="I309" t="n">
+        <v>-6175968.852437775</v>
+      </c>
+      <c r="J309" t="n">
+        <v>0</v>
+      </c>
+      <c r="K309" t="n">
+        <v>0</v>
+      </c>
+      <c r="L309" t="n">
+        <v>5758633.728101807</v>
+      </c>
+      <c r="M309" t="n">
+        <v>14135421.24424726</v>
+      </c>
+      <c r="N309" t="n">
+        <v>28795.54647775697</v>
+      </c>
+      <c r="O309" t="n">
+        <v>0</v>
+      </c>
+      <c r="P309" t="n">
+        <v>28795.54647775697</v>
+      </c>
+      <c r="Q309" t="n">
+        <v>28793.16864050905</v>
+      </c>
+      <c r="R309" t="n">
+        <v>0</v>
+      </c>
+      <c r="S309" t="n">
+        <v>0</v>
+      </c>
+      <c r="T309" t="n">
+        <v>0</v>
+      </c>
+      <c r="U309" t="n">
+        <v>2.377837248085973</v>
+      </c>
+      <c r="V309" t="n">
+        <v>32.55499982833862</v>
+      </c>
+      <c r="W309" t="n">
+        <v>14135421.24424726</v>
+      </c>
+      <c r="X309" t="n">
+        <v>14135421.24424726</v>
+      </c>
+      <c r="Y309" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z309" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB309" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC309" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD309" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE309" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427165250_dh_1_ctax_200_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>11845403.99952259</v>
+      </c>
+      <c r="B310" t="n">
+        <v>4538050.562209255</v>
+      </c>
+      <c r="C310" t="n">
+        <v>3270443.163997726</v>
+      </c>
+      <c r="D310" t="n">
+        <v>5336310.469893104</v>
+      </c>
+      <c r="E310" t="n">
+        <v>0</v>
+      </c>
+      <c r="F310" t="n">
+        <v>9874361.032102359</v>
+      </c>
+      <c r="G310" t="n">
+        <v>3270443.163997726</v>
+      </c>
+      <c r="H310" t="n">
+        <v>2375805.790269469</v>
+      </c>
+      <c r="I310" t="n">
+        <v>-10648943.73729197</v>
+      </c>
+      <c r="J310" t="n">
+        <v>0</v>
+      </c>
+      <c r="K310" t="n">
+        <v>0</v>
+      </c>
+      <c r="L310" t="n">
+        <v>6973737.750445007</v>
+      </c>
+      <c r="M310" t="n">
+        <v>11845403.99952259</v>
+      </c>
+      <c r="N310" t="n">
+        <v>34871.0530406885</v>
+      </c>
+      <c r="O310" t="n">
+        <v>0</v>
+      </c>
+      <c r="P310" t="n">
+        <v>34871.0530406885</v>
+      </c>
+      <c r="Q310" t="n">
+        <v>34868.6887522248</v>
+      </c>
+      <c r="R310" t="n">
+        <v>0</v>
+      </c>
+      <c r="S310" t="n">
+        <v>0</v>
+      </c>
+      <c r="T310" t="n">
+        <v>0</v>
+      </c>
+      <c r="U310" t="n">
+        <v>2.364288464074968</v>
+      </c>
+      <c r="V310" t="n">
+        <v>34.94099998474121</v>
+      </c>
+      <c r="W310" t="n">
+        <v>11845403.99952259</v>
+      </c>
+      <c r="X310" t="n">
+        <v>11845403.99952259</v>
+      </c>
+      <c r="Y310" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z310" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA310" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB310" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC310" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD310" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE310" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427165544_dh_1_ctax_200_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>8628877.226422502</v>
+      </c>
+      <c r="B311" t="n">
+        <v>4475227.494509907</v>
+      </c>
+      <c r="C311" t="n">
+        <v>3246768.487683256</v>
+      </c>
+      <c r="D311" t="n">
+        <v>5280428.892087047</v>
+      </c>
+      <c r="E311" t="n">
+        <v>0</v>
+      </c>
+      <c r="F311" t="n">
+        <v>9755656.386596955</v>
+      </c>
+      <c r="G311" t="n">
+        <v>3246768.487683256</v>
+      </c>
+      <c r="H311" t="n">
+        <v>5212220.118178348</v>
+      </c>
+      <c r="I311" t="n">
+        <v>-19543031.80854589</v>
+      </c>
+      <c r="J311" t="n">
+        <v>0</v>
+      </c>
+      <c r="K311" t="n">
+        <v>0</v>
+      </c>
+      <c r="L311" t="n">
+        <v>9957264.04250983</v>
+      </c>
+      <c r="M311" t="n">
+        <v>8628877.226422502</v>
+      </c>
+      <c r="N311" t="n">
+        <v>49788.66201082327</v>
+      </c>
+      <c r="O311" t="n">
+        <v>0</v>
+      </c>
+      <c r="P311" t="n">
+        <v>49788.66201082327</v>
+      </c>
+      <c r="Q311" t="n">
+        <v>49786.32021254912</v>
+      </c>
+      <c r="R311" t="n">
+        <v>0</v>
+      </c>
+      <c r="S311" t="n">
+        <v>0</v>
+      </c>
+      <c r="T311" t="n">
+        <v>0</v>
+      </c>
+      <c r="U311" t="n">
+        <v>2.341798274153146</v>
+      </c>
+      <c r="V311" t="n">
+        <v>42.70900011062622</v>
+      </c>
+      <c r="W311" t="n">
+        <v>8628877.226422502</v>
+      </c>
+      <c r="X311" t="n">
+        <v>8628877.226422502</v>
+      </c>
+      <c r="Y311" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z311" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA311" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB311" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC311" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD311" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE311" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427165841_dh_1_ctax_200_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>2616869.349735666</v>
+      </c>
+      <c r="B312" t="n">
+        <v>30880088.53854013</v>
+      </c>
+      <c r="C312" t="n">
+        <v>4397244.793864213</v>
+      </c>
+      <c r="D312" t="n">
+        <v>22184191.95416575</v>
+      </c>
+      <c r="E312" t="n">
+        <v>0</v>
+      </c>
+      <c r="F312" t="n">
+        <v>53064280.49270587</v>
+      </c>
+      <c r="G312" t="n">
+        <v>4397244.793864213</v>
+      </c>
+      <c r="H312" t="n">
+        <v>5259533.663618163</v>
+      </c>
+      <c r="I312" t="n">
+        <v>-71021920.2287309</v>
+      </c>
+      <c r="J312" t="n">
+        <v>0</v>
+      </c>
+      <c r="K312" t="n">
+        <v>0</v>
+      </c>
+      <c r="L312" t="n">
+        <v>10917730.62827832</v>
+      </c>
+      <c r="M312" t="n">
+        <v>2616869.349735666</v>
+      </c>
+      <c r="N312" t="n">
+        <v>54593.43240887266</v>
+      </c>
+      <c r="O312" t="n">
+        <v>0</v>
+      </c>
+      <c r="P312" t="n">
+        <v>54593.43240887266</v>
+      </c>
+      <c r="Q312" t="n">
+        <v>54588.65314139157</v>
+      </c>
+      <c r="R312" t="n">
+        <v>0</v>
+      </c>
+      <c r="S312" t="n">
+        <v>0</v>
+      </c>
+      <c r="T312" t="n">
+        <v>0</v>
+      </c>
+      <c r="U312" t="n">
+        <v>4.779267481068855</v>
+      </c>
+      <c r="V312" t="n">
+        <v>35.28699994087219</v>
+      </c>
+      <c r="W312" t="n">
+        <v>2616869.349735666</v>
+      </c>
+      <c r="X312" t="n">
+        <v>2616869.349735666</v>
+      </c>
+      <c r="Y312" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z312" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB312" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC312" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD312" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE312" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427170147_dh_1_ctax_200_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>-9394885.140655778</v>
+      </c>
+      <c r="B313" t="n">
+        <v>31256936.19164934</v>
+      </c>
+      <c r="C313" t="n">
+        <v>4433512.990636175</v>
+      </c>
+      <c r="D313" t="n">
+        <v>22445490.82275625</v>
+      </c>
+      <c r="E313" t="n">
+        <v>0</v>
+      </c>
+      <c r="F313" t="n">
+        <v>53702427.01440559</v>
+      </c>
+      <c r="G313" t="n">
+        <v>4433512.990636175</v>
+      </c>
+      <c r="H313" t="n">
+        <v>6142757.432533278</v>
+      </c>
+      <c r="I313" t="n">
+        <v>-85004801.85163751</v>
+      </c>
+      <c r="J313" t="n">
+        <v>0</v>
+      </c>
+      <c r="K313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L313" t="n">
+        <v>11331219.27340668</v>
+      </c>
+      <c r="M313" t="n">
+        <v>-9394885.140655778</v>
+      </c>
+      <c r="N313" t="n">
+        <v>56660.92839219856</v>
+      </c>
+      <c r="O313" t="n">
+        <v>0</v>
+      </c>
+      <c r="P313" t="n">
+        <v>56660.92839219856</v>
+      </c>
+      <c r="Q313" t="n">
+        <v>56656.09636703345</v>
+      </c>
+      <c r="R313" t="n">
+        <v>0</v>
+      </c>
+      <c r="S313" t="n">
+        <v>0</v>
+      </c>
+      <c r="T313" t="n">
+        <v>0</v>
+      </c>
+      <c r="U313" t="n">
+        <v>4.83202516511338</v>
+      </c>
+      <c r="V313" t="n">
+        <v>24.78299999237061</v>
+      </c>
+      <c r="W313" t="n">
+        <v>-9394885.140655778</v>
+      </c>
+      <c r="X313" t="n">
+        <v>-9394885.140655778</v>
+      </c>
+      <c r="Y313" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z313" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA313" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB313" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC313" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD313" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE313" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427170446_dh_1_ctax_200_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>-21606303.51892786</v>
+      </c>
+      <c r="B314" t="n">
+        <v>31511866.04814287</v>
+      </c>
+      <c r="C314" t="n">
+        <v>4458047.696165243</v>
+      </c>
+      <c r="D314" t="n">
+        <v>22620186.0841522</v>
+      </c>
+      <c r="E314" t="n">
+        <v>0</v>
+      </c>
+      <c r="F314" t="n">
+        <v>54132052.13229507</v>
+      </c>
+      <c r="G314" t="n">
+        <v>4458047.696165243</v>
+      </c>
+      <c r="H314" t="n">
+        <v>6494241.632415947</v>
+      </c>
+      <c r="I314" t="n">
+        <v>-98095453.45735762</v>
+      </c>
+      <c r="J314" t="n">
+        <v>0</v>
+      </c>
+      <c r="K314" t="n">
+        <v>0</v>
+      </c>
+      <c r="L314" t="n">
+        <v>11404808.47755349</v>
+      </c>
+      <c r="M314" t="n">
+        <v>-21606303.51892786</v>
+      </c>
+      <c r="N314" t="n">
+        <v>57028.90730154092</v>
+      </c>
+      <c r="O314" t="n">
+        <v>0</v>
+      </c>
+      <c r="P314" t="n">
+        <v>57028.90730154092</v>
+      </c>
+      <c r="Q314" t="n">
+        <v>57024.04238776748</v>
+      </c>
+      <c r="R314" t="n">
+        <v>0</v>
+      </c>
+      <c r="S314" t="n">
+        <v>0</v>
+      </c>
+      <c r="T314" t="n">
+        <v>0</v>
+      </c>
+      <c r="U314" t="n">
+        <v>4.864913773432199</v>
+      </c>
+      <c r="V314" t="n">
+        <v>22.22899985313416</v>
+      </c>
+      <c r="W314" t="n">
+        <v>-21606303.51892786</v>
+      </c>
+      <c r="X314" t="n">
+        <v>-21606303.51892786</v>
+      </c>
+      <c r="Y314" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z314" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB314" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC314" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD314" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_200_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE314" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427170734_dh_1_ctax_200_el_price_400</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>19524535.64056375</v>
+      </c>
+      <c r="B315" t="n">
+        <v>4659843.477449745</v>
+      </c>
+      <c r="C315" t="n">
+        <v>3316341.26636558</v>
+      </c>
+      <c r="D315" t="n">
+        <v>5423270.998084607</v>
+      </c>
+      <c r="E315" t="n">
+        <v>0</v>
+      </c>
+      <c r="F315" t="n">
+        <v>10083114.47553435</v>
+      </c>
+      <c r="G315" t="n">
+        <v>3316341.26636558</v>
+      </c>
+      <c r="H315" t="n">
+        <v>1224910.381786528</v>
+      </c>
+      <c r="I315" t="n">
+        <v>-1980263.106916449</v>
+      </c>
+      <c r="J315" t="n">
+        <v>0</v>
+      </c>
+      <c r="K315" t="n">
+        <v>0</v>
+      </c>
+      <c r="L315" t="n">
+        <v>6880432.623793736</v>
+      </c>
+      <c r="M315" t="n">
+        <v>19524535.64056375</v>
+      </c>
+      <c r="N315" t="n">
+        <v>27524.1200844764</v>
+      </c>
+      <c r="O315" t="n">
+        <v>0</v>
+      </c>
+      <c r="P315" t="n">
+        <v>27524.1200844764</v>
+      </c>
+      <c r="Q315" t="n">
+        <v>27521.73049517488</v>
+      </c>
+      <c r="R315" t="n">
+        <v>0</v>
+      </c>
+      <c r="S315" t="n">
+        <v>0</v>
+      </c>
+      <c r="T315" t="n">
+        <v>0</v>
+      </c>
+      <c r="U315" t="n">
+        <v>2.389589301485172</v>
+      </c>
+      <c r="V315" t="n">
+        <v>27.34199976921082</v>
+      </c>
+      <c r="W315" t="n">
+        <v>19524535.64056375</v>
+      </c>
+      <c r="X315" t="n">
+        <v>19524535.64056375</v>
+      </c>
+      <c r="Y315" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z315" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB315" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC315" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD315" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_50</t>
+        </is>
+      </c>
+      <c r="AE315" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427171018_dh_1_ctax_250_el_price_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>17543076.6973171</v>
+      </c>
+      <c r="B316" t="n">
+        <v>4648938.173464869</v>
+      </c>
+      <c r="C316" t="n">
+        <v>3312231.332204011</v>
+      </c>
+      <c r="D316" t="n">
+        <v>5416584.186724368</v>
+      </c>
+      <c r="E316" t="n">
+        <v>0</v>
+      </c>
+      <c r="F316" t="n">
+        <v>10065522.36018924</v>
+      </c>
+      <c r="G316" t="n">
+        <v>3312231.332204011</v>
+      </c>
+      <c r="H316" t="n">
+        <v>1224561.899785555</v>
+      </c>
+      <c r="I316" t="n">
+        <v>-3965751.748076953</v>
+      </c>
+      <c r="J316" t="n">
+        <v>0</v>
+      </c>
+      <c r="K316" t="n">
+        <v>0</v>
+      </c>
+      <c r="L316" t="n">
+        <v>6906512.853215252</v>
+      </c>
+      <c r="M316" t="n">
+        <v>17543076.6973171</v>
+      </c>
+      <c r="N316" t="n">
+        <v>27628.43967800427</v>
+      </c>
+      <c r="O316" t="n">
+        <v>0</v>
+      </c>
+      <c r="P316" t="n">
+        <v>27628.43967800427</v>
+      </c>
+      <c r="Q316" t="n">
+        <v>27626.05141286098</v>
+      </c>
+      <c r="R316" t="n">
+        <v>0</v>
+      </c>
+      <c r="S316" t="n">
+        <v>0</v>
+      </c>
+      <c r="T316" t="n">
+        <v>0</v>
+      </c>
+      <c r="U316" t="n">
+        <v>2.388265143398415</v>
+      </c>
+      <c r="V316" t="n">
+        <v>33.71900010108948</v>
+      </c>
+      <c r="W316" t="n">
+        <v>17543076.6973171</v>
+      </c>
+      <c r="X316" t="n">
+        <v>17543076.6973171</v>
+      </c>
+      <c r="Y316" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z316" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB316" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC316" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD316" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_100</t>
+        </is>
+      </c>
+      <c r="AE316" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427171310_dh_1_ctax_250_el_price_100</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>15549757.36890917</v>
+      </c>
+      <c r="B317" t="n">
+        <v>4635761.670708279</v>
+      </c>
+      <c r="C317" t="n">
+        <v>3307265.601336647</v>
+      </c>
+      <c r="D317" t="n">
+        <v>5408236.799222298</v>
+      </c>
+      <c r="E317" t="n">
+        <v>0</v>
+      </c>
+      <c r="F317" t="n">
+        <v>10043998.46993058</v>
+      </c>
+      <c r="G317" t="n">
+        <v>3307265.601336647</v>
+      </c>
+      <c r="H317" t="n">
+        <v>1255231.953246706</v>
+      </c>
+      <c r="I317" t="n">
+        <v>-6035298.032959656</v>
+      </c>
+      <c r="J317" t="n">
+        <v>0</v>
+      </c>
+      <c r="K317" t="n">
+        <v>0</v>
+      </c>
+      <c r="L317" t="n">
+        <v>6978559.377354894</v>
+      </c>
+      <c r="M317" t="n">
+        <v>15549757.36890917</v>
+      </c>
+      <c r="N317" t="n">
+        <v>27916.62394534922</v>
+      </c>
+      <c r="O317" t="n">
+        <v>0</v>
+      </c>
+      <c r="P317" t="n">
+        <v>27916.62394534922</v>
+      </c>
+      <c r="Q317" t="n">
+        <v>27914.23750941952</v>
+      </c>
+      <c r="R317" t="n">
+        <v>0</v>
+      </c>
+      <c r="S317" t="n">
+        <v>0</v>
+      </c>
+      <c r="T317" t="n">
+        <v>0</v>
+      </c>
+      <c r="U317" t="n">
+        <v>2.386435929657156</v>
+      </c>
+      <c r="V317" t="n">
+        <v>42.1560001373291</v>
+      </c>
+      <c r="W317" t="n">
+        <v>15549757.36890917</v>
+      </c>
+      <c r="X317" t="n">
+        <v>15549757.36890917</v>
+      </c>
+      <c r="Y317" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z317" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB317" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC317" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD317" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_150</t>
+        </is>
+      </c>
+      <c r="AE317" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427171607_dh_1_ctax_250_el_price_150</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>13456711.11061308</v>
+      </c>
+      <c r="B318" t="n">
+        <v>4618217.043744873</v>
+      </c>
+      <c r="C318" t="n">
+        <v>3300653.410577182</v>
+      </c>
+      <c r="D318" t="n">
+        <v>5396591.502625176</v>
+      </c>
+      <c r="E318" t="n">
+        <v>0</v>
+      </c>
+      <c r="F318" t="n">
+        <v>10014808.54637005</v>
+      </c>
+      <c r="G318" t="n">
+        <v>3300653.410577182</v>
+      </c>
+      <c r="H318" t="n">
+        <v>1673035.513892536</v>
+      </c>
+      <c r="I318" t="n">
+        <v>-9051234.74855946</v>
+      </c>
+      <c r="J318" t="n">
+        <v>0</v>
+      </c>
+      <c r="K318" t="n">
+        <v>0</v>
+      </c>
+      <c r="L318" t="n">
+        <v>7519448.388332774</v>
+      </c>
+      <c r="M318" t="n">
+        <v>13456711.11061308</v>
+      </c>
+      <c r="N318" t="n">
+        <v>30080.17709907817</v>
+      </c>
+      <c r="O318" t="n">
+        <v>0</v>
+      </c>
+      <c r="P318" t="n">
+        <v>30080.17709907817</v>
+      </c>
+      <c r="Q318" t="n">
+        <v>30077.79355333088</v>
+      </c>
+      <c r="R318" t="n">
+        <v>0</v>
+      </c>
+      <c r="S318" t="n">
+        <v>0</v>
+      </c>
+      <c r="T318" t="n">
+        <v>0</v>
+      </c>
+      <c r="U318" t="n">
+        <v>2.383545747458101</v>
+      </c>
+      <c r="V318" t="n">
+        <v>45.6729998588562</v>
+      </c>
+      <c r="W318" t="n">
+        <v>13456711.11061308</v>
+      </c>
+      <c r="X318" t="n">
+        <v>13456711.11061308</v>
+      </c>
+      <c r="Y318" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z318" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB318" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC318" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD318" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_200</t>
+        </is>
+      </c>
+      <c r="AE318" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427171916_dh_1_ctax_250_el_price_200</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>10792939.08735517</v>
+      </c>
+      <c r="B319" t="n">
+        <v>4593373.011286577</v>
+      </c>
+      <c r="C319" t="n">
+        <v>3291290.814093813</v>
+      </c>
+      <c r="D319" t="n">
+        <v>5378880.435665888</v>
+      </c>
+      <c r="E319" t="n">
+        <v>0</v>
+      </c>
+      <c r="F319" t="n">
+        <v>9972253.446952466</v>
+      </c>
+      <c r="G319" t="n">
+        <v>3291290.814093813</v>
+      </c>
+      <c r="H319" t="n">
+        <v>3416516.434283135</v>
+      </c>
+      <c r="I319" t="n">
+        <v>-15525217.10342116</v>
+      </c>
+      <c r="J319" t="n">
+        <v>0</v>
+      </c>
+      <c r="K319" t="n">
+        <v>0</v>
+      </c>
+      <c r="L319" t="n">
+        <v>9638095.495446917</v>
+      </c>
+      <c r="M319" t="n">
+        <v>10792939.08735517</v>
+      </c>
+      <c r="N319" t="n">
+        <v>38554.76039017046</v>
+      </c>
+      <c r="O319" t="n">
+        <v>0</v>
+      </c>
+      <c r="P319" t="n">
+        <v>38554.76039017046</v>
+      </c>
+      <c r="Q319" t="n">
+        <v>38552.3819817876</v>
+      </c>
+      <c r="R319" t="n">
+        <v>0</v>
+      </c>
+      <c r="S319" t="n">
+        <v>0</v>
+      </c>
+      <c r="T319" t="n">
+        <v>0</v>
+      </c>
+      <c r="U319" t="n">
+        <v>2.378408382812473</v>
+      </c>
+      <c r="V319" t="n">
+        <v>53.88599991798401</v>
+      </c>
+      <c r="W319" t="n">
+        <v>10792939.08735517</v>
+      </c>
+      <c r="X319" t="n">
+        <v>10792939.08735517</v>
+      </c>
+      <c r="Y319" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z319" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB319" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC319" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD319" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_250</t>
+        </is>
+      </c>
+      <c r="AE319" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427172228_dh_1_ctax_250_el_price_250</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>5161275.771872403</v>
+      </c>
+      <c r="B320" t="n">
+        <v>31475976.17174264</v>
+      </c>
+      <c r="C320" t="n">
+        <v>4454593.618400224</v>
+      </c>
+      <c r="D320" t="n">
+        <v>22595709.69279263</v>
+      </c>
+      <c r="E320" t="n">
+        <v>0</v>
+      </c>
+      <c r="F320" t="n">
+        <v>54071685.86453527</v>
+      </c>
+      <c r="G320" t="n">
+        <v>4454593.618400224</v>
+      </c>
+      <c r="H320" t="n">
+        <v>4449684.874718445</v>
+      </c>
+      <c r="I320" t="n">
+        <v>-69749420.06843559</v>
+      </c>
+      <c r="J320" t="n">
+        <v>0</v>
+      </c>
+      <c r="K320" t="n">
+        <v>0</v>
+      </c>
+      <c r="L320" t="n">
+        <v>11934731.48265406</v>
+      </c>
+      <c r="M320" t="n">
+        <v>5161275.771872403</v>
+      </c>
+      <c r="N320" t="n">
+        <v>47743.78637374489</v>
+      </c>
+      <c r="O320" t="n">
+        <v>0</v>
+      </c>
+      <c r="P320" t="n">
+        <v>47743.78637374489</v>
+      </c>
+      <c r="Q320" t="n">
+        <v>47738.92593061625</v>
+      </c>
+      <c r="R320" t="n">
+        <v>0</v>
+      </c>
+      <c r="S320" t="n">
+        <v>0</v>
+      </c>
+      <c r="T320" t="n">
+        <v>0</v>
+      </c>
+      <c r="U320" t="n">
+        <v>4.860443128641434</v>
+      </c>
+      <c r="V320" t="n">
+        <v>34.76099991798401</v>
+      </c>
+      <c r="W320" t="n">
+        <v>5161275.771872403</v>
+      </c>
+      <c r="X320" t="n">
+        <v>5161275.771872403</v>
+      </c>
+      <c r="Y320" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z320" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB320" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC320" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD320" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_300</t>
+        </is>
+      </c>
+      <c r="AE320" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427172549_dh_1_ctax_250_el_price_300</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>-6679112.879832396</v>
+      </c>
+      <c r="B321" t="n">
+        <v>31677578.71586813</v>
+      </c>
+      <c r="C321" t="n">
+        <v>4473996.049806509</v>
+      </c>
+      <c r="D321" t="n">
+        <v>22732670.9539523</v>
+      </c>
+      <c r="E321" t="n">
+        <v>0</v>
+      </c>
+      <c r="F321" t="n">
+        <v>54410249.66982044</v>
+      </c>
+      <c r="G321" t="n">
+        <v>4473996.049806509</v>
+      </c>
+      <c r="H321" t="n">
+        <v>5635645.202939743</v>
+      </c>
+      <c r="I321" t="n">
+        <v>-84271769.49594164</v>
+      </c>
+      <c r="J321" t="n">
+        <v>0</v>
+      </c>
+      <c r="K321" t="n">
+        <v>0</v>
+      </c>
+      <c r="L321" t="n">
+        <v>13072765.69354255</v>
+      </c>
+      <c r="M321" t="n">
+        <v>-6679112.879832396</v>
+      </c>
+      <c r="N321" t="n">
+        <v>52295.94761383977</v>
+      </c>
+      <c r="O321" t="n">
+        <v>0</v>
+      </c>
+      <c r="P321" t="n">
+        <v>52295.94761383977</v>
+      </c>
+      <c r="Q321" t="n">
+        <v>52291.06277417023</v>
+      </c>
+      <c r="R321" t="n">
+        <v>0</v>
+      </c>
+      <c r="S321" t="n">
+        <v>0</v>
+      </c>
+      <c r="T321" t="n">
+        <v>0</v>
+      </c>
+      <c r="U321" t="n">
+        <v>4.884839669543479</v>
+      </c>
+      <c r="V321" t="n">
+        <v>32.83599996566772</v>
+      </c>
+      <c r="W321" t="n">
+        <v>-6679112.879832396</v>
+      </c>
+      <c r="X321" t="n">
+        <v>-6679112.879832396</v>
+      </c>
+      <c r="Y321" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB321" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC321" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD321" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_350</t>
+        </is>
+      </c>
+      <c r="AE321" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427173513_dh_1_ctax_250_el_price_350</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>-18820871.0889231</v>
+      </c>
+      <c r="B322" t="n">
+        <v>31847832.37810469</v>
+      </c>
+      <c r="C322" t="n">
+        <v>4490381.433322094</v>
+      </c>
+      <c r="D322" t="n">
+        <v>22847254.13138407</v>
+      </c>
+      <c r="E322" t="n">
+        <v>0</v>
+      </c>
+      <c r="F322" t="n">
+        <v>54695086.50948876</v>
+      </c>
+      <c r="G322" t="n">
+        <v>4490381.433322094</v>
+      </c>
+      <c r="H322" t="n">
+        <v>6262022.573766897</v>
+      </c>
+      <c r="I322" t="n">
+        <v>-97882404.51257789</v>
+      </c>
+      <c r="J322" t="n">
+        <v>0</v>
+      </c>
+      <c r="K322" t="n">
+        <v>0</v>
+      </c>
+      <c r="L322" t="n">
+        <v>13614042.90707704</v>
+      </c>
+      <c r="M322" t="n">
+        <v>-18820871.0889231</v>
+      </c>
+      <c r="N322" t="n">
+        <v>54461.07560714655</v>
+      </c>
+      <c r="O322" t="n">
+        <v>0</v>
+      </c>
+      <c r="P322" t="n">
+        <v>54461.07560714655</v>
+      </c>
+      <c r="Q322" t="n">
+        <v>54456.17162830814</v>
+      </c>
+      <c r="R322" t="n">
+        <v>0</v>
+      </c>
+      <c r="S322" t="n">
+        <v>0</v>
+      </c>
+      <c r="T322" t="n">
+        <v>0</v>
+      </c>
+      <c r="U322" t="n">
+        <v>4.903978838420235</v>
+      </c>
+      <c r="V322" t="n">
+        <v>33.34400010108948</v>
+      </c>
+      <c r="W322" t="n">
+        <v>-18820871.0889231</v>
+      </c>
+      <c r="X322" t="n">
+        <v>-18820871.0889231</v>
+      </c>
+      <c r="Y322" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z322" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB322" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC322" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD322" t="inlineStr">
+        <is>
+          <t>dh_1_ctax_250_el_price_400</t>
+        </is>
+      </c>
+      <c r="AE322" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\technology_selection\20260427173816_dh_1_ctax_250_el_price_400</t>
         </is>
       </c>
     </row>
